--- a/data/mel_database.xlsx
+++ b/data/mel_database.xlsx
@@ -566,7 +566,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -609,6 +609,15 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1168,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK133"/>
+  <dimension ref="A1:AP157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1199,6 +1208,11 @@
     <col width="28" customWidth="1" min="34" max="34"/>
     <col width="28" customWidth="1" min="35" max="35"/>
     <col width="70" customWidth="1" min="37" max="37"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="24" customWidth="1" min="39" max="39"/>
+    <col width="42" customWidth="1" min="40" max="40"/>
+    <col width="42" customWidth="1" min="41" max="41"/>
+    <col width="42" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1387,6 +1401,31 @@
           <t>Protocol Method Summary</t>
         </is>
       </c>
+      <c r="AL1" s="12" t="inlineStr">
+        <is>
+          <t>Summary Confidence</t>
+        </is>
+      </c>
+      <c r="AM1" s="12" t="inlineStr">
+        <is>
+          <t>Protocol ID</t>
+        </is>
+      </c>
+      <c r="AN1" s="12" t="inlineStr">
+        <is>
+          <t>Protocol Template URL</t>
+        </is>
+      </c>
+      <c r="AO1" s="12" t="inlineStr">
+        <is>
+          <t>Data Sheet URL</t>
+        </is>
+      </c>
+      <c r="AP1" s="12" t="inlineStr">
+        <is>
+          <t>Stats Workbook URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="240" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -1563,6 +1602,19 @@
           <t>Methods review — no primary data collection. It catalogues and compares field techniques for measuring habitat and biodiversity provisioning at seaweed farms, indicator by indicator (epibiota, mobile fauna, benthic infauna, sediment, community composition), with the trade-offs and standardisation notes for each. Use it to pick which method fits a given indicator, then follow the primary papers it cites for the step-by-step procedure.</t>
         </is>
       </c>
+      <c r="AL2" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM2" s="18" t="inlineStr">
+        <is>
+          <t>corrigan_2022</t>
+        </is>
+      </c>
+      <c r="AN2" s="19" t="n"/>
+      <c r="AO2" s="19" t="n"/>
+      <c r="AP2" s="19" t="n"/>
     </row>
     <row r="3" ht="240" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -1737,6 +1789,19 @@
           <t>To map your seaweed canopy and community as a baseline for habitat/community indicators, fly a drone carrying a hyperspectral (or multispectral) camera along transects over the site at low tide. Process the imagery in GIS software and classify each pixel into seaweed types using a supervised classifier. Validate the map by reading quadrats on the ground at points spread across the tidal range, then score overall accuracy against those points. The result is a repeatable canopy/habitat map rather than a direct measure of farm-derived fauna or chemistry.</t>
         </is>
       </c>
+      <c r="AL3" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM3" s="18" t="inlineStr">
+        <is>
+          <t>diruit_2022</t>
+        </is>
+      </c>
+      <c r="AN3" s="19" t="n"/>
+      <c r="AO3" s="19" t="n"/>
+      <c r="AP3" s="19" t="n"/>
     </row>
     <row r="4" ht="240" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1909,6 +1974,19 @@
           <t>Reference — no primary data collection. It systematically compiles and ranks the ecological risks of expanding seaweed farming in Europe (disease, genetic effects, habitat change and others) and prioritises the key knowledge gaps. It tells a programme what negative-impact dimensions may need watching but does not prescribe how to measure any of them.</t>
         </is>
       </c>
+      <c r="AL4" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM4" s="18" t="inlineStr">
+        <is>
+          <t>campbell_2019</t>
+        </is>
+      </c>
+      <c r="AN4" s="19" t="n"/>
+      <c r="AO4" s="19" t="n"/>
+      <c r="AP4" s="19" t="n"/>
     </row>
     <row r="5" ht="240" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -2081,6 +2159,19 @@
           <t>To map the extent of your farm footprint and track nearby macroalgal (green-tide) blooms, combine satellite imagery with drone flights and, if available, field spectroradiometer readings, then classify the images to delineate farm and bloom areas. Repeat over a short campaign to capture change through the season. This yields farm-area and bloom-extent figures for context or as an input to a separate nutrient-removal calculation, rather than a direct ecosystem-benefit measurement.</t>
         </is>
       </c>
+      <c r="AL5" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM5" s="18" t="inlineStr">
+        <is>
+          <t>xing_2019</t>
+        </is>
+      </c>
+      <c r="AN5" s="19" t="n"/>
+      <c r="AO5" s="19" t="n"/>
+      <c r="AP5" s="19" t="n"/>
     </row>
     <row r="6" ht="240" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -2253,6 +2344,19 @@
           <t>To compare the biodiversity on and around your kelp farm against a nearby non-farm reference (~100 m away, at matched depth and substrate), run three complementary methods and repeat them across seasons. Deploy time-lapse GoPro cameras — one on the seabed in both the farm and reference areas, plus a surface camera on farm structure — recording for ~2 hours (a frame every 0.5 s) once a month to score mobile fish and crustaceans, treating each camera drop as one sample. Hang invertebrate collectors (mesh bags of cheap round scrubber sponges, kept free of biofouling) at grow-line depth (~2 m), several per area, retrieving them each sampling period, then in the lab freeze, tease apart and flush the sponges to identify and count the settled invertebrates. Optionally collect paired water samples (Niskin) alongside and filter them for eDNA (fish 12S and eukaryote 18S markers) to cross-check the visual data. Compare species richness and Shannon diversity between farm and reference with nested ANOVA, and community composition with PERMANOVA and NMDS.</t>
         </is>
       </c>
+      <c r="AL6" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM6" s="18" t="inlineStr">
+        <is>
+          <t>schutt_2023</t>
+        </is>
+      </c>
+      <c r="AN6" s="19" t="n"/>
+      <c r="AO6" s="19" t="n"/>
+      <c r="AP6" s="19" t="n"/>
     </row>
     <row r="7" ht="240" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -2428,6 +2532,19 @@
           <t>To test whether your farm structure provides habitat for attached organisms (epibiota) and for mobile fish and invertebrates, sample the farm side-by-side with two comparators — a nearby vegetated habitat such as seagrass and a bare-bottom site — placed far enough apart and from shore to stay independent. Measure two things. For attached growth, anchor a small quadrat (roughly 0.1 × 0.1 m) over your gear, enclose it in fine (~1 mm) mesh so nothing escapes, remove all attached algae and animals by suction or scraping, then dry and weigh the material as grams dry weight per m²; repeat each season, averaging several quadrats per site into a few replicates. For mobile animals, sample with a seine (or comparable gear) at several fixed spots per habitat, repeated across seasons and — if fish behaviour matters — both day and night, identifying and counting fish and invertebrates. Compare farm against comparators using ANOVA for abundance and biomass, and a multivariate ordination such as NMDS for community differences.</t>
         </is>
       </c>
+      <c r="AL7" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM7" s="18" t="inlineStr">
+        <is>
+          <t>powers_2007</t>
+        </is>
+      </c>
+      <c r="AN7" s="19" t="n"/>
+      <c r="AO7" s="19" t="n"/>
+      <c r="AP7" s="19" t="n"/>
     </row>
     <row r="8" ht="240" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -2600,6 +2717,31 @@
           <t>To document what lives on and around your farm — organisms growing on the lines and mobile animals drawn to the site — run three surveys in parallel and repeat them monthly through the growing season. For attached life (epibionts), pull a set length of header/cultivation line (e.g. 0.5 m sections) onto the boat at two spots along each longline, cut the growth off near the line, and back on land estimate the cover and identity of the organisms on the rope and on the kelp. For mobile fauna, deploy a baited underwater video camera (BRUV) on the seabed near the farm for about an hour per drop, scoring the peak number of each fish type visible at once (MaxN) and analysing only footage clear enough to identify animals. For marine mammals, moor a self-logging acoustic click-detector for continuous multi-week periods and export detection-positive minutes per day for each species. Compare these measures across sites and seasons; temperature, light, current and pH/salinity sensors can be logged alongside for context.</t>
         </is>
       </c>
+      <c r="AL8" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM8" s="18" t="inlineStr">
+        <is>
+          <t>berger_2024</t>
+        </is>
+      </c>
+      <c r="AN8" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/templates/berger_2024.pdf</t>
+        </is>
+      </c>
+      <c r="AO8" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/datasheets/berger_2024.pdf</t>
+        </is>
+      </c>
+      <c r="AP8" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/workbooks/berger_2024.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="240" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -2776,6 +2918,19 @@
           <t>To test whether cultivating seaweed on soft sediment changes the benthic animals (and the shorebirds that feed on them), use a Before-After Control-Impact layout: establish several cultivated plots and several bare control plots, and sample all of them before cultivation, after cultivation, and after harvest across a full year. In each plot on each occasion take replicate sediment cores (e.g. a ~10 cm corer to 15 cm depth, three per plot), sieve them through fine mesh, and identify, count and weigh the macroinvertebrates (wet, dry and ash-free dry weight). For the birds, run repeated fixed-position visual scans over the plots during the low-tide feeding window, counting birds by species and activity, and optionally film focal foraging birds to estimate prey intake. Look for a farming effect as a significant treatment × period interaction using generalised linear mixed models (with plot as a random effect), and compare community composition with PERMANOVA and SIMPER on Bray–Curtis dissimilarities.</t>
         </is>
       </c>
+      <c r="AL9" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM9" s="18" t="inlineStr">
+        <is>
+          <t>martinezcurci_2023</t>
+        </is>
+      </c>
+      <c r="AN9" s="19" t="n"/>
+      <c r="AO9" s="19" t="n"/>
+      <c r="AP9" s="19" t="n"/>
     </row>
     <row r="10" ht="240" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -2948,6 +3103,19 @@
           <t>To characterise the fauna your kelp farm supports and compare it with wild kelp forest and open water (a control for the structure alone), sample fish, invertebrates and eDNA at all three habitat types. Set multi-mesh gill nets (a few per habitat) at grow-line depth over several days and nights, identifying and measuring the catch, and note fish on the kelp at harvest; run cameras for daytime fish observations. For invertebrates, hand-strip epifauna off kelp blades and holdfasts and scrape set lengths of rope and buoys, and hang untwisted-rope fauna traps retrieved after ~2–3 days, then rinse everything over a fine (~250 µm) sieve and identify and count the animals. Collect triplicate water samples per habitat (Niskin), filter them for eDNA using fish (12S) and invertebrate (COI) markers, and process the reads into community lists. Compare communities among farm, forest and open water with PERMANOVA, PERMDISP and nMDS, test alpha diversity with ANOVA, and use indicator-species analysis to find taxa characteristic of each habitat.</t>
         </is>
       </c>
+      <c r="AL10" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM10" s="18" t="inlineStr">
+        <is>
+          <t>andrews_2025</t>
+        </is>
+      </c>
+      <c r="AN10" s="19" t="n"/>
+      <c r="AO10" s="19" t="n"/>
+      <c r="AP10" s="19" t="n"/>
     </row>
     <row r="11" ht="240" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -3129,6 +3297,19 @@
           <t>Methods review — no primary data collection. It surveys the data-collection techniques (camera/video, eDNA, sediment sampling, netting and others) used to monitor how wild species associate with aquaculture sites across shellfish, finfish and seaweed. It helps scope which monitoring method suits a given context but defers procedural detail to the primary papers it cites.</t>
         </is>
       </c>
+      <c r="AL11" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM11" s="18" t="inlineStr">
+        <is>
+          <t>english_2024</t>
+        </is>
+      </c>
+      <c r="AN11" s="19" t="n"/>
+      <c r="AO11" s="19" t="n"/>
+      <c r="AP11" s="19" t="n"/>
     </row>
     <row r="12" ht="240" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -3293,6 +3474,19 @@
           <t>To test whether seaweed (and shellfish) cultivation affects the seabed community, sample sediment at stations inside the culture areas and at reference stations outside the farm, ideally with a pre-cultivation baseline to compare against. At each station take a single grab sample (e.g. a 0.1 m² Day grab), subsample a little sediment for particle-size analysis, then sieve the rest over a 1 mm sieve and identify, count and weigh the retained animals (typically to family), keeping stations at least ~200 m apart for independence. Repeat in the same season across successive years. Compare abundance, richness, biomass and diversity between culture and reference areas (and across years) with two-way PERMANOVA, describe community and sediment differences with nMDS and SIMPER, and relate assemblage patterns to depth and sediment variables with distance-based linear models.</t>
         </is>
       </c>
+      <c r="AL12" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM12" s="18" t="inlineStr">
+        <is>
+          <t>corrigan_2025</t>
+        </is>
+      </c>
+      <c r="AN12" s="19" t="n"/>
+      <c r="AO12" s="19" t="n"/>
+      <c r="AP12" s="19" t="n"/>
     </row>
     <row r="13" ht="240" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -3469,6 +3663,19 @@
           <t>Methods review — no primary data collection. It reviews satellite-, aerial- and acoustic-remote-sensing techniques for detecting and estimating the biomass of wild kelp and discusses what they mean for harvesting. It offers a conceptual comparison of tools rather than a standardised, repeatable protocol; useful mainly as background for mapping wild kelp in a farm-versus-wild comparison.</t>
         </is>
       </c>
+      <c r="AL13" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM13" s="18" t="inlineStr">
+        <is>
+          <t>bennion_2019</t>
+        </is>
+      </c>
+      <c r="AN13" s="19" t="n"/>
+      <c r="AO13" s="19" t="n"/>
+      <c r="AP13" s="19" t="n"/>
     </row>
     <row r="14" ht="240" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -3641,6 +3848,19 @@
           <t>To measure the small mobile animals (epifauna) and attached plants your farm supports, and how that compares with a nearby natural habitat, sample the farm alongside a comparator such as a seagrass bed at matched depth. Place a small quadrat (e.g. 0.2 × 0.2 m) with a bag over it, scrape or cut everything inside — macrophytes plus all the animals living on them — bag it, and on land rinse the fauna through a ~1 mm sieve, identify and count the animals, and dry and weigh both plants and animals. Take several replicate quadrats per habitat at each site (e.g. ~10 for plant biomass, ~5 of those also worked up for fauna), and count fish along fixed belt transects (e.g. 25 × 2 m) by snorkel or dive in the same areas. Compare habitats with mixed-effects models (habitat as the fixed factor, site as random) and describe community differences with Bray–Curtis nMDS and PERMANOVA. Use a single observer for all fish counts to remove observer bias.</t>
         </is>
       </c>
+      <c r="AL14" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM14" s="18" t="inlineStr">
+        <is>
+          <t>tano_2016</t>
+        </is>
+      </c>
+      <c r="AN14" s="19" t="n"/>
+      <c r="AO14" s="19" t="n"/>
+      <c r="AP14" s="19" t="n"/>
     </row>
     <row r="15" ht="240" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -3805,6 +4025,19 @@
           <t>To monitor which organisms colonise your farm and the wider community present (epibiota and community composition), deploy artificial settlement plates on racks at the farm and collect filtered water samples for environmental DNA on a set schedule spanning one to a few months. Retrieve the plates and process both plates and water for DNA, which is PCR-amplified and sequenced (sequencing is usually outsourced as a service). Cluster the sequences into taxa (OTUs) and analyse community composition and indicator species, comparing across time or against a reference site. The workflow is written to be repeatable at other seaweed farms.</t>
         </is>
       </c>
+      <c r="AL15" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM15" s="18" t="inlineStr">
+        <is>
+          <t>bernard_2019</t>
+        </is>
+      </c>
+      <c r="AN15" s="19" t="n"/>
+      <c r="AO15" s="19" t="n"/>
+      <c r="AP15" s="19" t="n"/>
     </row>
     <row r="16" ht="240" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -3963,6 +4196,19 @@
           <t>A community-based monitoring protocol for shore and benthic macrophytes covering both qualitative (species-richness) and quantitative (species-diversity) sampling. The practitioner lays 0.25 m² quadrats by stratified random placement and either destructively harvests the seaweed (scraped into labelled bags for sorting, identification and pressing) or records cover non-destructively with gridded photo-quadrats and point-count photogrammetry, with tagged plants followed for demographic and succession studies. Percent cover, Pielou species-area curves, diversity indices and a precision index are used to guide how much to sample. It also explains using seaweeds as biomonitors of eutrophication and aquaculture nutrient loading, and recommends a pilot study before full rollout. Full PDF was read in a prior pass (not among the current project files).</t>
         </is>
       </c>
+      <c r="AL16" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM16" s="18" t="inlineStr">
+        <is>
+          <t>seaweeds_nd</t>
+        </is>
+      </c>
+      <c r="AN16" s="19" t="n"/>
+      <c r="AO16" s="19" t="n"/>
+      <c r="AP16" s="19" t="n"/>
     </row>
     <row r="17" ht="240" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -4139,6 +4385,19 @@
           <t>To test whether your seaweed farm changes local fish communities, count fish by underwater visual census along belt transects at three zones: inside the farm, immediately adjacent to it, and at an unfarmed reference site at least ~100 m away. Lay several fixed-size transects per zone (e.g. five 20 × 5 m belts), placed consistently (e.g. parallel to the reef to hold depth constant) with random start points, and have a single diver identify every fish to species and estimate its length, converting lengths to biomass with published length–weight relationships. Average species richness, abundance and biomass per zone. Test farm-zone effects with PERMANOVA (checking dispersion with PERMDISP), using a Bray–Curtis matrix on square-root-transformed abundances, and identify the species driving differences with SIMPER. If other pressures differ among sites (e.g. protection status), build them into the design as an additional factor.</t>
         </is>
       </c>
+      <c r="AL17" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM17" s="18" t="inlineStr">
+        <is>
+          <t>hehre_2015</t>
+        </is>
+      </c>
+      <c r="AN17" s="19" t="n"/>
+      <c r="AO17" s="19" t="n"/>
+      <c r="AP17" s="19" t="n"/>
     </row>
     <row r="18" ht="240" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -4311,6 +4570,19 @@
           <t>To compare the fish your farm supports against an unfarmed site, and to check whether farmed seaweed is entering the local food web, sample a farmed and a nearby control site in parallel using two methods repeated monthly across the year. Set baited traditional basket traps (a few per site) along the seaward edge, leave them overnight, then retrieve, empty and re-bait them over several consecutive days each month; separately, have one snorkeler record fish species and numbers along a fixed transect (e.g. 2 × 12 m) for a set time. Identify and count the catch, and dissect a subset of fish to examine stomach contents — identifying food items, scoring trophic level, and looking specifically for your farmed species in the guts. Compare abundance between sites with a chi-square test, diversity with Shannon–Wiener and Pielou indices (plus a diversity t-test), and trophic proportions and the occurrence of farmed seaweed in stomachs with Fisher's exact test.</t>
         </is>
       </c>
+      <c r="AL18" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM18" s="18" t="inlineStr">
+        <is>
+          <t>anyango_2017</t>
+        </is>
+      </c>
+      <c r="AN18" s="19" t="n"/>
+      <c r="AO18" s="19" t="n"/>
+      <c r="AP18" s="19" t="n"/>
     </row>
     <row r="19" ht="240" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -4487,6 +4759,19 @@
           <t>To assess how your farm affects fish assemblages, count fish by underwater visual census along belt transects run at the farm and at two control sites (one nearby, one further away). For each transect (e.g. a 20 m tape set perpendicular to shore) make separate passes — first counting fast-moving fish within a wider band, then slowly recording cryptic and bottom fish within a narrow band on each side — using a single observer throughout. Run several replicate transects per site (e.g. ~10), spread across tidal states, and at the end of each transect record the bottom cover (seaweed, seagrass, coral, sand) with a line-intercept method. Compare fish communities among farm and controls using Bray–Curtis nMDS with ANOSIM and SIMPER, relate fish patterns to substrate with a matrix-correlation test (RELATE), and test diversity and abundance with ANOVA (with appropriate transformation and multiple-test correction).</t>
         </is>
       </c>
+      <c r="AL19" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM19" s="18" t="inlineStr">
+        <is>
+          <t>bergman_2001</t>
+        </is>
+      </c>
+      <c r="AN19" s="19" t="n"/>
+      <c r="AO19" s="19" t="n"/>
+      <c r="AP19" s="19" t="n"/>
     </row>
     <row r="20" ht="240" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -4657,6 +4942,19 @@
           <t>To measure how many young fish settle and recruit into your mussel farm compared with natural habitats, deploy standard fish-recruitment collectors (SMURFs — mesh-covered units built to a fixed specification) in the farm and in reference habitats such as natural reef and bare soft-sediment. Set several units per habitat (e.g. ~10), spaced well apart and split between a near-surface and a near-seabed depth, tying the farm units to the backbone lines; then clear the fish from each unit on a set schedule (e.g. monthly, timed to the new moon) by lifting it into a fine scoop net, and identify, measure and count the catch, splitting key species into settler/juvenile/adult size classes. To relate recruitment to the habitat, also quantify the kelp/biofouling biomass by stripping short sections of several dropper lines at each depth and weighing the material. Model fish abundance across habitat, depth and month with linear mixed-effects models, compare diversity with Shannon/evenness indices and Kruskal–Wallis, and compare community composition with Bray–Curtis NMDS and PERMANOVA.</t>
         </is>
       </c>
+      <c r="AL20" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM20" s="18" t="inlineStr">
+        <is>
+          <t>underwood_2023</t>
+        </is>
+      </c>
+      <c r="AN20" s="19" t="n"/>
+      <c r="AO20" s="19" t="n"/>
+      <c r="AP20" s="19" t="n"/>
     </row>
     <row r="21" ht="240" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -4827,6 +5125,19 @@
           <t>This is a reference paper rather than a standalone protocol: it reviews and signposts useful monitoring methods for mobile fauna and community composition at integrated mussel-and-seaweed farms, with citations to the primary sources that describe each method. Use it to locate the cited primary protocols relevant to your Habitat &amp; Biodiversity indicators, then follow those for execution. Open access.</t>
         </is>
       </c>
+      <c r="AL21" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM21" s="18" t="inlineStr">
+        <is>
+          <t>corrigan_2024</t>
+        </is>
+      </c>
+      <c r="AN21" s="19" t="n"/>
+      <c r="AO21" s="19" t="n"/>
+      <c r="AP21" s="19" t="n"/>
     </row>
     <row r="22" ht="240" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -5008,6 +5319,19 @@
           <t>This is a systematic review and meta-analysis (65 studies), not a sampling protocol. It synthesises the habitat value of bivalve and seaweed aquaculture for fish and invertebrates and reports pooled effect sizes (log response ratios), which you can use to anticipate the likely magnitude of habitat effects and to pick gear, species and farm-type combinations that maximise them. Use it to scope and design a primary study rather than to execute measurements.</t>
         </is>
       </c>
+      <c r="AL22" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM22" s="18" t="inlineStr">
+        <is>
+          <t>theuerkauf_2022</t>
+        </is>
+      </c>
+      <c r="AN22" s="19" t="n"/>
+      <c r="AO22" s="19" t="n"/>
+      <c r="AP22" s="19" t="n"/>
     </row>
     <row r="23" ht="240" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -5184,6 +5508,19 @@
           <t>To measure how your seaweed farm affects local fish catches, sample with the traditional basket traps fishers already use, comparing the farm against control habitats — ideally a nearby seagrass bed and a bare-sand site at similar depth. Set several traps per site (e.g. five, ~20 m apart), bait them with the local mix, soak ~24 h, and rotate traps among sites each day so trap differences don't bias the comparison; repeat over multiple days and tidal cycles, then pool days as replicates. Weigh, measure and identify the whole catch and assign each species to a feeding/trophic group, and estimate the cover of seaweed, seagrass and sand at each trap for context. Compare catch, biomass, species number and size among habitats with ANOVA (with transformation and multiple-test correction where needed), and compare catch composition with Bray–Curtis nMDS, ANOSIM and SIMPER, linking composition to habitat cover with an environmental-matching routine (BIO-ENV). A within-farm version — traps beside the seaweed vs. on bare sand — tests microhabitat effects.</t>
         </is>
       </c>
+      <c r="AL23" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM23" s="18" t="inlineStr">
+        <is>
+          <t>eklof_2006</t>
+        </is>
+      </c>
+      <c r="AN23" s="19" t="n"/>
+      <c r="AO23" s="19" t="n"/>
+      <c r="AP23" s="19" t="n"/>
     </row>
     <row r="24" ht="240" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -5360,6 +5697,19 @@
           <t>To assess whether long-term seaweed farming is changing local water quality, sample at the culture site and at two comparison sites — a control just outside the farm (a few hundred metres away) and a reference site further off (~1–1.5 km) with similar conditions but no farming — and, where possible, compare against historical baseline data for the area. Sample across seasons rather than once, collecting surface water with a Niskin sampler and reading temperature, salinity, dissolved oxygen, pH, turbidity and total dissolved solids on the spot with a multiparameter sonde, while taking bottles for nutrients (ammonia, nitrate, nitrite, phosphate, silicate), chlorophyll-a, primary productivity (light/dark bottle) and BOD by standard laboratory methods; confirm DO by Winkler titration. Test spatial (culture vs control vs reference) and seasonal differences with one-way ANOVA and Tukey post-hoc tests, and group sites by their water-quality signature using cluster analysis, MDS and PCA.</t>
         </is>
       </c>
+      <c r="AL24" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM24" s="18" t="inlineStr">
+        <is>
+          <t>abhilash_2019</t>
+        </is>
+      </c>
+      <c r="AN24" s="19" t="n"/>
+      <c r="AO24" s="19" t="n"/>
+      <c r="AP24" s="19" t="n"/>
     </row>
     <row r="25" ht="240" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -5532,6 +5882,19 @@
           <t>To track how your farm affects phytoplankton and water quality, sample surface water (about 0.5 m) at several stations inside each culture area alongside paired blank stations in adjacent non-culture water, repeated across the growing season (roughly monthly). At each station measure temperature, dissolved oxygen, salinity and pH in situ with a multiparameter probe, read water clarity with a Secchi disk, and collect water in clean bottles for chlorophyll-a (filter onto GF/F, extract in 90% acetone, read on a spectrophotometer) and for total nitrogen and phosphorus (potassium-persulfate digestion). For the phytoplankton community, filter a separate 1 L sample onto a 0.22 um membrane, extract DNA and sequence the 18S rRNA gene, classifying reads into OTUs at 97% similarity and computing richness and Shannon/Chao diversity. Compare culture versus blank sites with ANOSIM and NMDS, and relate community differences to the measured water-quality variables with redundancy analysis (RDA).</t>
         </is>
       </c>
+      <c r="AL25" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM25" s="18" t="inlineStr">
+        <is>
+          <t>zhu_2023</t>
+        </is>
+      </c>
+      <c r="AN25" s="19" t="n"/>
+      <c r="AO25" s="19" t="n"/>
+      <c r="AP25" s="19" t="n"/>
     </row>
     <row r="26" ht="240" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -5570,7 +5933,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Seaweed Water Quality — Indicators 1.1.1 (N and P bioextraction via Gracilaria tissue uptake), 2.1.1 (chlorophyll-a / phytoplankton response). Climate Change Indicator 2.1.1 (pH) likely also.</t>
+          <t>Seaweed Water Quality Indicator 1.2.1 (dissolved oxygen) and Climate Change Indicator 2.1.1 (pH), both measured in situ. Demonstrates N and P bioremediation via water-column DIN/DIP drawdown along paired transects (one through the Gracilaria area, one not) - not via tissue analysis. [v30 reconciliation: prior tags WQ 1.1.1 (tissue bioextraction) and WQ 2.1.1 (chlorophyll-a) removed - not supported by the methods; see Notes.]</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -5580,7 +5943,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Yes for bioextraction quantification — standard methods combining seawater nutrient sampling with Gracilaria tissue %N/%P analysis × biomass. Direct precursor to the Xiao 2017 calculation chain.</t>
+          <t>Yes, for a water-column bioremediation demonstration - paired through-algae vs alongside transect sampling of DIN, DIP, DO, pH and COD, plus crop growth (specific growth rate). No tissue %N/%P or CHN analysis is performed, so this is NOT a tissue x biomass x area bioextraction quantification (per the narrow WQ 1.1.1 rule).</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -5595,7 +5958,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Water samplers, nutrient analyser, biomass scales, CHN analyser for tissue</t>
+          <t>Water samplers; YSI-85 multiprobe (T, S, Secchi, pH, DO); flow-injection nutrient analyser for DIN/DIP; balances for rope biomass/growth</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
@@ -5625,7 +5988,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>Foundational Chinese Gracilaria bioremediation paper; provides species-specific bioextraction reference data analogous to Xiao 2017's Saccharina values.</t>
+          <t>Foundational Chinese Gracilaria bioremediation paper; provides species-specific bioextraction reference data analogous to Xiao 2017's Saccharina values. | v30 AK-vs-I reconciliation: full methods (Xu 2008, read) show water-column DIN/DIP transect sampling only - no tissue %N/%P, no CHN analyser, no chlorophyll-a. Removed WQ 1.1.1 (tissue bioextraction) and WQ 2.1.1 (chl-a); retained WQ 1.2.1 (DO) and CC 2.1.1 (pH). Bioremediation inferred from water-column drawdown, not tissue uptake. Original I: 'Seaweed Water Quality — Indicators 1.1.1 (N and P bioextraction via Gracilaria tissue uptake), 2.1.1 (chlorophyll-a / phytoplankton response). Climate Change Indicator 2.1.1 (pH) likely also.' | v32: matching column (MEL Indicator multi-select) re-tagged from 'WQ 1.1.1; WQ 2.1.1' to 'WQ 1.2.1 (DO); CC 2.1.1 (pH)' so the reconciliation drives tool matching (user-approved). Tool now surfaces row 26 under DO and pH, not bioextraction/chl-a.</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
@@ -5650,7 +6013,7 @@
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>WQ 1.1.1 — N and P bioextraction, WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 1.2.1 — Dissolved oxygen, CC 2.1.1 — pH / ocean acidification</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -5703,6 +6066,24 @@
           <t>Not exposure-specific</t>
         </is>
       </c>
+      <c r="AK26" s="16" t="inlineStr">
+        <is>
+          <t>To show that a seaweed crop draws down nutrients from nearby aquaculture effluent, set two transects radiating from the effluent outlet - one passing through the seaweed cultivation area and one alongside it that does not - with a series of stations along each. During ebb-tide effluent discharge, sample surface water at each station about weekly through the growing season, measuring temperature, salinity, Secchi depth, pH, dissolved oxygen and chemical oxygen demand in situ with a multiprobe and dissolved inorganic nitrogen and phosphorus on a flow-injection nutrient analyser; weigh tagged ropes at fixed intervals to track crop specific growth rate in parallel. Compare matched through-algae versus alongside stations with a t-test - lower downstream DIN and DIP along the through-algae transect is the bioremediation signal. Note this design infers nutrient removal from water-column differences rather than from a tissue-nitrogen x biomass measurement, so it evidences a water-quality response rather than a tissue-based bioextraction figure.</t>
+        </is>
+      </c>
+      <c r="AL26" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM26" s="18" t="inlineStr">
+        <is>
+          <t>xu_2008</t>
+        </is>
+      </c>
+      <c r="AN26" s="19" t="n"/>
+      <c r="AO26" s="19" t="n"/>
+      <c r="AP26" s="19" t="n"/>
     </row>
     <row r="27" ht="240" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -5879,6 +6260,19 @@
           <t>To use fouling macroalgae as a bioindicator of water-quality differences between sites, sample the community growing on standardised hard structures — here, established mooring buoys that have been in place long enough to be fully colonised — choosing several sites spanning a suspected nutrient/turbidity gradient. At each site scrape all the fouling off several replicate buoys (e.g. ~10) into fine (~1 mm) mesh bags, preserve it, then sort and identify the macroalgae (to genus) and dry and weigh them, standardising biomass to the surface area sampled. Pair these community data with water-quality measurements for each site (e.g. nitrate, phosphate, water clarity). Compare taxon richness and biomass among sites (e.g. Kruskal–Wallis with pairwise tests) and community composition with multivariate methods (Jaccard for presence/absence, Bray–Curtis for biomass, via ANOSIM and SIMPER), and relate the site groupings to the water-quality gradient with PCA or cluster analysis.</t>
         </is>
       </c>
+      <c r="AL27" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM27" s="18" t="inlineStr">
+        <is>
+          <t>drakard_2018</t>
+        </is>
+      </c>
+      <c r="AN27" s="19" t="n"/>
+      <c r="AO27" s="19" t="n"/>
+      <c r="AP27" s="19" t="n"/>
     </row>
     <row r="28" ht="240" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -6058,6 +6452,19 @@
           <t>To monitor water quality across a mixed culture area, sample at fixed stations covering both the enclosed pond and the open cage or raft zones, repeated in a few campaigns spanning the growth, breeding and harvest phases of the season. Measure pH, temperature, salinity and dissolved oxygen on site with a multiparameter water-quality analyser at a set depth (for example about 0.5 m in ponds and a few metres down in deeper cage areas), and collect water for laboratory chlorophyll-a (DMF extraction, absorbance against a standard) plus supporting nutrients - molybdenum-blue phosphorus, dissolved inorganic nitrogen on a continuous-flow analyser, and chemical oxygen demand. Standardise each variable (z-score) and run principal component analysis to find the dominant water-quality gradients, then use Spearman correlations to identify the parameters driving them. This gives a comparable per-season, per-location water-quality picture that flags dissolved-oxygen and chlorophyll changes associated with the culture.</t>
         </is>
       </c>
+      <c r="AL28" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM28" s="18" t="inlineStr">
+        <is>
+          <t>zhang_2020</t>
+        </is>
+      </c>
+      <c r="AN28" s="19" t="n"/>
+      <c r="AO28" s="19" t="n"/>
+      <c r="AP28" s="19" t="n"/>
     </row>
     <row r="29" ht="240" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -6233,6 +6640,19 @@
           <t>This is a design-of-experiments reference for open-water water-quality monitoring, not an indicator-measurement protocol. Read it before designing the WQ component of a farm programme: it covers how to choose reference sites in complex hydrodynamic settings, how to set sampling resolution, when data can be pooled, how to run post-hoc power tests, and the trade-offs between discrete grab sampling and continuous logging. Use its guidance to size and lay out your sampling design, then draw the actual measurement procedures from the indicator-specific protocols.</t>
         </is>
       </c>
+      <c r="AL29" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM29" s="18" t="inlineStr">
+        <is>
+          <t>jansen_2016</t>
+        </is>
+      </c>
+      <c r="AN29" s="19" t="n"/>
+      <c r="AO29" s="19" t="n"/>
+      <c r="AP29" s="19" t="n"/>
     </row>
     <row r="30" ht="240" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -6407,6 +6827,19 @@
           <t>To assess whether large-scale seaweed cultivation changes local water quality, sample the culture area together with non-culture control sites just outside it (on the order of 100 m to 1 km away) and, ideally, a further reference site of similar depth and hydrography with no farming. Sample at about 0.2 m depth on several occasions through the cultivation season. Measure temperature, salinity, pH and dissolved oxygen in situ with a multiparameter instrument and read transparency with a Secchi disk; collect water for chlorophyll-a (filter onto GF/F ~0.45 um, extract and read on a UV-Vis spectrophotometer by the standard method), dissolved nutrients (ammonium, nitrate, nitrite, phosphate on an autoanalyser), total suspended solids (gravimetric on a pre-weighed filter dried at 105 C), and dissolved organic carbon and total nitrogen on a carbon-nitrogen analyser. Compare culture against control and reference with one-way ANOVA and Tukey tests, and use PCA with hierarchical clustering to group stations by their water-quality signature.</t>
         </is>
       </c>
+      <c r="AL30" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM30" s="18" t="inlineStr">
+        <is>
+          <t>liang_2022</t>
+        </is>
+      </c>
+      <c r="AN30" s="19" t="n"/>
+      <c r="AO30" s="19" t="n"/>
+      <c r="AP30" s="19" t="n"/>
     </row>
     <row r="31" ht="240" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -6574,6 +7007,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK31" s="16" t="inlineStr">
+        <is>
+          <t>To attribute water-quality and phytoplankton changes to kelp farming rather than to background variation, sample paired stations inside the kelp farm and in an adjacent control area both during the cultivation season and again after harvest - the post-harvest return to no difference is what confirms the farm as the cause. Collect surface and near-bottom water with a Niskin bottle, measure temperature and salinity with a probe, transparency with a Secchi disk, dissolved oxygen by Winkler titration and pH with a meter, and take frozen samples for dissolved inorganic N, P and silicate, suspended solids and chlorophyll-a (size-fractionated through 20, 2 and 0.7 um filters to split micro-, nano- and picophytoplankton). Settle and identify phytoplankton and compute species number, Margalef richness, Shannon diversity and Pielou evenness. Compare farm against control with non-parametric ANOVA (Scheirer-Ray-Hare) and Kruskal-Wallis, and community structure with ANOSIM and SIMPER on log-transformed Bray-Curtis similarities; track community-composition shifts (for example reduced dinoflagellate dominance), not just biomass.</t>
+        </is>
+      </c>
+      <c r="AL31" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM31" s="18" t="inlineStr">
+        <is>
+          <t>jiang_2020</t>
+        </is>
+      </c>
+      <c r="AN31" s="19" t="n"/>
+      <c r="AO31" s="19" t="n"/>
+      <c r="AP31" s="19" t="n"/>
     </row>
     <row r="32" ht="240" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -6612,7 +7063,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Seaweed Water Quality — Indicators 1.2.1 (dissolved oxygen), 2.1.1 (chlorophyll-a). Primary data included salinity, pH, sea-surface temperature, dissolved oxygen, nitrate, phosphate, water substrates, currents, clarity, turbidity, and water depth. Note: WQ 1.1.1 not applicable — water-column nutrient analysis only; no biomass-bioextraction.</t>
+          <t>Seaweed Water Quality — Indicators 1.2.1 (dissolved oxygen) [WQ 2.1.1 chlorophyll-a removed in v30 reconciliation - not measured]. Primary data included salinity, pH, sea-surface temperature, dissolved oxygen, nitrate, phosphate, water substrates, currents, clarity, turbidity, and water depth. Note: WQ 1.1.1 not applicable — water-column nutrient analysis only; no biomass-bioextraction.</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -6667,7 +7118,7 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>Carrying capacity framing suggests this paper is methodologically useful for any framework user scaling up cultivation.</t>
+          <t>Carrying capacity framing suggests this paper is methodologically useful for any framework user scaling up cultivation. | v30 AK-vs-I reconciliation: methods (Rahadiati 2017, read) measure DO, nutrients and physical parameters plus GIS suitability/carrying-capacity - no chlorophyll-a. Removed WQ 2.1.1; retained WQ 1.2.1 (DO). | v32: matching column re-tagged - removed WQ 2.1.1 (chl-a, not measured); retained WQ 1.2.1 (DO) (user-approved).</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -6692,7 +7143,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t>WQ 1.2.1 — Dissolved oxygen, WQ 2.1.1 — Chlorophyll-a</t>
+          <t>WQ 1.2.1 — Dissolved oxygen</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -6750,6 +7201,19 @@
           <t>This protocol pairs seasonal water-quality measurement with a GIS suitability-and-carrying-capacity assessment for siting seaweed cultivation. Choose stations that represent the cultivation areas (purposive sampling) and measure across the year to capture seasonal change: water depth (portable sounder), current velocity (drift float), clarity (Secchi disk), salinity (refractometer), pH and sea-surface temperature (combined meter) and dissolved oxygen (DO meter) on site, with water samples taken to a lab for nitrate, phosphate and turbidity. Feed the physical, chemical, biological and infrastructural parameters into a GIS matching analysis that scores each area against minimum cultivation requirements, then calculate carrying capacity from the suitable area and the space one cultivation unit occupies to estimate how many units the waters can sustainably support. Use it to decide where, and at what density, cultivation can expand without degrading the coastal environment.</t>
         </is>
       </c>
+      <c r="AL32" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM32" s="18" t="inlineStr">
+        <is>
+          <t>rahadiati_2017</t>
+        </is>
+      </c>
+      <c r="AN32" s="19" t="n"/>
+      <c r="AO32" s="19" t="n"/>
+      <c r="AP32" s="19" t="n"/>
     </row>
     <row r="33" ht="240" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -6926,6 +7390,19 @@
           <t>This is a foundational conceptual reference for using seaweed as a biofilter in IMTA and land-based systems; it establishes the framing rather than a measurement procedure and contains no explicit sampling protocol. It has been superseded methodologically by later quantitative work. Use it for context on the bioextraction concept, then go to the primary quantitative papers for the actual tissue-content x biomass measurement.</t>
         </is>
       </c>
+      <c r="AL33" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM33" s="18" t="inlineStr">
+        <is>
+          <t>troell_1999</t>
+        </is>
+      </c>
+      <c r="AN33" s="19" t="n"/>
+      <c r="AO33" s="19" t="n"/>
+      <c r="AP33" s="19" t="n"/>
     </row>
     <row r="34" ht="240" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -7100,6 +7577,19 @@
           <t>This is a methods review (several hundred papers), not a standalone protocol. It classifies carbon-uptake methods - tissue carbon content x biomass, eddy covariance, isotope tracing, all relatively mature - and carbon-permanence methods (still immature, no consensus), and maps which method suits which monitoring need, but defers procedural detail to the primary papers it reviews. Use it as the entry point for matching a carbon method to your Climate Change indicator, then jump to a primary protocol for execution.</t>
         </is>
       </c>
+      <c r="AL34" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM34" s="18" t="inlineStr">
+        <is>
+          <t>rose_2023</t>
+        </is>
+      </c>
+      <c r="AN34" s="19" t="n"/>
+      <c r="AO34" s="19" t="n"/>
+      <c r="AP34" s="19" t="n"/>
     </row>
     <row r="35" ht="240" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -7272,6 +7762,19 @@
           <t>This is a basin-scale modelling framework rather than a farm-side measurement method: it predicts seaweed yield, nutrient extraction and carbon-dioxide impact from model outputs, not from samples you collect. To reproduce it, drive a prognostic macroalgal growth model with operational ocean-model outputs (currents, temperature, nutrients), route the results through a 2D nutrient-transport scheme to estimate downstream nutrient effects, and validate predicted yields against published data before running mass-balance and CO2 accounting at chosen production scales. Use it for scenario-scale projections of nutrient and carbon impact, not for site-level indicator measurement.</t>
         </is>
       </c>
+      <c r="AL35" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM35" s="18" t="inlineStr">
+        <is>
+          <t>johnson_2024</t>
+        </is>
+      </c>
+      <c r="AN35" s="19" t="n"/>
+      <c r="AO35" s="19" t="n"/>
+      <c r="AP35" s="19" t="n"/>
     </row>
     <row r="36" ht="240" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
@@ -7444,6 +7947,19 @@
           <t>This is a scaling-up accounting synthesis, not a primary protocol. It combines production statistics with published tissue-content multipliers to produce region-scale annual carbon, nitrogen, phosphorus and oxygen fluxes for the seaweed sector, and benchmarks them against riverine nutrient loads. Use it to bridge farm-level MEL measurements to the regional and national aggregate figures that policymakers use, applying the same tissue-content x biomass logic at larger scale.</t>
         </is>
       </c>
+      <c r="AL36" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM36" s="18" t="inlineStr">
+        <is>
+          <t>xiong_2023</t>
+        </is>
+      </c>
+      <c r="AN36" s="19" t="n"/>
+      <c r="AO36" s="19" t="n"/>
+      <c r="AP36" s="19" t="n"/>
     </row>
     <row r="37" ht="240" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -7614,6 +8130,19 @@
           <t>To map how your farm changes surrounding water quality, run a spatially-resolved survey across many fixed stations covering the farm, its near field, and reference water outside any farm influence. At each station measure dissolved oxygen, pH, pCO2 (with an underway pCO2 analyser or derived from DIC plus alkalinity), dissolved inorganic carbon, nutrients and chlorophyll-a, using a multiprobe plus water samples from a Niskin bottle. Interpolate the station data geostatistically (semivariogram fitting and kriging) to delineate the farm's zone of influence, and compare zones with ANOVA. Tune station spacing to the cultivated species, since influence-zone size is species-dependent - kilometre-scale for some species, under about 100 m for others.</t>
         </is>
       </c>
+      <c r="AL37" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM37" s="18" t="inlineStr">
+        <is>
+          <t>wu_2025</t>
+        </is>
+      </c>
+      <c r="AN37" s="19" t="n"/>
+      <c r="AO37" s="19" t="n"/>
+      <c r="AP37" s="19" t="n"/>
     </row>
     <row r="38" ht="240" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -7788,6 +8317,19 @@
           <t>To quantify the nitrogen and phosphorus your crop removes from the water (bioextraction), measure the tissue nitrogen and phosphorus content of harvested seaweed and multiply by the biomass harvested and the cultivated area. Collect representative tissue samples at harvest, dry them, and have a partner lab run elemental (CHN) analysis for %N and %P; combine these with recorded harvest weight and farm footprint to get total N and P extracted. The paper also supplies published %N/%P values for major cultivated species, so it can serve as a reference source if you cannot measure tissue directly, though site-measured values are more defensible. Pair with a primary tissue-measurement protocol for the CHN and isotope side.</t>
         </is>
       </c>
+      <c r="AL38" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM38" s="18" t="inlineStr">
+        <is>
+          <t>xiao_2017</t>
+        </is>
+      </c>
+      <c r="AN38" s="19" t="n"/>
+      <c r="AO38" s="19" t="n"/>
+      <c r="AP38" s="19" t="n"/>
     </row>
     <row r="39" ht="240" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -7960,6 +8502,19 @@
           <t>This is a technology review, not a protocol: it surveys satellite, autonomous underwater vehicle and other autonomous-platform options for observing chlorophyll-a and phytoplankton blooms. Use it to decide which remote-sensing or autonomous approach fits your monitoring need and budget, then follow the primary source for that platform's procedure.</t>
         </is>
       </c>
+      <c r="AL39" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM39" s="18" t="inlineStr">
+        <is>
+          <t>bell_2020</t>
+        </is>
+      </c>
+      <c r="AN39" s="19" t="n"/>
+      <c r="AO39" s="19" t="n"/>
+      <c r="AP39" s="19" t="n"/>
     </row>
     <row r="40" ht="240" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -8136,6 +8691,19 @@
           <t>To quantify how much nitrogen your kelp removes from the water near a fed farm - and to show the nitrogen actually came from that farm - deploy juvenile Saccharina latissima sporophytes on ropes at a farm-side station and at a reference station some kilometres away, hanging replicate 1 m ropes at several depths (for example 2, 5 and 8 m). Each month measure blade length to get growth rate, and sample the meristem (new-growth) tissue: dry it, grind it, and run it through an elemental analyser for carbon and nitrogen content and through an isotope-ratio mass spectrometer for delta-15-N. In parallel, collect integrated water samples with a tube sampler for dissolved inorganic nitrogen (ammonium, nitrate plus nitrite) and chlorophyll-a on an autoanalyser and fluorometer, and estimate the farm's nitrogen release with a simple mass-balance model. A raised tissue %N together with a delta-15-N shifted toward the farm's feed/waste signature (relative to the reference plants) confirms farm-derived uptake; multiply tissue %N by harvested biomass to convert to nitrogen extracted per unit area, and regress growth and N-content against ambient dissolved inorganic nitrogen.</t>
         </is>
       </c>
+      <c r="AL40" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM40" s="18" t="inlineStr">
+        <is>
+          <t>wang_2014</t>
+        </is>
+      </c>
+      <c r="AN40" s="19" t="n"/>
+      <c r="AO40" s="19" t="n"/>
+      <c r="AP40" s="19" t="n"/>
     </row>
     <row r="41" ht="240" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -8312,6 +8880,19 @@
           <t>This is a regional nitrogen and phosphorus accounting paper, not a primary protocol; it combines a catchment-loading model with a phytoplankton-biomass synthesis. It has been superseded methodologically by later bioextraction accounting work. Use it only for background on regional N and P balance around aquaculture.</t>
         </is>
       </c>
+      <c r="AL41" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM41" s="18" t="inlineStr">
+        <is>
+          <t>sara_2011</t>
+        </is>
+      </c>
+      <c r="AN41" s="19" t="n"/>
+      <c r="AO41" s="19" t="n"/>
+      <c r="AP41" s="19" t="n"/>
     </row>
     <row r="42" ht="240" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
@@ -8484,6 +9065,19 @@
           <t>To characterise plankton and background water quality around an integrated seaweed-and-shellfish farm, sample at three stations - one upstream of the prevailing current (a reference unaffected by the farm), one midstream and one downstream - timing visits to the same tidal phase, weekly in the productive spring and summer and fortnightly in autumn and winter. Collect water with a Niskin bottle at two depths (near-surface and below the seasonal thermocline) for dissolved nutrients (nitrate, nitrite, ammonium, phosphate, silicate by segmented-flow colourimetry), profile temperature, salinity and clarity with a CTD and Secchi disk, and take a preserved (Lugol's iodine) sample for phytoplankton. Count phytoplankton by the Utermohl settling method under an inverted microscope, convert cell counts to biovolume and then carbon biomass grouped into functional groups; for zooplankton, haul a 200 um ring net from near the seabed to the surface, preserve, and count under a microscope. Average by month and test differences among stations, depths and months with PERMANOVA (Euclidean for nutrients, Bray-Curtis on fourth-root-transformed abundance and biomass for communities), visualising with PCA and metric MDS ordination.</t>
         </is>
       </c>
+      <c r="AL42" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM42" s="18" t="inlineStr">
+        <is>
+          <t>walker_2023</t>
+        </is>
+      </c>
+      <c r="AN42" s="19" t="n"/>
+      <c r="AO42" s="19" t="n"/>
+      <c r="AP42" s="19" t="n"/>
     </row>
     <row r="43" ht="240" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -8659,6 +9253,19 @@
           <t>To measure how a farm shapes phytoplankton along a distance gradient, set stations at the culture-area centre and edge and at fixed distances outward (for example about 100 m and 1000 m from the edge), sampling both surface (~0.5 m) and near-bottom water in the relevant culture seasons. Measure depth, transparency (Secchi), pH, temperature and salinity in situ, determine dissolved oxygen by Winkler titration, and filter water (pre-combusted GF/F, 0.45 um) for chlorophyll-a (fluorometer), dissolved nutrients (colourimetric), total organic carbon (elemental analyser) and suspended solids (gravimetric). For phytoplankton, settle a preserved (4% formalin) sub-sample and count at least 300 units per sample under a light microscope, expressing abundance per litre and computing dominance for the commonest taxa. Test differences among culture types, stations and water layers with multi-way ANOVA (with Kruskal-Wallis where assumptions fail), and examine community structure with NMDS (Bray-Curtis on fourth-root data), ANOSIM and canonical correspondence analysis against the environmental variables.</t>
         </is>
       </c>
+      <c r="AL43" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM43" s="18" t="inlineStr">
+        <is>
+          <t>jiang_2012</t>
+        </is>
+      </c>
+      <c r="AN43" s="19" t="n"/>
+      <c r="AO43" s="19" t="n"/>
+      <c r="AP43" s="19" t="n"/>
     </row>
     <row r="44" ht="240" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
@@ -8831,6 +9438,19 @@
           <t>To test a seaweed farm's effects on the seabed and surrounding fauna, use an asymmetric before/after control-impact design: sample the farm and several control sites of similar depth and sediment a few kilometres away, before and after the cultivation season. Measure benthic oxygen flux in situ with a benthic chamber lander (enclosing a set area of sediment under bottom water, with oxygen, salinity and turbidity sensors logging at short intervals over several hours). Sample benthic infauna with a van Veen grab (0.1 m2), sieve through 1 mm mesh, preserve in ethanol, identify and compute diversity (rarefaction, effective number of species and a regional benthic quality index); assess mobile fauna with baited cages left on the seabed for a few days. Collect dissolved nutrients (nitrate plus nitrite, ammonium, phosphate, silicate) from syringe-filtered (0.2 um) water at set depths on an autoanalyser, and optionally log light to quantify farm shading. Compare farm against control with PERMANOVA/PCO and mixed models, using the BACI contrast (control-after minus control-before minus farm-after plus farm-before) to isolate the farm effect.</t>
         </is>
       </c>
+      <c r="AL44" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM44" s="18" t="inlineStr">
+        <is>
+          <t>visch_2020</t>
+        </is>
+      </c>
+      <c r="AN44" s="19" t="n"/>
+      <c r="AO44" s="19" t="n"/>
+      <c r="AP44" s="19" t="n"/>
     </row>
     <row r="45" ht="240" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -9003,6 +9623,19 @@
           <t>Although developed at fish farms, this benthic-bioindicator method transfers directly to seaweed-farm sediment monitoring. Collect macrobenthos close to the culture structures (within about 10 m) with a small grab (Ekman or van Veen, roughly 0.04-0.1 m2) and a 1 mm sieve; identify the animals, count species and individuals, and record biomass (wet weight, excluding shells), then compute diversity as Shannon H', species richness and evenness. From the same grab take the top ~1 cm of sediment with a corer for total nitrogen, total organic carbon and acid-volatile sulphide, and sample the water just above the sediment for dissolved oxygen. Relate the macrofauna metrics to the sediment-chemistry values to flag organic-enrichment stress - the derived thresholds (notably an acid-volatile-sulphide limit around 1.9 mg S per g as a hard boundary) give ready benchmarks for judging benthic condition under a farm.</t>
         </is>
       </c>
+      <c r="AL45" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM45" s="18" t="inlineStr">
+        <is>
+          <t>yokoyama_2007</t>
+        </is>
+      </c>
+      <c r="AN45" s="19" t="n"/>
+      <c r="AO45" s="19" t="n"/>
+      <c r="AP45" s="19" t="n"/>
     </row>
     <row r="46" ht="240" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
@@ -9175,6 +9808,19 @@
           <t>To test whether your farm locally buffers ocean acidification, sample surface water at the farm and at a paired control site outside its influence, timed to the weeks before harvest when biomass is highest. Collect water for the carbonate system - high-accuracy pH, pCO2, dissolved oxygen, and DIC plus total alkalinity by titration, with certified reference materials for quality control - following the standard carbonate-chemistry SOPs. Derive the full carbonate system with CO2SYS and compare farm against control (and across seasons) with ANOVA to detect any pH rise and pCO2 deficit. A simpler in-situ pH/DO buoy gives a coarser version of the same signal if the full titration setup is out of reach.</t>
         </is>
       </c>
+      <c r="AL46" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM46" s="18" t="inlineStr">
+        <is>
+          <t>xiao_2021</t>
+        </is>
+      </c>
+      <c r="AN46" s="19" t="n"/>
+      <c r="AO46" s="19" t="n"/>
+      <c r="AP46" s="19" t="n"/>
     </row>
     <row r="47" ht="240" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -9339,6 +9985,19 @@
           <t>This is a strategic scoping paper on co-locating kelp farming with marine renewable energy, not a monitoring protocol, and it maps only tangentially to the MEL indicators. Use it for strategic-fit and siting context rather than for any ecosystem-service measurement.</t>
         </is>
       </c>
+      <c r="AL47" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM47" s="18" t="inlineStr">
+        <is>
+          <t>rose_2022</t>
+        </is>
+      </c>
+      <c r="AN47" s="19" t="n"/>
+      <c r="AO47" s="19" t="n"/>
+      <c r="AP47" s="19" t="n"/>
     </row>
     <row r="48" ht="240" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
@@ -9513,6 +10172,19 @@
           <t>This is an analytical modelling method for coastal-protection benefit rather than a field-sampling protocol. To estimate wave attenuation by a seaweed farm, apply a 1D cross-shore wave model adapted for suspended culture, supplying water depth, vegetation density and longline density as inputs, then run a sensitivity analysis across those parameters to bound the attenuation you can expect. Empirical validation is limited, so treat the outputs as indicative; relevant only where coastal protection is an additional benefit beyond Habitat &amp; Biodiversity, Water Quality and Climate Change.</t>
         </is>
       </c>
+      <c r="AL48" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM48" s="18" t="inlineStr">
+        <is>
+          <t>bodycomb_2023</t>
+        </is>
+      </c>
+      <c r="AN48" s="19" t="n"/>
+      <c r="AO48" s="19" t="n"/>
+      <c r="AP48" s="19" t="n"/>
     </row>
     <row r="49" ht="240" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -9685,6 +10357,19 @@
           <t>This is a site-assessment engineering reference, not an ecosystem-service protocol. It provides Specific Exposure Energy (SEE) and Exposure Velocity (EV) index calculations for classifying a site's wave-and-current exposure. Use it to characterise the baseline exposure of a candidate farm site, which helps explain why monitoring results vary between exposed and sheltered farms.</t>
         </is>
       </c>
+      <c r="AL49" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM49" s="18" t="inlineStr">
+        <is>
+          <t>heasman_2024</t>
+        </is>
+      </c>
+      <c r="AN49" s="19" t="n"/>
+      <c r="AO49" s="19" t="n"/>
+      <c r="AP49" s="19" t="n"/>
     </row>
     <row r="50" ht="240" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
@@ -9862,6 +10547,19 @@
           <t>To grade the seabed condition under a co-culture farm with an internationally recognised sediment protocol, apply the MOM-B survey at stations spread across the culture zones. At each station take at least two grabs with a van Veen sampler; on each, measure sediment pH and redox potential (Eh) with probes and score the sensory state (colour, odour, consistency, gas bubbling and the depth of accumulated sludge). Sieve the sediment through 1 mm mesh and record whether living macrofauna are present or absent, then combine the three parameter groups - fauna presence/absence, chemistry (pH and Eh) and sensory scores - into the standard MOM-B condition classes (1 best to 4 unacceptable). Repeating across seasons and years lets you track whether organic loading from the farm is pushing sediment condition toward the unacceptable category.</t>
         </is>
       </c>
+      <c r="AL50" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM50" s="18" t="inlineStr">
+        <is>
+          <t>zhang_2020-b</t>
+        </is>
+      </c>
+      <c r="AN50" s="19" t="n"/>
+      <c r="AO50" s="19" t="n"/>
+      <c r="AP50" s="19" t="n"/>
     </row>
     <row r="51" ht="240" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -10034,6 +10732,19 @@
           <t>This is an engineering and economics case study, not an indicator-measurement method. It describes a low-cost small-farm kelp system - drag-embedment anchors with subsurface flotation - tested over three years in the North Atlantic. Use it for the technical and cost baseline of small exposed farms, not for ecosystem-service monitoring.</t>
         </is>
       </c>
+      <c r="AL51" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM51" s="18" t="inlineStr">
+        <is>
+          <t>stgelais_2022</t>
+        </is>
+      </c>
+      <c r="AN51" s="19" t="n"/>
+      <c r="AO51" s="19" t="n"/>
+      <c r="AP51" s="19" t="n"/>
     </row>
     <row r="52" ht="240" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
@@ -10198,6 +10909,19 @@
           <t>This is a framework and decision-support document - a European counterpart to the TNC MEL framework - rather than a sampling protocol. It catalogues indicators and candidate methods for habitat, water-quality and climate monitoring rather than prescribing procedures. Read it alongside the TNC framework when implementing MEL in a European context to cross-check indicator and method choices.</t>
         </is>
       </c>
+      <c r="AL52" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM52" s="18" t="inlineStr">
+        <is>
+          <t>tonk_2021</t>
+        </is>
+      </c>
+      <c r="AN52" s="19" t="n"/>
+      <c r="AO52" s="19" t="n"/>
+      <c r="AP52" s="19" t="n"/>
     </row>
     <row r="53" ht="240" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -10374,6 +11098,19 @@
           <t>To track what colonises your cultivated kelp over the season, sample whole kelp plants monthly through the growing period. Each month collect several plants from a set of independent dropper lines spread across the farm (sampling at more than one depth on the line to capture variation), bag and freeze them, then in the lab rinse each plant over a fine (~0.5 mm) sieve to collect mobile animals, pick off the sessile and colonial organisms (recording colonial cover as a percentage), and identify, count and weigh everything. Also record kelp size (biomass, blade area, and holdfast volume by water displacement), since more habitat supports more species. Treat each dropper line — not each plant — as the replicate, averaging its plants together, and compare months and treatments with PERMANOVA and multivariate ordination (mMDS on Bray–Curtis). To test whether biodiversity persists after harvest, leave some lines intact, strip others bare, and partially cut others, then resample the following season.</t>
         </is>
       </c>
+      <c r="AL53" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM53" s="18" t="inlineStr">
+        <is>
+          <t>corrigan_2023</t>
+        </is>
+      </c>
+      <c r="AN53" s="19" t="n"/>
+      <c r="AO53" s="19" t="n"/>
+      <c r="AP53" s="19" t="n"/>
     </row>
     <row r="54" ht="240" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
@@ -10548,6 +11285,19 @@
           <t>To measure the mobile fauna your kelp farm hosts and compare it with natural kelp forest, sample kelp-associated animals at the farm, at nearby wild kelp forest, and — as a control for the effect of simply adding rope/structure — in open water away from both. Use two capture methods: divers enclose whole kelp plants in a cotton bag before cutting them free (catching the animals living on them), and untwisted-rope fauna traps are hung at the same depth for a couple of days to sample the mobile invertebrate community. Take several replicates (e.g. three) of each at each location and depth, then rinse the catch over a fine (~250 µm) sieve, preserve it, and identify, count and weigh the animals. Compare community composition among farm, wild forest and open water with ordination (e.g. DCA) and test differences in abundance, richness, biomass and diversity with ANOVA, using ANCOVA to check for any effect of how long the kelp has been growing.</t>
         </is>
       </c>
+      <c r="AL54" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM54" s="18" t="inlineStr">
+        <is>
+          <t>bekkby_2023</t>
+        </is>
+      </c>
+      <c r="AN54" s="19" t="n"/>
+      <c r="AO54" s="19" t="n"/>
+      <c r="AP54" s="19" t="n"/>
     </row>
     <row r="55" ht="240" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -10722,6 +11472,19 @@
           <t>This is the international standard set of SOPs for seawater carbonate-system measurement, underpinning any pH, total alkalinity, DIC or pCO2 work around a farm. On the farm side the task is water collection following the sampling SOP - fill without bubbles, poison the sample to halt biological activity, and store it correctly; a partner lab then runs the analyses (DIC by coulometry or infrared, total alkalinity by titration, pCO2 by equilibration, and pH by electrode or m-cresol-purple spectrophotometry) with quality assurance against certified reference materials. Use it as the procedural backbone whenever a carbonate-chemistry indicator such as pH is being measured.</t>
         </is>
       </c>
+      <c r="AL55" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM55" s="18" t="inlineStr">
+        <is>
+          <t>dickson_2007</t>
+        </is>
+      </c>
+      <c r="AN55" s="19" t="n"/>
+      <c r="AO55" s="19" t="n"/>
+      <c r="AP55" s="19" t="n"/>
     </row>
     <row r="56" ht="240" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
@@ -10896,6 +11659,19 @@
           <t>To follow how the fouling community builds up on your cultivated kelp over the season (succession), sample seeded dropper lines repeatedly across the growing months. On each occasion collect several replicate droppers by diver using close-fitting mesh bags (to avoid losing loosely attached animals), then cut short standard sections (e.g. 10 cm) from each and, in the lab, work through a fixed amount of frond material (a size set from a species-accumulation curve), identifying all epifauna and epiphytes and keeping holdfast and blade/stipe material separate. Record species presence/absence and biomass per section, with sections nested within droppers within months. Compare richness and community turnover across months and years with nested ANOVA and multivariate ordination (MDS on a turnover-focused dissimilarity), and identify influential species with a SIMPER-style test. Running artificial kelp 'mimics' alongside the real plants lets you separate the effect of the living kelp from the structure itself.</t>
         </is>
       </c>
+      <c r="AL56" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM56" s="18" t="inlineStr">
+        <is>
+          <t>walls_2017</t>
+        </is>
+      </c>
+      <c r="AN56" s="19" t="n"/>
+      <c r="AO56" s="19" t="n"/>
+      <c r="AP56" s="19" t="n"/>
     </row>
     <row r="57" ht="240" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -11070,6 +11846,19 @@
           <t>To survey the biodiversity your farm structures support, pair environmental-DNA water sampling with direct visual surveys, comparing the farm against a nearby natural seafloor site. Collect replicate water samples near the culture gear with a Niskin sampler, filter each through a 0.45 um membrane, extract DNA, and amplify standard markers (a fish 12S marker and an invertebrate COI marker) for high-throughput (Illumina) sequencing, running field, filter and extraction blanks as controls. In parallel, have divers record the species seen on and around the structures. Cluster the sequences into OTUs and compare farm against reference for community composition and alpha/beta diversity, using indicator-species analysis to flag taxa associated with the farm.</t>
         </is>
       </c>
+      <c r="AL57" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM57" s="18" t="inlineStr">
+        <is>
+          <t>mercaldoallen_2021</t>
+        </is>
+      </c>
+      <c r="AN57" s="19" t="n"/>
+      <c r="AO57" s="19" t="n"/>
+      <c r="AP57" s="19" t="n"/>
     </row>
     <row r="58" ht="240" customHeight="1">
       <c r="A58" t="inlineStr">
@@ -11245,6 +12034,19 @@
           <t>This is a synthesis of methods for measuring shellfish-aquaculture effects on fish habitat rather than a single executable protocol: it reviews video, diver counts, traps, towed gear and acoustics, and argues for before/after control-impact (especially asymmetric-BACI) designs and for sampling directly beneath suspended lines. Use it to choose an appropriate survey design and to locate the primary references for each technique.</t>
         </is>
       </c>
+      <c r="AL58" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM58" s="18" t="inlineStr">
+        <is>
+          <t>mckindsey_2006</t>
+        </is>
+      </c>
+      <c r="AN58" s="19" t="n"/>
+      <c r="AO58" s="19" t="n"/>
+      <c r="AP58" s="19" t="n"/>
     </row>
     <row r="59" ht="240" customHeight="1">
       <c r="A59" t="inlineStr">
@@ -11421,6 +12223,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK59" s="16" t="inlineStr">
+        <is>
+          <t>To measure the habitat value of on-bottom oyster cages against natural comparators, sample the farm gear alongside a seagrass bed and a bare soft-bottom site across all four seasons with replication. For mobile fauna, have a diver place a fine-mesh (2 mm) lift-net under a cage a couple of weeks ahead (so animals disturbed by the deployment return), then enclose the cage on recovery and collect all free-swimming epifauna over about 5 mm; sample the vegetated and bare sites the same way with a drop-net and a suction dredge. For attached (sessile) growth, estimate percent cover in small quadrats (roughly 0.02 m2) on the cage, the bags and a subsample of oysters, and scale to total gear surface area referenced back to seabed area. Record temperature, salinity and dissolved oxygen each season and characterise sediment with a corer and dry-sieve grain size; compare habitats with two-way ANOVA (habitat x season) and Tukey tests, and summarise community with species richness (Jackknife), Shannon diversity and evenness.</t>
+        </is>
+      </c>
+      <c r="AL59" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM59" s="18" t="inlineStr">
+        <is>
+          <t>dealteris_2004</t>
+        </is>
+      </c>
+      <c r="AN59" s="19" t="n"/>
+      <c r="AO59" s="19" t="n"/>
+      <c r="AP59" s="19" t="n"/>
     </row>
     <row r="60" ht="240" customHeight="1">
       <c r="A60" t="inlineStr">
@@ -11599,6 +12419,19 @@
           <t>To characterise how a farm alters local currents and waves (relevant to coastal-protection benefit and siting), deploy a moored acoustic Doppler current profiler (ADCP) inside the farm for several weeks to log the vertical current profile continuously, and run vessel-mounted ADCP transects across the farm over a tidal cycle. Analyse the moored record with tidal harmonic analysis, comparing tidal constituents and current speed upstream versus inside and downstream to quantify attenuation and any redistribution of flow above and below the culture ropes, and compute shear. This yields a physical picture of current and wave attenuation to inform farm design and siting, rather than a biological or chemical indicator.</t>
         </is>
       </c>
+      <c r="AL60" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM60" s="18" t="inlineStr">
+        <is>
+          <t>mascordacabre_2024</t>
+        </is>
+      </c>
+      <c r="AN60" s="19" t="n"/>
+      <c r="AO60" s="19" t="n"/>
+      <c r="AP60" s="19" t="n"/>
     </row>
     <row r="61" ht="240" customHeight="1">
       <c r="A61" t="inlineStr">
@@ -11777,6 +12610,19 @@
           <t>To judge whether farm organic loading is degrading the seabed, sample sediment at the farm and at reference stations, sieve and identify the infauna, and compute benthic biotic indices - AMBI and the Infaunal Trophic Index (ITI) alongside abundance, biomass and diversity. Support the biology with sediment measurements (redox potential, silt fraction, total organic matter) and current speed from an ADCP. Relate the indices to the enrichment gradient and, with multi-site data, partition how much variation is explained by hydrography, sediment and the cages using variance partitioning (partial redundancy analysis); AMBI and ITI tend to respond most consistently to aquaculture enrichment.</t>
         </is>
       </c>
+      <c r="AL61" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM61" s="18" t="inlineStr">
+        <is>
+          <t>borja_2009</t>
+        </is>
+      </c>
+      <c r="AN61" s="19" t="n"/>
+      <c r="AO61" s="19" t="n"/>
+      <c r="AP61" s="19" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -11955,6 +12801,31 @@
           <t>To monitor water quality continuously at your farm with minimal effort, moor a low-power sensor string on a buoy and let it log automatically. Fit sensors for the parameters of interest — here temperature at several depths, conductivity/salinity, dissolved oxygen and pressure (depth) — set them to log on a fixed short interval (e.g. every 10 minutes), and calibrate the DO sensor before deployment. Leave the string in place for months, visiting periodically (e.g. monthly) to lift the lightweight instrument chain with a boat hook or the winch you use for mussel lines, download the data to a handheld shuttle, and scrub off biofouling. Then clean the data with simple quality-control rules: drop readings outside sensible ranges, discard the first couple of hours after each deployment or cleaning, remove sudden single-point spikes, and cut the gradual drift that builds before each cleaning (biofouling); convert conductivity to salinity in software. The pressure sensor also flags when the string has floated to the surface, so those readings can be excluded.</t>
         </is>
       </c>
+      <c r="AL62" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM62" s="18" t="inlineStr">
+        <is>
+          <t>schmidt_2018</t>
+        </is>
+      </c>
+      <c r="AN62" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/templates/schmidt_2018.pdf</t>
+        </is>
+      </c>
+      <c r="AO62" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/datasheets/schmidt_2018.pdf</t>
+        </is>
+      </c>
+      <c r="AP62" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/workbooks/schmidt_2018.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12133,6 +13004,19 @@
           <t>To detect a large (multi-kilometre) farm's effect on chlorophyll-a from satellite, assemble a long run of single-pass ocean-colour images (for example MODIS-Aqua) over the farm and several control areas. For each image, interpolate the chlorophyll field with kriging (fitting linear or exponential semivariogram models) and test whether values over the farm differ significantly from the kriged background and from the control areas. Aggregating many passes over years lets you resolve small effects (here a chlorophyll reduction of order one percent extending over about 1.5x the farm area) - a useful reminder to set realistic detectability expectations at farm scale.</t>
         </is>
       </c>
+      <c r="AL63" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM63" s="18" t="inlineStr">
+        <is>
+          <t>pinkerton_2018</t>
+        </is>
+      </c>
+      <c r="AN63" s="19" t="n"/>
+      <c r="AO63" s="19" t="n"/>
+      <c r="AP63" s="19" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -12311,6 +13195,19 @@
           <t>To account for the nitrogen a mussel farm removes and recycles at bay scale, build a whole-bay nitrogen budget: measure the nitrogen harvested in the crop (tissue %N x biomass x cultivated area), the nitrogen excreted and biodeposited by the stock, and the water-column and sediment nitrogen fluxes, then compare these against external inputs such as agricultural runoff. A dynamic box (lower-trophic-level) ecosystem model can be run alongside the budget to simulate scenarios, and the two approaches should converge. The harvested-nitrogen term is the bioextraction measure - it needs tissue elemental analysis on representative harvested biomass scaled to farm area.</t>
         </is>
       </c>
+      <c r="AL64" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM64" s="18" t="inlineStr">
+        <is>
+          <t>cranford_2007</t>
+        </is>
+      </c>
+      <c r="AN64" s="19" t="n"/>
+      <c r="AO64" s="19" t="n"/>
+      <c r="AP64" s="19" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -12489,6 +13386,19 @@
           <t>To quantify nitrogen removal at a mussel farm, pair the farm with a reference site and sample across several seasons. Take sediment cores to measure sediment nitrogen pools, nitrification and denitrification rates and benthic chlorophyll/phaeophytin, measure ammonium excretion directly on mussels, and sieve sediment for infauna. Combine harvest removal (tissue nitrogen x biomass) with denitrification losses to estimate total nitrogen loss from the system; note that the detrital community living on the ropes themselves can denitrify several times faster than the underlying sediment, so incubating rope material separately is worthwhile.</t>
         </is>
       </c>
+      <c r="AL65" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM65" s="18" t="inlineStr">
+        <is>
+          <t>kaspar_1985</t>
+        </is>
+      </c>
+      <c r="AN65" s="19" t="n"/>
+      <c r="AO65" s="19" t="n"/>
+      <c r="AP65" s="19" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12667,6 +13577,19 @@
           <t>To close a nitrogen and phosphorus budget for benthic clam culture, incubate intact sediment cores (roughly 20 cm diameter) from farmed plots at contrasting stocking densities and from a control, using paired light and dark flux chambers across the growing season. Measure solute fluxes across the sediment-water interface and analyse mollusc tissue for N and P; the harvested-nutrient term is tissue content x biomass x area. Compare fluxes and budgets across density treatments with ANOVA; expect only a small fraction of biodeposited nutrients (here roughly 6% of N and 3% of P) to actually leave the system via harvest, the rest being recycled or buried.</t>
         </is>
       </c>
+      <c r="AL66" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM66" s="18" t="inlineStr">
+        <is>
+          <t>nizzoli_2006</t>
+        </is>
+      </c>
+      <c r="AN66" s="19" t="n"/>
+      <c r="AO66" s="19" t="n"/>
+      <c r="AP66" s="19" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -12845,6 +13768,19 @@
           <t>To measure a suspended mussel farm's true effect on oxygen and nutrient cycling, run in-situ benthic flux chambers on the sediment and, separately, incubate a length of mussel rope so the rope community's fluxes are quantified apart from the sediment. Measure oxygen demand and dissolved N and P regeneration in each, then scale to whole-farm area. The key methodological lesson: the rope community can account for the large majority (here 70-90%) of total farm oxygen demand and nutrient regeneration, so a sediment-only survey grossly underestimates farm impact.</t>
         </is>
       </c>
+      <c r="AL67" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM67" s="18" t="inlineStr">
+        <is>
+          <t>nizzoli_2005</t>
+        </is>
+      </c>
+      <c r="AN67" s="19" t="n"/>
+      <c r="AO67" s="19" t="n"/>
+      <c r="AP67" s="19" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13015,6 +13951,19 @@
           <t>To compare culture modes at one site, measure benthic fluxes for infaunal clam plots and for suspended mussel ropes side by side across all seasons, again incubating rope communities separately from the sediment. Quantify dissolved-oxygen demand and inorganic N and P regeneration and integrate to farm scale, comparing seasons and culture types with ANOVA. The important interpretive finding: filter feeders are not an automatic eutrophication buffer - in summer, nutrient regeneration can overwhelm removal, so timing of measurement matters.</t>
         </is>
       </c>
+      <c r="AL68" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM68" s="18" t="inlineStr">
+        <is>
+          <t>nizzoli_2011</t>
+        </is>
+      </c>
+      <c r="AN68" s="19" t="n"/>
+      <c r="AO68" s="19" t="n"/>
+      <c r="AP68" s="19" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13180,6 +14129,14 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AM69" s="18" t="inlineStr">
+        <is>
+          <t>mizuta_2012</t>
+        </is>
+      </c>
+      <c r="AN69" s="19" t="n"/>
+      <c r="AO69" s="19" t="n"/>
+      <c r="AP69" s="19" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13356,6 +14313,14 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AM70" s="18" t="inlineStr">
+        <is>
+          <t>morozova_2005</t>
+        </is>
+      </c>
+      <c r="AN70" s="19" t="n"/>
+      <c r="AO70" s="19" t="n"/>
+      <c r="AP70" s="19" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13526,6 +14491,19 @@
           <t>This doctoral thesis bundles several transferable lagoon-monitoring methods for mollusc culture: seasonal benthic respiration and N and P flux measurement from intact sediment cores and in-situ chambers; 15N tracer experiments (in microcosms) to trace nitrogen pathways through oysters and sediment; and a remote-sensing time series (Sentinel/Landsat) for chlorophyll-a, suspended solids and Secchi depth, combined into an anoxia-risk assessment. Treat it as a menu of methods - the anoxia-risk framework for lagoon siting is its most distinctive contribution; pull individual chapter methods when a specific indicator is needed.</t>
         </is>
       </c>
+      <c r="AL71" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM71" s="18" t="inlineStr">
+        <is>
+          <t>pagani_2025</t>
+        </is>
+      </c>
+      <c r="AN71" s="19" t="n"/>
+      <c r="AO71" s="19" t="n"/>
+      <c r="AP71" s="19" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13704,6 +14682,36 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK72" s="16" t="inlineStr">
+        <is>
+          <t>To find which substrate best recruits wild oyster spat for a community-scale collection or reef effort, build simple multi-compartment bamboo mattresses and fill the compartments with candidate substrates (for example windowpane shell, live oyster shell, dead oyster shell, and stone/rubble), deploying them side by side in the intertidal over a settlement season. Every two weeks photograph each compartment against a fixed quadrat reference (about 38 x 38 cm) and count settled spat from the images to track density over time, alongside basic water-quality readings. Compare substrate performance with a substrate-by-time analysis (for example PCA plus standard significance tests). The low-cost, locally-built design suits community-led implementation and doubles as an ecosystem-engineering, coastal-defence structure.</t>
+        </is>
+      </c>
+      <c r="AL72" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM72" s="18" t="inlineStr">
+        <is>
+          <t>hossain_2013</t>
+        </is>
+      </c>
+      <c r="AN72" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/templates/hossain_2013.pdf</t>
+        </is>
+      </c>
+      <c r="AO72" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/datasheets/hossain_2013.pdf</t>
+        </is>
+      </c>
+      <c r="AP72" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/workbooks/hossain_2013.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13879,6 +14887,19 @@
           <t>This is a broad review of marine-biodiversity sampling methods (nets, traps, grabs, visual and video, scuba, acoustics, eDNA, artificial substrata) and of global monitoring programmes, and it introduces the Essential Biodiversity/Ocean Variables framework that parallels the MEL indicator structure. Use it as a method-landscape reference when designing a biodiversity-monitoring component; it points to primary protocols rather than prescribing one.</t>
         </is>
       </c>
+      <c r="AL73" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM73" s="18" t="inlineStr">
+        <is>
+          <t>costello_2016</t>
+        </is>
+      </c>
+      <c r="AN73" s="19" t="n"/>
+      <c r="AO73" s="19" t="n"/>
+      <c r="AP73" s="19" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -13941,7 +14962,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not time-specific — not site-specific</t>
+          <t>Not site-specific</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -14049,6 +15070,19 @@
           <t>This is an empirical account of how fish and invertebrates use the habitat on a working oyster farm and how gear-handling and harvest activity affect that use. The abstract does not specify the survey methods, so treat it as directional evidence on farm habitat value and confirm the sampling approach (visual, trap or video) from the full text before replicating.</t>
         </is>
       </c>
+      <c r="AL74" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM74" s="18" t="inlineStr">
+        <is>
+          <t>ambrose_2025</t>
+        </is>
+      </c>
+      <c r="AN74" s="19" t="n"/>
+      <c r="AO74" s="19" t="n"/>
+      <c r="AP74" s="19" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -14224,6 +15258,19 @@
           <t>This is a framework-level synthesis of indicators and thresholds for assessing shellfish-aquaculture impacts on coastal habitat, and the companion to the McKindsey methods review. It operationalises which indicators to track across water quality and habitat rather than giving a measurement procedure; use it to select indicators and threshold benchmarks, then draw the methods from the primary literature it cites.</t>
         </is>
       </c>
+      <c r="AL75" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM75" s="18" t="inlineStr">
+        <is>
+          <t>cranford_2006</t>
+        </is>
+      </c>
+      <c r="AN75" s="19" t="n"/>
+      <c r="AO75" s="19" t="n"/>
+      <c r="AP75" s="19" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -14402,6 +15449,19 @@
           <t>Although developed at finfish farms, this broad-scale benthic method transfers to mollusc-farm monitoring. Sample sediment at farms and matched reference sites with grabs, identify the infaunal community, and measure sediment chemistry (total organic carbon, sulphides, redox). Compare farm against reference with multivariate community analysis and ANOVA across a range of farms to characterise the typical footprint and its extent.</t>
         </is>
       </c>
+      <c r="AL76" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM76" s="18" t="inlineStr">
+        <is>
+          <t>edgar_2005</t>
+        </is>
+      </c>
+      <c r="AN76" s="19" t="n"/>
+      <c r="AO76" s="19" t="n"/>
+      <c r="AP76" s="19" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -14477,7 +15537,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short campaign (days to 2 weeks) — one-time / discrete campaign</t>
+          <t>One-time / discrete campaign</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
@@ -14585,6 +15645,19 @@
           <t>This observational study documents how mollusc shell debris accumulates on the seabed beneath coastal cages, altering benthic substrate composition. It is descriptive rather than a hypothesis-testing protocol, but the approach - sediment grabs/cores and visual survey along a distance gradient to map shell-debris distribution - transfers by analogy to monitoring benthic-substrate change around bivalve farms.</t>
         </is>
       </c>
+      <c r="AL77" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM77" s="18" t="inlineStr">
+        <is>
+          <t>sanchezjerez_2019</t>
+        </is>
+      </c>
+      <c r="AN77" s="19" t="n"/>
+      <c r="AO77" s="19" t="n"/>
+      <c r="AP77" s="19" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -14660,7 +15733,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t xml:space="preserve">One-time (no sampling — desk-based) — model runs</t>
+          <t>One-time / model runs</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -14768,6 +15841,19 @@
           <t>This is a modelling contribution rather than a field method: it couples a shellfish-production model (likely of the ShellSIM/FARM family) with a benthic-impact framework to explore trade-offs between production and benthic-biodiversity outcomes under different scenarios. To use it, parameterise the production model for your site and run scenarios, then validate the outputs against field data; it supports siting and stocking decisions but does not itself measure an indicator.</t>
         </is>
       </c>
+      <c r="AL78" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM78" s="18" t="inlineStr">
+        <is>
+          <t>sequeira_2008</t>
+        </is>
+      </c>
+      <c r="AN78" s="19" t="n"/>
+      <c r="AO78" s="19" t="n"/>
+      <c r="AP78" s="19" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -14951,6 +16037,19 @@
           <t>This paper compares the biodiversity of mussel assemblages under two cultivation methods, focusing on epibiont and associated infaunal communities via diver/video sampling, sorting and taxonomy with standard diversity indices. Use it as a template and comparator for culture-method contrasts; confirm the exact structures compared from the full text.</t>
         </is>
       </c>
+      <c r="AL79" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM79" s="18" t="inlineStr">
+        <is>
+          <t>murray_2007</t>
+        </is>
+      </c>
+      <c r="AN79" s="19" t="n"/>
+      <c r="AO79" s="19" t="n"/>
+      <c r="AP79" s="19" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -15134,6 +16233,19 @@
           <t>To compare the seabed impact of bottom versus suspended (longline) mussel culture, sample sediment along distance transects at both culture types and at reference sites, identifying infauna and measuring sediment chemistry. Compare across culture method and distance with ANOVA and multivariate community analysis to see which mode leaves the larger benthic footprint and how far it extends.</t>
         </is>
       </c>
+      <c r="AL80" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM80" s="18" t="inlineStr">
+        <is>
+          <t>ysebaert_2009</t>
+        </is>
+      </c>
+      <c r="AN80" s="19" t="n"/>
+      <c r="AO80" s="19" t="n"/>
+      <c r="AP80" s="19" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -15312,6 +16424,19 @@
           <t>To test whether farm gear and biodeposition enhance mobile epibenthic fauna (an artificial-reef effect), sample the farm and reference sites with replicated diver/video counts, benthic sampling and traps for mobile invertebrates. Compare abundance and community composition farm against reference with ANOVA to see whether the structure locally boosts epibenthic fauna.</t>
         </is>
       </c>
+      <c r="AL81" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM81" s="18" t="inlineStr">
+        <is>
+          <t>damours_2008</t>
+        </is>
+      </c>
+      <c r="AN81" s="19" t="n"/>
+      <c r="AO81" s="19" t="n"/>
+      <c r="AP81" s="19" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -15495,6 +16620,19 @@
           <t>To assess a shellfish farm's benthic footprint, sample sediment at the farm and matched reference sites with grabs, identify infauna and measure sediment chemistry, comparing with ANOVA and multivariate community analysis. A standard replicated paired-site benthic-impact design suitable for oyster or mussel farms.</t>
         </is>
       </c>
+      <c r="AL82" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM82" s="18" t="inlineStr">
+        <is>
+          <t>crawford_2003</t>
+        </is>
+      </c>
+      <c r="AN82" s="19" t="n"/>
+      <c r="AO82" s="19" t="n"/>
+      <c r="AP82" s="19" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -15668,6 +16806,19 @@
           <t>This study documents how mussel reefs host a distinct, more diverse mobile-fauna assemblage than non-reef habitat, using paired reef-versus-non-reef sampling (diver/video and traps) with diversity indices and community ordination. Use it as evidence and a design template for reef biodiversity comparisons; confirm from the full text whether the reefs are cultivated, restored or natural, as that affects tagging.</t>
         </is>
       </c>
+      <c r="AL83" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM83" s="18" t="inlineStr">
+        <is>
+          <t>yoo_2024</t>
+        </is>
+      </c>
+      <c r="AN83" s="19" t="n"/>
+      <c r="AO83" s="19" t="n"/>
+      <c r="AP83" s="19" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -15848,6 +16999,19 @@
           <t>This paper reports routine seasonal physical-chemical seawater parameters (temperature, salinity, dissolved oxygen, nutrients, chlorophyll-a) at mollusc culture sites, using standard multiprobe/CTD and Niskin sampling with laboratory nutrient analysis. It is descriptive baseline monitoring rather than an impact test; use it as a reference for expected parameter ranges in a subtropical culture setting.</t>
         </is>
       </c>
+      <c r="AL84" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM84" s="18" t="inlineStr">
+        <is>
+          <t>ferreira_2006</t>
+        </is>
+      </c>
+      <c r="AN84" s="19" t="n"/>
+      <c r="AO84" s="19" t="n"/>
+      <c r="AP84" s="19" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -16031,6 +17195,19 @@
           <t>To detect whether oyster culture changes local water quality, run repeated moving-vessel transects through the farm footprint and in the water just outside it, with about half of each transect passing through the cages and half outside, and the number of transects scaled to farm size. Sample during the two-to-four-hour window bracketing peak tidal current, towing a water-quality sonde that logs temperature, salinity, chlorophyll-a fluorescence, turbidity and dissolved oxygen continuously, alongside an acoustic Doppler profiler for current speed. Because these variables drift with time of day and salinity, detrend the underway data against time and salinity using the outside-farm points, then subsample each variable at the spatial interval beyond which it is no longer autocorrelated. Compare inside versus outside (crossed with site and season) using two- and three-way ANOVA with post-hoc testing; optionally add a simple filtration calculation (water contact time x oyster number x per-oyster filtration rate divided by farm water volume) to gauge the fraction of passing water the stock could filter.</t>
         </is>
       </c>
+      <c r="AL85" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM85" s="18" t="inlineStr">
+        <is>
+          <t>turner_2019</t>
+        </is>
+      </c>
+      <c r="AN85" s="19" t="n"/>
+      <c r="AO85" s="19" t="n"/>
+      <c r="AP85" s="19" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -16214,6 +17391,19 @@
           <t>To quantify a longline mussel farm's effect on sediment oxygen and nitrogen cycling, collect intact sediment cores at the farm and a reference site across seasons and incubate them (with oxygen microelectrodes where possible) to measure oxygen uptake and nitrogen fluxes, alongside infaunal sampling. Compare farm against reference with mass-balance and ANOVA; close in method to the other intact-core mussel-farm nitrogen-cycle studies.</t>
         </is>
       </c>
+      <c r="AL86" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM86" s="18" t="inlineStr">
+        <is>
+          <t>christensen_2003</t>
+        </is>
+      </c>
+      <c r="AN86" s="19" t="n"/>
+      <c r="AO86" s="19" t="n"/>
+      <c r="AP86" s="19" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -16397,6 +17587,19 @@
           <t>This foundational multidisciplinary design combines several benthic measurements at a mussel farm and reference: sediment chemistry, infaunal identification, biodeposition traps, and foraminiferal analysis as a sensitive enrichment indicator. Deploy traps to quantify biodeposition, grab sediment for infauna and chemistry, and compare farm against reference with ANOVA and community analysis - the multi-method approach is its enduring value.</t>
         </is>
       </c>
+      <c r="AL87" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM87" s="18" t="inlineStr">
+        <is>
+          <t>grant_1995</t>
+        </is>
+      </c>
+      <c r="AN87" s="19" t="n"/>
+      <c r="AO87" s="19" t="n"/>
+      <c r="AP87" s="19" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -16575,6 +17778,19 @@
           <t>To document a farm's influence on water-column chemistry, sample farm-zone and non-farm-zone stations across seasons with Niskin bottles, analysing nitrogen, phosphorus and silicon nutrients and chlorophyll-a (fluorometer) and identifying phytoplankton by microscopy. Compare zones along a spatial gradient to reveal how dense oyster culture reshapes nutrient stoichiometry and phytoplankton structure.</t>
         </is>
       </c>
+      <c r="AL88" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM88" s="18" t="inlineStr">
+        <is>
+          <t>souchu_2001</t>
+        </is>
+      </c>
+      <c r="AN88" s="19" t="n"/>
+      <c r="AO88" s="19" t="n"/>
+      <c r="AP88" s="19" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -16650,7 +17866,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year)</t>
+          <t>Multi-year monitoring (&gt;1 year)</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
@@ -16758,6 +17974,19 @@
           <t>To monitor chlorophyll-a across a shellfish-farming bay from satellite, pair in-situ sampling with Sentinel-2 imagery. On cloud-free dates that coincide with a satellite overpass, visit fixed stations inside and outside the bay, measure Secchi depth and temperature/salinity profiles with a CTD, and collect water for chlorophyll-a (filter onto GF/F, extract in 90% acetone, read absorbance on a spectrophotometer). Atmospherically correct the Level-1 imagery with a coastal neural-net processor (such as C2RCC), compute a set of blue, red and red-edge spectral-band indices, and calibrate then validate the chlorophyll-a retrieval models against the in-situ match-ups (split the data, for example 70% calibration and 30% validation, judging fit by mean absolute error, RMSE and bias). Apply the best model to all clear images to produce chlorophyll-a maps - masking farm structures and implausibly high pixels - which then feed food-availability and carrying-capacity estimates for the bay.</t>
         </is>
       </c>
+      <c r="AL89" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM89" s="18" t="inlineStr">
+        <is>
+          <t>fernandeztejedor_2022</t>
+        </is>
+      </c>
+      <c r="AN89" s="19" t="n"/>
+      <c r="AO89" s="19" t="n"/>
+      <c r="AP89" s="19" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -16833,7 +18062,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year)</t>
+          <t>Multi-year monitoring (&gt;1 year)</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -16941,6 +18170,19 @@
           <t>This two-year descriptive study tracks seasonal phytoplankton community, seston and environmental variables at oyster culture sites alongside oyster growth, using Niskin sampling, phytoplankton microscopy and seston dry-weight filtration. It is monitoring rather than hypothesis-testing; use it to understand seasonal food-supply variation and its link to shellfish performance.</t>
         </is>
       </c>
+      <c r="AL90" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM90" s="18" t="inlineStr">
+        <is>
+          <t>toro_1999</t>
+        </is>
+      </c>
+      <c r="AN90" s="19" t="n"/>
+      <c r="AO90" s="19" t="n"/>
+      <c r="AP90" s="19" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -17119,6 +18361,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK91" s="16" t="inlineStr">
+        <is>
+          <t>To use phytoplankton as a bioindicator of aquaculture-effluent impact, compare an effluent-influenced area against a distant non-impacted reference area, sampling several times across the year to capture the farm's operating and non-operating phases. Lay transects perpendicular to the shore with sampling points at set distances from the coast (here roughly 50, 150 and 300 m) and spaced from each other. For community composition, take a horizontal surface tow with a fine (~30 um) plankton net, preserve in 4% formalin and identify under a compound microscope; for abundance, collect a fixed water volume (for example 500 mL) at depth with a Van Dorn bottle, preserve in Lugol's-acetate, settle by the Utermohl method in sedimentation chambers and count under an inverted microscope, converting to cells per litre. Summarise each area and season with Shannon and Margalef diversity indices and compare impacted against reference to detect an effluent signal in community structure and abundance.</t>
+        </is>
+      </c>
+      <c r="AL91" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM91" s="18" t="inlineStr">
+        <is>
+          <t>valenzuelasanchez_2021</t>
+        </is>
+      </c>
+      <c r="AN91" s="19" t="n"/>
+      <c r="AO91" s="19" t="n"/>
+      <c r="AP91" s="19" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -17302,6 +18562,19 @@
           <t>To measure sediment stability and resuspension under mussel gear, use an erosion device (for example a Gust microcosm erosion chamber) to determine the critical shear stress and erosion rate of the bed, deploy sediment traps to capture resuspended and deposited material, and analyse grain size. Compare farm against reference to see whether biodeposition and gear alter bed erodibility.</t>
         </is>
       </c>
+      <c r="AL92" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM92" s="18" t="inlineStr">
+        <is>
+          <t>walker_2009</t>
+        </is>
+      </c>
+      <c r="AN92" s="19" t="n"/>
+      <c r="AO92" s="19" t="n"/>
+      <c r="AP92" s="19" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -17372,7 +18645,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t xml:space="preserve">One-time (no sampling — desk-based) — model runs</t>
+          <t>One-time / model runs</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -17480,6 +18753,19 @@
           <t>This is a modelling method for predicting where bivalve biodeposits (faeces and pseudofaeces) settle: couple a hydrodynamic model with Lagrangian particle-tracking of settling particles to map the deposition footprint, ideally validating against sediment-trap field data. Use it to anticipate the spatial extent of benthic loading for siting and monitoring design rather than as a direct measurement.</t>
         </is>
       </c>
+      <c r="AL93" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM93" s="18" t="inlineStr">
+        <is>
+          <t>silva_2019</t>
+        </is>
+      </c>
+      <c r="AN93" s="19" t="n"/>
+      <c r="AO93" s="19" t="n"/>
+      <c r="AP93" s="19" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -17663,6 +18949,19 @@
           <t>This proof-of-concept study asks whether co-cultivated macroalgae can locally buffer acidification for shell-forming bivalves in an IMTA layout, monitoring dissolved oxygen alongside carbonate chemistry (pH, DIC) and bivalve growth in paired treatments. Within the MEL scope its transferable element is the dissolved-oxygen and co-culture design (carbonate chemistry sits outside the MEL indicator set); treat it as evidence for IMTA co-benefits rather than a standalone indicator protocol.</t>
         </is>
       </c>
+      <c r="AL94" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM94" s="18" t="inlineStr">
+        <is>
+          <t>fernandez_2019</t>
+        </is>
+      </c>
+      <c r="AN94" s="19" t="n"/>
+      <c r="AO94" s="19" t="n"/>
+      <c r="AP94" s="19" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -17836,6 +19135,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK95" s="16" t="inlineStr">
+        <is>
+          <t>To compare the fish and crab community your gear supports against natural habitats, run paired underwater-video surveys at the farm's gear types (for example oyster flipbags, on-bottom oysters, clam nets) and at nearby reference habitats (eelgrass, bare sediment) 30-60 m away at similar depth. Mount cameras in pairs about 30 cm above the bed angled down ~20 degrees, with two poles marking a 1 m2 field of view, and record short clips (for example 2 min every 10 min) over the few hours around high tide when visibility is best, keeping the clearest camera and day. Count and identify all fish and crabs in the 1 m2 view, sum across clips per site, and group by vertical niche (pelagic, demersal, benthic). Compare communities with NMDS/PERMANOVA and SIMPER, and model richness, diversity and key species' abundance with generalised linear mixed models (site and year as random effects, AICc for selection).</t>
+        </is>
+      </c>
+      <c r="AL95" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM95" s="18" t="inlineStr">
+        <is>
+          <t>ferriss_2021</t>
+        </is>
+      </c>
+      <c r="AN95" s="19" t="n"/>
+      <c r="AO95" s="19" t="n"/>
+      <c r="AP95" s="19" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18009,6 +19326,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK96" s="16" t="inlineStr">
+        <is>
+          <t>To grade benthic condition and trace the food supporting an intertidal clam farm, combine a MOM-B sediment survey with stable-isotope food-source analysis across stations spanning the tidal gradient. For MOM-B, take replicate grabs/cores per station and score three groups - macrofauna presence/absence, chemistry (pH and redox potential by microelectrode), and sensory state (colour, odour, consistency, gas, sludge) - combining them into condition classes 1 (best) to 4 (unacceptable), with chemistry taking precedence. For food sources, size-fractionate water (20, 2, 0.45 um) for chlorophyll-a, collect particulate organic matter on pre-combusted GF/F and sediment organic matter, and analyse clam adductor muscle plus these sources for delta-13-C and delta-15-N on an elemental-analyser IRMS, then partition the contribution of sediment versus suspended organic carbon with a mixing model. Continuous bottom-water temperature loggers and plankton-net larval sampling round out the assessment.</t>
+        </is>
+      </c>
+      <c r="AL96" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM96" s="18" t="inlineStr">
+        <is>
+          <t>liu_2024</t>
+        </is>
+      </c>
+      <c r="AN96" s="19" t="n"/>
+      <c r="AO96" s="19" t="n"/>
+      <c r="AP96" s="19" t="n"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -18190,6 +19525,19 @@
           <t>To assess whether intertidal clam farming with predator-exclusion netting changes the infaunal community, sample seeded and netted clam beds and reference flats with sediment cores across seasons and, ideally, across several regions, identifying and weighing the infauna. Compare farm against reference with ANOVA and community analysis; site-scale effects may be limited even where regional-scale cumulative effects warrant a broader baseline.</t>
         </is>
       </c>
+      <c r="AL97" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM97" s="18" t="inlineStr">
+        <is>
+          <t>whiteley_2007</t>
+        </is>
+      </c>
+      <c r="AN97" s="19" t="n"/>
+      <c r="AO97" s="19" t="n"/>
+      <c r="AP97" s="19" t="n"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -18366,6 +19714,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK98" s="16" t="inlineStr">
+        <is>
+          <t>To measure whether your farm habitat supports foraging (not just presence), score feeding behaviour from underwater video at the gear types and at eelgrass and mudflat reference sites. Deploy paired downward-angled cameras ~30 cm above the bed marking a 1 m2 view, recording around high tide, and analyse a fixed set of clips per habitat (for example ten 2-min segments spanning the hour before and after high tide) in behavioural-scoring software. For each fish or crab in view record a feeding versus not-feeding classification and its functional group (pelagic, demersal, benthic), noting cover type (bare, algae, eelgrass) and a visibility rating to correct for observation bias. Model the probability of foraging by habitat type with generalised linear mixed models (site as a random effect, AICc selection), analysing each functional group separately.</t>
+        </is>
+      </c>
+      <c r="AL98" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM98" s="18" t="inlineStr">
+        <is>
+          <t>veggerby_2024</t>
+        </is>
+      </c>
+      <c r="AN98" s="19" t="n"/>
+      <c r="AO98" s="19" t="n"/>
+      <c r="AP98" s="19" t="n"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -18542,6 +19908,14 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AM99" s="18" t="inlineStr">
+        <is>
+          <t>zydelis_2009</t>
+        </is>
+      </c>
+      <c r="AN99" s="19" t="n"/>
+      <c r="AO99" s="19" t="n"/>
+      <c r="AP99" s="19" t="n"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -18720,6 +20094,19 @@
           <t>To link biodiversity to trophic function at a raft mussel farm, compare the farm against a structurally similar non-mussel floating structure (for example a dock) as a control for substrate alone. Sample fouling macrofauna and macroalgae biomass and take sediment cores, then run stable-isotope analysis (delta-13-C and delta-15-N) on the community and summarise food-web structure with Layman metrics. Compare diversity (Shannon) and trophic metrics between farm and structural control to separate the mussels' effect from that of hard substrate.</t>
         </is>
       </c>
+      <c r="AL100" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM100" s="18" t="inlineStr">
+        <is>
+          <t>maurin_2019</t>
+        </is>
+      </c>
+      <c r="AN100" s="19" t="n"/>
+      <c r="AO100" s="19" t="n"/>
+      <c r="AP100" s="19" t="n"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -18903,6 +20290,19 @@
           <t>To evaluate which benthic indicators best capture mussel-farm impact, sample along within-line and between-line transects with a van Veen grab and add sediment-profile imaging (SPI) for a visual cross-section of the sediment. Measure particle size, organic matter and the infaunal community, and compute a suite of indices (abundance, biomass, Margalef richness, Shannon diversity, Pielou evenness, AMBI). Compare across the transect gradient with ANOVA and multivariate analysis; farms differ in whether they show a clear enrichment gradient, so multi-indicator, multi-site sampling is advisable.</t>
         </is>
       </c>
+      <c r="AL101" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM101" s="18" t="inlineStr">
+        <is>
+          <t>callier_2008</t>
+        </is>
+      </c>
+      <c r="AN101" s="19" t="n"/>
+      <c r="AO101" s="19" t="n"/>
+      <c r="AP101" s="19" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -18973,7 +20373,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — annual sampling July/August across 8+ years</t>
+          <t>Multi-year (annual sampling July/August across 8+ years)</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -19081,6 +20481,19 @@
           <t>To document a farm's biogenic-reef and biodiversity effects over the long term, run a before/after control-impact design (with a before-after-gradient element) using repeated annual camera surveys - towed video, ROV and baited remote underwater video (BRUV) - at the farm and control areas. Normalise counts to density per square metre and analyse community change with multivariate methods and BACI/BAG contrasts. A multi-year record is what makes reef formation and rising diversity detectable.</t>
         </is>
       </c>
+      <c r="AL102" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM102" s="18" t="inlineStr">
+        <is>
+          <t>mascordacabre_2024-b</t>
+        </is>
+      </c>
+      <c r="AN102" s="19" t="n"/>
+      <c r="AO102" s="19" t="n"/>
+      <c r="AP102" s="19" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19259,6 +20672,19 @@
           <t>To assess the habitat value of structured oyster culture, compare the farm (for example concrete posts with attached oysters) against adjacent unstructured mudflat, sampling resident macrobenthos with cores across seasons and quantifying density, biomass and diversity. Contrast structured against unstructured habitat to reveal the biodiversity uplift the oyster structure provides, and watch for invasive species when interpreting.</t>
         </is>
       </c>
+      <c r="AL103" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM103" s="18" t="inlineStr">
+        <is>
+          <t>chan_2022</t>
+        </is>
+      </c>
+      <c r="AN103" s="19" t="n"/>
+      <c r="AO103" s="19" t="n"/>
+      <c r="AP103" s="19" t="n"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19437,6 +20863,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK104" s="16" t="inlineStr">
+        <is>
+          <t>To assess the seabed under a bivalve-and-seaweed culture bay with the standard MOM-B protocol, sample sediment at stations spread across the culture zones (plus a no-culture reference) with a gravity corer or Van Veen grab, at least two grabs per station. On each, measure pH and redox potential (Eh) - ideally at 2 cm depth intervals down to about 8 cm - with calibrated probes, record the sensory state (colour, odour, consistency, gas ebullition, sludge thickness), then sieve through 1 mm mesh and note macrofauna presence/absence, preserving retained animals in ethanol for identification. Score the three parameter groups (fauna, chemistry, sensory) into MOM-B condition classes 1-4; an empty grab on repeated attempts indicates hard bottom with no organic accumulation.</t>
+        </is>
+      </c>
+      <c r="AL104" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM104" s="18" t="inlineStr">
+        <is>
+          <t>zhang_2009</t>
+        </is>
+      </c>
+      <c r="AN104" s="19" t="n"/>
+      <c r="AO104" s="19" t="n"/>
+      <c r="AP104" s="19" t="n"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19618,6 +21062,19 @@
           <t>To separate the benthic effects of bottom stock-enhancement from suspended culture, sample three treatments - a bottom stock-enhancement area, a suspended-raft oyster farm, and a control - for sediment properties (moisture, acid-volatile sulphide, total organic carbon, grain size, trace metals by ICP-MS) and benthic fauna. Compare with cluster analysis and ANOVA; suspended raft culture tends to elevate sediment sulphide and metals beneath the rafts, whereas infaunal bivalve enhancement leaves a lighter footprint.</t>
         </is>
       </c>
+      <c r="AL105" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM105" s="18" t="inlineStr">
+        <is>
+          <t>ping_2023</t>
+        </is>
+      </c>
+      <c r="AN105" s="19" t="n"/>
+      <c r="AO105" s="19" t="n"/>
+      <c r="AP105" s="19" t="n"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19791,6 +21248,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK106" s="16" t="inlineStr">
+        <is>
+          <t>To monitor non-indigenous and associated species around a farm, deploy a mix of baited traps (for example minnow and goby traps), habitat collectors (mesh baskets or boxes holding rocks or shells to create refuges) and PVC fouling plates across habitat types and depths (for example 1, 2 and 3 m), tied to buoys or structures. Retrieve, rinse and empty the traps and collectors every 2-4 weeks, returning them to the same spot so you can also gauge how catch changes with soak time; leave fouling plates about 50 days, then score organisms in randomly chosen grid squares on each face. Identify and count all organisms (to genus or species where feasible) and summarise richness, abundance and Shannon diversity. Use rarefaction curves (against soak time and number of gears) to check whether sampling effort was sufficient, and compare gear, habitat and depth with mixed-model ANOVA.</t>
+        </is>
+      </c>
+      <c r="AL106" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM106" s="18" t="inlineStr">
+        <is>
+          <t>outinen_2019</t>
+        </is>
+      </c>
+      <c r="AN106" s="19" t="n"/>
+      <c r="AO106" s="19" t="n"/>
+      <c r="AP106" s="19" t="n"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -19969,6 +21444,19 @@
           <t>To compare benthic impact across many farms and culture methods, sample sediment infauna at each farm, identify the community, and classify each taxon by biological traits, then analyse with linear mixed models plus trait-based methods (RLQ and fourth-corner analysis) alongside standard diversity indices (Margalef, Shannon, Pielou, AMBI). This trait approach shows that culture method (suspended cages, hanging ropes, bottom culture) drives community-trait composition more than the cultivated species, with bottom culture generally lightest.</t>
         </is>
       </c>
+      <c r="AL107" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM107" s="18" t="inlineStr">
+        <is>
+          <t>sun_2021</t>
+        </is>
+      </c>
+      <c r="AN107" s="19" t="n"/>
+      <c r="AO107" s="19" t="n"/>
+      <c r="AP107" s="19" t="n"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20039,7 +21527,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — 5-yr annual monitoring</t>
+          <t>Multi-year (5 yr annual monitoring)</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
@@ -20142,6 +21630,24 @@
           <t>Exposed</t>
         </is>
       </c>
+      <c r="AK108" s="16" t="inlineStr">
+        <is>
+          <t>To document how an offshore longline mussel farm reshapes the seabed community over time, monitor rope plots and unfished control plots annually, from before deployment through several years after. Use three video methods: a towed underwater video system running about 1 m off the ropes and a remotely operated vehicle directly beneath them for sessile and sedentary taxa and mussel-shell cover, and baited remote underwater video (about 30 min per drop) for mobile taxa. Calibrate the field of view with paired scaling lasers; quantify percent mussel cover from a grid overlay on subsampled frame grabs, count sessile taxa in a digital quadrat, and score mobile taxa as the maximum number on screen per minute (MaxN). Analyse abundance and richness with generalised linear mixed models (time-since-deployment x treatment, trial station as random) and assemblage change with PERMANOVA and SIMPER on square-root-transformed Bray-Curtis data.</t>
+        </is>
+      </c>
+      <c r="AL108" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM108" s="18" t="inlineStr">
+        <is>
+          <t>bridger_2022</t>
+        </is>
+      </c>
+      <c r="AN108" s="19" t="n"/>
+      <c r="AO108" s="19" t="n"/>
+      <c r="AP108" s="19" t="n"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20217,7 +21723,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — quarterly, 5-year programme</t>
+          <t>Quarterly (5-year programme)</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -20325,6 +21831,19 @@
           <t>To run a regulatory-style monitoring programme for shellfish-production waters, sample a network of fixed stations spanning your coastal, estuarine and lagoon water bodies on a quarterly cycle over several years. At each station collect surface water with a Niskin bottle or clean container and measure temperature and pH in situ (probes calibrated to standards), determine salinity with a salinometer, dissolved oxygen by the Winkler method in duplicate, and suspended particulate matter gravimetrically (filter a fixed volume through pre-weighed 0.45 um membranes, then dry and re-weigh). Collect live bivalves at each representative point and quantify faecal coliforms/E. coli by a multiple-tube fermentation method with chromogenic-agar confirmation, reporting most-probable-number per 100 g of flesh. Group stations by water-body type and use PCA plus non-parametric tests (Kruskal-Wallis, Mann-Whitney) to compare systems and identify the drivers - such as rainfall and freshwater discharge - behind the physico-chemical and microbial patterns.</t>
         </is>
       </c>
+      <c r="AL109" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM109" s="18" t="inlineStr">
+        <is>
+          <t>pedro_2026</t>
+        </is>
+      </c>
+      <c r="AN109" s="19" t="n"/>
+      <c r="AO109" s="19" t="n"/>
+      <c r="AP109" s="19" t="n"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -20400,7 +21919,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t xml:space="preserve">One-time (no sampling — desk-based) — multi-decade hindcast + projection (10-year reference + 2× 10-year future periods)</t>
+          <t>Multi-decade hindcast + projection (10-year reference + 2× 10-year future periods)</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -20508,6 +22027,19 @@
           <t>This is a coupled-model framework (3D hydrodynamics plus pelagic biogeochemistry, a sediment-benthos model and a dynamic-energy-budget mussel module) applied to project chlorophyll-a and dissolved oxygen for a shallow eutrophic estuary under climate scenarios. It provides validated, decision-relevant water-quality and carrying-capacity projections rather than a field procedure; use it to think about how indicator baselines might shift forward under climate change.</t>
         </is>
       </c>
+      <c r="AL110" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM110" s="18" t="inlineStr">
+        <is>
+          <t>maar_2024</t>
+        </is>
+      </c>
+      <c r="AN110" s="19" t="n"/>
+      <c r="AO110" s="19" t="n"/>
+      <c r="AP110" s="19" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20583,7 +22115,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuous (sensor / autonomous) — multi-year, 30-min intervals</t>
+          <t>Continuous (multi-year, 30-min intervals)</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
@@ -20686,6 +22218,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK111" s="16" t="inlineStr">
+        <is>
+          <t>To run continuous, decision-useful water-quality monitoring across a region of shellfish leases, deploy multi-parameter sondes at a network of lease sites logging temperature, salinity, dissolved oxygen, depth, turbidity and chlorophyll at a fixed short interval (for example every 30 minutes). Where possible, stream the data live over cellular telemetry to a shared dashboard so growers can see conditions in near-real time. Use the time series to flag events that matter to the crop - hypoxia or salinity excursions - and to compare conditions across sites, rather than relying on infrequent grab samples. Sustained low-oxygen or high-chlorophyll patterns then inform siting, stocking and harvest-timing decisions.</t>
+        </is>
+      </c>
+      <c r="AL111" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM111" s="18" t="inlineStr">
+        <is>
+          <t>bergquist_2009</t>
+        </is>
+      </c>
+      <c r="AN111" s="19" t="n"/>
+      <c r="AO111" s="19" t="n"/>
+      <c r="AP111" s="19" t="n"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -20756,7 +22306,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short campaign (days to 2 weeks) — multi-survey</t>
+          <t>Short campaign (multi-survey)</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
@@ -20859,6 +22409,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK112" s="16" t="inlineStr">
+        <is>
+          <t>To measure a floating/raft oyster farm's effect on water-column nitrogen, pair an ammonium (total ammonia nitrogen, TAN) excretion assay with an upstream/downstream field survey. For excretion, incubate a set number of market-size oysters in aerated site water and sample every 30 min over about 2 h, filtering (GF/F) and measuring TAN colorimetrically (salicylate method) to get a per-oyster excretion rate. In the field, determine flow direction (float-and-compass) and speed at the facility, then collect paired upstream (inflow) and downstream (outflow) water for DO, salinity and temperature (handheld meter) and filtered samples for TAN, nitrate, nitrite, reactive phosphorus and chlorophyll-a. Test up- versus downstream change with paired t-tests, regress the change against flow speed, and close the loop with a simple mass balance (excretion rate x oyster number relative to facility volume and flow) to check whether excretion explains the observed change; optionally scrape and dry sessile algae from floats to estimate competing nitrogen uptake.</t>
+        </is>
+      </c>
+      <c r="AL112" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM112" s="18" t="inlineStr">
+        <is>
+          <t>ray_2015</t>
+        </is>
+      </c>
+      <c r="AN112" s="19" t="n"/>
+      <c r="AO112" s="19" t="n"/>
+      <c r="AP112" s="19" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -20934,7 +22502,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — annual growth + tissue assay</t>
+          <t>Multi-season / annual (growth + tissue assay)</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -21037,6 +22605,14 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AM113" s="18" t="inlineStr">
+        <is>
+          <t>carmichael_2012</t>
+        </is>
+      </c>
+      <c r="AN113" s="19" t="n"/>
+      <c r="AO113" s="19" t="n"/>
+      <c r="AP113" s="19" t="n"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -21107,7 +22683,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — annual cycle, 12-month sampling</t>
+          <t>Annual cycle (12-month sampling)</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
@@ -21210,6 +22786,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK114" s="16" t="inlineStr">
+        <is>
+          <t>To trace what a bivalve farm's stock is actually eating (its trophic sources) over a full year, deploy known cohorts of oysters and mussels on ropes at set depths and sample seston plus candidate food sources (river inputs, a marine end-member, microphytobenthos, sediment, seagrass) alongside. On each date measure total and inorganic particulate matter (pre-combusted, pre-weighed GF/C filters, dried then ashed) and chlorophyll-a (GF/F, 90% acetone, spectrofluorometer), and freeze filters for carbon stable isotopes (delta-13-C) and fatty-acid biomarkers. Acidify samples to remove carbonates, then run tissue and particulate organic matter through an elemental-analyser IRMS for delta-13-C and a gas chromatograph for fatty-acid methyl esters (neutral lipids track diet). Compare inside versus outside the farming area and across dates with split-plot ANOVA, and cluster the fatty-acid time series to link the stock's diet to specific organic-matter sources.</t>
+        </is>
+      </c>
+      <c r="AL114" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM114" s="18" t="inlineStr">
+        <is>
+          <t>pernet_2012</t>
+        </is>
+      </c>
+      <c r="AN114" s="19" t="n"/>
+      <c r="AO114" s="19" t="n"/>
+      <c r="AP114" s="19" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -21280,7 +22874,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months) — two seasons (Feb + Jul 2002); short field campaigns with multi-day lab incubation</t>
+          <t>Two seasons (Feb + Jul 2002); short campaigns with multi-day lab incubation</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
@@ -21388,6 +22982,19 @@
           <t>To measure sediment nitrogen-cycling pathways under different culture types, incubate intact sediment cores (Plexiglas tubes with overlying water) from a mussel-trellis station, a bottom-clam station and a control in dark incubations for oxygen, carbon-dioxide and dissolved-nitrogen fluxes, and add a 15N-nitrate tracer to quantify denitrification and DNRA by isotope pairing (the gold-standard alternative to acetylene inhibition). Analyse the 15N in evolved gases by isotope-ratio mass spectrometry. Infaunal clam farming tends to stimulate coupled nitrification-denitrification (net nitrogen loss to the atmosphere), whereas suspended mussel culture shifts the balance differently.</t>
         </is>
       </c>
+      <c r="AL115" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM115" s="18" t="inlineStr">
+        <is>
+          <t>nizzoli_2006-b</t>
+        </is>
+      </c>
+      <c r="AN115" s="19" t="n"/>
+      <c r="AO115" s="19" t="n"/>
+      <c r="AP115" s="19" t="n"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -21458,7 +23065,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — annual (winter) sampling, 40-year time series</t>
+          <t>Annual (winter), 40-year time series</t>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
@@ -21566,6 +23173,19 @@
           <t>To run a bivalve-tissue bioindicator programme, sample pooled soft tissue of the target species at a network of coastal stations once a year at a fixed season (here late winter), freeze-dry and grind it, and analyse carbon and nitrogen content plus delta-13-C and delta-15-N on an elemental analyser coupled to an isotope-ratio mass spectrometer, calibrated against certified reference standards (for example IAEA and USGS materials). Sustained annually, this yields long time series that track nutrient and organic-matter conditions; compare across regions, species and years with non-parametric tests (Kruskal-Wallis with post-hoc) and trend analysis.</t>
         </is>
       </c>
+      <c r="AL116" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM116" s="18" t="inlineStr">
+        <is>
+          <t>lienart_2025</t>
+        </is>
+      </c>
+      <c r="AN116" s="19" t="n"/>
+      <c r="AO116" s="19" t="n"/>
+      <c r="AP116" s="19" t="n"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -21636,7 +23256,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months)</t>
+          <t>Multi-season</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
@@ -21739,6 +23359,24 @@
           <t>Mixed exposure</t>
         </is>
       </c>
+      <c r="AK117" s="16" t="inlineStr">
+        <is>
+          <t>To use mussel Condition Index (CI) as an integrative environmental bioindicator when choosing between farm sites, sample mussels and water monthly at candidate sites (for example one with strong riverine influence and one without) over a year. Measure the environment - temperature, salinity, DO and pH by multiprobe; chlorophyll-a by spectrophotometry after acetone extraction; and seston as suspended particulate matter and particulate organic and inorganic matter by gravimetry - deriving food quantity/quality ratios (chl-a/POM, POM/SPM). Compute CI for a fixed size class as dry soft-tissue weight divided by internal shell-cavity capacity, times 1000, and classify each month as high or low relative to the annual mean. Reduce the environmental variables with PCA and relate them to CI with stepwise multiple regression and discriminant analysis to identify which drivers - and therefore which site - best support mussel condition.</t>
+        </is>
+      </c>
+      <c r="AL117" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM117" s="18" t="inlineStr">
+        <is>
+          <t>sasikumar_2011</t>
+        </is>
+      </c>
+      <c r="AN117" s="19" t="n"/>
+      <c r="AO117" s="19" t="n"/>
+      <c r="AP117" s="19" t="n"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -21809,7 +23447,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuous (sensor / autonomous) — 5-day revisit, tide-resolving with composite-cycle binning</t>
+          <t>Continuous (5-day revisit, tide-resolving with composite-cycle binning)</t>
         </is>
       </c>
       <c r="Q118" t="inlineStr">
@@ -21912,6 +23550,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK118" s="16" t="inlineStr">
+        <is>
+          <t>To monitor turbidity, chlorophyll-a and even oyster feeding conditions across a farming bay from satellite, pair in-situ bio-optical measurements with Sentinel-2 imagery. In the field, measure above-water reflectance with radiometers plus water samples for turbidity, suspended particulate matter (gravimetric on GF/F) and chlorophyll-a (HPLC pigments) to calibrate and validate the retrieval. Atmospherically correct the imagery for turbid water (for example the ACOLITE SWIR method) and apply red/red-edge/near-infrared band algorithms to map SPM and chl-a; because these vary strongly with the tide, sort scenes by tidal stage into neap and spring composites. Then convert the mapped SPM and chl-a per pixel into oyster clearance rate (a known non-linear function of SPM) and chlorophyll consumption to show where and when high turbidity would suppress feeding.</t>
+        </is>
+      </c>
+      <c r="AL118" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM118" s="18" t="inlineStr">
+        <is>
+          <t>gernez_2017</t>
+        </is>
+      </c>
+      <c r="AN118" s="19" t="n"/>
+      <c r="AO118" s="19" t="n"/>
+      <c r="AP118" s="19" t="n"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -21987,7 +23643,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuous (sensor / autonomous) — in-situ tag deployment (intended)</t>
+          <t>Continuous (in-situ tag deployment, intended)</t>
         </is>
       </c>
       <c r="Q119" t="inlineStr">
@@ -22090,6 +23746,14 @@
           <t>Not exposure-specific</t>
         </is>
       </c>
+      <c r="AM119" s="18" t="inlineStr">
+        <is>
+          <t>wu_2022</t>
+        </is>
+      </c>
+      <c r="AN119" s="19" t="n"/>
+      <c r="AO119" s="19" t="n"/>
+      <c r="AP119" s="19" t="n"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -22165,7 +23829,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months) — hourly logging across farming cycle</t>
+          <t>Multi-season (hourly logging across farming cycle)</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
@@ -22268,6 +23932,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK120" s="16" t="inlineStr">
+        <is>
+          <t>To characterise the pH and dissolved-oxygen conditions a raft mussel crop actually experiences, suspend water-quality sondes (logging temperature, salinity, pH, DO and chlorophyll) at more than one depth (for example 1 and 7 m) in the centre of the raft and log hourly over an extended period, calibrating monthly. To capture the microenvironment inside mussel clumps, embed a pH electrode and an oxygen probe in the centre of mesh bags of mussels hung beside the sondes. Test season and depth effects with two-way ANOVA (rank-transformed), and run a threshold/excursion analysis - counting sustained drops below critical pH or DO limits (for example two consecutive hours below a set threshold) and comparing their frequency and duration across season and depth. This captures both ambient conditions and the more extreme acidification and hypoxia excursions the animals endure within aggregations.</t>
+        </is>
+      </c>
+      <c r="AL120" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM120" s="18" t="inlineStr">
+        <is>
+          <t>george_2019</t>
+        </is>
+      </c>
+      <c r="AN120" s="19" t="n"/>
+      <c r="AO120" s="19" t="n"/>
+      <c r="AP120" s="19" t="n"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -22343,7 +24025,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — farming-cycle scale, 2–3 yr cohort</t>
+          <t>Multi-season (farming-cycle scale, 2–3 yr cohort)</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
@@ -22451,6 +24133,19 @@
           <t>To track how benthic fluxes change over a clam-farming cycle, incubate intact sediment cores from a farmed experimental plot and a control at intervals from young stock to harvest, measuring dissolved-oxygen and ammonium fluxes across the sediment-water interface (spectrophotometric ammonium, oxygen by microsensor or Winkler). Compare farm against control fluxes through the cycle; this temporal trajectory complements the snapshot pathway measurements from companion studies at the same site.</t>
         </is>
       </c>
+      <c r="AL121" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM121" s="18" t="inlineStr">
+        <is>
+          <t>nizzoli_2007</t>
+        </is>
+      </c>
+      <c r="AN121" s="19" t="n"/>
+      <c r="AO121" s="19" t="n"/>
+      <c r="AP121" s="19" t="n"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -22526,7 +24221,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — 13-month</t>
+          <t>Annual (13-month)</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
@@ -22629,6 +24324,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK122" s="16" t="inlineStr">
+        <is>
+          <t>To detect chlorophyll-a depletion by a mussel farm, profile chlorophyll fluorescence inside and just outside the farm and check whether it varies over the tidal cycle. Moor a CTD with a fluorometer on a longline at mid-depth and log fluorescence at short intervals over several tidal cycles (with a bottom-mounted current profiler for the tide), and on repeat surveys profile chlorophyll through the water column at randomly chosen on-farm stations, each paired with an outside station at equal distance from shore. Calibrate the fluorometer against water samples analysed for chlorophyll-a (90% acetone extraction, laboratory fluorometer), building a monthly conversion regression. Monitor ambient chlorophyll and dissolved nutrients (nitrate plus nitrite, reactive phosphorus, ammonium on an autoanalyser) outside the farm with an integrated tube sampler, and compare inside versus outside to quantify the depletion signal.</t>
+        </is>
+      </c>
+      <c r="AL122" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM122" s="18" t="inlineStr">
+        <is>
+          <t>ogilvie_2000</t>
+        </is>
+      </c>
+      <c r="AN122" s="19" t="n"/>
+      <c r="AO122" s="19" t="n"/>
+      <c r="AP122" s="19" t="n"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -22704,7 +24417,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — 13-month, monthly cruises</t>
+          <t>Annual (13-month, monthly cruises)</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
@@ -22807,6 +24520,14 @@
           <t>Exposed (offshore Bay of Biscay)</t>
         </is>
       </c>
+      <c r="AM123" s="18" t="inlineStr">
+        <is>
+          <t>muniz_2019</t>
+        </is>
+      </c>
+      <c r="AN123" s="19" t="n"/>
+      <c r="AO123" s="19" t="n"/>
+      <c r="AP123" s="19" t="n"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -22877,7 +24598,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months) — campaign</t>
+          <t>Multi-season campaign</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
@@ -22985,6 +24706,19 @@
           <t>To measure phytoplankton depletion at a large suspended mussel farm across scales, combine methods: pulse-shape flow cytometry on water samples for phytoplankton community composition; CTD casts with chlorophyll and Secchi plus a mooring array for continuous in-farm and reference conditions; a synoptic vessel survey mapping the chlorophyll halo; and drone or satellite (Sentinel) imagery for the surface chlorophyll field. Cross-check depletion across methods and validate against a hydrodynamic model; agreement across independent modalities is what makes a farm-scale depletion signal credible.</t>
         </is>
       </c>
+      <c r="AL124" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM124" s="18" t="inlineStr">
+        <is>
+          <t>taylor_2024</t>
+        </is>
+      </c>
+      <c r="AN124" s="19" t="n"/>
+      <c r="AO124" s="19" t="n"/>
+      <c r="AP124" s="19" t="n"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -23060,7 +24794,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t xml:space="preserve">One-time (no sampling — desk-based) — annual / multi-year simulation</t>
+          <t>Annual / multi-year simulation</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
@@ -23168,6 +24902,19 @@
           <t>This is a coupled 2D hydro-sedimentary, primary-production and filter-feeder model of a major shellfish bay that partitions grazing pressure among cultivated species, an invasive species and wild natives, validated against in-situ chlorophyll and nutrients. Its lesson for monitoring: where wild and invasive filter feeders are abundant, attributing chlorophyll depletion specifically to aquaculture requires disentangling their contributions. Use it as a model reference for carrying-capacity and attribution questions.</t>
         </is>
       </c>
+      <c r="AL125" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM125" s="18" t="inlineStr">
+        <is>
+          <t>cugier_2010</t>
+        </is>
+      </c>
+      <c r="AN125" s="19" t="n"/>
+      <c r="AO125" s="19" t="n"/>
+      <c r="AP125" s="19" t="n"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -23238,7 +24985,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — 10 cruises 2009–2015</t>
+          <t>Multi-year (10 cruises 2009–2015)</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
@@ -23341,6 +25088,24 @@
           <t>Sheltered</t>
         </is>
       </c>
+      <c r="AK126" s="16" t="inlineStr">
+        <is>
+          <t>To attribute changes in phytoplankton biomass and community to an oyster farm, sample paired stations at the farm centre and in a control area a few hundred metres to about 1 km outside, at surface and bottom, repeated across seasons (ideally spanning years, and comparing an old and a relocated farm for causal weight). Collect water with Niskin bottles; measure DO by Winkler titration and transparency by Secchi, and take frozen samples for nutrients (0.45 um filtered), total organic carbon and suspended solids. Size-fractionate chlorophyll-a (&gt;20, 2-20, &lt;2 um) by sequential filtration and read on a fluorometer after acetone extraction, and measure pheopigments (chl-a degradation products) as a grazing indicator; settle and count phytoplankton (at least 300 units) under a microscope for richness, Shannon and Pielou indices. Compare farm versus control with two-way ANOVA (or Mann-Whitney) and ANOSIM on log-transformed Bray-Curtis data, and correlate the biomass reduction with environmental drivers.</t>
+        </is>
+      </c>
+      <c r="AL126" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM126" s="18" t="inlineStr">
+        <is>
+          <t>jiang_2019</t>
+        </is>
+      </c>
+      <c r="AN126" s="19" t="n"/>
+      <c r="AO126" s="19" t="n"/>
+      <c r="AP126" s="19" t="n"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -23411,7 +25176,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Year-long study (12 months) — 14-month, multi-season</t>
+          <t>Annual / multi-season (14-month)</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
@@ -23519,6 +25284,19 @@
           <t>To fingerprint an oyster farm's effect on phytoplankton by size and type, sample a farmed area and a reference area over a full seasonal cycle, size-fractionate the water (for example through 20, 2.7 and 0.7 um) and analyse diagnostic pigments by HPLC (chlorophyll-a plus marker pigments such as fucoxanthin and peridinin). Compare pigment communities with ANOSIM/SIMPER and quantify chlorophyll reduction per size class; this reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
         </is>
       </c>
+      <c r="AL127" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM127" s="18" t="inlineStr">
+        <is>
+          <t>jiang_2016</t>
+        </is>
+      </c>
+      <c r="AN127" s="19" t="n"/>
+      <c r="AO127" s="19" t="n"/>
+      <c r="AP127" s="19" t="n"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -23589,7 +25367,7 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months)</t>
+          <t>Multi-season</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
@@ -23697,6 +25475,19 @@
           <t>This is primarily a physiological method but yields filtering parameters useful for water-quality modelling: measure clearance rate and particle-capture efficiency of each bivalve species on natural seston in flow-through chambers, characterising the particle field by size (Coulter counter or flow cytometer) and chlorophyll. Comparing species and seasons gives the species-specific clearance rates needed to parameterise mass-balance and carrying-capacity models, rather than a direct field water-quality measurement.</t>
         </is>
       </c>
+      <c r="AL128" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM128" s="18" t="inlineStr">
+        <is>
+          <t>rahman_2020</t>
+        </is>
+      </c>
+      <c r="AN128" s="19" t="n"/>
+      <c r="AO128" s="19" t="n"/>
+      <c r="AP128" s="19" t="n"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -23764,7 +25555,7 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year)</t>
+          <t>Multi-year</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
@@ -23872,6 +25663,19 @@
           <t>This synthesis documents how reef-building bivalves reshape local hydrodynamics and sediment morphology (sometimes hundreds of metres beyond the reef), provide habitat and deliver coastal-protection services. It embeds standard reef-establishment and monitoring approaches (epibiota cover, infaunal cores, RTK sediment-elevation surveys, before/after reef-versus-control contrasts). Use it as a framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
         </is>
       </c>
+      <c r="AL129" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM129" s="18" t="inlineStr">
+        <is>
+          <t>ysebaert_2018</t>
+        </is>
+      </c>
+      <c r="AN129" s="19" t="n"/>
+      <c r="AO129" s="19" t="n"/>
+      <c r="AP129" s="19" t="n"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -23942,7 +25746,7 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — 3-yr pilot</t>
+          <t>Multi-year (3 yr pilot)</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
@@ -24045,6 +25849,24 @@
           <t>Mixed exposure</t>
         </is>
       </c>
+      <c r="AK130" s="16" t="inlineStr">
+        <is>
+          <t>To evaluate a longline-mussel nature-based solution for its reef-building and biodiversity value, monitor the dropper-line community, the surrounding seabed and the mussels themselves using a before/after control-impact design. Sample seabed macrobenthos with a Van Veen grab (0.1 m2, rinsed over 1 mm mesh, fixed in formaldehyde, rose-bengal stained) at fixed reef stations and control stations about 50 m outside, before installation and repeatedly after. Retrieve dropper-line segments to assess the biofouling community (top versus bottom 50 cm, rinsed over a 0.5 mm sieve, subsampled by quartering) and mussel metrics - size distribution, primary versus secondary attachment (a detachment-risk ratio), and condition. Add qualitative diver-video transects along the line for reef state and epifauna, and analyse macrobenthos richness and diversity with generalised or linear mixed models (site fixed, time random) plus SIMPER for the taxa driving community differences.</t>
+        </is>
+      </c>
+      <c r="AL130" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM130" s="18" t="inlineStr">
+        <is>
+          <t>goedefroo_2022</t>
+        </is>
+      </c>
+      <c r="AN130" s="19" t="n"/>
+      <c r="AO130" s="19" t="n"/>
+      <c r="AP130" s="19" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -24115,7 +25937,7 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short campaign (days to 2 weeks) — multi-day, covering tidal cycles</t>
+          <t>Multi-day campaign (covering tidal cycles)</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
@@ -24218,6 +26040,14 @@
           <t>Exposed</t>
         </is>
       </c>
+      <c r="AM131" s="18" t="inlineStr">
+        <is>
+          <t>lin_2016</t>
+        </is>
+      </c>
+      <c r="AN131" s="19" t="n"/>
+      <c r="AO131" s="19" t="n"/>
+      <c r="AP131" s="19" t="n"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -24293,7 +26123,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-season (3–9 months) — summer + winter comparison</t>
+          <t>Multi-season (seasonal summer + winter comparison)</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
@@ -24401,6 +26231,19 @@
           <t>To measure how dense infaunal bivalves affect sediment stability, compare a cultivation zone with an adjacent bare flat, co-deploying an acoustic Doppler velocimeter for turbulent flow and a wave-tide recorder to derive bed shear stress, alongside sediment grain-size and organic-content analysis and benthic cores. Track bed-level change and compute the critical erosion shear stress at each site; note the counterintuitive result that high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed rather than protect it - the opposite of reef-building bivalves.</t>
         </is>
       </c>
+      <c r="AL132" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM132" s="18" t="inlineStr">
+        <is>
+          <t>shi_2020</t>
+        </is>
+      </c>
+      <c r="AN132" s="19" t="n"/>
+      <c r="AO132" s="19" t="n"/>
+      <c r="AP132" s="19" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -24473,7 +26316,7 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-year monitoring (&gt; 1 year) — multi-scale: seasonal (4× 1998+1999 at 3 sites), spatial snapshot (winter 2014, 74 sites), decadal (3-yr intervals 1987–2014 at 10 sites)</t>
+          <t>Multi-scale: seasonal (4 × 1998+1999 at 3 sites), spatial snapshot (winter 2014, 74 sites), decadal (3-yr intervals 1987–2014 at 10 sites)</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
@@ -24581,6 +26424,4440 @@
           <t>To establish a multi-scale bivalve-tissue bioindicator baseline, sample pooled soft tissue of the target species at many coastal stations (following a national mussel-watch protocol), depurate briefly in site water, freeze-dry and homogenise, then analyse carbon and nitrogen content and delta-13-C/delta-15-N on an elemental analyser coupled to an IRMS against certified standards. Design the sampling across spatial (many sites in one season), seasonal (repeated within a year) and multi-decadal scales so you can run typology comparisons (Kruskal-Wallis) and trend/shift detection (Pettitt, Mann-Kendall) on the long series.</t>
         </is>
       </c>
+      <c r="AL133" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM133" s="18" t="inlineStr">
+        <is>
+          <t>briant_2018</t>
+        </is>
+      </c>
+      <c r="AN133" s="19" t="n"/>
+      <c r="AO133" s="19" t="n"/>
+      <c r="AP133" s="19" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO / Tennenbaum Marine Observatories Network</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>MarineGEO Fouling Community Monitoring Protocol</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Smithsonian Institution</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Standardized settlement-panel protocol for sessile fouling/epibiont communities on submerged hard structures — directly transferable to bivalve/seaweed gear (ropes, cages, longlines) to quantify native epibiota colonising farmed biomass. Repeated farm vs reference, also informs community composition and settlement/recruitment.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Yes — full field package (PDF step-by-step methods, printable field sheet, data-submission workbook). Panels deployed for a set soak, photographed and/or scraped; sessile cover and taxa scored. Replicable by another team.</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Partial — panel deployment/retrieval and photography are farmer-doable; species-level ID of fouling taxa needs a taxonomist or image-analysis partner.</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Settlement panels (PVC), lines/weights, underwater camera; lab microscope for ID</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Low–Medium — panels and gear inexpensive; cost sits in ID/processing time</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Seasonal (1–3 months)</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Percent-cover scoring, taxa richness/diversity; farm-vs-reference comparison</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Yes — Open (DOI-published, CC)</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>https://marinegeo.github.io/fouling-community.html ; collection DOI https://doi.org/10.25573/serc.c.5506377</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO suite — the closest direct analogue to the Oyster-Reef protocol for the epibiota-on-structures case. ARMS (Autonomous Reef Monitoring Structures) is the metabarcoding-based cousin for cryptobiota where panel ID is impractical. Built for natural hard-bottom; transfers cleanly to aquaculture gear.</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W134" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK134" s="16" t="inlineStr">
+        <is>
+          <t>To quantify the attached (fouling/epibiont) community your gear supports, deploy standardized settlement panels (e.g. roughly hand-sized PVC plates) on the farm structures and at a reference site, leaving them for a set soak of a few months. Retrieve, photograph each panel and/or scrape it, and score percent cover and identify the sessile taxa under a microscope. Compare farm versus reference for cover, richness and community composition. A printable field sheet and data-submission workbook accompany the protocol; where hands-on ID is impractical, an autonomous-reef-monitoring-structure (ARMS) plus metabarcoding variant covers cryptic fauna.</t>
+        </is>
+      </c>
+      <c r="AL134" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM134" s="18" t="inlineStr">
+        <is>
+          <t>smithsonianmarinegeo_2022</t>
+        </is>
+      </c>
+      <c r="AN134" s="19" t="n"/>
+      <c r="AO134" s="19" t="n"/>
+      <c r="AP134" s="19" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>MarineGEO Oyster Reef Habitat Monitoring Protocol</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Smithsonian Institution</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Standard survey design for eastern-oyster reef habitat: reef area &amp; height, composition, oyster density &amp; size, rugosity, and associated mobile + sessile biodiversity. Methodology adopted from the Baggett/TNC handbook (universal metrics).</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Yes — reproducible reef-structure metrics plus associated-fauna collection, with site-selection, layout, workflow and data-submission guidance. Comparable across MarineGEO sites.</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Partial — reef metrics (area, height, density, size) and fauna collection are farmer-doable; faunal ID/sorting needs a partner.</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Quadrats, calipers, transect tape, excavation trays, mesh bags; lab for ID</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Low–Medium</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Seasonal (1–3 months)</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Density/size-frequency, rugosity, diversity indices; farm/reference comparison</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Yes — Open (DOI-published)</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>https://marinegeo.si.edu/protocols/oyster-reefs</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Specific to eastern oyster (Crassostrea virginica) but design transfers to other bivalve reef/longline contexts. Pairs with the Baggett 2014 handbook (next row), the methodological parent.</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W135" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>Eastern oyster (Crassostrea virginica)</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK135" s="16" t="inlineStr">
+        <is>
+          <t>To monitor oyster-reef habitat (and by extension bivalve reef/longline structure), survey reef areal extent and height, oyster density and size, and rugosity, alongside the associated mobile and sessile fauna. Lay transects and place quadrats to measure density and size-frequency (calipers), record rugosity, and collect associated organisms (excavation trays, mesh bags) for lab identification. Compare farm/reef against a reference with density, size-frequency and diversity metrics. The design follows the universal reef metrics of the Baggett/TNC handbook, so results are comparable across sites.</t>
+        </is>
+      </c>
+      <c r="AL135" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM135" s="18" t="inlineStr">
+        <is>
+          <t>smithsonianmarinegeo_2022-b</t>
+        </is>
+      </c>
+      <c r="AN135" s="19" t="n"/>
+      <c r="AO135" s="19" t="n"/>
+      <c r="AP135" s="19" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Baggett, L.P.; Powers, S.P.; Brumbaugh, R.D.; Coen, L.D.; DeAngelis, B.M.; Greene, J.K.; Hancock, B.T.; Morlock, S.M.</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Oyster Habitat Restoration Monitoring and Assessment Handbook</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>The Nature Conservancy</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>96 pp</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>2014</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>The Nature Conservancy, Arlington, VA</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>TNC's standard for oyster reef monitoring. Four Universal Metrics (reef areal dimension, height, oyster density, size-frequency) + three Universal Environmental Variables (temperature, salinity, dissolved oxygen) + goal-based metrics for four ecosystem-service goals (incl. associated biodiversity and coastal protection / shoreline stabilisation).</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Yes — defines metrics, units, performance criteria and field methods in replicable detail; peer-reviewed companion is Baggett et al. 2015 (Restoration Ecology). Practitioners without capacity are explicitly told to collaborate.</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Partial — universal reef metrics and DO/temp/salinity (handheld probe) are farmer-executable; associated-biodiversity, disease and recruitment metrics need a partner lab.</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Quadrats, calipers, transect tape, handheld multiprobe (T/S/DO), shell/recruitment trays</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Low–Medium</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Multi-year monitoring (&gt; 1 year)</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Universal-metric comparison to performance criteria; size-frequency; goal-based analysis</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Yes — Open (free PDF)</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>http://www.oyster-restoration.org/wp-content/uploads/2014/01/Oyster-Habitat-Restoration-Monitoring-and-Assessment-Handbook.pdf</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>TNC-authored — direct lineage with this MEL framework. Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming H&amp;B/WQ. The coastal-protection goal-based metric set is the practitioner route to CC 3.1.1 (shoreline position/elevation + wave-gauge/pressure-logger field methods).</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W136" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity, Water Quality, Climate Change</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, WQ 1.2.1 — Dissolved oxygen, CC 3.1.1 — Wave attenuation / coastal protection</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>Eastern oyster (Crassostrea virginica)</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>Visual survey, Water chemistry</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK136" s="16" t="inlineStr">
+        <is>
+          <t>This TNC handbook is the standard for oyster-reef monitoring and defines exactly what to measure: four Universal Metrics (reef areal dimension, height, oyster density, size-frequency), three Universal Environmental Variables (temperature, salinity, dissolved oxygen via a handheld multiprobe), plus goal-based metrics for specific ecosystem services. Measure the universal metrics with quadrats, calipers and transect tape against defined performance criteria, and add the goal-based set for the service you care about - the coastal-protection metrics (shoreline position/elevation plus a wave gauge) are the practitioner route to a wave-attenuation indicator. It shares direct lineage with this MEL framework, its metrics and environmental variables transfer to bivalve farming, and teams without capacity are advised to collaborate.</t>
+        </is>
+      </c>
+      <c r="AL136" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM136" s="18" t="inlineStr">
+        <is>
+          <t>baggett_2014</t>
+        </is>
+      </c>
+      <c r="AN136" s="19" t="n"/>
+      <c r="AO136" s="19" t="n"/>
+      <c r="AP136" s="19" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Native Oyster Network (UK &amp; Ireland); Native Oyster Restoration Alliance (NORA)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>European Native Oyster Habitat Restoration Monitoring Guidelines</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Native Oyster Restoration Alliance (NORA)</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>NORA / ZSL Native Oyster Network</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>European adaptation (39 authors, 7 countries) of the Baggett handbook for Ostrea edulis: Universal, Supplementary and Goal-Based Metrics suited to European native-oyster settings.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Yes — metric definitions with multiple method options per metric; designed to answer performance questions for European native-oyster restoration.</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Partial — universal/structural metrics farmer-doable; biodiversity and some supplementary metrics need partner lab.</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Quadrats, transect tape, calipers; lab for ID</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Low–Medium</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Multi-year monitoring (&gt; 1 year)</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Universal/supplementary/goal-based metric analysis</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Yes — Open (online guidelines)</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>https://nativeoysternetwork.org/2021/05/04/native-oyster-monitoring-guidelines/</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Use for European flat-oyster (Ostrea edulis) contexts where Baggett 2014 methods need adaptation. Complementary to the MarineGEO Oyster-Reef protocol and Baggett handbook.</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W137" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity, Climate Change</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.1.1 — Community composition, H&amp;B 2.2.1 — Spawning, CC 3.1.1 — Wave attenuation / coastal protection</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>Temperate Atlantic</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>European flat oyster (Ostrea edulis)</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK137" s="16" t="inlineStr">
+        <is>
+          <t>This is the European adaptation of the TNC oyster handbook for the native flat oyster (Ostrea edulis), giving Universal, Supplementary and Goal-Based metrics with several method options per metric. Measure reef/bed extent, oyster density and size with quadrats, transect tape and calipers, choosing the method option that fits your setting, and analyse against the restoration performance questions. Use it in European native-oyster contexts where the Baggett handbook methods need adapting.</t>
+        </is>
+      </c>
+      <c r="AL137" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM137" s="18" t="inlineStr">
+        <is>
+          <t>ukireland_2021</t>
+        </is>
+      </c>
+      <c r="AN137" s="19" t="n"/>
+      <c r="AO137" s="19" t="n"/>
+      <c r="AP137" s="19" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>MarineGEO Diver Visual Survey Protocol</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Smithsonian Institution</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Standardized diver/snorkel belt-transect visual census of mobile fauna (fish, mobile invertebrates). Directly applicable to counting mobile fauna associated with a farm site.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Yes — fixed transect design with counts/size estimates and data sheet; on-the-spot ID. Reproducible across sites.</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Yes — belt/visual transects with field ID guides are farmer/diver-executable with no obligatory lab step (the canonical practitioner-tier method).</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Transect tape, slate, dive/snorkel gear, ID guide</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Seasonal (1–3 months)</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Abundance/size counts per transect; diversity indices</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Yes — Open (DOI-published)</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.25573/serc.14717796</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Reef Life Survey (RLS) provides an equivalent globally standardized diver visual-census methods manual and trained-diver network — an alternative where added rigour or a citizen-science cohort is wanted. Requires dive competency and reasonable water clarity.</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W138" s="7" t="inlineStr">
+        <is>
+          <t>4 — Practitioner</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk, Finfish</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.2.1 — Mobile fauna</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>Clear (visual methods feasible)</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>Shallow nearshore (2–10 m)</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK138" s="16" t="inlineStr">
+        <is>
+          <t>To count mobile fauna (fish and mobile invertebrates) around a farm, run a standardized diver or snorkel belt-transect visual census: swim a fixed-length, fixed-width transect and record species and size estimates on a slate as you go. Repeat transects at the farm and a reference site and summarise as abundance and size per transect plus diversity indices. It needs dive/snorkel competency and reasonable water clarity; Reef Life Survey offers an equivalent standardized method and trained-diver network where more rigour or a citizen-science cohort is wanted.</t>
+        </is>
+      </c>
+      <c r="AL138" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM138" s="18" t="inlineStr">
+        <is>
+          <t>smithsonianmarinegeo_2021</t>
+        </is>
+      </c>
+      <c r="AN138" s="19" t="n"/>
+      <c r="AO138" s="19" t="n"/>
+      <c r="AP138" s="19" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>MarineGEO Beach Seine Protocol</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Smithsonian Institution</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Standardized beach-seine sampling of nekton (fish, mobile crustacea) in shallow soft-sediment habitats; transfers to nearshore farm-margin mobile-fauna sampling.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Yes — standardized net, haul design and processing with data sheet; reproducible.</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Yes — seine hauls with field ID/measure are farmer-executable; no obligatory lab step.</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Beach seine net, measuring board, buckets, ID guide</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Seasonal (1–3 months)</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Catch-per-haul abundance/size; diversity</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Yes — Open (DOI-published)</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.25573/serc.14925105</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Best for shallow, wadeable, soft-bottom margins; complements diver/BRUV methods for the mobile-fauna indicator.</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W139" s="7" t="inlineStr">
+        <is>
+          <t>4 — Practitioner</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk, Finfish</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.2.1 — Mobile fauna</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>Variable / seasonal</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>Intertidal / very shallow (&lt; 2 m)</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>Sheltered</t>
+        </is>
+      </c>
+      <c r="AK139" s="16" t="inlineStr">
+        <is>
+          <t>To sample nekton (fish and mobile crustaceans) along shallow, wadeable farm margins, use a standardized beach-seine haul: deploy the net over a set area, retrieve it, then identify, count and measure the catch on a board before release. Express results as catch-per-haul abundance and size, with diversity indices, comparing farm-margin to reference hauls. Best for shallow soft-bottom margins; it complements diver and baited-camera methods for the mobile-fauna indicator.</t>
+        </is>
+      </c>
+      <c r="AL139" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM139" s="18" t="inlineStr">
+        <is>
+          <t>smithsonianmarinegeo_2021-b</t>
+        </is>
+      </c>
+      <c r="AN139" s="19" t="n"/>
+      <c r="AO139" s="19" t="n"/>
+      <c r="AP139" s="19" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>MarineGEO Benthic Photoquadrat Protocol</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Smithsonian Institution</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Standardized photo-quadrat survey of benthic cover/community (point-count image analysis). Supports characterising the epibenthic community around a farm; for true infauna use grab-based methods (SEPA/NS 9410).</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Yes — quadrat photo design with point-count image analysis (e.g., CoralNet); reproducible and re-auditable.</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Partial — photo capture is farmer-doable; point-count image annotation/ID is a skilled (often partner) step.</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Quadrat frame, underwater camera; image-analysis software (CoralNet/CPCe)</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Low–Medium</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Seasonal (1–3 months)</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Point-count percent cover; community composition</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Yes — Open (DOI-published)</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.25573/serc.14717823</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Image archives are re-analysable and auditable. Captures epibenthic cover (not soft-sediment infauna). Pairs with the Sediment Organic Matter protocol for soft-sediment characterisation.</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W140" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 2.1.1 — Community composition</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>Clear (visual methods feasible)</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>Shallow nearshore (2–10 m)</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK140" s="16" t="inlineStr">
+        <is>
+          <t>To characterise the epibenthic community (cover) around a farm, photograph benthic quadrats along transects and analyse the images by point-count (e.g. CoralNet or CPCe), scoring percent cover per taxon. Repeat at farm and reference sites and compare community composition. The image archive is re-analysable and auditable; note this captures epibenthic cover, not soft-sediment infauna - pair it with a sediment protocol for the seabed itself.</t>
+        </is>
+      </c>
+      <c r="AL140" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM140" s="18" t="inlineStr">
+        <is>
+          <t>smithsonianmarinegeo_2021-c</t>
+        </is>
+      </c>
+      <c r="AN140" s="19" t="n"/>
+      <c r="AO140" s="19" t="n"/>
+      <c r="AP140" s="19" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>MarineGEO Sediment Organic Matter Protocol</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Smithsonian Environmental Research Center (MarineGEO Protocols)</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Smithsonian Institution</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Standardized sediment sampling + loss-on-ignition for organic-matter content (a core sediment-condition descriptor under and around a farm).</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Yes — coring/grab + drying + loss-on-ignition with data sheet; reproducible.</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Partial — sediment collection farmer-doable; LOI needs a drying oven/muffle furnace (basic lab step).</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Sediment corer/grab, drying oven, muffle furnace, balance</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Seasonal (1–3 months)</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>%LOI / organic-matter content; farm-vs-reference</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Yes — Open (DOI-published)</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.25573/serc.14925111</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, DIN flux) use the SEPA / NS 9410 benthic standards (rows below).</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W141" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.4.1 — Sediment</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>Sediment sampling</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK141" s="16" t="inlineStr">
+        <is>
+          <t>To measure sediment organic-matter content under and around a farm, collect sediment by corer or grab, dry the sample, then combust it in a muffle furnace and weigh before and after to get percent loss-on-ignition (organic-matter content). Sample farm and reference stations and compare. It is a simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, nutrient flux) use the SEPA or NS 9410 benthic standards.</t>
+        </is>
+      </c>
+      <c r="AL141" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM141" s="18" t="inlineStr">
+        <is>
+          <t>smithsonianmarinegeo_2021-d</t>
+        </is>
+      </c>
+      <c r="AN141" s="19" t="n"/>
+      <c r="AO141" s="19" t="n"/>
+      <c r="AP141" s="19" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Langlois, T.; Goetze, J.; Bond, T.; et al. (NESP Marine Biodiversity Hub)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>A field and video-annotation guide for baited remote underwater stereo-video (stereo-BRUV) surveys of demersal fish assemblages</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Methods in Ecology and Evolution / open NESP field manual</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1401–1409</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Wiley / NESP Marine Biodiversity Hub</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>The first globally accepted standardized guide for stereo-BRUV surveys of fish assemblages — design, camera settings, field operations, and video annotation, with links to data validation/archiving (GlobalArchive). Covers mobile fauna and the finfish fish-attraction case.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Yes — fully documented field + annotation SOP intended for cross-study interoperability (FAIR workflows).</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Partial — baited-camera deployment is practitioner-doable, but stereo calibration and photogrammetric annotation/measurement (EventMeasure) need a trained analyst or partner.</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Stereo camera pair + frame, bait arm, ropes/floats; annotation software (EventMeasure)</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Short campaign (days to 2 weeks)</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>MaxN relative abundance, length/biomass from stereo; assemblage composition</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Yes — Open (CC-BY; open GitHub manual)</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>https://benthic-bruvs-field-manual.github.io/ ; https://doi.org/10.1111/2041-210X.13470</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Single-camera baited cameras (BRUVs) are a lower-cost practitioner variant (relative abundance only, no lengths). GlobalArchive (globalarchive.org) is the standardized data repository. Part of the NESP Marine Sampling Field Manuals collection (next row). For finfish, this is the route to the fish-attraction facet of Finfish H&amp;B 2.1.1.</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W142" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Mollusk, Finfish, Seaweed</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.2.1 — Mobile fauna</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>Clear (visual methods feasible)</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>BRUVs / video</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>Coastal (10–30 m)</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK142" s="16" t="inlineStr">
+        <is>
+          <t>To survey fish assemblages (mobile fauna, and fish attraction at finfish farms) without diving, deploy baited remote underwater stereo-video (stereo-BRUV): a paired-camera frame with a bait arm, set on the seabed for a standard soak. Annotate the video to relative abundance (MaxN) and, from the stereo pair, individual lengths and biomass, following the standardized field-and-annotation SOP for cross-study comparability. A single-camera BRUV is a lower-cost practitioner variant (relative abundance only, no lengths), and data archive to a standardized repository (GlobalArchive).</t>
+        </is>
+      </c>
+      <c r="AL142" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM142" s="18" t="inlineStr">
+        <is>
+          <t>langlois_2020</t>
+        </is>
+      </c>
+      <c r="AN142" s="19" t="n"/>
+      <c r="AO142" s="19" t="n"/>
+      <c r="AP142" s="19" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Przeslawski, R.; Foster, S. (eds.) — NESP Marine Biodiversity Hub</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Field Manuals for Marine Sampling to Monitor Australian Waters (BRUVs, grabs, sleds, towed video, AUVs)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>NESP Marine Biodiversity Hub</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>2018</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>National Environmental Science Program (Australia)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>A collection of standardized field-sampling SOPs (benthic stereo-BRUVs, grabs/cores, sleds, towed video, multibeam) used as a national design standard, spanning mobile fauna, benthic infauna and sediment.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Reference (usable design tool / SOP collection)</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Adequate as a design/standardisation resource: each manual gives equipment, deployment and QA guidance a programme is built from; individual manuals are themselves executable protocols.</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>No — most manuals assume a research vessel and specialist gear/expertise across the workflow.</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Varies by manual (research vessel, grabs, towed/stereo video, multibeam)</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Not time-specific</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Per-manual standardized analysis</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Yes — Open (CC-BY)</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Abstract only</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>https://www.nespmarine.edu.au/field-manuals</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Most useful for designing comparable benthic/mobile-fauna campaigns; lifts indicator-specific manuals (e.g., the stereo-BRUV manual above) into a coherent programme. Tier T2 as a researcher-grade design tool.</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W143" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk, Finfish</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity, Cross-cutting / Framework</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.2.1 — Mobile fauna, H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment, Cross-cutting / framework</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>Mixed methods</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK143" s="16" t="inlineStr">
+        <is>
+          <t>This is a collection of standardized Australian field-sampling manuals (benthic stereo-BRUVs, grabs and cores, towed video, sleds, multibeam) used as a national design standard spanning mobile fauna, benthic infauna and sediment. Use it to design comparable benthic and mobile-fauna campaigns and to lift indicator-specific manuals (such as the stereo-BRUV manual) into a coherent programme, rather than as a single procedure.</t>
+        </is>
+      </c>
+      <c r="AL143" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM143" s="18" t="inlineStr">
+        <is>
+          <t>przeslawski_2018</t>
+        </is>
+      </c>
+      <c r="AN143" s="19" t="n"/>
+      <c r="AO143" s="19" t="n"/>
+      <c r="AP143" s="19" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Scottish Environment Protection Agency (SEPA)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Fish Farm Manual — Benthic Monitoring (Standard &amp; Extended surveys; Infaunal Quality Index)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SEPA Aquaculture regulatory guidance</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Scottish Environment Protection Agency</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Regulated benthic-monitoring SOP for marine farms: benthic grab survey, sediment chemistry, and the Infaunal Quality Index (IQI = taxa diversity + AMBI + Simpson evenness). Finfish-origin but the infauna+sediment methodology transfers to bivalve/seaweed farm monitoring.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Yes — prescriptive grab design, sieving/fixation, taxonomic processing and index computation with reporting templates. Compliance-grade reproducibility.</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Partial — grab sampling from a small vessel is farmer-doable, but macrofauna sorting/ID and sediment chemistry require an accredited partner lab.</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Day/van-Veen grab, sieves (0.5/1 mm), sample jars; partner lab for taxonomy + sediment chem</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Medium–High</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Seasonal (1–3 months)</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>IQI/AMBI biotic indices; sediment-chemistry thresholds; mixing-zone assessment</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Yes — Open (SEPA PDF)</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>https://www.sepa.org.uk/media/115592/fish-farm-manual-benthic-extended.pdf</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>A regulatory impact-monitoring standard rather than a benefit protocol, but the grab→IQI workflow is the standard route to the benthic-infauna and sediment indicators. Directly comparable to Norway NS 9410 / MOM (next row).</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W144" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Mollusk, Finfish</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>Temperate Atlantic</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>Sediment sampling</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Coastal (10–30 m)</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK144" s="16" t="inlineStr">
+        <is>
+          <t>Although written for finfish farms, this regulated benthic-monitoring SOP transfers to bivalve/seaweed farm seabed monitoring. Take grab samples (day or van Veen) along the farm and mixing-zone gradient, sieve (0.5-1 mm) and fix the retained infauna, then have a partner lab identify taxa and measure sediment chemistry. Compute the Infaunal Quality Index (taxa diversity + AMBI + Simpson evenness) and compare against sediment-chemistry thresholds and a mixing-zone assessment. The grab-to-IQI workflow is a compliance-grade route to the benthic-infauna and sediment indicators, directly comparable to Norway's NS 9410 / MOM.</t>
+        </is>
+      </c>
+      <c r="AL144" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM144" s="18" t="inlineStr">
+        <is>
+          <t>sepa_2019</t>
+        </is>
+      </c>
+      <c r="AN144" s="19" t="n"/>
+      <c r="AO144" s="19" t="n"/>
+      <c r="AP144" s="19" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Standards Norway</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>NS 9410 — Environmental monitoring of benthic impact from marine aquaculture (MOM B- and C-assessments)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Norwegian Standard (Standards Norway)</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>2016</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Standards Norway</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Norway's legally required benthic-monitoring standard built on the MOM approach. B-assessment (under-cage): pH, redox potential, sensory attributes and macrofauna presence; C-assessment (30–500 m zones): full soft-bottom community + sediment chemistry, NSI/biotic indices.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Yes — standardized field sampling and scoring with defined thresholds; the B-survey is a rapid field assessment, the C-survey a full benthic/chemistry programme.</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Partial — the B-survey (grab + field pH/redox/sensory) is largely field-executable; the C-survey needs full taxonomy + sediment chemistry via partner lab.</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Grab, field pH/redox probes; partner lab for C-survey taxonomy/chemistry</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Seasonal (1–3 months)</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>B-index scoring; NSI/biotic indices; sediment chemistry</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>No — Paywalled (purchase via Standards Norway)</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Abstract only</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>https://www.standard.no (NS 9410)</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Standard document is paywalled; methodology well-documented in secondary literature. Tier set conservatively at T2 (Sub-rule 14a) pending a read of the standard itself — the B-survey component is plausibly T3/Partnership once confirmed. Directly comparable to the SEPA manual.</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W145" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Mollusk, Finfish</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.3.1 — Benthic infauna, H&amp;B 1.4.1 — Sediment</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>Boreal / Arctic</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>Sediment sampling</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>Coastal (10–30 m)</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK145" s="16" t="inlineStr">
+        <is>
+          <t>This is Norway's legally required benthic-monitoring standard, built on the MOM approach, with two tiers. The under-cage B-assessment is a rapid field survey scoring sediment pH, redox potential, sensory attributes and macrofauna presence/absence into condition classes; the zone (C) assessment is a fuller soft-bottom community survey plus sediment chemistry with biotic indices. Sample with a grab and field pH/redox probes for the B-survey, adding lab taxonomy and chemistry for the C-survey. (Summary from secondary sources - the standard itself is paywalled, so confirm exact thresholds from the document before relying on them.)</t>
+        </is>
+      </c>
+      <c r="AL145" s="17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AM145" s="18" t="inlineStr">
+        <is>
+          <t>standardsnorway_2016</t>
+        </is>
+      </c>
+      <c r="AN145" s="19" t="n"/>
+      <c r="AO145" s="19" t="n"/>
+      <c r="AP145" s="19" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Scottish Salmon Producers' Org. (Code of Good Practice); Institute of Marine Research (Norway); Norwegian Food Safety Authority</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Sea lice counting &amp; surveillance protocols (farmed and wild fish)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Industry Code of Good Practice / national surveillance protocols</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Multiple (Scotland; Norway)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Standardized protocols for counting sea lice on farmed salmon (and sentinel/wild salmonids): fixed sampling design (e.g., 5 fish × 5 pens = 25 fish), stage-resolved lice counts, and trigger levels. Under the finfish indicator set this is the parasite/pathogen-surveillance facet of Finfish H&amp;B 2.1.1 (farmed + nearby wild stock).</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Yes — prescriptive fish-sampling and lice-staging counts with defined trigger thresholds; farm-staff counts validated against dedicated teams.</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Partial — farm-level counting on netted fish is genuinely farm-staff (practitioner) executable; the rigorous wild-salmonid surveillance variant needs IMR-style certification and sentinel-cage/trawl capacity (partner).</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Anaesthetic/handling kit, hand lens/loupe; (automated camera systems emerging)</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Low–Medium</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Multi-year monitoring (&gt; 1 year)</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Prevalence/abundance per fish (negative-binomial/normal); trigger-level comparison</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Yes — Open (CoGP &amp; national guidance)</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Scottish Code of Good Practice: thecodeofgoodpractice.co.uk ; Norway IMR: https://www.hi.no/en/hi/nettrapporter/rapport-fra-havforskningen-en-2024-61</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>The Norwegian Salmon Lice Directive (FOR-2009-08-18-1095) is the regulatory framework mandating counting; the IMR protocol is the certified standardized count for the national wild-salmonid programme. Farm-level counting alone is closer to T4; tier set at T3 to cover the full indicator (incl. wild-population surveillance to ~2.5 km). Tagged with the generic 'H&amp;B 2.1.1' string; under the finfish set this is fish-attraction / parasite surveillance.</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W146" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Finfish</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>H&amp;B 2.1.1 — Community composition</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>Temperate Atlantic</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Floating cage / tray</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>Monoculture</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>Coastal (10–30 m)</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK146" s="16" t="inlineStr">
+        <is>
+          <t>To monitor sea-lice burden on farmed salmon (the parasite/pathogen-surveillance facet of the finfish community-composition indicator), follow a fixed sampling design - for example five fish from each of five pens (25 fish) on a set schedule - anaesthetising and examining each fish and counting lice by life stage under a hand lens. Report prevalence and abundance per fish and compare against defined trigger levels that prompt action. Farm-staff counts are typically validated against dedicated teams, and sentinel/wild-salmonid counting extends the same method beyond the farm.</t>
+        </is>
+      </c>
+      <c r="AL146" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM146" s="18" t="inlineStr">
+        <is>
+          <t>scottishsalmon_2023</t>
+        </is>
+      </c>
+      <c r="AN146" s="19" t="n"/>
+      <c r="AO146" s="19" t="n"/>
+      <c r="AP146" s="19" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Reichert-Nguyen, J.; Cornwell, J.; et al. — Oyster BMP Expert Panel (Chesapeake Bay Program / Oyster Recovery Partnership)</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Oyster BMP Expert Panel Reports — Nutrient &amp; Suspended-Sediment Reduction Effectiveness Protocols (First Report 2016; Second Report 2023)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Chesapeake Bay Program / Oyster Recovery Partnership</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Chesapeake Bay Program</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Crediting-and-verification protocols defining reduction-effectiveness for oyster practices: N &amp; P assimilation in tissue, N &amp; P assimilation in shell, enhanced denitrification, and N/P burial. The tissue/shell protocols are the standardized bioextraction route; the denitrification protocol is one of very few packaged methods for that indicator.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Yes — defines harvest accounting (count × size → tissue/shell N&amp;P via published content) and the enhanced-denitrification crediting method, with verification guidelines. Decision-framework + effectiveness estimates.</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Partial — counting/measuring harvested oysters is farmer-executable; tissue/shell %N&amp;P (CHN analyser) and denitrification (N2-flux/15N) need a partner lab, though published default coefficients allow a desk estimate.</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Harvest records, calipers; partner lab CHN analyser; (denitrification: benthic-flux/15N)</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Year-long study (12 months)</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Reduction-effectiveness accounting; verification protocol</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Yes — Open (CBP PDFs)</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>https://d18lev1ok5leia.cloudfront.net/chesapeakebay/documents/Oyster-BMP-Expert-Panel-Second-Report.pdf</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>TNC-relevant (TNC sits on the partnership). Restoration + aquaculture both covered. Shell-assimilation accounting is N/P (not carbon); a shell-CARBON storage protocol for CC 2.1.1 (mollusc) does not yet exist. Default tissue/shell coefficients make a desk estimate feasible without a lab.</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W147" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>Water Quality</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>WQ 1.1.1 — N and P bioextraction, WQ 1.1.2 — Rate of denitrification</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>Temperate Atlantic</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>Eastern oyster (Crassostrea virginica)</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>Tissue analysis</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK147" s="16" t="inlineStr">
+        <is>
+          <t>This crediting-and-verification protocol standardizes how to account for nutrients an oyster practice removes: nitrogen and phosphorus assimilated in harvested tissue and shell, plus enhanced denitrification and burial. For the bioextraction route, record harvest (count x size) and convert to tissue/shell N and P using published content coefficients (or a partner-lab CHN analysis); the denitrification route uses benthic-flux or 15N methods. Default coefficients make a credible desk estimate feasible without a lab. Note shell accounting here is for N and P, not carbon - no shell-carbon storage protocol yet exists.</t>
+        </is>
+      </c>
+      <c r="AL147" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM147" s="18" t="inlineStr">
+        <is>
+          <t>reichertnguyen_2023</t>
+        </is>
+      </c>
+      <c r="AN147" s="19" t="n"/>
+      <c r="AO147" s="19" t="n"/>
+      <c r="AP147" s="19" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Maryland Department of Natural Resources</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Oyster Reef Restoration Nutrient Assimilation BMP</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Maryland DNR (Critical Area / CBP BMP)</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Maryland Department of Natural Resources</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Crediting protocol for N &amp; P assimilated in live oyster tissue and shell gained through reef restoration in tidal Chesapeake waters — the restoration-side application of the Oyster BMP framework.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Yes — defines the restoration nutrient-assimilation accounting with lookup tables (Expert Panel Appendix G) and credit duration.</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Partial — reef survey/oyster counts farmer-doable; tissue/shell N&amp;P via lab or published coefficients.</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Reef survey gear; partner lab / published coefficients</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Low–Medium</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Year-long study (12 months)</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Assimilation accounting via lookup tables</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Yes — Open (MD DNR PDF)</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>https://dnr.maryland.gov/criticalarea/Documents/Oyster_Reef_Restoration_Assimilation_BMP.pdf</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Implements the Chesapeake Oyster BMP framework (previous row) for restoration credits. Useful where reef restoration rather than harvest is the practice.</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W148" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Water Quality</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>WQ 1.1.1 — N and P bioextraction</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Temperate Atlantic</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>Eastern oyster (Crassostrea virginica)</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>Tissue analysis</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK148" s="16" t="inlineStr">
+        <is>
+          <t>This is the restoration-side application of the Chesapeake oyster nutrient-crediting framework: it accounts for nitrogen and phosphorus assimilated in live oyster tissue and shell gained through reef restoration. Survey the reef for oyster numbers and size, then apply the published lookup tables (Expert Panel appendices) to convert to assimilated N and P over the credited duration. Use it where reef restoration, rather than harvest, is the practice.</t>
+        </is>
+      </c>
+      <c r="AL148" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM148" s="18" t="inlineStr">
+        <is>
+          <t>marylanddepartment_2021</t>
+        </is>
+      </c>
+      <c r="AN148" s="19" t="n"/>
+      <c r="AO148" s="19" t="n"/>
+      <c r="AP148" s="19" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Hawkins, A.J.S.; et al. (ShellSIM)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ShellSIM — bivalve filtration, growth and environmental-effects model (software tool)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>shellsim.com</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>PML Applications / ShellSIM</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>User-friendly mechanistic model of suspension-feeding bivalves: predicts particle clearance/filtration rate, ammonium loss, faecal loss, oxygen uptake and growth for up to 14 species, individual→culture-area scale. The practical route to the filtration indicator and a complement to bioextraction/DO.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Reference (usable model / design tool)</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Adequate as a quantification tool rather than a field protocol: given environmental drivers + stock it outputs clearance/filtration and nutrient/oxygen fluxes. Requires parameterisation, not field sampling.</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>No — marketed for growers/managers/regulators but parameterisation and interpretation need modelling expertise.</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Software (ShellSIM); environmental driver data</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Low (tool free; cost is expertise/data)</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>One-time (no sampling — desk-based)</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Dynamic energy-balance simulation; scenario analysis</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Yes — Open (free tool)</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>http://shellsim.com</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Farm-/bay-scale carrying-capacity models (FARM, EcoWin) and the Dame depletion indices (clearance vs. residence vs. primary-production time) are the complementary frameworks for filtration-as-service. Modelling tool → T2.</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W149" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>Water Quality</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>WQ 1.3.1 — Rate of water filtration, WQ 1.1.1 — N and P bioextraction, WQ 1.2.1 — Dissolved oxygen</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>Multi-species / mixed</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>Modelling</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK149" s="16" t="inlineStr">
+        <is>
+          <t>This is a user-friendly mechanistic model of suspension-feeding bivalves rather than a field method: given environmental drivers and stock, it predicts clearance/filtration rate, ammonium and faecal losses, oxygen uptake and growth for many species, from individual to culture-area scale. Use it to quantify the water-filtration service (and to complement bioextraction and dissolved-oxygen work) by parameterising and running scenarios; farm/bay carrying-capacity models (FARM, EcoWin) and Dame's depletion indices are the complementary frameworks.</t>
+        </is>
+      </c>
+      <c r="AL149" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM149" s="18" t="inlineStr">
+        <is>
+          <t>hawkins_2013</t>
+        </is>
+      </c>
+      <c r="AN149" s="19" t="n"/>
+      <c r="AO149" s="19" t="n"/>
+      <c r="AP149" s="19" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>OSPAR Commission (JAMP); ICES</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JAMP Eutrophication Monitoring Guidelines: Chlorophyll a in Water (with ICES TIMES chlorophyll procedure)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>OSPAR Commission / ICES Techniques in Marine Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>2012</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>OSPAR Commission</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Intergovernmental standardized procedure for chlorophyll-a determination (sampling, filtration, extraction, spectrophotometric/HPLC analysis; ISO 10260; in-situ fluorometer calibration). The standard route to the chlorophyll-a indicator.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Yes — prescribes collection→filtration→extraction→analysis with QA (accredited labs, reference checks). Reproducible analytical SOP.</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Partial — water sampling/filtration farmer-doable; spectrophotometric/HPLC analysis needs a partner lab (or a calibrated fluorometer + QC).</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Niskin/bottle, filtration rig, GF/F filters; spectrophotometer/HPLC or calibrated fluorometer</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Low–Medium</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Year-long study (12 months)</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Standardized chl-a quantification; eutrophication assessment</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Yes — Open (OSPAR/JRC PDF)</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>https://mcc.jrc.ec.europa.eu/documents/OSPAR/Eutrophication_MonitoringGuidelinesch_%20a.pdf</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>The ICES TIMES 'Standard procedure for the determination of chlorophyll a by spectroscopic methods' (Aminot &amp; Rey 2000) and the UNESCO/SCOR pigment monographs (Jeffrey et al. 1997) are the underpinning analytical references. Satellite ocean-colour chl-a is the remote-sensing complement.</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W150" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Water Quality</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>WQ 2.1.1 — Chlorophyll-a</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>Pigment HPLC, Water chemistry</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK150" s="16" t="inlineStr">
+        <is>
+          <t>This intergovernmental SOP is the standard route to the chlorophyll-a indicator. Collect water (Niskin/bottle), filter onto GF/F, extract the pigment and determine chlorophyll-a spectrophotometrically or by HPLC (ISO 10260), or calibrate an in-situ fluorometer against these samples, all under defined quality assurance (accredited labs, reference checks). Follow it for comparable, eutrophication-grade chlorophyll data; the ICES TIMES procedure and UNESCO/SCOR pigment monographs are the underpinning analytical references, and satellite ocean-colour chlorophyll is the remote-sensing complement.</t>
+        </is>
+      </c>
+      <c r="AL150" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM150" s="18" t="inlineStr">
+        <is>
+          <t>jamp_2012</t>
+        </is>
+      </c>
+      <c r="AN150" s="19" t="n"/>
+      <c r="AO150" s="19" t="n"/>
+      <c r="AP150" s="19" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Karlson, B.; Cusack, C.; Bresnan, E. (eds.) — UNESCO/IOC</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Microscopic and Molecular Methods for Quantitative Phytoplankton Analysis (IOC Manuals and Guides No. 55)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>IOC Manuals and Guides, UNESCO</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>55</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>UNESCO/IOC</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Canonical manual for quantitative phytoplankton community analysis: sampling, microscopy/Utermöhl counts, and molecular (qPCR) methods. The standard route to the microorganism/plankton-community indicator.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Yes — documents sampling + enumeration/identification methods in replicable detail across microscopy and molecular approaches.</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Partial — net-tow/bottle sampling farmer-doable; microscopy enumeration/ID and qPCR need a taxonomist/partner lab.</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Plankton net/Niskin, settling chambers, inverted microscope; (qPCR for molecular)</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Year-long study (12 months)</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Utermöhl counts; community composition; molecular enumeration</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Yes — Open (UNESCO/IOC PDF)</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>https://unesdoc.unesco.org (IOC Manuals &amp; Guides 55, 2010)</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>HELCOM Phytoplankton Expert Group species lists and the AQUACOSM phytoplankton SOP give the practical sampling/ID workflow. eDNA metabarcoding (row 24) is the emerging molecular complement.</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W151" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>Water Quality</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>WQ 2.1.2 — Microorganisms</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>Plankton sampling</t>
+        </is>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK151" s="16" t="inlineStr">
+        <is>
+          <t>This canonical manual is the standard route to the phytoplankton/microorganism indicator. Collect water with a net or Niskin, settle sub-samples in chambers and count/identify phytoplankton by inverted microscope (Utermohl method), or use molecular (qPCR) enumeration for the community. Follow it for replicable community composition and abundance; HELCOM species lists and the AQUACOSM SOP give a practical workflow, and eDNA metabarcoding is the emerging molecular complement.</t>
+        </is>
+      </c>
+      <c r="AL151" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM151" s="18" t="inlineStr">
+        <is>
+          <t>karlson_2010</t>
+        </is>
+      </c>
+      <c r="AN151" s="19" t="n"/>
+      <c r="AO151" s="19" t="n"/>
+      <c r="AP151" s="19" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Practical Best Practices for Ocean Acidification Monitoring (the 'OA Cookbook') + GOA-ON in a Box kit</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>GOA-ON (PubPub)</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Global Ocean Acidification Observing Network</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Practitioner-level SOPs for coastal carbonate-system monitoring (pH via spectrophotometry / iSAMI sensor, total alkalinity, CO2SYS), built around the low-cost GOA-ON in a Box kit and explicitly aimed at low-resource teams. The practical route to the pH / ocean-acidification indicator.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Yes — step-by-step SOPs (site selection, sampling, sensor operation, spectrophotometric pH with m-cresol purple, reference-material QC, CO2SYS) to weather-quality targets.</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Partial — the in-a-Box kit lets a practitioner sample and measure pH; alkalinity titration, reference-material QC and CO2SYS still need training/partner support.</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>GOA-ON in a Box kit, CTD-Diver, iSAMI pH sensor, spectrophotometer, reagents</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Multi-season (3–9 months)</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Carbonate-system computation (CO2SYS); QA against reference materials</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Yes — Open (PubPub)</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>https://oceanacidificationcookbook.org</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Lowers the OA-monitoring barrier dramatically vs. research-grade SOPs (next row). The EPA 'Guidelines for Measuring Changes in Seawater pH... Eastern US' (Pimenta &amp; Grear 2018) and the SDG 14.3.1 indicator methodology are companion references. Also relevant to mollusc shell/carbonate contexts.</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W152" s="7" t="inlineStr">
+        <is>
+          <t>3 — Partnership</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>Climate Change</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>CC 2.1.1 — pH / ocean acidification</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>Carbonate chemistry</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK152" s="16" t="inlineStr">
+        <is>
+          <t>This practitioner-level protocol lowers the barrier to carbonate-system (pH / ocean-acidification) monitoring, built around the low-cost 'GOA-ON in a Box' kit for low-resource teams. Follow its step-by-step SOPs: site selection, water sampling, sensor operation, spectrophotometric pH with m-cresol purple (or an iSAMI sensor) and total alkalinity, then compute the carbonate system with CO2SYS, with quality control against certified reference materials to weather-quality targets. It is the practical route to the pH indicator (and relevant to mollusc shell/carbonate contexts); the research-grade Dickson guide is the analytical reference behind it.</t>
+        </is>
+      </c>
+      <c r="AL152" s="17" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="AM152" s="18" t="inlineStr">
+        <is>
+          <t>goaon_2024</t>
+        </is>
+      </c>
+      <c r="AN152" s="19" t="n"/>
+      <c r="AO152" s="19" t="n"/>
+      <c r="AP152" s="19" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Dickson, A.G.; Sabine, C.L.; Christian, J.R. (eds.); Riebesell, U.; et al.</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Guide to Best Practices for Ocean Acidification Research and Data Reporting (+ addendum)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>GOA-ON / EU / IOCCP</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Publications Office of the European Union</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>The authoritative research-grade SOPs for seawater carbonate-system measurement and OA experimental design/data reporting — the analytical reference underpinning the OA Cookbook.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Reference (authoritative SOP / usable design tool)</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Adequate as the analytical gold-standard reference: defines high-accuracy pH/DIC/TA/pCO2 methods and reporting; a research programme is built from it.</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>No — research-grade carbonate chemistry throughout (CRM-traceable, high-precision instrumentation).</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Research-grade spectrophotometry/coulometry, certified reference materials</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Not time-specific</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>High-accuracy carbonate-system SOPs; OA experimental design</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Yes — Open (PDF + addendum)</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>https://goa-on.org/resources/manuals.php</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>The reference standard for weather-quality OA data; pair with the practitioner-facing OA Cookbook (previous row) for field deployment. Tier T2 as a researcher-grade design tool.</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W153" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>Climate Change</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>CC 2.1.1 — pH / ocean acidification</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>Carbonate chemistry</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK153" s="16" t="inlineStr">
+        <is>
+          <t>This is the authoritative research-grade reference for seawater carbonate-system measurement and ocean-acidification experimental design and data reporting - the analytical gold standard (high-accuracy pH, DIC, total alkalinity, pCO2) underpinning the practitioner OA cookbook. Use it to build a weather-quality ocean-acidification programme or to anchor methods; pair it with the cookbook for low-cost field deployment.</t>
+        </is>
+      </c>
+      <c r="AL153" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM153" s="18" t="inlineStr">
+        <is>
+          <t>dickson_2010</t>
+        </is>
+      </c>
+      <c r="AN153" s="19" t="n"/>
+      <c r="AO153" s="19" t="n"/>
+      <c r="AP153" s="19" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Verra; Oceans 2050 (input)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Methodology Framework for Seaweed Carbon Projects (VCS M0172; incl. archived seaweed-aquaculture removals methodology)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Verra (Verified Carbon Standard)</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Verra</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Carbon-crediting methodology framework for seaweed projects (in development). Its cradle-to-grave project-emissions accounting (LCA) maps to seaweed CC 1.2.1 (GHG); its core carbon-removal/sequestration crediting falls OUTSIDE the MEL indicator set (the framework deliberately excludes seaweed carbon sequestration as too uncertain to account).</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Reference (carbon-accounting methodology framework)</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Adequate only for the GHG-accounting (LCA) component vis-à-vis MEL; the sequestration/removals crediting it primarily addresses has no MEL indicator home (Sub-rule 1b note).</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>No — project-level carbon MRV requires specialist accounting/verification.</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>LCA/MRV accounting (remote sensing, sampling, modelling)</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>One-time (no sampling — desk-based)</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Carbon-accounting methodology; net-removal computation</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Yes — Open (Verra methodology page)</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Abstract only</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>https://verra.org/methodologies/</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Included to flag a live grey-lit area (seaweed carbon MRV) that the MEL framework intentionally does NOT measure — only the cradle-to-grave GHG (CC 1.2.1) overlaps. The earlier standalone removals methodology was archived (June 2024); development moved into M0172. Tier T2.</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W154" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>Climate Change</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>CC 1.2.1 — Cradle-to-grave GHG emissions, Not in MEL framework</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>Modelling, Remote sensing</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK154" s="16" t="inlineStr">
+        <is>
+          <t>This is an in-development carbon-crediting methodology framework for seaweed projects. Only its cradle-to-grave project-emissions (life-cycle) accounting maps to the seaweed GHG indicator; its core carbon-removal/sequestration crediting sits deliberately outside the MEL indicator set (the framework itself excludes seaweed carbon sequestration). It is included to flag that live grey-literature area - MEL measures only the cradle-to-grave GHG overlap, not sequestration MRV.</t>
+        </is>
+      </c>
+      <c r="AL154" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM154" s="18" t="inlineStr">
+        <is>
+          <t>verra_2024</t>
+        </is>
+      </c>
+      <c r="AN154" s="19" t="n"/>
+      <c r="AO154" s="19" t="n"/>
+      <c r="AP154" s="19" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Pacific Northwest National Laboratory (PNNL)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Macroalgae mCDR: LCA, Carbon Sequestration/Permanence and MRV Methods Review (PNNL-33997)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PNNL Technical Report</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PNNL-33997</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>US DOE / Pacific Northwest National Laboratory</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Technical report reviewing LCA + monitoring/reporting/verification (MRV) methods for macroalgae carbon-dioxide removal (remote sensing, physical/sediment sampling, eDNA+coring for permanence, modelling, forensic carbon accounting). LCA/GHG-accounting maps to seaweed CC 1.2.1; the sequestration-permanence focus sits outside the MEL indicator set.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Reference (methods review / usable design tool)</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Adequate as an MRV methods inventory a programme is built from; not a single executable protocol. LCA component aligns to CC 1.2.1.</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>No — carbon MRV/LCA is specialist throughout.</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>LCA software, remote sensing, sediment coring, eDNA</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>One-time (no sampling — desk-based)</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>LCA; MRV method comparison</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Yes — Open (PNNL PDF)</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>https://www.pnnl.gov/main/publications/external/technical_reports/PNNL-33997.pdf</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Honest caveat across this literature: there are as yet no established MRV protocols for macroalgae carbon capture/permanence. The EDF 'Carbon Sequestration by Seaweed' report is a companion NGO context piece. Only the cradle-to-grave GHG (CC 1.2.1) overlaps MEL.</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W155" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>Climate Change</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>CC 1.2.1 — Cradle-to-grave GHG emissions, Not in MEL framework</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>Modelling, Remote sensing, eDNA</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK155" s="16" t="inlineStr">
+        <is>
+          <t>This technical report reviews life-cycle-assessment and monitoring/reporting/verification methods for macroalgae carbon-dioxide removal (remote sensing, sediment sampling, eDNA-plus-coring for permanence, modelling, forensic carbon accounting). Within MEL scope only the LCA/GHG-accounting component maps to the seaweed GHG indicator; the sequestration/permanence side has no MEL home. Its honest takeaway is that there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
+        </is>
+      </c>
+      <c r="AL155" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM155" s="18" t="inlineStr">
+        <is>
+          <t>pnnl_2023</t>
+        </is>
+      </c>
+      <c r="AN155" s="19" t="n"/>
+      <c r="AO155" s="19" t="n"/>
+      <c r="AP155" s="19" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ISO; BSI (PAS 2050)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Life-cycle assessment standards for cradle-to-grave GHG (ISO 14040 / ISO 14044; PAS 2050)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>ISO / BSI</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>International Organization for Standardization / BSI</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>The underlying standards for cradle-to-grave GHG/carbon-footprint accounting that operationalise the GHG-emissions indicator across all three sectors. Cradle-to-grave GHG = CC 1.1.1 (molluscs &amp; finfish) and CC 1.2.1 (seaweed).</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Reference (standards / usable design tool)</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Adequate as the methodological backbone for any aquaculture LCA/carbon-footprint; a footprint study is built from these standards (often with seafood-specific guidance).</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>No — LCA specialists.</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>LCA software + life-cycle inventory data</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Medium–High</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>One-time (no sampling — desk-based)</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Life-cycle inventory + impact assessment (GWP)</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>No — Paywalled (ISO; PAS 2050 via BSI)</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Title only (no abstract or DOI)</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>https://www.iso.org/standard/37456.html (ISO 14040)</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>General-knowledge entry (not a fetched source this session); included so the cradle-to-grave GHG indicator has a protocol home. Seafood-specific LCA guidance and ASC/MSC footprint work build on these. Note the dual numbering: cradle-to-grave GHG = CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W156" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk, Finfish</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>Climate Change</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>CC 1.1.1 — Cradle-to-grave GHG, CC 1.2.1 — Cradle-to-grave GHG emissions</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>Modelling</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK156" s="16" t="inlineStr">
+        <is>
+          <t>These are the underlying life-cycle-assessment standards (ISO 14040/14044, PAS 2050) that operationalise cradle-to-grave GHG / carbon-footprint accounting across all sectors. A footprint study is built from them - compile a life-cycle inventory and run impact assessment (global-warming potential) - typically with seafood-specific guidance layered on. Included so the GHG indicator has a methodological home; note the dual numbering (cradle-to-grave GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed). (Entry from general knowledge - consult the standards themselves for procedure.)</t>
+        </is>
+      </c>
+      <c r="AL156" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM156" s="18" t="inlineStr">
+        <is>
+          <t>iso_2021</t>
+        </is>
+      </c>
+      <c r="AN156" s="19" t="n"/>
+      <c r="AO156" s="19" t="n"/>
+      <c r="AP156" s="19" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Gold, Z.; Sprague, J.; Kushner, D.J.; et al.</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>A manager's guide to using eDNA metabarcoding in marine ecosystems</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PeerJ</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>e14071</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>PeerJ</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Practitioner-/manager-facing guide to designing eDNA metabarcoding monitoring programmes (primer selection, reference databases, decontamination, pilot variance, archiving). Cross-cutting biodiversity tool serving epibiota, mobile fauna, community composition, and plankton indicators.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Reference (usable design tool / manager guide)</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Adequate as a programme-design guide: five decision steps for a defensible eDNA monitoring programme; not itself a single bench protocol.</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>No — water sampling/filtration is simple, but the metabarcoding pipeline (extraction, PCR, sequencing, bioinformatics) is specialist throughout.</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Filtration kit; molecular lab (extraction, PCR, sequencing); bioinformatics</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Not time-specific</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Site-occupancy decontamination; metabarcoding bioinformatics</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Yes — Open (PeerJ, CC-BY)</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Abstract + Methods (fetched)</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>https://peerj.com/articles/14071/</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>A Springer protocol chapter ('Environmental DNA from Marine Waters and Substrates: Protocols for Sampling and eDNA Extraction') gives the bench SOP; formal ISO/CEN eDNA standardisation is still in progress. Pairs with MarineGEO Fouling/ARMS (cryptobiota) and IOC phytoplankton. The framework already cites Mercaldo-Allen 2021 (eDNA at oyster cages).</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Provided by Claude (grey/white-lit protocol search)</t>
+        </is>
+      </c>
+      <c r="W157" s="7" t="inlineStr">
+        <is>
+          <t>2 — Researcher</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Seaweed, Mollusk, Finfish</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity, Water Quality</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition, WQ 2.1.2 — Microorganisms</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>Cross-zone / global</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>Not species-specific</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>Not scale-specific</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>Not site-specific</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>Not specific</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Not algae-specific</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>Not depth-specific</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>Not exposure-specific</t>
+        </is>
+      </c>
+      <c r="AK157" s="16" t="inlineStr">
+        <is>
+          <t>This manager-facing guide helps design a defensible eDNA metabarcoding monitoring programme - primer selection, reference databases, decontamination, pilot variance and archiving - as a cross-cutting biodiversity tool (epibiota, mobile fauna, community composition, plankton). Use it to plan the programme; a Springer protocol chapter gives the bench sampling/extraction SOP, and formal ISO/CEN eDNA standardisation is still in progress. It pairs with the MarineGEO fouling/ARMS and IOC phytoplankton methods.</t>
+        </is>
+      </c>
+      <c r="AL157" s="17" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="AM157" s="18" t="inlineStr">
+        <is>
+          <t>gold_2022</t>
+        </is>
+      </c>
+      <c r="AN157" s="19" t="n"/>
+      <c r="AO157" s="19" t="n"/>
+      <c r="AP157" s="19" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="9">
@@ -25273,7 +31550,7 @@
     <row r="17">
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC 1.1.1 — Biomass replacement of emissions-intensive products</t>
+          <t>CC 1.1.1 — Cradle-to-grave GHG</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -25295,7 +31572,7 @@
     <row r="18">
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC 1.2.1 — Cradle-to-grave GHG emissions</t>
+          <t>CC 1.2.1 — Carbon cycling</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">

--- a/data/mel_database.xlsx
+++ b/data/mel_database.xlsx
@@ -1177,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP157"/>
+  <dimension ref="A1:AS157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1213,6 +1213,7 @@
     <col width="42" customWidth="1" min="40" max="40"/>
     <col width="42" customWidth="1" min="41" max="41"/>
     <col width="42" customWidth="1" min="42" max="42"/>
+    <col width="42" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1426,11 +1427,26 @@
           <t>Stats Workbook URL</t>
         </is>
       </c>
+      <c r="AQ1" s="12" t="inlineStr">
+        <is>
+          <t>Normalized Protocol Title</t>
+        </is>
+      </c>
+      <c r="AR1" s="12" t="inlineStr">
+        <is>
+          <t>Authors (full)</t>
+        </is>
+      </c>
+      <c r="AS1" s="12" t="inlineStr">
+        <is>
+          <t>Refinement Log</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="240" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrigan, Sophie; Brown, Andrew Ross; Ashton, Ian GC; Smale, Dan A; Tyler, Charles R; </t>
+          <t>Corrigan, S., et al.</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1517,11 +1533,7 @@
           <t>https://onlinelibrary.wiley.com/doi/10.1111/raq.12669 ; PDF: https://plymsea.ac.uk/id/eprint/9643/</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Cited directly in the MEL framework Tools &amp; Resources (p. 37). Best used to choose WHICH method to apply per indicator, then to chase the primary protocol papers it cites.</t>
-        </is>
-      </c>
+      <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -1615,11 +1627,26 @@
       <c r="AN2" s="19" t="n"/>
       <c r="AO2" s="19" t="n"/>
       <c r="AP2" s="19" t="n"/>
+      <c r="AQ2" s="16" t="inlineStr">
+        <is>
+          <t>Choosing Field Methods for Farm Habitat &amp; Biodiversity (Methods Review)</t>
+        </is>
+      </c>
+      <c r="AR2" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrigan, Sophie; Brown, Andrew Ross; Ashton, Ian GC; Smale, Dan A; Tyler, Charles R; </t>
+        </is>
+      </c>
+      <c r="AS2" s="16" t="inlineStr">
+        <is>
+          <t>Cited directly in the MEL framework Tools &amp; Resources (p. 37). Best used to choose WHICH method to apply per indicator, then to chase the primary protocol papers it cites.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="240" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diruit, Wendy; Le Bris, Anthony; Bajjouk, Touria; Richier, Sophie; Helias, Mathieu; Burel, Thomas; Lennon, Marc; Guyot, Alexandre; Ar Gall, Erwan; </t>
+          <t>Diruit, W., et al.</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1706,7 +1733,7 @@
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>About wild intertidal macroalgae, not farms — transferable for site context / baseline mapping rather than direct indicator measurement.</t>
+          <t>Developed on wild intertidal macroalgae, so use it for site/baseline mapping rather than direct farm-indicator measurement.</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
@@ -1802,11 +1829,26 @@
       <c r="AN3" s="19" t="n"/>
       <c r="AO3" s="19" t="n"/>
       <c r="AP3" s="19" t="n"/>
+      <c r="AQ3" s="16" t="inlineStr">
+        <is>
+          <t>Hyperspectral Mapping of Seaweed Canopy &amp; Community</t>
+        </is>
+      </c>
+      <c r="AR3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diruit, Wendy; Le Bris, Anthony; Bajjouk, Touria; Richier, Sophie; Helias, Mathieu; Burel, Thomas; Lennon, Marc; Guyot, Alexandre; Ar Gall, Erwan; </t>
+        </is>
+      </c>
+      <c r="AS3" s="16" t="inlineStr">
+        <is>
+          <t>About wild intertidal macroalgae, not farms — transferable for site context / baseline mapping rather than direct indicator measurement.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="240" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Campbell, Iona; Macleod, Adrian; Sahlmann, Christian; Neves, Luiza; Funderud, Jon; Øverland, Margareth; Hughes, Adam D; Stanley, Michele; </t>
+          <t>Campbell, I., et al.</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1889,11 +1931,7 @@
           <t>https://www.frontiersin.org/articles/10.3389/fmars.2019.00107</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>Companion-level scoping paper to Corrigan 2022. Use to identify which negative-impact dimensions a programme may need to monitor alongside the MEL ecosystem-service indicators.</t>
-        </is>
-      </c>
+      <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -1987,11 +2025,26 @@
       <c r="AN4" s="19" t="n"/>
       <c r="AO4" s="19" t="n"/>
       <c r="AP4" s="19" t="n"/>
+      <c r="AQ4" s="16" t="inlineStr">
+        <is>
+          <t>Ranking the Ecological Risks of Seaweed Farming (Scoping Reference)</t>
+        </is>
+      </c>
+      <c r="AR4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Campbell, Iona; Macleod, Adrian; Sahlmann, Christian; Neves, Luiza; Funderud, Jon; Øverland, Margareth; Hughes, Adam D; Stanley, Michele; </t>
+        </is>
+      </c>
+      <c r="AS4" s="16" t="inlineStr">
+        <is>
+          <t>Companion-level scoping paper to Corrigan 2022. Use to identify which negative-impact dimensions a programme may need to monitor alongside the MEL ecosystem-service indicators.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="240" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xing, Qianguo; An, Deyu; Zheng, Xiangyang; Wei, Zhenning; Wang, Xinhua; Li, Lin; Tian, Liqiao; Chen, Jun; </t>
+          <t>Xing, Q., et al.</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2076,7 +2129,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Negative-impact / hazard monitoring rather than benefit monitoring. Best framed as supporting "farm area mapping" inputs rather than a benefit indicator protocol.</t>
+          <t>This is hazard/area mapping, not a benefit indicator - use it to delineate farm extent.</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -2172,11 +2225,26 @@
       <c r="AN5" s="19" t="n"/>
       <c r="AO5" s="19" t="n"/>
       <c r="AP5" s="19" t="n"/>
+      <c r="AQ5" s="16" t="inlineStr">
+        <is>
+          <t>Satellite Mapping of Farm Footprint &amp; Nearby Blooms</t>
+        </is>
+      </c>
+      <c r="AR5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xing, Qianguo; An, Deyu; Zheng, Xiangyang; Wei, Zhenning; Wang, Xinhua; Li, Lin; Tian, Liqiao; Chen, Jun; </t>
+        </is>
+      </c>
+      <c r="AS5" s="16" t="inlineStr">
+        <is>
+          <t>Negative-impact / hazard monitoring rather than benefit monitoring. Best framed as supporting "farm area mapping" inputs rather than a benefit indicator protocol.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="240" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schutt, Emilly; Francolini, Rene; Price, Nichole; Olson, Zachary; Byron, Carrie J; </t>
+          <t>Schutt, E., et al.</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2261,7 +2329,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>Cited in MEL Table 1 (p. 16). Useful temperate counter-example — farms in this study did NOT enhance biodiversity, highlighting Archetype-dependence. Kitchen-scrubber-sponge collector design is exceptionally practical for farmers.</t>
+          <t>A useful counter-example: these farms did NOT enhance biodiversity, so results are archetype-dependent. The scrubber-sponge collector design is very practical.</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -2357,11 +2425,26 @@
       <c r="AN6" s="19" t="n"/>
       <c r="AO6" s="19" t="n"/>
       <c r="AP6" s="19" t="n"/>
+      <c r="AQ6" s="16" t="inlineStr">
+        <is>
+          <t>Kelp-Farm vs Reference Biodiversity Comparison (Low-Cost Collectors)</t>
+        </is>
+      </c>
+      <c r="AR6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schutt, Emilly; Francolini, Rene; Price, Nichole; Olson, Zachary; Byron, Carrie J; </t>
+        </is>
+      </c>
+      <c r="AS6" s="16" t="inlineStr">
+        <is>
+          <t>Cited in MEL Table 1 (p. 16). Useful temperate counter-example — farms in this study did NOT enhance biodiversity, highlighting Archetype-dependence. Kitchen-scrubber-sponge collector design is exceptionally practical for farmers.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="240" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Powers, Monica J; Peterson, Charles H; Summerson, Henry C; Powers, Sean P; </t>
+          <t>Powers, M. J., et al.</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2449,7 +2532,7 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>Bivalve aquaculture study, not seaweed — but the methods (paired farm/seagrass/sandflat comparisons) are directly applicable to seaweed Archetype 3 sampling per MEL Figure 3.</t>
+          <t>From a bivalve-netting study, but the paired farm/seagrass/bare-sediment design transfers directly to seaweed.</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
@@ -2545,11 +2628,26 @@
       <c r="AN7" s="19" t="n"/>
       <c r="AO7" s="19" t="n"/>
       <c r="AP7" s="19" t="n"/>
+      <c r="AQ7" s="16" t="inlineStr">
+        <is>
+          <t>Farm Structure as Habitat: Paired Farm/Seagrass/Sandflat Survey</t>
+        </is>
+      </c>
+      <c r="AR7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Powers, Monica J; Peterson, Charles H; Summerson, Henry C; Powers, Sean P; </t>
+        </is>
+      </c>
+      <c r="AS7" s="16" t="inlineStr">
+        <is>
+          <t>Bivalve aquaculture study, not seaweed — but the methods (paired farm/seagrass/sandflat comparisons) are directly applicable to seaweed Archetype 3 sampling per MEL Figure 3.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="240" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Berger, Christian; Papazova, Polina; Marshall, Beth; Evans, Fergus; Williams, Craig; </t>
+          <t>Berger, C., et al.</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2632,121 +2730,136 @@
           <t>https://www.biorxiv.org/content/10.1101/2024.02.15.580450v1</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
+      <c r="U8" s="16" t="inlineStr">
+        <is>
+          <t>BRUV results are conservative in turbid water (classify footage; use only clear frames), the bait biases detection toward generalist carnivores and under-detects cryptic and juvenile flatfish, and Nmax can be inflated by species that linger at the bait. Acoustic monitoring gives relative presence, not abundance, and a single detector covers a small area (patterns can differ within ~1 km), so deploy several for larger sites; boat traffic can confound diurnal patterns. Given the short timeframe and small farm scale, treat the results as a baseline rather than a conclusive link between farming and biodiversity. Detailed sub-methods are defined by cited sources (Unsworth 2014 for BRUV/Nmax; the detector's own software).</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Original list</t>
+        </is>
+      </c>
+      <c r="W8" s="10" t="inlineStr">
+        <is>
+          <t>4 — Practitioner</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>Habitat &amp; Biodiversity</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Temperate Atlantic</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Saccharina (sugar kelp)</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Longline (surface)</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>Medium (1–20 ha)</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Variable / seasonal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>Monoculture</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>BRUVs / video, Visual survey, Acoustic</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>Coastal (10–30 m)</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr">
+        <is>
+          <t>Exposed</t>
+        </is>
+      </c>
+      <c r="AK8" s="16" t="inlineStr">
+        <is>
+          <t>To document what lives on and around your farm — organisms growing on the lines and mobile animals drawn to the site — run three surveys in parallel and repeat them monthly through the growing season. For attached life (epibionts), pull a set length of header/cultivation line (e.g. 0.5 m sections) onto the boat at two spots along each longline, cut the growth off near the line, and back on land estimate the cover and identity of the organisms on the rope and on the kelp. For mobile fauna, deploy a baited underwater video camera (BRUV) on the seabed near the farm for about an hour per drop, scoring the peak number of each fish type visible at once (Nmax) and analysing only footage clear enough to identify animals. For marine mammals, moor a self-logging acoustic click-detector for continuous multi-week periods and export detection-positive minutes per day for each species. Compare these measures across sites and seasons; temperature, light, current and pH/salinity sensors can be logged alongside for context.</t>
+        </is>
+      </c>
+      <c r="AL8" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM8" s="18" t="inlineStr">
+        <is>
+          <t>berger_2024</t>
+        </is>
+      </c>
+      <c r="AN8" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/templates/berger_2024.pdf</t>
+        </is>
+      </c>
+      <c r="AO8" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/datasheets/berger_2024.pdf</t>
+        </is>
+      </c>
+      <c r="AP8" s="19" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/workbooks/berger_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="AQ8" s="16" t="inlineStr">
+        <is>
+          <t>Integrated Biodiversity Monitoring on a Seaweed Farm</t>
+        </is>
+      </c>
+      <c r="AR8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Berger, Christian; Papazova, Polina; Marshall, Beth; Evans, Fergus; Williams, Craig; </t>
+        </is>
+      </c>
+      <c r="AS8" s="16" t="inlineStr">
         <is>
           <t>One of the most practitioner-oriented monitoring designs in the seaweed literature. Notably did not use eDNA in this site due to sediment-poor, high-current conditions — useful framing of when eDNA isn't the answer.</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>Original list</t>
-        </is>
-      </c>
-      <c r="W8" s="10" t="inlineStr">
-        <is>
-          <t>4 — Practitioner</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>Seaweed</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>Habitat &amp; Biodiversity</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 1.2.1 — Mobile fauna, H&amp;B 2.1.1 — Community composition</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>Temperate Atlantic</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>Saccharina (sugar kelp)</t>
-        </is>
-      </c>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>Longline (surface)</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>Medium (1–20 ha)</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr">
-        <is>
-          <t>Variable / seasonal</t>
-        </is>
-      </c>
-      <c r="AF8" s="3" t="inlineStr">
-        <is>
-          <t>Monoculture</t>
-        </is>
-      </c>
-      <c r="AG8" s="3" t="inlineStr">
-        <is>
-          <t>BRUVs / video, Visual survey, Acoustic</t>
-        </is>
-      </c>
-      <c r="AH8" s="3" t="inlineStr">
-        <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="AI8" s="3" t="inlineStr">
-        <is>
-          <t>Coastal (10–30 m)</t>
-        </is>
-      </c>
-      <c r="AJ8" s="3" t="inlineStr">
-        <is>
-          <t>Exposed</t>
-        </is>
-      </c>
-      <c r="AK8" s="16" t="inlineStr">
-        <is>
-          <t>To document what lives on and around your farm — organisms growing on the lines and mobile animals drawn to the site — run three surveys in parallel and repeat them monthly through the growing season. For attached life (epibionts), pull a set length of header/cultivation line (e.g. 0.5 m sections) onto the boat at two spots along each longline, cut the growth off near the line, and back on land estimate the cover and identity of the organisms on the rope and on the kelp. For mobile fauna, deploy a baited underwater video camera (BRUV) on the seabed near the farm for about an hour per drop, scoring the peak number of each fish type visible at once (MaxN) and analysing only footage clear enough to identify animals. For marine mammals, moor a self-logging acoustic click-detector for continuous multi-week periods and export detection-positive minutes per day for each species. Compare these measures across sites and seasons; temperature, light, current and pH/salinity sensors can be logged alongside for context.</t>
-        </is>
-      </c>
-      <c r="AL8" s="17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AM8" s="18" t="inlineStr">
-        <is>
-          <t>berger_2024</t>
-        </is>
-      </c>
-      <c r="AN8" s="19" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/templates/berger_2024.pdf</t>
-        </is>
-      </c>
-      <c r="AO8" s="19" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/datasheets/berger_2024.pdf</t>
-        </is>
-      </c>
-      <c r="AP8" s="19" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/workbooks/berger_2024.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9" ht="240" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martínez‐Curci, Natalia S; Fierro, Pablo; Navedo, Juan G; </t>
+          <t>Martínez‐Curci, N. S., et al.</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2835,7 +2948,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>Important Southern Hemisphere mudflat study — adds nuance to the framework by showing that "more benthic biomass" can have mixed shorebird-population consequences (favoured tactile foragers over visual ones).</t>
+          <t>Shows 'more benthic biomass' can have mixed consequences - it favoured some shorebird foragers over others, so interpret benthic gains carefully.</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
@@ -2931,11 +3044,26 @@
       <c r="AN9" s="19" t="n"/>
       <c r="AO9" s="19" t="n"/>
       <c r="AP9" s="19" t="n"/>
+      <c r="AQ9" s="16" t="inlineStr">
+        <is>
+          <t>Does Seaweed Cultivation Change Benthic Communities &amp; Shorebird Prey?</t>
+        </is>
+      </c>
+      <c r="AR9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Martínez‐Curci, Natalia S; Fierro, Pablo; Navedo, Juan G; </t>
+        </is>
+      </c>
+      <c r="AS9" s="16" t="inlineStr">
+        <is>
+          <t>Important Southern Hemisphere mudflat study — adds nuance to the framework by showing that "more benthic biomass" can have mixed shorebird-population consequences (favoured tactile foragers over visual ones).</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="240" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andrews, Adam Jon; Christie, Hartvig; Præbel, Kim; Brandner, Melissa; Torstensen, Ragnhild Grimm; Lewis, Larisa; Hestness, Ragnhild Beck; Berg, Paul Ragnar; Bekkby, Trine; Hancke, Kasper; </t>
+          <t>Andrews, A. J., et al.</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -3018,11 +3146,7 @@
           <t>https://www.frontiersin.org/journals/marine-science/articles/10.3389/fmars.2025.1717725/full</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>Most recent multi-method temperate-Atlantic kelp study; alongside Schutt 2023 and Bekkby 2023, completes a strong methodological triad for European/Atlantic farms.</t>
-        </is>
-      </c>
+      <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -3116,11 +3240,26 @@
       <c r="AN10" s="19" t="n"/>
       <c r="AO10" s="19" t="n"/>
       <c r="AP10" s="19" t="n"/>
+      <c r="AQ10" s="16" t="inlineStr">
+        <is>
+          <t>Multi-Method (eDNA + Traditional) Kelp-Farm Biodiversity Survey</t>
+        </is>
+      </c>
+      <c r="AR10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andrews, Adam Jon; Christie, Hartvig; Præbel, Kim; Brandner, Melissa; Torstensen, Ragnhild Grimm; Lewis, Larisa; Hestness, Ragnhild Beck; Berg, Paul Ragnar; Bekkby, Trine; Hancke, Kasper; </t>
+        </is>
+      </c>
+      <c r="AS10" s="16" t="inlineStr">
+        <is>
+          <t>Most recent multi-method temperate-Atlantic kelp study; alongside Schutt 2023 and Bekkby 2023, completes a strong methodological triad for European/Atlantic farms.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="240" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">English, Greg; Lawrence, Michael J; McKindsey, Christopher W; Lacoursière‐Roussel, Anaïs; Bergeron, Hannah; Gauthier, Stéphane; Wringe, Brendan F; Trudel, Marc; </t>
+          <t>English, G., et al.</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -3212,11 +3351,7 @@
           <t>Paywall: https://onlinelibrary.wiley.com/doi/10.1111/raq.12781</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>Companion review to Corrigan 2022 but broader (includes shellfish and finfish). Useful in tandem when scoping which monitoring methods fit a particular aquaculture context. | v15 Rule 12 cross-database refinement (bivalve CSV): Confirmed methodological-review paper covering shellfish + finfish aquaculture; retained as X = Not specific because the review is genuinely multi-aquaculture-type. Bivalve relevance: shellfish-monitoring methods (camera, eDNA, sediment) are a major focus.</t>
-        </is>
-      </c>
+      <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -3310,11 +3445,26 @@
       <c r="AN11" s="19" t="n"/>
       <c r="AO11" s="19" t="n"/>
       <c r="AP11" s="19" t="n"/>
+      <c r="AQ11" s="16" t="inlineStr">
+        <is>
+          <t>Monitoring Methods for Fish &amp; Fauna at Aquaculture Sites (Review)</t>
+        </is>
+      </c>
+      <c r="AR11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English, Greg; Lawrence, Michael J; McKindsey, Christopher W; Lacoursière‐Roussel, Anaïs; Bergeron, Hannah; Gauthier, Stéphane; Wringe, Brendan F; Trudel, Marc; </t>
+        </is>
+      </c>
+      <c r="AS11" s="16" t="inlineStr">
+        <is>
+          <t>Companion review to Corrigan 2022 but broader (includes shellfish and finfish). Useful in tandem when scoping which monitoring methods fit a particular aquaculture context. | v15 Rule 12 cross-database refinement (bivalve CSV): Confirmed methodological-review paper covering shellfish + finfish aquaculture; retained as X = Not specific because the review is genuinely multi-aquaculture-type. Bivalve relevance: shellfish-monitoring methods (camera, eDNA, sediment) are a major focus.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="240" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrigan, Sophie; Smale, Dan A; Tyler, Charles R; Daniels, Carly L; Brown, Andrew; </t>
+          <t>Corrigan, S., et al.</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -3391,7 +3541,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>Complements Visch 2020 (Saccharina-only Sweden) by showing minimal benthic effect at a co-culture (lobster + mussel + kelp) UK farm after 2 seasons. Useful Archetype 1 baseline-design template.</t>
+          <t>A useful baseline template showing minimal benthic effect at a co-culture farm after two seasons.</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -3487,11 +3637,26 @@
       <c r="AN12" s="19" t="n"/>
       <c r="AO12" s="19" t="n"/>
       <c r="AP12" s="19" t="n"/>
+      <c r="AQ12" s="16" t="inlineStr">
+        <is>
+          <t>Seabed Community Effects of Seaweed &amp; Shellfish Co-Culture</t>
+        </is>
+      </c>
+      <c r="AR12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrigan, Sophie; Smale, Dan A; Tyler, Charles R; Daniels, Carly L; Brown, Andrew; </t>
+        </is>
+      </c>
+      <c r="AS12" s="16" t="inlineStr">
+        <is>
+          <t>Complements Visch 2020 (Saccharina-only Sweden) by showing minimal benthic effect at a co-culture (lobster + mussel + kelp) UK farm after 2 seasons. Useful Archetype 1 baseline-design template.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="240" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bennion, Matthew; Fisher, Jessica; Yesson, Chris; Brodie, Juliet; </t>
+          <t>Bennion, M., et al.</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3580,7 +3745,7 @@
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>Wild-harvest monitoring orientation. Useful as background for any farm-vs-wild Archetype 3 comparison where wild kelp coverage needs to be mapped.</t>
+          <t>Oriented to wild-kelp mapping - handy for farm-vs-wild comparisons where you need to map wild kelp cover.</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
@@ -3676,11 +3841,26 @@
       <c r="AN13" s="19" t="n"/>
       <c r="AO13" s="19" t="n"/>
       <c r="AP13" s="19" t="n"/>
+      <c r="AQ13" s="16" t="inlineStr">
+        <is>
+          <t>Remote-Sensing Tools for Mapping Kelp (Review)</t>
+        </is>
+      </c>
+      <c r="AR13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bennion, Matthew; Fisher, Jessica; Yesson, Chris; Brodie, Juliet; </t>
+        </is>
+      </c>
+      <c r="AS13" s="16" t="inlineStr">
+        <is>
+          <t>Wild-harvest monitoring orientation. Useful as background for any farm-vs-wild Archetype 3 comparison where wild kelp coverage needs to be mapped.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="240" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tano, Stina; Eggertsen, Maria; Wikström, Sofia A; Berkström, Charlotte; Buriyo, AS; Halling, Christina; </t>
+          <t>Tano, S., et al.</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3765,7 +3945,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>About natural seaweed beds, not farms — provides a reference baseline that a tropical farm could use as its wild comparator for Archetype 4 sampling.</t>
+          <t>From natural seaweed beds - use as a wild comparator baseline for a tropical farm.</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
@@ -3861,11 +4041,26 @@
       <c r="AN14" s="19" t="n"/>
       <c r="AO14" s="19" t="n"/>
       <c r="AP14" s="19" t="n"/>
+      <c r="AQ14" s="16" t="inlineStr">
+        <is>
+          <t>Measuring Mobile Epifauna in Tropical Seaweed Beds</t>
+        </is>
+      </c>
+      <c r="AR14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tano, Stina; Eggertsen, Maria; Wikström, Sofia A; Berkström, Charlotte; Buriyo, AS; Halling, Christina; </t>
+        </is>
+      </c>
+      <c r="AS14" s="16" t="inlineStr">
+        <is>
+          <t>About natural seaweed beds, not farms — provides a reference baseline that a tropical farm could use as its wild comparator for Archetype 4 sampling.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="240" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bernard, MS; Tonk, L; de Groot, GA; Glorius, S; Jansen, HM; </t>
+          <t>Bernard, M., et al.</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3940,11 +4135,7 @@
           <t>https://research.wur.nl/en/publications/biodiversity-monitoring-in-seaweed-farms-by-dna-metabarcoding-usi ; DOI 10.18174/496237</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>Sister report to Tonk et al. 2021 (Row 56). Together they form the Wageningen "framework + protocol" pairing for European seaweed monitoring.</t>
-        </is>
-      </c>
+      <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -4038,11 +4229,26 @@
       <c r="AN15" s="19" t="n"/>
       <c r="AO15" s="19" t="n"/>
       <c r="AP15" s="19" t="n"/>
+      <c r="AQ15" s="16" t="inlineStr">
+        <is>
+          <t>DNA-Metabarcoding Biodiversity Monitoring on Seaweed Farms</t>
+        </is>
+      </c>
+      <c r="AR15" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernard, MS; Tonk, L; de Groot, GA; Glorius, S; Jansen, HM; </t>
+        </is>
+      </c>
+      <c r="AS15" s="16" t="inlineStr">
+        <is>
+          <t>Sister report to Tonk et al. 2021 (Row 56). Together they form the Wageningen "framework + protocol" pairing for European seaweed monitoring.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="240" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAWEEDS, OF; </t>
+          <t>SEAWEEDS, O.</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -4111,11 +4317,7 @@
           <t>Full PDF provided by user (Chopin 1997, Marine Biodiversity Monitoring Committee report to EMAN/Environment Canada)</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>Foundational Canadian government-monitoring protocol by Thierry Chopin (UNB Centre for Coastal Studies and Aquaculture). Specifically discusses seaweeds as biomonitors of aquaculture nutrient loading and integrated aquaculture systems (pp. 16–17). Methodologically well-aligned with the MEL framework approach; the document is a strong template for community-based seaweed monitoring even though it predates the framework itself. Recommends pilot studies before full implementation, 0.25 m² quadrat as default, and stratified random sampling for patchy communities.</t>
-        </is>
-      </c>
+      <c r="U16" s="3" t="inlineStr"/>
       <c r="V16" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -4209,11 +4411,26 @@
       <c r="AN16" s="19" t="n"/>
       <c r="AO16" s="19" t="n"/>
       <c r="AP16" s="19" t="n"/>
+      <c r="AQ16" s="16" t="inlineStr">
+        <is>
+          <t>Community-Based Shore &amp; Benthic Macrophyte Monitoring</t>
+        </is>
+      </c>
+      <c r="AR16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEAWEEDS, OF; </t>
+        </is>
+      </c>
+      <c r="AS16" s="16" t="inlineStr">
+        <is>
+          <t>Foundational Canadian government-monitoring protocol by Thierry Chopin (UNB Centre for Coastal Studies and Aquaculture). Specifically discusses seaweeds as biomonitors of aquaculture nutrient loading and integrated aquaculture systems (pp. 16–17). Methodologically well-aligned with the MEL framework approach; the document is a strong template for community-based seaweed monitoring even though it predates the framework itself. Recommends pilot studies before full implementation, 0.25 m² quadrat as default, and stratified random sampling for patchy communities.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="240" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hehre, E James; Meeuwig, JJ; </t>
+          <t>Hehre, E. J. &amp; Meeuwig, J.</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -4302,7 +4519,7 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>Important tropical counter-finding: seaweed farms reduced rather than enhanced fish diversity, especially near MPAs. Worth pairing with Hehre 2016 (PLoS ONE follow-up on siganid catch) for a fuller picture.</t>
+          <t>Counter-finding: these farms reduced rather than raised fish diversity, especially near marine protected areas - a caution for siting.</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
@@ -4398,11 +4615,26 @@
       <c r="AN17" s="19" t="n"/>
       <c r="AO17" s="19" t="n"/>
       <c r="AP17" s="19" t="n"/>
+      <c r="AQ17" s="16" t="inlineStr">
+        <is>
+          <t>Fish-Assemblage Response to a Seaweed Farm (Visual Census)</t>
+        </is>
+      </c>
+      <c r="AR17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hehre, E James; Meeuwig, JJ; </t>
+        </is>
+      </c>
+      <c r="AS17" s="16" t="inlineStr">
+        <is>
+          <t>Important tropical counter-finding: seaweed farms reduced rather than enhanced fish diversity, especially near MPAs. Worth pairing with Hehre 2016 (PLoS ONE follow-up on siganid catch) for a fuller picture.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="240" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anyango, James Ochieng; Mlewa, Chrisestom Mwatete; Mwaluma, James; </t>
+          <t>Anyango, J. O., et al.</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4485,11 +4717,7 @@
           <t>https://www.fisheriesjournal.com/archives/?year=2017&amp;vol=5&amp;issue=3&amp;part=F&amp;ArticleId=1253</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>Tropical (East African) counterpart to Hehre 2015. Cited in Schutt 2023 and Theuerkauf 2022 as one of the foundational positive-effect studies in tropical seaweed-farm habitat literature.</t>
-        </is>
-      </c>
+      <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -4583,11 +4811,26 @@
       <c r="AN18" s="19" t="n"/>
       <c r="AO18" s="19" t="n"/>
       <c r="AP18" s="19" t="n"/>
+      <c r="AQ18" s="16" t="inlineStr">
+        <is>
+          <t>Wild-Fish Abundance &amp; Diversity Around Seaweed Farms</t>
+        </is>
+      </c>
+      <c r="AR18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anyango, James Ochieng; Mlewa, Chrisestom Mwatete; Mwaluma, James; </t>
+        </is>
+      </c>
+      <c r="AS18" s="16" t="inlineStr">
+        <is>
+          <t>Tropical (East African) counterpart to Hehre 2015. Cited in Schutt 2023 and Theuerkauf 2022 as one of the foundational positive-effect studies in tropical seaweed-farm habitat literature.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="240" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bergman, Kajsa C; Svensson, Sara; Öhman, Marcus C; </t>
+          <t>Bergman, K. C., et al.</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4674,11 +4917,7 @@
           <t>Paywall: https://pubmed.ncbi.nlm.nih.gov/11827126/</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t>Older foundational tropical study; provides the comparative-lagoon design template that several subsequent papers (Anyango 2017, Hehre 2015) build on.</t>
-        </is>
-      </c>
+      <c r="U19" s="3" t="inlineStr"/>
       <c r="V19" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -4772,11 +5011,26 @@
       <c r="AN19" s="19" t="n"/>
       <c r="AO19" s="19" t="n"/>
       <c r="AP19" s="19" t="n"/>
+      <c r="AQ19" s="16" t="inlineStr">
+        <is>
+          <t>Fish-Assemblage Effects of Algal Farming (Lagoon Census)</t>
+        </is>
+      </c>
+      <c r="AR19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bergman, Kajsa C; Svensson, Sara; Öhman, Marcus C; </t>
+        </is>
+      </c>
+      <c r="AS19" s="16" t="inlineStr">
+        <is>
+          <t>Older foundational tropical study; provides the comparative-lagoon design template that several subsequent papers (Anyango 2017, Hehre 2015) build on.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="240" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Underwood, Lucy H; Jeffs, Andrew G; </t>
+          <t>Underwood, L. H. &amp; Jeffs, A. G.</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4857,11 +5111,7 @@
           <t>https://doi.org/10.3354/aei00454 ; PDF: https://www.int-res.com/articles/aei2023/15/q015p085.pdf</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t>New Zealand study at Esk Point, Coromandel — first quantitative comparison of fish settlement and recruitment in mussel-kelp co-culture vs mussel monoculture vs adjacent natural habitats (rocky reef, soft-sediment seafloor). Methods are directly transferable to seaweed-only aquaculture for fish recruitment monitoring. Companion paper Underwood, van der Reis &amp; Jeffs (2023) examines snapper diet in mussel farms (already at Row 22 in some database versions).</t>
-        </is>
-      </c>
+      <c r="U20" s="3" t="inlineStr"/>
       <c r="V20" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -4955,11 +5205,26 @@
       <c r="AN20" s="19" t="n"/>
       <c r="AO20" s="19" t="n"/>
       <c r="AP20" s="19" t="n"/>
+      <c r="AQ20" s="16" t="inlineStr">
+        <is>
+          <t>Fish Settlement &amp; Recruitment in Mussel Farms</t>
+        </is>
+      </c>
+      <c r="AR20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Underwood, Lucy H; Jeffs, Andrew G; </t>
+        </is>
+      </c>
+      <c r="AS20" s="16" t="inlineStr">
+        <is>
+          <t>New Zealand study at Esk Point, Coromandel — first quantitative comparison of fish settlement and recruitment in mussel-kelp co-culture vs mussel monoculture vs adjacent natural habitats (rocky reef, soft-sediment seafloor). Methods are directly transferable to seaweed-only aquaculture for fish recruitment monitoring. Companion paper Underwood, van der Reis &amp; Jeffs (2023) examines snapper diet in mussel farms (already at Row 22 in some database versions).</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="240" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrigan, Sophie; Smale, Dan A; Tyler, Charles R; Brown, A Ross; </t>
+          <t>Corrigan, S., et al.</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -5040,11 +5305,7 @@
           <t>https://doi.org/10.3354/aei00478</t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t>Reference paper providing citation guidance for finfish monitoring methods at integrated mussel and seaweed farms. Practitioners can follow citations within to identify potentially applicable primary protocols. Open access at Aquaculture Environment Interactions.</t>
-        </is>
-      </c>
+      <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -5138,11 +5399,26 @@
       <c r="AN21" s="19" t="n"/>
       <c r="AO21" s="19" t="n"/>
       <c r="AP21" s="19" t="n"/>
+      <c r="AQ21" s="16" t="inlineStr">
+        <is>
+          <t>Finfish-Assemblage Monitoring at Mussel/Seaweed Farms (Reference)</t>
+        </is>
+      </c>
+      <c r="AR21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrigan, Sophie; Smale, Dan A; Tyler, Charles R; Brown, A Ross; </t>
+        </is>
+      </c>
+      <c r="AS21" s="16" t="inlineStr">
+        <is>
+          <t>Reference paper providing citation guidance for finfish monitoring methods at integrated mussel and seaweed farms. Practitioners can follow citations within to identify potentially applicable primary protocols. Open access at Aquaculture Environment Interactions.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="240" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Theuerkauf, Seth J; Barrett, Luke T; Alleway, Heidi K; Costa‐Pierce, Barry A; St. Gelais, Adam; Jones, Robert C; </t>
+          <t>Theuerkauf, S. J., et al.</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5234,11 +5510,7 @@
           <t>https://onlinelibrary.wiley.com/doi/10.1111/raq.12584 ; TNC summary: https://www.aquaculturescience.org/habitat-value-of-shellfish-and-seaweed-aquaculture/</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t>Major TNC-co-authored review — explicitly cited in the MEL framework. Use to size expected effects and to identify gear/species/typology combinations that maximise habitat value.</t>
-        </is>
-      </c>
+      <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -5332,11 +5604,26 @@
       <c r="AN22" s="19" t="n"/>
       <c r="AO22" s="19" t="n"/>
       <c r="AP22" s="19" t="n"/>
+      <c r="AQ22" s="16" t="inlineStr">
+        <is>
+          <t>Habitat Value of Shellfish &amp; Seaweed Aquaculture (Meta-Analysis)</t>
+        </is>
+      </c>
+      <c r="AR22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theuerkauf, Seth J; Barrett, Luke T; Alleway, Heidi K; Costa‐Pierce, Barry A; St. Gelais, Adam; Jones, Robert C; </t>
+        </is>
+      </c>
+      <c r="AS22" s="16" t="inlineStr">
+        <is>
+          <t>Major TNC-co-authored review — explicitly cited in the MEL framework. Use to size expected effects and to identify gear/species/typology combinations that maximise habitat value.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="240" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eklöf, Johan S; de la Torre-Castro, Maricela; Nilsson, Camilla; Rönnbäck, Patrik; </t>
+          <t>Eklöf, J. S., et al.</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5425,7 +5712,7 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>Strong tropical artisanal-fishery design — particularly suitable as a model for community-based monitoring at Zanzibar / Tanzania / Kenya farms.</t>
+          <t>A good model for community-based catch monitoring at tropical artisanal farms.</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -5521,11 +5808,26 @@
       <c r="AN23" s="19" t="n"/>
       <c r="AO23" s="19" t="n"/>
       <c r="AP23" s="19" t="n"/>
+      <c r="AQ23" s="16" t="inlineStr">
+        <is>
+          <t>How a Seaweed Farm Affects Local Fishery Catches</t>
+        </is>
+      </c>
+      <c r="AR23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eklöf, Johan S; de la Torre-Castro, Maricela; Nilsson, Camilla; Rönnbäck, Patrik; </t>
+        </is>
+      </c>
+      <c r="AS23" s="16" t="inlineStr">
+        <is>
+          <t>Strong tropical artisanal-fishery design — particularly suitable as a model for community-based monitoring at Zanzibar / Tanzania / Kenya farms.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="240" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abhilash, KR; Sankar, R; Purvaja, R; Deepak, Samuel V; Sreeraj, CR; Krishnan, P; Sekar, V; Biswas, Amit K; Kumarapandiyan, G; Ramesh, R; </t>
+          <t>Abhilash, K., et al.</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5614,7 +5916,7 @@
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>Long-time-series (decadal) tropical Kappaphycus farming case study with a clear null finding (no significant farm-vs-control variation). Particularly useful as a template for tropical farms where the question is whether established commercial-scale farming is altering background hydrography against monsoonal noise. [Caveat re Chl-a]: This paper defers to Grasshoff et al. 1999 (Methods of Seawater Analysis) for chlorophyll-a procedure without specifying it. If you want to measure Chl-a using this paper's framing, use it alongside Grasshoff et al. 1999.</t>
+          <t>A decadal case study with a null result (no farm-vs-control difference) - a useful template for the 'is established farming changing water quality?' question.</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
@@ -5710,11 +6012,26 @@
       <c r="AN24" s="19" t="n"/>
       <c r="AO24" s="19" t="n"/>
       <c r="AP24" s="19" t="n"/>
+      <c r="AQ24" s="16" t="inlineStr">
+        <is>
+          <t>Long-Term Water-Quality Monitoring at a Seaweed Farm</t>
+        </is>
+      </c>
+      <c r="AR24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abhilash, KR; Sankar, R; Purvaja, R; Deepak, Samuel V; Sreeraj, CR; Krishnan, P; Sekar, V; Biswas, Amit K; Kumarapandiyan, G; Ramesh, R; </t>
+        </is>
+      </c>
+      <c r="AS24" s="16" t="inlineStr">
+        <is>
+          <t>Long-time-series (decadal) tropical Kappaphycus farming case study with a clear null finding (no significant farm-vs-control variation). Particularly useful as a template for tropical farms where the question is whether established commercial-scale farming is altering background hydrography against monsoonal noise. [Caveat re Chl-a]: This paper defers to Grasshoff et al. 1999 (Methods of Seawater Analysis) for chlorophyll-a procedure without specifying it. If you want to measure Chl-a using this paper's framing, use it alongside Grasshoff et al. 1999.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="240" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhu, Yaojia; Wang, Zhiyin; Song, Li; Gu, Jiali; Ye, Zhanjiang; Jin, Runjie; Wu, Jiaping; </t>
+          <t>Zhu, Y., et al.</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5797,11 +6114,7 @@
           <t>https://doi.org/10.1016/j.scitotenv.2023.165305</t>
         </is>
       </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t>One of several Chinese seaweed-farm water-quality studies in the original list. Together with Rows 26, 32, 33, 34 forms a Chinese-context cluster useful for IMTA / nutrient cycling indicators.</t>
-        </is>
-      </c>
+      <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -5895,11 +6208,26 @@
       <c r="AN25" s="19" t="n"/>
       <c r="AO25" s="19" t="n"/>
       <c r="AP25" s="19" t="n"/>
+      <c r="AQ25" s="16" t="inlineStr">
+        <is>
+          <t>Farm Effects on Phytoplankton &amp; Water Quality (18S Metabarcoding)</t>
+        </is>
+      </c>
+      <c r="AR25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zhu, Yaojia; Wang, Zhiyin; Song, Li; Gu, Jiali; Ye, Zhanjiang; Jin, Runjie; Wu, Jiaping; </t>
+        </is>
+      </c>
+      <c r="AS25" s="16" t="inlineStr">
+        <is>
+          <t>One of several Chinese seaweed-farm water-quality studies in the original list. Together with Rows 26, 32, 33, 34 forms a Chinese-context cluster useful for IMTA / nutrient cycling indicators.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="240" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xu, Yongjian; Fang, Jianguang; Tang, Qisheng; Lin, Junda; Le, Guanzong; Liao, Lv; </t>
+          <t>Xu, Y., et al.</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5988,7 +6316,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>Foundational Chinese Gracilaria bioremediation paper; provides species-specific bioextraction reference data analogous to Xiao 2017's Saccharina values. | v30 AK-vs-I reconciliation: full methods (Xu 2008, read) show water-column DIN/DIP transect sampling only - no tissue %N/%P, no CHN analyser, no chlorophyll-a. Removed WQ 1.1.1 (tissue bioextraction) and WQ 2.1.1 (chl-a); retained WQ 1.2.1 (DO) and CC 2.1.1 (pH). Bioremediation inferred from water-column drawdown, not tissue uptake. Original I: 'Seaweed Water Quality — Indicators 1.1.1 (N and P bioextraction via Gracilaria tissue uptake), 2.1.1 (chlorophyll-a / phytoplankton response). Climate Change Indicator 2.1.1 (pH) likely also.' | v32: matching column (MEL Indicator multi-select) re-tagged from 'WQ 1.1.1; WQ 2.1.1' to 'WQ 1.2.1 (DO); CC 2.1.1 (pH)' so the reconciliation drives tool matching (user-approved). Tool now surfaces row 26 under DO and pH, not bioextraction/chl-a.</t>
+          <t>Shows bioremediation by comparing water passing through the crop vs alongside it - it evidences nutrient drawdown, not a tissue-based removal figure.</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
@@ -6084,11 +6412,26 @@
       <c r="AN26" s="19" t="n"/>
       <c r="AO26" s="19" t="n"/>
       <c r="AP26" s="19" t="n"/>
+      <c r="AQ26" s="16" t="inlineStr">
+        <is>
+          <t>Seaweed Nutrient Drawdown via Through-Crop Transects</t>
+        </is>
+      </c>
+      <c r="AR26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xu, Yongjian; Fang, Jianguang; Tang, Qisheng; Lin, Junda; Le, Guanzong; Liao, Lv; </t>
+        </is>
+      </c>
+      <c r="AS26" s="16" t="inlineStr">
+        <is>
+          <t>Foundational Chinese Gracilaria bioremediation paper; provides species-specific bioextraction reference data analogous to Xiao 2017's Saccharina values. | v30 AK-vs-I reconciliation: full methods (Xu 2008, read) show water-column DIN/DIP transect sampling only - no tissue %N/%P, no CHN analyser, no chlorophyll-a. Removed WQ 1.1.1 (tissue bioextraction) and WQ 2.1.1 (chl-a); retained WQ 1.2.1 (DO) and CC 2.1.1 (pH). Bioremediation inferred from water-column drawdown, not tissue uptake. Original I: 'Seaweed Water Quality — Indicators 1.1.1 (N and P bioextraction via Gracilaria tissue uptake), 2.1.1 (chlorophyll-a / phytoplankton response). Climate Change Indicator 2.1.1 (pH) likely also.' | v32: matching column (MEL Indicator multi-select) re-tagged from 'WQ 1.1.1; WQ 2.1.1' to 'WQ 1.2.1 (DO); CC 2.1.1 (pH)' so the reconciliation drives tool matching (user-approved). Tool now surfaces row 26 under DO and pH, not bioextraction/chl-a.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="240" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drakard, Veronica Farrugia; Lanfranco, Sandro; Schembri, Patrick J; </t>
+          <t>Drakard, V. F., et al.</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6177,7 +6520,7 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>Cleverly uses fouling communities themselves as bioindicators — directly relevant if a farm wants water-quality proxy data without chemistry equipment.</t>
+          <t>Lets you get a water-quality proxy from the fouling community itself, without chemistry gear.</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
@@ -6273,11 +6616,26 @@
       <c r="AN27" s="19" t="n"/>
       <c r="AO27" s="19" t="n"/>
       <c r="AP27" s="19" t="n"/>
+      <c r="AQ27" s="16" t="inlineStr">
+        <is>
+          <t>Fouling Macroalgae as a Water-Quality Bioindicator</t>
+        </is>
+      </c>
+      <c r="AR27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drakard, Veronica Farrugia; Lanfranco, Sandro; Schembri, Patrick J; </t>
+        </is>
+      </c>
+      <c r="AS27" s="16" t="inlineStr">
+        <is>
+          <t>Cleverly uses fouling communities themselves as bioindicators — directly relevant if a farm wants water-quality proxy data without chemistry equipment.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="240" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhang, Xianyu; Zhang, Yingqi; Zhang, Qian; Liu, Peiwu; Guo, Rui; Jin, Shengyi; Liu, Jiawen; Chen, Lei; Ma, Zhen; Liu, Ying; </t>
+          <t>Zhang, X., et al.</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6367,11 +6725,7 @@
           <t>https://doi.org/10.3390/ijerph17041446</t>
         </is>
       </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t>Generic title — likely Chinese-context water-quality survey; not distinctive methodologically. | v15 Rule 12 cross-database refinement (bivalve CSV): Confirmed as bivalve-relevant marine aquaculture WQ paper; X retained as 'Not specific' because the original paper does not specify aquaculture type. Bivalve relevance: marine aquaculture area = shellfish-cultivation context in Chinese coastal-aquaculture literature.</t>
-        </is>
-      </c>
+      <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -6465,11 +6819,26 @@
       <c r="AN28" s="19" t="n"/>
       <c r="AO28" s="19" t="n"/>
       <c r="AP28" s="19" t="n"/>
+      <c r="AQ28" s="16" t="inlineStr">
+        <is>
+          <t>Water-Quality Survey of a Mixed Marine Culture Area</t>
+        </is>
+      </c>
+      <c r="AR28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zhang, Xianyu; Zhang, Yingqi; Zhang, Qian; Liu, Peiwu; Guo, Rui; Jin, Shengyi; Liu, Jiawen; Chen, Lei; Ma, Zhen; Liu, Ying; </t>
+        </is>
+      </c>
+      <c r="AS28" s="16" t="inlineStr">
+        <is>
+          <t>Generic title — likely Chinese-context water-quality survey; not distinctive methodologically. | v15 Rule 12 cross-database refinement (bivalve CSV): Confirmed as bivalve-relevant marine aquaculture WQ paper; X retained as 'Not specific' because the original paper does not specify aquaculture type. Bivalve relevance: marine aquaculture area = shellfish-cultivation context in Chinese coastal-aquaculture literature.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="240" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jansen, Henrice M; Reid, Gregor K; Bannister, RJ; Husa, Vivian; Robinson, SMC; Cooper, John Andrew; Quinton, Cheryl; Strand, Øivind; </t>
+          <t>Jansen, H. M., et al.</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6555,11 +6924,7 @@
           <t>https://www.int-res.com/abstracts/aei/v8/p463-480/ ; DOI 10.3354/aei00192</t>
         </is>
       </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t>Co-author Henrice Jansen also co-authored the Wageningen Bernard 2019 metabarcoding protocol (Row 15) and Tonk 2021 framework (Row 56) — these three papers together represent the Wageningen "design + protocol + framework" stack for aquaculture environmental monitoring. Read this one before doing any discrete WQ sampling at a farm. [Rule 12 cross-DB refinement: methodology for discrete water-quality sampling transfers across seaweed and mollusk open-water sites; broadened from 'Not specific' to capture both. Original Jansen 2016 paper appears in both seaweed and mollusk CSV batches.]</t>
-        </is>
-      </c>
+      <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -6653,11 +7018,26 @@
       <c r="AN29" s="19" t="n"/>
       <c r="AO29" s="19" t="n"/>
       <c r="AP29" s="19" t="n"/>
+      <c r="AQ29" s="16" t="inlineStr">
+        <is>
+          <t>Designing Open-Water Aquaculture Water-Quality Sampling (Reference)</t>
+        </is>
+      </c>
+      <c r="AR29" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jansen, Henrice M; Reid, Gregor K; Bannister, RJ; Husa, Vivian; Robinson, SMC; Cooper, John Andrew; Quinton, Cheryl; Strand, Øivind; </t>
+        </is>
+      </c>
+      <c r="AS29" s="16" t="inlineStr">
+        <is>
+          <t>Co-author Henrice Jansen also co-authored the Wageningen Bernard 2019 metabarcoding protocol (Row 15) and Tonk 2021 framework (Row 56) — these three papers together represent the Wageningen "design + protocol + framework" stack for aquaculture environmental monitoring. Read this one before doing any discrete WQ sampling at a farm. [Rule 12 cross-DB refinement: methodology for discrete water-quality sampling transfers across seaweed and mollusk open-water sites; broadened from 'Not specific' to capture both. Original Jansen 2016 paper appears in both seaweed and mollusk CSV batches.]</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="240" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liang, Zhourui; Wang, Wenjun; Liu, Lulei; Li, Guoliang; Xia, Bin; </t>
+          <t>Liang, Z., et al.</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6744,7 +7124,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>Commercial-scale rather than experimental — particularly relevant for farms approaching the size threshold where bioextraction becomes measurable at site scale.</t>
+          <t>Commercial-scale rather than experimental - relevant once a farm is large enough for bioextraction to show at site scale.</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -6840,11 +7220,26 @@
       <c r="AN30" s="19" t="n"/>
       <c r="AO30" s="19" t="n"/>
       <c r="AP30" s="19" t="n"/>
+      <c r="AQ30" s="16" t="inlineStr">
+        <is>
+          <t>Water-Quality Effects of Commercial-Scale Seaweed Cultivation</t>
+        </is>
+      </c>
+      <c r="AR30" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liang, Zhourui; Wang, Wenjun; Liu, Lulei; Li, Guoliang; Xia, Bin; </t>
+        </is>
+      </c>
+      <c r="AS30" s="16" t="inlineStr">
+        <is>
+          <t>Commercial-scale rather than experimental — particularly relevant for farms approaching the size threshold where bioextraction becomes measurable at site scale.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="240" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiang, Zhibing; Liu, Jingjing; Li, Shanglu; Chen, Yue; Du, Ping; Zhu, Yuanli; Liao, Yibo; Chen, Quanzhen; Shou, Lu; Yan, Xiaojun; </t>
+          <t>Jiang, Z., et al.</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6929,7 +7324,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>Strong protocol with two design features worth replicating: (a) the post-harvest re-sampling that anchors causal attribution; (b) the specific finding that kelp farming reduced dinoflagellate Prorocentrum minimum dominance, suggesting phytoplankton community composition (not just biomass) is a useful indicator. Highly eutrophic-bay context — most directly applicable to coastal China, Korea, and Vietnam, but methodologically transferable.</t>
+          <t>Two design features worth copying: post-harvest re-sampling to prove cause, and tracking shifts in harmful-bloom dominance (not just biomass).</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -7025,11 +7420,26 @@
       <c r="AN31" s="19" t="n"/>
       <c r="AO31" s="19" t="n"/>
       <c r="AP31" s="19" t="n"/>
+      <c r="AQ31" s="16" t="inlineStr">
+        <is>
+          <t>Attributing Water-Quality &amp; Phytoplankton Change to Kelp Farming</t>
+        </is>
+      </c>
+      <c r="AR31" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jiang, Zhibing; Liu, Jingjing; Li, Shanglu; Chen, Yue; Du, Ping; Zhu, Yuanli; Liao, Yibo; Chen, Quanzhen; Shou, Lu; Yan, Xiaojun; </t>
+        </is>
+      </c>
+      <c r="AS31" s="16" t="inlineStr">
+        <is>
+          <t>Strong protocol with two design features worth replicating: (a) the post-harvest re-sampling that anchors causal attribution; (b) the specific finding that kelp farming reduced dinoflagellate Prorocentrum minimum dominance, suggesting phytoplankton community composition (not just biomass) is a useful indicator. Highly eutrophic-bay context — most directly applicable to coastal China, Korea, and Vietnam, but methodologically transferable.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="240" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rahadiati, Ati; Soewardi, Kadarwan; Wardiatno, Yusli; </t>
+          <t>Rahadiati, A., et al.</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7118,7 +7528,7 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>Carrying capacity framing suggests this paper is methodologically useful for any framework user scaling up cultivation. | v30 AK-vs-I reconciliation: methods (Rahadiati 2017, read) measure DO, nutrients and physical parameters plus GIS suitability/carrying-capacity - no chlorophyll-a. Removed WQ 2.1.1; retained WQ 1.2.1 (DO). | v32: matching column re-tagged - removed WQ 2.1.1 (chl-a, not measured); retained WQ 1.2.1 (DO) (user-approved).</t>
+          <t>Oriented to siting and carrying capacity; it measures dissolved oxygen and physical parameters, not chlorophyll.</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
@@ -7214,11 +7624,26 @@
       <c r="AN32" s="19" t="n"/>
       <c r="AO32" s="19" t="n"/>
       <c r="AP32" s="19" t="n"/>
+      <c r="AQ32" s="16" t="inlineStr">
+        <is>
+          <t>Water-Quality &amp; Carrying-Capacity Siting for Seaweed</t>
+        </is>
+      </c>
+      <c r="AR32" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rahadiati, Ati; Soewardi, Kadarwan; Wardiatno, Yusli; </t>
+        </is>
+      </c>
+      <c r="AS32" s="16" t="inlineStr">
+        <is>
+          <t>Carrying capacity framing suggests this paper is methodologically useful for any framework user scaling up cultivation. | v30 AK-vs-I reconciliation: methods (Rahadiati 2017, read) measure DO, nutrients and physical parameters plus GIS suitability/carrying-capacity - no chlorophyll-a. Removed WQ 2.1.1; retained WQ 1.2.1 (DO). | v32: matching column re-tagged - removed WQ 2.1.1 (chl-a, not measured); retained WQ 1.2.1 (DO) (user-approved).</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="240" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troell, Max; Rönnbäck, Patrik; Halling, Christina; Kautsky, Nils; Buschmann, A; </t>
+          <t>Troell, M., et al.</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7305,11 +7730,7 @@
           <t>https://doi.org/10.1023/A:1008070400208</t>
         </is>
       </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t>Foundational ecological-engineering / seaweed-bioremediation concept paper. Establishes the framing that later quantitative work operationalises. Useful for context but not for protocol selection.</t>
-        </is>
-      </c>
+      <c r="U33" s="3" t="inlineStr"/>
       <c r="V33" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -7403,11 +7824,26 @@
       <c r="AN33" s="19" t="n"/>
       <c r="AO33" s="19" t="n"/>
       <c r="AP33" s="19" t="n"/>
+      <c r="AQ33" s="16" t="inlineStr">
+        <is>
+          <t>Seaweed as a Nutrient Biofilter in IMTA (Concept Reference)</t>
+        </is>
+      </c>
+      <c r="AR33" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troell, Max; Rönnbäck, Patrik; Halling, Christina; Kautsky, Nils; Buschmann, A; </t>
+        </is>
+      </c>
+      <c r="AS33" s="16" t="inlineStr">
+        <is>
+          <t>Foundational ecological-engineering / seaweed-bioremediation concept paper. Establishes the framing that later quantitative work operationalises. Useful for context but not for protocol selection.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="240" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rose, Deborah J; Hemery, Lenaïg G; </t>
+          <t>Rose, D. J. &amp; Hemery, L. G.</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7492,11 +7928,7 @@
           <t>https://www.mdpi.com/2077-1312/11/1/175 ; also OSTI: https://www.osti.gov/pages/biblio/1908888</t>
         </is>
       </c>
-      <c r="U34" s="3" t="inlineStr">
-        <is>
-          <t>Cited in MEL Tools &amp; Resources for Climate Change (p. 41). Best read as the entry-point for matching a C method to a monitoring need, then jumping to a primary protocol paper for execution. | v1.4 refinement: CC indicator labels corrected — old v1.3 assigned cradle-to-grave to CC 1.1.1 and "Carbon cycling" to CC 1.2.1; v1.4 Seaweed framework reverses this (CC 1.1.1 = biomass replacement of emissions-intensive products, CC 1.2.1 = cradle-to-grave GHG emissions). "Carbon cycling" is not a v1.4 indicator.</t>
-        </is>
-      </c>
+      <c r="U34" s="3" t="inlineStr"/>
       <c r="V34" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -7590,11 +8022,26 @@
       <c r="AN34" s="19" t="n"/>
       <c r="AO34" s="19" t="n"/>
       <c r="AP34" s="19" t="n"/>
+      <c r="AQ34" s="16" t="inlineStr">
+        <is>
+          <t>Methods for Measuring Carbon Uptake &amp; Permanence (Review)</t>
+        </is>
+      </c>
+      <c r="AR34" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rose, Deborah J; Hemery, Lenaïg G; </t>
+        </is>
+      </c>
+      <c r="AS34" s="16" t="inlineStr">
+        <is>
+          <t>Cited in MEL Tools &amp; Resources for Climate Change (p. 41). Best read as the entry-point for matching a C method to a monitoring need, then jumping to a primary protocol paper for execution. | v1.4 refinement: CC indicator labels corrected — old v1.3 assigned cradle-to-grave to CC 1.1.1 and "Carbon cycling" to CC 1.2.1; v1.4 Seaweed framework reverses this (CC 1.1.1 = biomass replacement of emissions-intensive products, CC 1.2.1 = cradle-to-grave GHG emissions). "Carbon cycling" is not a v1.4 indicator.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="240" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Johnson, Martin; Jutard, Quentin; Jaouen, Maël; Maltsev, Nikolai; Boyer, Margaux; Guillerme, Chloe; McElligott, Deirdre; Paolacci, Simona; Maguire, Julie; Mangin, Antoine; </t>
+          <t>Johnson, M., et al.</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7677,11 +8124,7 @@
           <t>https://doi.org/10.3389/fmars.2024.1405303</t>
         </is>
       </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t>Likely useful for scenario-scale impact projections rather than indicator-level measurement. | v1.4 refinement: CC indicator labels corrected — old v1.3 assigned cradle-to-grave to CC 1.1.1 and "Carbon cycling" to CC 1.2.1; v1.4 Seaweed framework reverses this (CC 1.1.1 = biomass replacement of emissions-intensive products, CC 1.2.1 = cradle-to-grave GHG emissions). "Carbon cycling" is not a v1.4 indicator. Paper is basin-scale CO₂ uptake / DIC drawdown modelling; biomass-replacement framing not central — collapsed to CC 1.2.1 only.</t>
-        </is>
-      </c>
+      <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -7775,11 +8218,26 @@
       <c r="AN35" s="19" t="n"/>
       <c r="AO35" s="19" t="n"/>
       <c r="AP35" s="19" t="n"/>
+      <c r="AQ35" s="16" t="inlineStr">
+        <is>
+          <t>Basin-Scale Modelling of Seaweed Nutrient, Carbon &amp; Fisheries Impact</t>
+        </is>
+      </c>
+      <c r="AR35" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Johnson, Martin; Jutard, Quentin; Jaouen, Maël; Maltsev, Nikolai; Boyer, Margaux; Guillerme, Chloe; McElligott, Deirdre; Paolacci, Simona; Maguire, Julie; Mangin, Antoine; </t>
+        </is>
+      </c>
+      <c r="AS35" s="16" t="inlineStr">
+        <is>
+          <t>Likely useful for scenario-scale impact projections rather than indicator-level measurement. | v1.4 refinement: CC indicator labels corrected — old v1.3 assigned cradle-to-grave to CC 1.1.1 and "Carbon cycling" to CC 1.2.1; v1.4 Seaweed framework reverses this (CC 1.1.1 = biomass replacement of emissions-intensive products, CC 1.2.1 = cradle-to-grave GHG emissions). "Carbon cycling" is not a v1.4 indicator. Paper is basin-scale CO₂ uptake / DIC drawdown modelling; biomass-replacement framing not central — collapsed to CC 1.2.1 only.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="240" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xiong, Yonglong; Gao, Lin; Qu, Liyin; Xu, Juntian; Ma, Zengling; Gao, Guang; </t>
+          <t>Xiong, Y., et al.</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -7862,11 +8320,7 @@
           <t>Paywall: https://www.sciencedirect.com/science/article/abs/pii/S0048969722061551 ; PubMed: https://pubmed.ncbi.nlm.nih.gov/36170919/ ; DOI 10.1016/j.scitotenv.2022.159056</t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t>Direct methodological successor to Xiao et al. 2017, scaling up the same tissue-content × biomass logic to province-by-year statistics. Provides the bridge between farm-level MEL measurements (which the framework targets) and the regional / national aggregate metrics that policymakers care about. | v1.4 refinement: CC indicator labels corrected — old v1.3 assigned cradle-to-grave to CC 1.1.1 and "Carbon cycling" to CC 1.2.1; v1.4 Seaweed framework reverses this (CC 1.1.1 = biomass replacement of emissions-intensive products, CC 1.2.1 = cradle-to-grave GHG emissions). "Carbon cycling" is not a v1.4 indicator. Province-scale CNPO flux accounting → CC 1.2.1 (cradle-to-grave). Biomass-replacement framing not central — collapsed to CC 1.2.1 only.</t>
-        </is>
-      </c>
+      <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -7960,11 +8414,26 @@
       <c r="AN36" s="19" t="n"/>
       <c r="AO36" s="19" t="n"/>
       <c r="AP36" s="19" t="n"/>
+      <c r="AQ36" s="16" t="inlineStr">
+        <is>
+          <t>Scaling Seaweed &amp; Fish Nutrient/Carbon Fluxes to Region (Synthesis)</t>
+        </is>
+      </c>
+      <c r="AR36" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xiong, Yonglong; Gao, Lin; Qu, Liyin; Xu, Juntian; Ma, Zengling; Gao, Guang; </t>
+        </is>
+      </c>
+      <c r="AS36" s="16" t="inlineStr">
+        <is>
+          <t>Direct methodological successor to Xiao et al. 2017, scaling up the same tissue-content × biomass logic to province-by-year statistics. Provides the bridge between farm-level MEL measurements (which the framework targets) and the regional / national aggregate metrics that policymakers care about. | v1.4 refinement: CC indicator labels corrected — old v1.3 assigned cradle-to-grave to CC 1.1.1 and "Carbon cycling" to CC 1.2.1; v1.4 Seaweed framework reverses this (CC 1.1.1 = biomass replacement of emissions-intensive products, CC 1.2.1 = cradle-to-grave GHG emissions). "Carbon cycling" is not a v1.4 indicator. Province-scale CNPO flux accounting → CC 1.2.1 (cradle-to-grave). Biomass-replacement framing not central — collapsed to CC 1.2.1 only.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="240" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wu, Zhenyu; Cai, Chunzhi; Ye, Zhanjiang; Wang, Nan; Zhu, Yaojia; Jin, Runjie; Christakos, George; Chen, Shuangshuang; Wang, Dongyu; Zhu, Junjie; </t>
+          <t>Wu, Z., et al.</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8047,7 +8516,7 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>Direct successor to Xiao et al. 2021 with two important advances: (a) much finer spatial resolution (52 stations vs. Xiao's coarser grid), and (b) species-resolved comparison showing that influence-zone size is species-dependent (Porphyra kilometre-scale vs. Hizikia localised). For a MEL implementation, this implies that effect-detection sampling design must be tuned to the cultivated species. Sampling effort detail: water-sampling campaign was 2 days; geostatistical/satellite-imagery analysis component extends the effective effort. Water depth at sites averages 10 m with maximum to 41 m (Coastal classification reflects the average).</t>
+          <t>Tune station spacing to your crop - the farm's influence zone is species-dependent (kilometre-scale for some seaweeds, under ~100 m for others).</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
@@ -8143,11 +8612,26 @@
       <c r="AN37" s="19" t="n"/>
       <c r="AO37" s="19" t="n"/>
       <c r="AP37" s="19" t="n"/>
+      <c r="AQ37" s="16" t="inlineStr">
+        <is>
+          <t>Mapping a Seaweed Farm's Water-Quality Footprint (DO, pH, Chlorophyll)</t>
+        </is>
+      </c>
+      <c r="AR37" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wu, Zhenyu; Cai, Chunzhi; Ye, Zhanjiang; Wang, Nan; Zhu, Yaojia; Jin, Runjie; Christakos, George; Chen, Shuangshuang; Wang, Dongyu; Zhu, Junjie; </t>
+        </is>
+      </c>
+      <c r="AS37" s="16" t="inlineStr">
+        <is>
+          <t>Direct successor to Xiao et al. 2021 with two important advances: (a) much finer spatial resolution (52 stations vs. Xiao's coarser grid), and (b) species-resolved comparison showing that influence-zone size is species-dependent (Porphyra kilometre-scale vs. Hizikia localised). For a MEL implementation, this implies that effect-detection sampling design must be tuned to the cultivated species. Sampling effort detail: water-sampling campaign was 2 days; geostatistical/satellite-imagery analysis component extends the effective effort. Water depth at sites averages 10 m with maximum to 41 m (Coastal classification reflects the average).</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="240" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xiao, Xi; Agusti, Susana; Lin, Fang; Li, Ke; Pan, Yaoru; Yu, Yan; Zheng, Yuhan; Wu, Jiaping; Duarte, Carlos M; </t>
+          <t>Xiao, X., et al.</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8234,7 +8718,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>Not a primary monitoring protocol — its value is (a) establishing the calculation chain and (b) providing reference %N and %P values for major species. PAIR WITH WANG 2014 (Row 42) for the primary tissue-measurement protocol (CHN analyser + δ¹⁵N) that produces defensible site-specific tissue values. Used together, these two papers cover the WQ 1.1.1 bioextraction indicator from primary measurement through to scaled accounting.</t>
+          <t>Pair it with a primary tissue-measurement protocol; on its own it supplies the calculation chain and reference %N/%P values.</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
@@ -8330,11 +8814,26 @@
       <c r="AN38" s="19" t="n"/>
       <c r="AO38" s="19" t="n"/>
       <c r="AP38" s="19" t="n"/>
+      <c r="AQ38" s="16" t="inlineStr">
+        <is>
+          <t>Nitrogen &amp; Phosphorus Bioextraction Accounting for Seaweed</t>
+        </is>
+      </c>
+      <c r="AR38" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xiao, Xi; Agusti, Susana; Lin, Fang; Li, Ke; Pan, Yaoru; Yu, Yan; Zheng, Yuhan; Wu, Jiaping; Duarte, Carlos M; </t>
+        </is>
+      </c>
+      <c r="AS38" s="16" t="inlineStr">
+        <is>
+          <t>Not a primary monitoring protocol — its value is (a) establishing the calculation chain and (b) providing reference %N and %P values for major species. PAIR WITH WANG 2014 (Row 42) for the primary tissue-measurement protocol (CHN analyser + δ¹⁵N) that produces defensible site-specific tissue values. Used together, these two papers cover the WQ 1.1.1 bioextraction indicator from primary measurement through to scaled accounting.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="240" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bell, Tom W; Nidzieko, Nick J; Siegel, David A; Miller, Robert J; Cavanaugh, Kyle C; Nelson, Norman B; Reed, Daniel C; Fedorov, Dmitry; Moran, Christopher; Snyder, Jordan N; </t>
+          <t>Bell, T. W., et al.</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8417,11 +8916,7 @@
           <t>https://doi.org/10.3389/fmars.2020.520223</t>
         </is>
       </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t>Complements Xing 2019 and Bennion 2019 in the remote-sensing methods cluster.</t>
-        </is>
-      </c>
+      <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -8515,11 +9010,26 @@
       <c r="AN39" s="19" t="n"/>
       <c r="AO39" s="19" t="n"/>
       <c r="AP39" s="19" t="n"/>
+      <c r="AQ39" s="16" t="inlineStr">
+        <is>
+          <t>Satellite &amp; Autonomous Platforms for Chlorophyll/Bloom Monitoring (Review)</t>
+        </is>
+      </c>
+      <c r="AR39" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bell, Tom W; Nidzieko, Nick J; Siegel, David A; Miller, Robert J; Cavanaugh, Kyle C; Nelson, Norman B; Reed, Daniel C; Fedorov, Dmitry; Moran, Christopher; Snyder, Jordan N; </t>
+        </is>
+      </c>
+      <c r="AS39" s="16" t="inlineStr">
+        <is>
+          <t>Complements Xing 2019 and Bennion 2019 in the remote-sensing methods cluster.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="240" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wang, Xinxin; Broch, Ole Jacob; Forbord, Silje; Handå, Aleksander; Skjermo, Jorunn; Reitan, Kjell Inge; Vadstein, Olav; Olsen, Yngvar; </t>
+          <t>Wang, X., et al.</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8608,7 +9118,7 @@
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>Already cited in MEL framework as a Water Quality 1.1.1 tool. Three things make this protocol particularly strong: (a) the δ¹⁵N source-attribution component lets the analyst say "the N in this kelp came from the salmon", not just "the kelp took up N"; (b) the 1 ha → 0.8-1.2 t N per season conversion is a directly useable benchmark; (c) the year-long monitoring with monthly resampling captures both seasonal kelp physiology and salmon-feed-pulse dynamics. Replication template for any IMTA design.</t>
+          <t>The isotope step needs a lab that runs isotope-ratio mass spectrometry; as a benchmark, a hectare of kelp removed ~0.8-1.2 t nitrogen per season here.</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
@@ -8704,11 +9214,26 @@
       <c r="AN40" s="19" t="n"/>
       <c r="AO40" s="19" t="n"/>
       <c r="AP40" s="19" t="n"/>
+      <c r="AQ40" s="16" t="inlineStr">
+        <is>
+          <t>Kelp Nitrogen Bioextraction Beside a Fed Farm (Isotope Source-Tracking)</t>
+        </is>
+      </c>
+      <c r="AR40" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wang, Xinxin; Broch, Ole Jacob; Forbord, Silje; Handå, Aleksander; Skjermo, Jorunn; Reitan, Kjell Inge; Vadstein, Olav; Olsen, Yngvar; </t>
+        </is>
+      </c>
+      <c r="AS40" s="16" t="inlineStr">
+        <is>
+          <t>Already cited in MEL framework as a Water Quality 1.1.1 tool. Three things make this protocol particularly strong: (a) the δ¹⁵N source-attribution component lets the analyst say "the N in this kelp came from the salmon", not just "the kelp took up N"; (b) the 1 ha → 0.8-1.2 t N per season conversion is a directly useable benchmark; (c) the year-long monitoring with monthly resampling captures both seasonal kelp physiology and salmon-feed-pulse dynamics. Replication template for any IMTA design.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="240" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sarà, G; Martire, M Lo; Sanfilippo, Marilena; Pulicanò, G; Cortese, Giuseppa; Mazzola, A; Manganaro, Antonio; Pusceddu, A; </t>
+          <t>Sarà, G., et al.</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -8797,7 +9322,7 @@
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>Older N/P accounting paper; superseded methodologically by Xiao 2017.</t>
+          <t>Superseded methodologically by later bioextraction accounting - use only for background.</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
@@ -8893,11 +9418,26 @@
       <c r="AN41" s="19" t="n"/>
       <c r="AO41" s="19" t="n"/>
       <c r="AP41" s="19" t="n"/>
+      <c r="AQ41" s="16" t="inlineStr">
+        <is>
+          <t>Regional Nitrogen &amp; Phosphorus Accounting for Aquaculture (Reference)</t>
+        </is>
+      </c>
+      <c r="AR41" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sarà, G; Martire, M Lo; Sanfilippo, Marilena; Pulicanò, G; Cortese, Giuseppa; Mazzola, A; Manganaro, Antonio; Pusceddu, A; </t>
+        </is>
+      </c>
+      <c r="AS41" s="16" t="inlineStr">
+        <is>
+          <t>Older N/P accounting paper; superseded methodologically by Xiao 2017.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="240" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walker, Cameron; Corrigan, Sophie; Daniels, Carly; Wilding, Catherine; Woodward, E Malcolm S; Widdicombe, Claire E; Smale, Dan A; Ashton, Ian GC; Brown, A Ross; </t>
+          <t>Walker, C., et al.</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -8982,7 +9522,7 @@
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>Important "negative result" paper that the framework should use as a counterweight to Xiao 2017 / Wang 2014. Co-authored by Sophie Corrigan (Corrigan 2022 review + Corrigan 2023 epibionts + Corrigan 2025 benthic), this completes a Corrigan-group trilogy on UK / English Channel kelp aquaculture. Key takeaway for MEL: at 16 ha and typical UK hydrodynamics, small-scale IMTA does not measurably regulate nutrients — practitioners should expect to need either much larger farms or much more enclosed sites before WQ 1.1.1 effects become detectable.</t>
+          <t>A valuable 'negative result' counterweight - no clear farm effect - useful for setting realistic expectations.</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
@@ -9078,11 +9618,26 @@
       <c r="AN42" s="19" t="n"/>
       <c r="AO42" s="19" t="n"/>
       <c r="AP42" s="19" t="n"/>
+      <c r="AQ42" s="16" t="inlineStr">
+        <is>
+          <t>Plankton &amp; Water-Quality Survey at a Seaweed-Shellfish Farm</t>
+        </is>
+      </c>
+      <c r="AR42" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Walker, Cameron; Corrigan, Sophie; Daniels, Carly; Wilding, Catherine; Woodward, E Malcolm S; Widdicombe, Claire E; Smale, Dan A; Ashton, Ian GC; Brown, A Ross; </t>
+        </is>
+      </c>
+      <c r="AS42" s="16" t="inlineStr">
+        <is>
+          <t>Important "negative result" paper that the framework should use as a counterweight to Xiao 2017 / Wang 2014. Co-authored by Sophie Corrigan (Corrigan 2022 review + Corrigan 2023 epibionts + Corrigan 2025 benthic), this completes a Corrigan-group trilogy on UK / English Channel kelp aquaculture. Key takeaway for MEL: at 16 ha and typical UK hydrodynamics, small-scale IMTA does not measurably regulate nutrients — practitioners should expect to need either much larger farms or much more enclosed sites before WQ 1.1.1 effects become detectable.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="240" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jiang, Zhi-Bing; Chen, Quan-Zhen; Zeng, Jiang-Ning; Liao, Yi-Bo; Shou, Lu; Liu, Jingjing; </t>
+          <t>Jiang, Z., et al.</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9168,11 +9723,7 @@
           <t>https://doi.org/10.3354/meps09499</t>
         </is>
       </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t>Standard phytoplankton-environmental gradient analysis. | v15 Rule 12 cross-database refinement (bivalve CSV #37): Confirmed identical paper (DOI 10.3354/meps09499). No semantic changes required — X = Not specific retained because original paper covers three aquaculture systems (fish + shellfish + IMTA) within a Chinese subtropical bay; Z = WQ 2.1.1 + 2.1.2 already correct.</t>
-        </is>
-      </c>
+      <c r="U43" s="3" t="inlineStr"/>
       <c r="V43" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -9266,11 +9817,26 @@
       <c r="AN43" s="19" t="n"/>
       <c r="AO43" s="19" t="n"/>
       <c r="AP43" s="19" t="n"/>
+      <c r="AQ43" s="16" t="inlineStr">
+        <is>
+          <t>Phytoplankton Community Along a Farm Distance Gradient</t>
+        </is>
+      </c>
+      <c r="AR43" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jiang, Zhi-Bing; Chen, Quan-Zhen; Zeng, Jiang-Ning; Liao, Yi-Bo; Shou, Lu; Liu, Jingjing; </t>
+        </is>
+      </c>
+      <c r="AS43" s="16" t="inlineStr">
+        <is>
+          <t>Standard phytoplankton-environmental gradient analysis. | v15 Rule 12 cross-database refinement (bivalve CSV #37): Confirmed identical paper (DOI 10.3354/meps09499). No semantic changes required — X = Not specific retained because original paper covers three aquaculture systems (fish + shellfish + IMTA) within a Chinese subtropical bay; Z = WQ 2.1.1 + 2.1.2 already correct.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="240" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visch, Wouter; Kononets, Mikhail; Hall, Per OJ; Nylund, Göran M; Pavia, Henrik; </t>
+          <t>Visch, W., et al.</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -9355,7 +9921,7 @@
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t>Cited directly in MEL framework. Particularly strong as a temperate empirical BACI template parallel to Corrigan 2025 (UK) and Visch 2020 (Sweden).</t>
+          <t>Thorough but resource-intensive - best for a farm that can commit to before-and-after sampling over two years, and the oxygen-flux part needs a benthic lander.</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
@@ -9451,11 +10017,26 @@
       <c r="AN44" s="19" t="n"/>
       <c r="AO44" s="19" t="n"/>
       <c r="AP44" s="19" t="n"/>
+      <c r="AQ44" s="16" t="inlineStr">
+        <is>
+          <t>Whole-Ecosystem BACI Assessment of Seaweed-Farm Seabed Impact</t>
+        </is>
+      </c>
+      <c r="AR44" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visch, Wouter; Kononets, Mikhail; Hall, Per OJ; Nylund, Göran M; Pavia, Henrik; </t>
+        </is>
+      </c>
+      <c r="AS44" s="16" t="inlineStr">
+        <is>
+          <t>Cited directly in MEL framework. Particularly strong as a temperate empirical BACI template parallel to Corrigan 2025 (UK) and Visch 2020 (Sweden).</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="240" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yokoyama, Hisashi; Nishimura, Akifumi; Inoue, Misa; </t>
+          <t>Yokoyama, H., et al.</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -9540,7 +10121,7 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>About FISH farming (not seaweed), but the AVS / TN / TOC thresholds and the macrobenthos-as-bioindicator framing transfer directly to seaweed-farm benthic monitoring per MEL Indicators 1.3.1 and 1.4.1. The AVS &gt; 1.9 mg S/g critical threshold is particularly useful as a hard sustainability boundary — if a seaweed farm's underlying sediment crosses this, the farm is no longer providing a benthic-habitat ecosystem service. Use as a quantitative threshold reference alongside the Visch 2020 / Corrigan 2025 paired farm/control designs. Sampling effort: two blocks of approximately 1 week each (Aug–Sept + Feb).</t>
+          <t>Developed at fish farms but transfers to seaweed; the acid-volatile-sulphide limit (~1.9 mg S/g) is a ready benchmark for benthic condition.</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
@@ -9636,11 +10217,26 @@
       <c r="AN45" s="19" t="n"/>
       <c r="AO45" s="19" t="n"/>
       <c r="AP45" s="19" t="n"/>
+      <c r="AQ45" s="16" t="inlineStr">
+        <is>
+          <t>Macrobenthos Bioindicators of Farm Sediment Impact (AVS/TN/TOC)</t>
+        </is>
+      </c>
+      <c r="AR45" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yokoyama, Hisashi; Nishimura, Akifumi; Inoue, Misa; </t>
+        </is>
+      </c>
+      <c r="AS45" s="16" t="inlineStr">
+        <is>
+          <t>About FISH farming (not seaweed), but the AVS / TN / TOC thresholds and the macrobenthos-as-bioindicator framing transfer directly to seaweed-farm benthic monitoring per MEL Indicators 1.3.1 and 1.4.1. The AVS &gt; 1.9 mg S/g critical threshold is particularly useful as a hard sustainability boundary — if a seaweed farm's underlying sediment crosses this, the farm is no longer providing a benthic-habitat ecosystem service. Use as a quantitative threshold reference alongside the Visch 2020 / Corrigan 2025 paired farm/control designs. Sampling effort: two blocks of approximately 1 week each (Aug–Sept + Feb).</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="240" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xiao, Xi; Agustí, Susana; Yu, Yan; Huang, Yuzhou; Chen, Weizhou; Hu, Jing; Li, Chao; Li, Ke; Wei, Fangyi; Lu, Yitian; </t>
+          <t>Xiao, X., et al.</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -9725,7 +10321,7 @@
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>Strong empirical demonstration of OA buffering by seaweed farms, but paywalled and equipment-heavy. For a farmer-facing approximation a basic in-situ pH/DO buoy would give a coarser version of the same signal.</t>
+          <t>A strong demonstration, but paywalled and equipment-heavy; a basic in-situ pH/DO buoy gives a coarser version of the same signal.</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
@@ -9821,11 +10417,26 @@
       <c r="AN46" s="19" t="n"/>
       <c r="AO46" s="19" t="n"/>
       <c r="AP46" s="19" t="n"/>
+      <c r="AQ46" s="16" t="inlineStr">
+        <is>
+          <t>Testing Whether a Seaweed Farm Buffers Ocean Acidification</t>
+        </is>
+      </c>
+      <c r="AR46" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xiao, Xi; Agustí, Susana; Yu, Yan; Huang, Yuzhou; Chen, Weizhou; Hu, Jing; Li, Chao; Li, Ke; Wei, Fangyi; Lu, Yitian; </t>
+        </is>
+      </c>
+      <c r="AS46" s="16" t="inlineStr">
+        <is>
+          <t>Strong empirical demonstration of OA buffering by seaweed farms, but paywalled and equipment-heavy. For a farmer-facing approximation a basic in-situ pH/DO buoy would give a coarser version of the same signal.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="240" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rose, Deborah J; Grear, Molly E; </t>
+          <t>Rose, D. J. &amp; Grear, M. E.</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -9900,11 +10511,7 @@
           <t>https://www.pnnl.gov/main/publications/external/technical_reports/PNNL-32776.pdf</t>
         </is>
       </c>
-      <c r="U47" s="3" t="inlineStr">
-        <is>
-          <t>Strategic-fit paper rather than monitoring methods paper.</t>
-        </is>
-      </c>
+      <c r="U47" s="3" t="inlineStr"/>
       <c r="V47" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -9998,11 +10605,26 @@
       <c r="AN47" s="19" t="n"/>
       <c r="AO47" s="19" t="n"/>
       <c r="AP47" s="19" t="n"/>
+      <c r="AQ47" s="16" t="inlineStr">
+        <is>
+          <t>Co-Locating Kelp Farming with Marine Renewable Energy (Scoping Reference)</t>
+        </is>
+      </c>
+      <c r="AR47" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rose, Deborah J; Grear, Molly E; </t>
+        </is>
+      </c>
+      <c r="AS47" s="16" t="inlineStr">
+        <is>
+          <t>Strategic-fit paper rather than monitoring methods paper.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="240" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bodycomb, Roma; Pomeroy, Andrew WM; Morris, Rebecca L; </t>
+          <t>Bodycomb, R., et al.</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -10089,7 +10711,7 @@
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
-          <t>Already cited in MEL framework. Useful where coastal protection is an additional benefit beyond H&amp;B/WQ/CC.</t>
+          <t>Relevant only where coastal protection is an added benefit; empirical validation is limited, so treat outputs as indicative.</t>
         </is>
       </c>
       <c r="V48" s="3" t="inlineStr">
@@ -10185,11 +10807,26 @@
       <c r="AN48" s="19" t="n"/>
       <c r="AO48" s="19" t="n"/>
       <c r="AP48" s="19" t="n"/>
+      <c r="AQ48" s="16" t="inlineStr">
+        <is>
+          <t>Modelling Wave Attenuation by a Kelp Farm (Coastal Protection)</t>
+        </is>
+      </c>
+      <c r="AR48" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bodycomb, Roma; Pomeroy, Andrew WM; Morris, Rebecca L; </t>
+        </is>
+      </c>
+      <c r="AS48" s="16" t="inlineStr">
+        <is>
+          <t>Already cited in MEL framework. Useful where coastal protection is an additional benefit beyond H&amp;B/WQ/CC.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="240" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heasman, Kevin G; Sclodnick, Tyler; Goseberg, Nils; Scott, Nicholas; Chambers, Michael; Dewhurst, Tobias; Rickerich, Samuel; Føre, Heidi Moe; Buck, Bela H; </t>
+          <t>Heasman, K. G., et al.</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10272,11 +10909,7 @@
           <t>https://doi.org/10.3389/faquc.2024.1427168</t>
         </is>
       </c>
-      <c r="U49" s="3" t="inlineStr">
-        <is>
-          <t>Engineering-side companion to monitoring; helps explain why Archetype-dependent results vary.</t>
-        </is>
-      </c>
+      <c r="U49" s="3" t="inlineStr"/>
       <c r="V49" s="3" t="inlineStr">
         <is>
           <t>Original list</t>
@@ -10370,11 +11003,26 @@
       <c r="AN49" s="19" t="n"/>
       <c r="AO49" s="19" t="n"/>
       <c r="AP49" s="19" t="n"/>
+      <c r="AQ49" s="16" t="inlineStr">
+        <is>
+          <t>Site-Exposure Indices for Farm Siting (Engineering Reference)</t>
+        </is>
+      </c>
+      <c r="AR49" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heasman, Kevin G; Sclodnick, Tyler; Goseberg, Nils; Scott, Nicholas; Chambers, Michael; Dewhurst, Tobias; Rickerich, Samuel; Føre, Heidi Moe; Buck, Bela H; </t>
+        </is>
+      </c>
+      <c r="AS49" s="16" t="inlineStr">
+        <is>
+          <t>Engineering-side companion to monitoring; helps explain why Archetype-dependent results vary.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="240" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhang, Jihong; Hansen, Pia Kupka; Wu, Wenguang; Liu, Yi; Zhao, Yunxia; Li, Yunchen; </t>
+          <t>Zhang, J., et al.</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -10464,7 +11112,7 @@
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>Particularly valuable because (a) it documents the MOM system being applied beyond finfish to seaweed + bivalve co-culture, providing a standardised internationally-recognisable benthic protocol; (b) it gives a 10-year-scale "best conditions" sediment finding under intensive Chinese co-culture, which is the longest time series in the original list. Use as the benchmark protocol for long-running benthic monitoring at any seaweed farm, and pair with Yokoyama 2007 for the underlying bioindicator-threshold logic. | v15 Rule 12 cross-database refinement (bivalve CSV): Confirmed IMTA (C. gigas + Chlamys farreri scallop + Laminaria/Saccharina). AB expanded to include all three species per fetched abstract. Companion to Zhang 2009 Sungo Bay MOM application (now row 95 = Stage 1 #12 new row).</t>
+          <t>Notable for applying the internationally-recognised MOM system beyond finfish to seaweed+bivalve co-culture, with a decade-scale record.</t>
         </is>
       </c>
       <c r="V50" s="3" t="inlineStr">
@@ -10560,11 +11208,26 @@
       <c r="AN50" s="19" t="n"/>
       <c r="AO50" s="19" t="n"/>
       <c r="AP50" s="19" t="n"/>
+      <c r="AQ50" s="16" t="inlineStr">
+        <is>
+          <t>MOM-B Seabed-Condition Grading Under a Co-Culture Farm</t>
+        </is>
+      </c>
+      <c r="AR50" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zhang, Jihong; Hansen, Pia Kupka; Wu, Wenguang; Liu, Yi; Zhao, Yunxia; Li, Yunchen; </t>
+        </is>
+      </c>
+      <c r="AS50" s="16" t="inlineStr">
+        <is>
+          <t>Particularly valuable because (a) it documents the MOM system being applied beyond finfish to seaweed + bivalve co-culture, providing a standardised internationally-recognisable benthic protocol; (b) it gives a 10-year-scale "best conditions" sediment finding under intensive Chinese co-culture, which is the longest time series in the original list. Use as the benchmark protocol for long-running benthic monitoring at any seaweed farm, and pair with Yokoyama 2007 for the underlying bioindicator-threshold logic. | v15 Rule 12 cross-database refinement (bivalve CSV): Confirmed IMTA (C. gigas + Chlamys farreri scallop + Laminaria/Saccharina). AB expanded to include all three species per fetched abstract. Companion to Zhang 2009 Sungo Bay MOM application (now row 95 = Stage 1 #12 new row).</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="240" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">St-Gelais, Adam T; Fredriksson, David W; Dewhurst, Tobias; Miller-Hope, Zachary S; Costa-Pierce, Barry Antonio; Johndrow, Kathryn; </t>
+          <t>St-Gelais, A. T., et al.</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -10649,7 +11312,7 @@
       </c>
       <c r="U51" s="3" t="inlineStr">
         <is>
-          <t>Not an MEL indicator paper, but useful for understanding the technical baseline of small-scale Atlantic farms (e.g., the kind of farms Schutt 2023 and Heasman 2024 monitored).</t>
+          <t>A technical and cost baseline for small farms, not an ecosystem-service method.</t>
         </is>
       </c>
       <c r="V51" s="3" t="inlineStr">
@@ -10745,11 +11408,26 @@
       <c r="AN51" s="19" t="n"/>
       <c r="AO51" s="19" t="n"/>
       <c r="AP51" s="19" t="n"/>
+      <c r="AQ51" s="16" t="inlineStr">
+        <is>
+          <t>Low-Cost Community-Scale Kelp System (Engineering Reference)</t>
+        </is>
+      </c>
+      <c r="AR51" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">St-Gelais, Adam T; Fredriksson, David W; Dewhurst, Tobias; Miller-Hope, Zachary S; Costa-Pierce, Barry Antonio; Johndrow, Kathryn; </t>
+        </is>
+      </c>
+      <c r="AS51" s="16" t="inlineStr">
+        <is>
+          <t>Not an MEL indicator paper, but useful for understanding the technical baseline of small-scale Atlantic farms (e.g., the kind of farms Schutt 2023 and Heasman 2024 monitored).</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="240" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tonk, L; Jansen, HM; Poelman, M; Nauta, RW; Jak, RG; Tamis, JE; Jongbloed, RH; Tonk, L; Jansen, HM; Poelman, M; </t>
+          <t>Tonk, L., et al.</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -10826,7 +11504,7 @@
       </c>
       <c r="U52" s="3" t="inlineStr">
         <is>
-          <t>European counterpart to the TNC MEL framework. Worth reading side-by-side when implementing the TNC framework in a European context.</t>
+          <t>Read alongside the TNC framework when working in a European context.</t>
         </is>
       </c>
       <c r="V52" s="3" t="inlineStr">
@@ -10922,11 +11600,26 @@
       <c r="AN52" s="19" t="n"/>
       <c r="AO52" s="19" t="n"/>
       <c r="AP52" s="19" t="n"/>
+      <c r="AQ52" s="16" t="inlineStr">
+        <is>
+          <t>European Framework for Seaweed Ecosystem-Service Evaluation (Reference)</t>
+        </is>
+      </c>
+      <c r="AR52" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tonk, L; Jansen, HM; Poelman, M; Nauta, RW; Jak, RG; Tamis, JE; Jongbloed, RH; Tonk, L; Jansen, HM; Poelman, M; </t>
+        </is>
+      </c>
+      <c r="AS52" s="16" t="inlineStr">
+        <is>
+          <t>European counterpart to the TNC MEL framework. Worth reading side-by-side when implementing the TNC framework in a European context.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="240" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Corrigan, Sophie; Brown, A. Ross; Tyler, Charles R.; Wilding, Catherine; Daniels, Carly; Ashton, Ian G. C.; Smale, Dan A.;</t>
+          <t>Corrigan, S., et al.</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -11013,11 +11706,7 @@
           <t>https://www.mdpi.com/2075-1729/13/1/209 ; PMC: https://pmc.ncbi.nlm.nih.gov/articles/PMC9865293/</t>
         </is>
       </c>
-      <c r="U53" s="4" t="inlineStr">
-        <is>
-          <t>Same Exeter / MBA group as Corrigan 2022. Together the two papers form a "what to do (2022 review) → how to do it (2023 protocol)" pair. Particularly strong for European Saccharina farms.</t>
-        </is>
-      </c>
+      <c r="U53" s="4" t="inlineStr"/>
       <c r="V53" s="4" t="inlineStr">
         <is>
           <t>Provided by Claude (chased from Corrigan 2022 &amp; Schutt 2023)</t>
@@ -11111,11 +11800,26 @@
       <c r="AN53" s="19" t="n"/>
       <c r="AO53" s="19" t="n"/>
       <c r="AP53" s="19" t="n"/>
+      <c r="AQ53" s="16" t="inlineStr">
+        <is>
+          <t>Seasonal Epibiont Assemblage Development on Cultivated Kelp</t>
+        </is>
+      </c>
+      <c r="AR53" s="16" t="inlineStr">
+        <is>
+          <t>Corrigan, Sophie; Brown, A. Ross; Tyler, Charles R.; Wilding, Catherine; Daniels, Carly; Ashton, Ian G. C.; Smale, Dan A.;</t>
+        </is>
+      </c>
+      <c r="AS53" s="16" t="inlineStr">
+        <is>
+          <t>Same Exeter / MBA group as Corrigan 2022. Together the two papers form a "what to do (2022 review) → how to do it (2023 protocol)" pair. Particularly strong for European Saccharina farms.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="240" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Bekkby, Trine; Torstensen, Ragnhild Ryther Grimm; Grünfeld, Lars Andreas Holm; Gundersen, Hege; Fredriksen, Stein; Rinde, Eli; Christie, Hartvig; Walday, Mats; Andersen, Guri Sogn; Brkljacic, Marijana S.; Neves, Luiza; Hancke, Kasper;</t>
+          <t>Bekkby, T., et al.</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -11200,11 +11904,7 @@
           <t>https://www.frontiersin.org/articles/10.3389/fmars.2023.1066101 ; DOAJ: https://doaj.org/article/8730b202079045fe863baffa3d6215b6</t>
         </is>
       </c>
-      <c r="U54" s="4" t="inlineStr">
-        <is>
-          <t>Norwegian Saccharina/Alaria farm vs. wild kelp forest reference — directly executes the MEL framework Archetype 3/4 sampling logic (farm-vs-similar-wild-habitat). Good companion to Schutt 2023 (Gulf of Maine, sponges) and Corrigan 2023 (UK, harvest-paired plants). | v1.4 refinement: Z corrected — I-column describes "farm vs similar-structure wild reference" (Archetype 3/4 community-composition sampling), which is H&amp;B 2.1.1 not H&amp;B 1.2.1 (mobile fauna). Chat A inconsistency between I-col reasoning and Z label.</t>
-        </is>
-      </c>
+      <c r="U54" s="4" t="inlineStr"/>
       <c r="V54" s="4" t="inlineStr">
         <is>
           <t>Provided by Claude (chased from Schutt 2023)</t>
@@ -11298,11 +11998,26 @@
       <c r="AN54" s="19" t="n"/>
       <c r="AO54" s="19" t="n"/>
       <c r="AP54" s="19" t="n"/>
+      <c r="AQ54" s="16" t="inlineStr">
+        <is>
+          <t>Kelp-Farm vs Wild-Forest Mobile-Fauna Comparison</t>
+        </is>
+      </c>
+      <c r="AR54" s="16" t="inlineStr">
+        <is>
+          <t>Bekkby, Trine; Torstensen, Ragnhild Ryther Grimm; Grünfeld, Lars Andreas Holm; Gundersen, Hege; Fredriksen, Stein; Rinde, Eli; Christie, Hartvig; Walday, Mats; Andersen, Guri Sogn; Brkljacic, Marijana S.; Neves, Luiza; Hancke, Kasper;</t>
+        </is>
+      </c>
+      <c r="AS54" s="16" t="inlineStr">
+        <is>
+          <t>Norwegian Saccharina/Alaria farm vs. wild kelp forest reference — directly executes the MEL framework Archetype 3/4 sampling logic (farm-vs-similar-wild-habitat). Good companion to Schutt 2023 (Gulf of Maine, sponges) and Corrigan 2023 (UK, harvest-paired plants). | v1.4 refinement: Z corrected — I-column describes "farm vs similar-structure wild reference" (Archetype 3/4 community-composition sampling), which is H&amp;B 2.1.1 not H&amp;B 1.2.1 (mobile fauna). Chat A inconsistency between I-col reasoning and Z label.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="240" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Dickson, Andrew G.; Sabine, Christopher L.; Christian, James R. (Eds.);</t>
+          <t>Dickson, A. G., et al.</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -11389,7 +12104,7 @@
       </c>
       <c r="U55" s="4" t="inlineStr">
         <is>
-          <t>Not on the original 55-paper list but is the methodological backbone for any paper measuring pH/TA/DIC/pCO₂ in seaweed-farm waters (including Xiao 2021). For practitioners, the takeaway is that a partner lab will follow these SOPs; the farmer side is sample collection following SOP 1.</t>
+          <t>The methodological backbone for any pH/alkalinity/DIC/pCO2 work - in practice a partner lab runs these SOPs.</t>
         </is>
       </c>
       <c r="V55" s="4" t="inlineStr">
@@ -11485,11 +12200,26 @@
       <c r="AN55" s="19" t="n"/>
       <c r="AO55" s="19" t="n"/>
       <c r="AP55" s="19" t="n"/>
+      <c r="AQ55" s="16" t="inlineStr">
+        <is>
+          <t>Standard SOPs for Seawater Carbonate-System Measurement</t>
+        </is>
+      </c>
+      <c r="AR55" s="16" t="inlineStr">
+        <is>
+          <t>Dickson, Andrew G.; Sabine, Christopher L.; Christian, James R. (Eds.);</t>
+        </is>
+      </c>
+      <c r="AS55" s="16" t="inlineStr">
+        <is>
+          <t>Not on the original 55-paper list but is the methodological backbone for any paper measuring pH/TA/DIC/pCO₂ in seaweed-farm waters (including Xiao 2021). For practitioners, the takeaway is that a partner lab will follow these SOPs; the farmer side is sample collection following SOP 1.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="240" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Walls, A. M.; Edwards, M. D.; Firth, L. B.; Johnson, M. P.;</t>
+          <t>Walls, A. M., et al.</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -11576,7 +12306,7 @@
       </c>
       <c r="U56" s="4" t="inlineStr">
         <is>
-          <t>Complements Corrigan 2023 by covering Alaria rather than Saccharina, and adds the predictability question (can epibiont arrival times be forecast year-to-year?). Useful for farms wanting to use harvest timing to manage epibiont colonisation.</t>
+          <t>Useful if you want to time harvest to manage epibiont fouling.</t>
         </is>
       </c>
       <c r="V56" s="4" t="inlineStr">
@@ -11672,11 +12402,26 @@
       <c r="AN56" s="19" t="n"/>
       <c r="AO56" s="19" t="n"/>
       <c r="AP56" s="19" t="n"/>
+      <c r="AQ56" s="16" t="inlineStr">
+        <is>
+          <t>Seasonal Fouling-Community Succession on Cultivated Kelp</t>
+        </is>
+      </c>
+      <c r="AR56" s="16" t="inlineStr">
+        <is>
+          <t>Walls, A. M.; Edwards, M. D.; Firth, L. B.; Johnson, M. P.;</t>
+        </is>
+      </c>
+      <c r="AS56" s="16" t="inlineStr">
+        <is>
+          <t>Complements Corrigan 2023 by covering Alaria rather than Saccharina, and adds the predictability question (can epibiont arrival times be forecast year-to-year?). Useful for farms wanting to use harvest timing to manage epibiont colonisation.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="240" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Mercaldo-Allen, Renee; Clark, Paul; Liu, Yuan; Phillips, Genevieve; Redman, Dylan; Auster, Peter J.; Estela, Eric; Milke, Lisa; Verkade, Alison; Rose, Julie M.;</t>
+          <t>Mercaldo-Allen, R., et al.</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -11761,11 +12506,7 @@
           <t>https://www.frontiersin.org/articles/10.3389/fmars.2021.690474/full</t>
         </is>
       </c>
-      <c r="U57" s="4" t="inlineStr">
-        <is>
-          <t>A clean, NOAA-led protocol for eDNA at aquaculture infrastructure that is directly transferable to seaweed-farm settings. Useful template for any monitoring programme considering adding an eDNA layer per the English 2024 review.</t>
-        </is>
-      </c>
+      <c r="U57" s="4" t="inlineStr"/>
       <c r="V57" s="4" t="inlineStr">
         <is>
           <t>Provided by Claude (chased from English et al. 2024 review)</t>
@@ -11859,11 +12600,26 @@
       <c r="AN57" s="19" t="n"/>
       <c r="AO57" s="19" t="n"/>
       <c r="AP57" s="19" t="n"/>
+      <c r="AQ57" s="16" t="inlineStr">
+        <is>
+          <t>eDNA Biodiversity Survey of Farm Structures</t>
+        </is>
+      </c>
+      <c r="AR57" s="16" t="inlineStr">
+        <is>
+          <t>Mercaldo-Allen, Renee; Clark, Paul; Liu, Yuan; Phillips, Genevieve; Redman, Dylan; Auster, Peter J.; Estela, Eric; Milke, Lisa; Verkade, Alison; Rose, Julie M.;</t>
+        </is>
+      </c>
+      <c r="AS57" s="16" t="inlineStr">
+        <is>
+          <t>A clean, NOAA-led protocol for eDNA at aquaculture infrastructure that is directly transferable to seaweed-farm settings. Useful template for any monitoring programme considering adding an eDNA layer per the English 2024 review.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="240" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>McKindsey, Christopher W; Anderson, M Robin; Barnes, Penelope; Courtenay, Simon; Landry, Thomas; Skinner, Marc</t>
+          <t>McKindsey, C. W., et al.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -11947,11 +12703,6 @@
       <c r="T58" t="inlineStr">
         <is>
           <t>https://www.dfo-mpo.gc.ca/csas-sccs/Publications/ResDocs-DocRech/2006/2006_011-eng.htm</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Foundational DFO synthesis on bivalve aquaculture / fish habitat interactions, written as a companion to Chamberlain et al. 2006 (PZDN models) and Cranford et al. 2006 (indicators &amp; thresholds). Argues for ecosystem-services framing — bivalve farms function partly as artificial reefs, supporting epifauna, mobile macroinvertebrates and fishes — aligning with the MEL framework's 'regenerative' perspective. Covers East Coast (Mytilus edulis, M. trossulus, C. virginica) and West Coast Canada (C. gigas, V. philippinarum, scallops).</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -12047,11 +12798,26 @@
       <c r="AN58" s="19" t="n"/>
       <c r="AO58" s="19" t="n"/>
       <c r="AP58" s="19" t="n"/>
+      <c r="AQ58" s="16" t="inlineStr">
+        <is>
+          <t>Methods for Shellfish-Aquaculture Effects on Fish Habitat (Synthesis)</t>
+        </is>
+      </c>
+      <c r="AR58" s="16" t="inlineStr">
+        <is>
+          <t>McKindsey, Christopher W; Anderson, M Robin; Barnes, Penelope; Courtenay, Simon; Landry, Thomas; Skinner, Marc</t>
+        </is>
+      </c>
+      <c r="AS58" s="16" t="inlineStr">
+        <is>
+          <t>Foundational DFO synthesis on bivalve aquaculture / fish habitat interactions, written as a companion to Chamberlain et al. 2006 (PZDN models) and Cranford et al. 2006 (indicators &amp; thresholds). Argues for ecosystem-services framing — bivalve farms function partly as artificial reefs, supporting epifauna, mobile macroinvertebrates and fishes — aligning with the MEL framework's 'regenerative' perspective. Covers East Coast (Mytilus edulis, M. trossulus, C. virginica) and West Coast Canada (C. gigas, V. philippinarum, scallops).</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="240" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DeAlteris, Joseph T; Kilpatrick, Brian D; Rheault, Robert B</t>
+          <t>DeAlteris, J. T., et al.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12145,7 +12911,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>Strong methodological template for habitat-value comparison of on-bottom oyster cages vs SAV vs bare seabed. The lift-net + emergent-surface-area approach is transferable to other rack/cage aquaculture types. Findings (SAG habitat value ≥ SAV, &gt;&gt; NVSB) are evidence for the ecosystem-service framing of mollusk aquaculture.</t>
+          <t>The lift-net plus surface-area approach transfers to other rack/cage aquaculture types.</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -12241,11 +13007,26 @@
       <c r="AN59" s="19" t="n"/>
       <c r="AO59" s="19" t="n"/>
       <c r="AP59" s="19" t="n"/>
+      <c r="AQ59" s="16" t="inlineStr">
+        <is>
+          <t>Habitat Value of On-Bottom Oyster Cages vs Natural Habitats</t>
+        </is>
+      </c>
+      <c r="AR59" s="16" t="inlineStr">
+        <is>
+          <t>DeAlteris, Joseph T; Kilpatrick, Brian D; Rheault, Robert B</t>
+        </is>
+      </c>
+      <c r="AS59" s="16" t="inlineStr">
+        <is>
+          <t>Strong methodological template for habitat-value comparison of on-bottom oyster cages vs SAV vs bare seabed. The lift-net + emergent-surface-area approach is transferable to other rack/cage aquaculture types. Findings (SAG habitat value ≥ SAV, &gt;&gt; NVSB) are evidence for the ecosystem-service framing of mollusk aquaculture.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="240" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mascorda-Cabre, Llucia; Sheehan, Emma V; Attrill, Martin J; Hosegood, Phil</t>
+          <t>Mascorda-Cabre, L., et al.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12336,7 +13117,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Hydrodynamic characterisation of an offshore longline mussel farm — informs siting and design of offshore shellfish/seaweed farms. Methodology transfers to offshore seaweed contexts (parallel to St-Gelais 2022 in row 51). | v1.4 refinement: Retagged from Cross-cutting/framework to CC 3.1.1 (Wave attenuation/coastal protection) — paper directly measures wave attenuation at offshore mussel farm via M-ADCP + VM-ADCP. v1.3 used Cross-cutting/framework because CC 3.1.1 didn't exist; v1.4 framework adds the indicator. Direct measurement, no Sub-rule 1c needed.</t>
+          <t>A physical/siting characterisation rather than a biological or chemical indicator; transfers to offshore seaweed.</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -12432,11 +13213,26 @@
       <c r="AN60" s="19" t="n"/>
       <c r="AO60" s="19" t="n"/>
       <c r="AP60" s="19" t="n"/>
+      <c r="AQ60" s="16" t="inlineStr">
+        <is>
+          <t>Current &amp; Wave Changes Around an Offshore Mussel Farm (ADCP)</t>
+        </is>
+      </c>
+      <c r="AR60" s="16" t="inlineStr">
+        <is>
+          <t>Mascorda-Cabre, Llucia; Sheehan, Emma V; Attrill, Martin J; Hosegood, Phil</t>
+        </is>
+      </c>
+      <c r="AS60" s="16" t="inlineStr">
+        <is>
+          <t>Hydrodynamic characterisation of an offshore longline mussel farm — informs siting and design of offshore shellfish/seaweed farms. Methodology transfers to offshore seaweed contexts (parallel to St-Gelais 2022 in row 51). | v1.4 refinement: Retagged from Cross-cutting/framework to CC 3.1.1 (Wave attenuation/coastal protection) — paper directly measures wave attenuation at offshore mussel farm via M-ADCP + VM-ADCP. v1.3 used Cross-cutting/framework because CC 3.1.1 didn't exist; v1.4 framework adds the indicator. Direct measurement, no Sub-rule 1c needed.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="240" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Borja, Ángel; Rodríguez, J Germán; Black, Kenny; Bodoy, Alain; Emblow, Chris; Fernandes, Teresa F; Forte, Janez; Karakassis, Ioannis; Muxika, Iñigo; Nickell, Thom D; Papageorgiou, Nafsika; Pranovi, Fabio; Sevastou, Katerina; Tomassetti, Paolo; Angel, Dror</t>
+          <t>Borja, Á., et al.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12527,7 +13323,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Multi-tagged Finfish+Mollusk per Rule 2: methodology (AMBI / ITI for organic enrichment) transfers between finfish and bivalve sites — the paper explicitly applies both indices across both farm types. Strong methodological template for benthic monitoring at shellfish farms in Europe.</t>
+          <t>AMBI and ITI respond most consistently to aquaculture enrichment, and work across finfish and bivalve sites.</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -12623,11 +13419,26 @@
       <c r="AN61" s="19" t="n"/>
       <c r="AO61" s="19" t="n"/>
       <c r="AP61" s="19" t="n"/>
+      <c r="AQ61" s="16" t="inlineStr">
+        <is>
+          <t>Benthic Indices (AMBI/ITI) for Farm Organic-Enrichment Impact</t>
+        </is>
+      </c>
+      <c r="AR61" s="16" t="inlineStr">
+        <is>
+          <t>Borja, Ángel; Rodríguez, J Germán; Black, Kenny; Bodoy, Alain; Emblow, Chris; Fernandes, Teresa F; Forte, Janez; Karakassis, Ioannis; Muxika, Iñigo; Nickell, Thom D; Papageorgiou, Nafsika; Pranovi, Fabio; Sevastou, Katerina; Tomassetti, Paolo; Angel, Dror</t>
+        </is>
+      </c>
+      <c r="AS61" s="16" t="inlineStr">
+        <is>
+          <t>Multi-tagged Finfish+Mollusk per Rule 2: methodology (AMBI / ITI for organic enrichment) transfers between finfish and bivalve sites — the paper explicitly applies both indices across both farm types. Strong methodological template for benthic monitoring at shellfish farms in Europe.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Schmidt, Wiebke; Raymond, David; Parish, David; Ashton, Ian G C; Miller, Peter I; Campos, Carlos J A; Shutler, Jamie D</t>
+          <t>Schmidt, W., et al.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12658,7 +13469,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Design + deployment of low-cost (&lt;£5K) autonomous monitoring buoy with sensors for T, salinity, water level, DO. Two deployments totaling 14 months (St Austell Bay mussel farm + estuary). Designed for non-scientific staff. Maps to WQ 1.2.1 (DO) and supports detection of harmful algae (Dinophysis) → tied to WQ 2.1.2.</t>
+          <t>Design + deployment of low-cost (&lt;£5K) autonomous monitoring buoy with sensors for T, salinity, water level, DO. Two deployments totaling 14 months (St Austell Bay mussel farm + estuary). Designed for non-scientific staff. Maps to WQ 1.2.1 (DO). (Physico-chemical proxies flag harmful-algae risk, but the buoy does not directly monitor microorganisms.)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -12716,9 +13527,9 @@
           <t>https://doi.org/10.1016/j.aquaeng.2017.12.002</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Practitioner-grade WQ monitoring paper for the mollusk database. Low-cost, robust, non-specialist operation — directly transferable to small/mid commercial shellfish operators. Strong complement to commercial systems like Berger 2024 (row 8) on the seaweed side.</t>
+      <c r="U62" s="16" t="inlineStr">
+        <is>
+          <t>Biofouling is the single biggest limiter of accuracy and deployment length — use antifouling guards, clean at every visit, and keep the QC rules that catch fouling drift. Storms can tangle the instrument string around the float or part the surface buoy from the mooring; a robust mooring and the pressure-sensor surface-flag mitigate this. Validation is only as good as the reference instrument — confirm it is calibrated and working. Some sensors (dissolved oxygen, conductivity) drift and need periodic recalibration. The buoy characterises physico-chemical water quality (DO, temperature, salinity); it does not directly measure microorganisms or algae.</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -12743,7 +13554,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>WQ 1.2.1 — Dissolved oxygen, WQ 2.1.2 — Microorganisms</t>
+          <t>WQ 1.2.1 — Dissolved oxygen</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12798,7 +13609,7 @@
       </c>
       <c r="AK62" s="16" t="inlineStr">
         <is>
-          <t>To monitor water quality continuously at your farm with minimal effort, moor a low-power sensor string on a buoy and let it log automatically. Fit sensors for the parameters of interest — here temperature at several depths, conductivity/salinity, dissolved oxygen and pressure (depth) — set them to log on a fixed short interval (e.g. every 10 minutes), and calibrate the DO sensor before deployment. Leave the string in place for months, visiting periodically (e.g. monthly) to lift the lightweight instrument chain with a boat hook or the winch you use for mussel lines, download the data to a handheld shuttle, and scrub off biofouling. Then clean the data with simple quality-control rules: drop readings outside sensible ranges, discard the first couple of hours after each deployment or cleaning, remove sudden single-point spikes, and cut the gradual drift that builds before each cleaning (biofouling); convert conductivity to salinity in software. The pressure sensor also flags when the string has floated to the surface, so those readings can be excluded.</t>
+          <t>To monitor water quality continuously at your farm with minimal effort, moor a low-power sensor string on a buoy and let it log automatically. Fit sensors for the parameters of interest — here temperature at several depths, conductivity/salinity, dissolved oxygen and pressure (depth) — set them to log on a fixed short interval (e.g. every 10 minutes), and calibrate the DO sensor before deployment. Leave the string in place for months, visiting periodically (e.g. monthly) to lift the lightweight instrument chain, download the data to a handheld shuttle, scrub off biofouling, and take a reading with a calibrated reference (e.g. a hand-held CTD) to check sensor accuracy (RMSE and bias). Then clean the data with simple quality-control rules: drop readings outside sensible ranges, discard the first couple of hours after each deployment or cleaning, remove sudden single-point spikes, and cut the gradual biofouling drift before each cleaning; convert conductivity to salinity in software. The pressure sensor also flags when the string has floated to the surface, so those readings can be excluded.</t>
         </is>
       </c>
       <c r="AL62" s="17" t="inlineStr">
@@ -12824,13 +13635,28 @@
       <c r="AP62" s="19" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/workbooks/schmidt_2018.xlsx</t>
+        </is>
+      </c>
+      <c r="AQ62" s="16" t="inlineStr">
+        <is>
+          <t>Continuous Water-Quality Monitoring with a Low-Cost Autonomous Sensor Buoy</t>
+        </is>
+      </c>
+      <c r="AR62" s="16" t="inlineStr">
+        <is>
+          <t>Schmidt, Wiebke; Raymond, David; Parish, David; Ashton, Ian G C; Miller, Peter I; Campos, Carlos J A; Shutler, Jamie D</t>
+        </is>
+      </c>
+      <c r="AS62" s="16" t="inlineStr">
+        <is>
+          <t>Practitioner-grade WQ monitoring paper for the mollusk database. Low-cost, robust, non-specialist operation — directly transferable to small/mid commercial shellfish operators. Strong complement to commercial systems like Berger 2024 (row 8) on the seaweed side.  |  Indicator trim (2026-08-06): WQ 2.1.2 (microorganisms) removed from the monitored set — buoy infers harmful-algae risk from DO/temperature proxies; direct detection was external agency sampling. Monitored: WQ 1.2.1.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pinkerton, Matt; Gall, Mark; Wood, Simon; Zeldis, John</t>
+          <t>Pinkerton, M., et al.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12921,7 +13747,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>Strongest remote-sensing protocol in the mollusk database for measuring large-scale (multi-km) farm effects on chl-a. Methodologically parallel to Bell 2020 (row 39) on the seaweed side. Effect size is small (−1.6% chl-a) — useful negative-result framing for managing detectability expectations at scale.</t>
+          <t>The effect is small (~-1.6% chlorophyll), so set realistic expectations - this suits multi-kilometre farms.</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -13017,11 +13843,26 @@
       <c r="AN63" s="19" t="n"/>
       <c r="AO63" s="19" t="n"/>
       <c r="AP63" s="19" t="n"/>
+      <c r="AQ63" s="16" t="inlineStr">
+        <is>
+          <t>Satellite Detection of Large-Farm Chlorophyll Effects</t>
+        </is>
+      </c>
+      <c r="AR63" s="16" t="inlineStr">
+        <is>
+          <t>Pinkerton, Matt; Gall, Mark; Wood, Simon; Zeldis, John</t>
+        </is>
+      </c>
+      <c r="AS63" s="16" t="inlineStr">
+        <is>
+          <t>Strongest remote-sensing protocol in the mollusk database for measuring large-scale (multi-km) farm effects on chl-a. Methodologically parallel to Bell 2020 (row 39) on the seaweed side. Effect size is small (−1.6% chl-a) — useful negative-result framing for managing detectability expectations at scale.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cranford, Peter J; Strain, Peter M; Dowd, Michael; Hargrave, Barry T; Grant, Jonathan; Archambault, Marie-Claude</t>
+          <t>Cranford, P. J., et al.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13112,7 +13953,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>v1.2 Sub-rule 1a worked example — bioextraction-as-component still gets WQ 1.1.1. Foundational template for whole-bay nutrient-budget approach to shellfish farms; integrates with Chamberlain et al. 2006 carrying-capacity work (Cranford 2006 paper still missing from project folder).</t>
+          <t>The harvested-nitrogen term is the bioextraction measure and needs tissue analysis scaled to farm area.</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -13208,11 +14049,26 @@
       <c r="AN64" s="19" t="n"/>
       <c r="AO64" s="19" t="n"/>
       <c r="AP64" s="19" t="n"/>
+      <c r="AQ64" s="16" t="inlineStr">
+        <is>
+          <t>Whole-Bay Nitrogen Budget for a Mussel Farm</t>
+        </is>
+      </c>
+      <c r="AR64" s="16" t="inlineStr">
+        <is>
+          <t>Cranford, Peter J; Strain, Peter M; Dowd, Michael; Hargrave, Barry T; Grant, Jonathan; Archambault, Marie-Claude</t>
+        </is>
+      </c>
+      <c r="AS64" s="16" t="inlineStr">
+        <is>
+          <t>v1.2 Sub-rule 1a worked example — bioextraction-as-component still gets WQ 1.1.1. Foundational template for whole-bay nutrient-budget approach to shellfish farms; integrates with Chamberlain et al. 2006 carrying-capacity work (Cranford 2006 paper still missing from project folder).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kaspar, H F; Gillespie, P A; Boyer, I C; MacKenzie, A L</t>
+          <t>Kaspar, H. F., et al.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -13303,7 +14159,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>Foundational early study (1985) on shellfish-aquaculture N biogeochemistry. The on-rope denitrification measurement (mussel-rope detritus communities denitrifying 2× the farm sediment rate, 10× reference sediment rate) is a methodological innovation still rare in newer studies. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — paper explicitly measures denitrification, including the methodological innovation that mussel-rope detritus communities denitrify 2× sediment rate and 10× reference. WQ 1.1.2 added to v1.4 framework (mollusc-only); previously missing from v1.3.</t>
+          <t>The rope-detritus community can denitrify several times faster than the sediment, so incubate rope material separately.</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -13399,11 +14255,26 @@
       <c r="AN65" s="19" t="n"/>
       <c r="AO65" s="19" t="n"/>
       <c r="AP65" s="19" t="n"/>
+      <c r="AQ65" s="16" t="inlineStr">
+        <is>
+          <t>Nitrogen Removal &amp; Denitrification at a Mussel Farm</t>
+        </is>
+      </c>
+      <c r="AR65" s="16" t="inlineStr">
+        <is>
+          <t>Kaspar, H F; Gillespie, P A; Boyer, I C; MacKenzie, A L</t>
+        </is>
+      </c>
+      <c r="AS65" s="16" t="inlineStr">
+        <is>
+          <t>Foundational early study (1985) on shellfish-aquaculture N biogeochemistry. The on-rope denitrification measurement (mussel-rope detritus communities denitrifying 2× the farm sediment rate, 10× reference sediment rate) is a methodological innovation still rare in newer studies. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — paper explicitly measures denitrification, including the methodological innovation that mussel-rope detritus communities denitrify 2× sediment rate and 10× reference. WQ 1.1.2 added to v1.4 framework (mollusc-only); previously missing from v1.3.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nizzoli, Daniele; Bartoli, Marco; Viaroli, Pierluigi</t>
+          <t>Nizzoli, D., et al.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13494,7 +14365,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>Direct bioextraction template for benthic mollusk culture (Manila clam) — pairs with Cranford 2007 (suspended mussel) for an end-to-end methodological pair across the two main mollusk farming modes. Result: only ~6% of biodeposited N and ~3% of P leave via harvest. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — in-situ intact-core incubations (canonical Sacca di Goro denitrification methodology); N+P budget closure (~6% leak) implies denitrification quantification. Confirm via PDF if precise k_denit values are needed for protocol replication.</t>
+          <t>Expect only a small fraction of biodeposited nutrients (~6% N, ~3% P) to actually leave via harvest - the rest is recycled or buried.</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -13590,11 +14461,26 @@
       <c r="AN66" s="19" t="n"/>
       <c r="AO66" s="19" t="n"/>
       <c r="AP66" s="19" t="n"/>
+      <c r="AQ66" s="16" t="inlineStr">
+        <is>
+          <t>Nitrogen &amp; Phosphorus Budget Over a Clam-Farming Cycle</t>
+        </is>
+      </c>
+      <c r="AR66" s="16" t="inlineStr">
+        <is>
+          <t>Nizzoli, Daniele; Bartoli, Marco; Viaroli, Pierluigi</t>
+        </is>
+      </c>
+      <c r="AS66" s="16" t="inlineStr">
+        <is>
+          <t>Direct bioextraction template for benthic mollusk culture (Manila clam) — pairs with Cranford 2007 (suspended mussel) for an end-to-end methodological pair across the two main mollusk farming modes. Result: only ~6% of biodeposited N and ~3% of P leave via harvest. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — in-situ intact-core incubations (canonical Sacca di Goro denitrification methodology); N+P budget closure (~6% leak) implies denitrification quantification. Confirm via PDF if precise k_denit values are needed for protocol replication.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Nizzoli, Daniele; Welsh, David T; Bartoli, Marco; Viaroli, Pierluigi</t>
+          <t>Nizzoli, D., et al.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13685,7 +14571,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Critical methodological insight: ignoring the rope-community contribution to O₂/N fluxes leads to gross underestimation of farm impacts. Counters the simple 'filter feeders are nutrient sinks' narrative — when biodeposition + rope community are integrated, net effect can be neutral or positive for water-column nutrient loading. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — mussel rope + sediment intact-core incubations with O₂ + N + P flux measurements (canonical Sacca di Goro denitrification methodology). Confirm via PDF.</t>
+          <t>Key point: the rope community drives most of the farm's oxygen demand and nutrient regeneration, so a sediment-only survey badly underestimates impact.</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -13781,11 +14667,26 @@
       <c r="AN67" s="19" t="n"/>
       <c r="AO67" s="19" t="n"/>
       <c r="AP67" s="19" t="n"/>
+      <c r="AQ67" s="16" t="inlineStr">
+        <is>
+          <t>True Oxygen &amp; Nutrient Fluxes of a Suspended Mussel Farm</t>
+        </is>
+      </c>
+      <c r="AR67" s="16" t="inlineStr">
+        <is>
+          <t>Nizzoli, Daniele; Welsh, David T; Bartoli, Marco; Viaroli, Pierluigi</t>
+        </is>
+      </c>
+      <c r="AS67" s="16" t="inlineStr">
+        <is>
+          <t>Critical methodological insight: ignoring the rope-community contribution to O₂/N fluxes leads to gross underestimation of farm impacts. Counters the simple 'filter feeders are nutrient sinks' narrative — when biodeposition + rope community are integrated, net effect can be neutral or positive for water-column nutrient loading. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — mussel rope + sediment intact-core incubations with O₂ + N + P flux measurements (canonical Sacca di Goro denitrification methodology). Confirm via PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Nizzoli, Daniele; Welsh, David Thomas; Viaroli, Pierluigi</t>
+          <t>Nizzoli, D., et al.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13868,7 +14769,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Key conclusion: filter-feeding bivalves are not an automatic eutrophication buffer — particularly in summer, regeneration overwhelms removal. Directly relevant methodological template for comparing infaunal vs suspended culture at the same site. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — same Sacca di Goro intact-core methodology as R65/R66; N+P regeneration flux measurements 4–14× control sediments imply denitrification quantification. Confirm via PDF.</t>
+          <t>A reminder that filter feeders are not an automatic nutrient sink - in summer regeneration can overwhelm removal, so timing matters.</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -13964,11 +14865,26 @@
       <c r="AN68" s="19" t="n"/>
       <c r="AO68" s="19" t="n"/>
       <c r="AP68" s="19" t="n"/>
+      <c r="AQ68" s="16" t="inlineStr">
+        <is>
+          <t>Benthic Clam vs Suspended Mussel Nutrient-Flux Comparison</t>
+        </is>
+      </c>
+      <c r="AR68" s="16" t="inlineStr">
+        <is>
+          <t>Nizzoli, Daniele; Welsh, David Thomas; Viaroli, Pierluigi</t>
+        </is>
+      </c>
+      <c r="AS68" s="16" t="inlineStr">
+        <is>
+          <t>Key conclusion: filter-feeding bivalves are not an automatic eutrophication buffer — particularly in summer, regeneration overwhelms removal. Directly relevant methodological template for comparing infaunal vs suspended culture at the same site. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — same Sacca di Goro intact-core methodology as R65/R66; N+P regeneration flux measurements 4–14× control sediments imply denitrification quantification. Confirm via PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mizuta, D D; Silveira Júnior, N; Fischer, C E; Lemos, D</t>
+          <t>Mizuta, D. D., et al.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -14051,7 +14967,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>Underrepresented climate zone in v11 (subtropical SW Atlantic). Strong demonstration that satellite-derived chl-a is a usable predictor of commercial oyster yield — directly transferable to siting and climate-adaptation planning elsewhere.</t>
+          <t>Shows satellite chlorophyll-a can predict commercial oyster yield - relevant to siting and climate planning.</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -14137,11 +15053,21 @@
       <c r="AN69" s="19" t="n"/>
       <c r="AO69" s="19" t="n"/>
       <c r="AP69" s="19" t="n"/>
+      <c r="AR69" s="16" t="inlineStr">
+        <is>
+          <t>Mizuta, D D; Silveira Júnior, N; Fischer, C E; Lemos, D</t>
+        </is>
+      </c>
+      <c r="AS69" s="16" t="inlineStr">
+        <is>
+          <t>Underrepresented climate zone in v11 (subtropical SW Atlantic). Strong demonstration that satellite-derived chl-a is a usable predictor of commercial oyster yield — directly transferable to siting and climate-adaptation planning elsewhere.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Morozova, T V; Orlova, T Yu</t>
+          <t>Morozova, T. V. &amp; Orlova, T. Y.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -14231,11 +15157,6 @@
       <c r="T70" t="inlineStr">
         <is>
           <t>https://link.springer.com/journal/11179</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Uses the newly-added vocab entry Bay mussel (Mytilus trossulus) — exactly the species this v1.2→v1.3 vocab addition was for. Replicable HAB-detection-oriented monitoring protocol; bridges to the Schmidt 2018 Dinophysis use case.</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -14321,11 +15242,21 @@
       <c r="AN70" s="19" t="n"/>
       <c r="AO70" s="19" t="n"/>
       <c r="AP70" s="19" t="n"/>
+      <c r="AR70" s="16" t="inlineStr">
+        <is>
+          <t>Morozova, T V; Orlova, T Yu</t>
+        </is>
+      </c>
+      <c r="AS70" s="16" t="inlineStr">
+        <is>
+          <t>Uses the newly-added vocab entry Bay mussel (Mytilus trossulus) — exactly the species this v1.2→v1.3 vocab addition was for. Replicable HAB-detection-oriented monitoring protocol; bridges to the Schmidt 2018 Dinophysis use case.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pagani, Samuele</t>
+          <t>Pagani, S.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -14408,7 +15339,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>Multi-chapter doctoral thesis — treat as a single database entry but flag that individual chapters may warrant separate evaluation if TNC pulls specific methodologies. The anoxia-risk assessment framework (Ch.4 Goro) is the most novel methodological contribution and directly relevant for siting/risk management of lagoon mollusk farms. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — Chapter 3 explicitly uses ¹⁵N tracer experiments on oyster holobionts + sediment N pathways (microcosms), matching v1.4 indicator definition "Rate of denitrification (¹⁵N-pairing technique etc.)". Mollusc-specific indicator.</t>
+          <t>A menu of methods; the anoxia-risk framework for lagoon siting is its most distinctive contribution.</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -14504,11 +15435,26 @@
       <c r="AN71" s="19" t="n"/>
       <c r="AO71" s="19" t="n"/>
       <c r="AP71" s="19" t="n"/>
+      <c r="AQ71" s="16" t="inlineStr">
+        <is>
+          <t>Lagoon Biogeochemistry &amp; Anoxia-Risk Methods for Mollusc Culture (Thesis)</t>
+        </is>
+      </c>
+      <c r="AR71" s="16" t="inlineStr">
+        <is>
+          <t>Pagani, Samuele</t>
+        </is>
+      </c>
+      <c r="AS71" s="16" t="inlineStr">
+        <is>
+          <t>Multi-chapter doctoral thesis — treat as a single database entry but flag that individual chapters may warrant separate evaluation if TNC pulls specific methodologies. The anoxia-risk assessment framework (Ch.4 Goro) is the most novel methodological contribution and directly relevant for siting/risk management of lagoon mollusk farms. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — Chapter 3 explicitly uses ¹⁵N tracer experiments on oyster holobionts + sediment N pathways (microcosms), matching v1.4 indicator definition "Rate of denitrification (¹⁵N-pairing technique etc.)". Mollusc-specific indicator.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hossain, M Shahadat; Rothuis, Arjo; Chowdhury, Sayedur Rahman; Smaal, Aad; Ysebaert, Tom; Sharifuzzaman, S M; van Sluis, Christiaan; Hellegers, Petra; van Duijn, Arie; Dankers, Petra; Chowdhury, Shah Nawaz; Sarker, Subrata</t>
+          <t>Hossain, M. S., et al.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -14544,7 +15490,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>24-week field experiment (May–Oct 2012) testing 4 substrates (windowpane shell, live oyster shell, dead oyster shell, stone/rubble) for natural oyster spat collection on bamboo mattresses at Cox's Bazar, Bangladesh. Fortnightly photographic counts; water-quality monitoring; Landsat + ArcGIS site mapping. Frames oyster reefs as 'living shoreline' for coastal defense + food production. Maps to H&amp;B 1.1.1 (epibiota, spat settlement), H&amp;B 2.2.1 (Spawning/recruitment), Cross-cutting (ecosystem-services framing).</t>
+          <t>24-week field experiment (May–Oct 2012) testing 4 substrates (windowpane shell, live oyster shell, dead oyster shell, stone/rubble) for natural oyster spat collection on bamboo mattresses at Cox's Bazar, Bangladesh. Fortnightly photographic counts; water-quality monitoring; Landsat + ArcGIS site mapping. Frames oyster reefs as 'living shoreline' for coastal defense + food production. Maps to H&amp;B 1.1.1 (epibiota, spat settlement), H&amp;B 2.2.1 (Spawning/recruitment).</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -14602,9 +15548,9 @@
           <t>https://www.aquaasiapac.com/</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Strongest practitioner-grade tropical mollusk protocol in the database. Designed for community-led implementation; couples food production with ecosystem-engineering / coastal-defense framing. Methodologically transferable to other tropical / developing-country contexts. Note: this is a magazine article (not peer-reviewed primary literature) but reports a substantive field experiment with replicable methods. | v1.4 refinement: Added CC 3.1.1 (Wave attenuation/coastal protection) per Sub-rule 1c — paper explicitly frames oyster reefs as "living shoreline" for coastal defense (Mollusc CC Obj 3.1). Cross-cutting/framework tag removed; the v1.4 indicator CC 3.1.1 now captures the coastal-protection contribution directly. Paper does not compute wave-decay coefficient itself but provides evidence toward the objective via reef-building framing.</t>
+      <c r="U72" s="16" t="inlineStr">
+        <is>
+          <t>Expect heavy post-settlement mortality where the season brings low salinity and high siltation; fouling organisms (anemones, snails, barnacles) compete for settlement space, and sediment smothering during heavy rain can kill or delay spat. Collector materials weaken in seawater and storms — plan for repairs. The photographic spat count/measure technique is defined by cited method papers (Loosanoff 1966; O'Sullivan 1978; Davenport &amp; Glasspool 1987; Hendriks 2005), not the source. The source does not fix replicate count, collector/compartment dimensions, or the instrument for each water-quality parameter — set these at your site.</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -14629,7 +15575,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.2.1 — Spawning, CC 3.1.1 — Wave attenuation / coastal protection</t>
+          <t>H&amp;B 1.1.1 — Epibiota, H&amp;B 2.2.1 — Spawning</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -14684,7 +15630,7 @@
       </c>
       <c r="AK72" s="16" t="inlineStr">
         <is>
-          <t>To find which substrate best recruits wild oyster spat for a community-scale collection or reef effort, build simple multi-compartment bamboo mattresses and fill the compartments with candidate substrates (for example windowpane shell, live oyster shell, dead oyster shell, and stone/rubble), deploying them side by side in the intertidal over a settlement season. Every two weeks photograph each compartment against a fixed quadrat reference (about 38 x 38 cm) and count settled spat from the images to track density over time, alongside basic water-quality readings. Compare substrate performance with a substrate-by-time analysis (for example PCA plus standard significance tests). The low-cost, locally-built design suits community-led implementation and doubles as an ecosystem-engineering, coastal-defence structure.</t>
+          <t>To find which substrate best recruits wild oyster spat for a community-scale collection or reef effort, build simple multi-compartment spat collectors (for example a locally-made bamboo-framed mattress) and fill the compartments with candidate substrates (such as windowpane shell, live oyster shell, dead oyster shell, and stone/rubble), deploying them side by side in the intertidal over a settlement season. Every two weeks — timed to the full and new moon — photograph each compartment against a fixed quadrat reference (about 38 x 38 cm) and, from the images, count settled spat and measure their length and width to track density, growth and survival over time, alongside basic water-quality readings. Compare substrate performance with a substrate-by-time analysis (for example PCA plus standard significance tests). The low-cost, locally-built design suits community-led implementation.</t>
         </is>
       </c>
       <c r="AL72" s="17" t="inlineStr">
@@ -14710,13 +15656,28 @@
       <c r="AP72" s="19" t="inlineStr">
         <is>
           <t>https://raw.githubusercontent.com/AquacultureScienceTNC/aquapip-survey/main/protocols/workbooks/hossain_2013.xlsx</t>
+        </is>
+      </c>
+      <c r="AQ72" s="16" t="inlineStr">
+        <is>
+          <t>Substrate-Comparison Monitoring of Oyster Spat Settlement</t>
+        </is>
+      </c>
+      <c r="AR72" s="16" t="inlineStr">
+        <is>
+          <t>Hossain, M Shahadat; Rothuis, Arjo; Chowdhury, Sayedur Rahman; Smaal, Aad; Ysebaert, Tom; Sharifuzzaman, S M; van Sluis, Christiaan; Hellegers, Petra; van Duijn, Arie; Dankers, Petra; Chowdhury, Shah Nawaz; Sarker, Subrata</t>
+        </is>
+      </c>
+      <c r="AS72" s="16" t="inlineStr">
+        <is>
+          <t>Strongest practitioner-grade tropical mollusk protocol in the database. Designed for community-led implementation; couples food production with ecosystem-engineering / coastal-defense framing. Methodologically transferable to other tropical / developing-country contexts. Note: this is a magazine article (not peer-reviewed primary literature) but reports a substantive field experiment with replicable methods. | v1.4 refinement: Added CC 3.1.1 (Wave attenuation/coastal protection) per Sub-rule 1c — paper explicitly frames oyster reefs as "living shoreline" for coastal defense (Mollusc CC Obj 3.1). Cross-cutting/framework tag removed; the v1.4 indicator CC 3.1.1 now captures the coastal-protection contribution directly. Paper does not compute wave-decay coefficient itself but provides evidence toward the objective via reef-building framing.  |  Indicator trim (2026-08-06): CC 3.1.1 (wave attenuation / coastal protection) removed from the monitored set — source frames oyster reefs as coastal defense and records wave height as context, but does not measure attenuation. Monitored: H&amp;B 1.1.1, H&amp;B 2.2.1.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Costello, Mark J; Basher, Zeenatul; McLeod, Laura; Asaad, Irawan; Claus, Simon; Vandepitte, Leen; Yasuhara, Moriaki; Gislason, Henrik; Edwards, Martin; Appeltans, Ward; Enevoldsen, Henrik; Edgar, Graham J; Miloslavich, Patricia; De Monte, Silvia; Sousa Pinto, Isabel; Obura, David; Bates, Amanda E</t>
+          <t>Costello, M. J., et al.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -14800,11 +15761,6 @@
       <c r="T73" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/978-3-319-27288-7_6</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Foundational cross-cutting methods reference for the entire MEL framework — every aquaculture-type database can benefit from this chapter. Introduces the EBV/EOV framework, conceptually parallel to TNC's MEL indicator structure. Multi-tagged across all aquaculture types per Rule 2 because the methodology surveyed transfers universally.</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -14900,11 +15856,26 @@
       <c r="AN73" s="19" t="n"/>
       <c r="AO73" s="19" t="n"/>
       <c r="AP73" s="19" t="n"/>
+      <c r="AQ73" s="16" t="inlineStr">
+        <is>
+          <t>Marine Biodiversity Sampling Methods (Cross-Cutting Reference)</t>
+        </is>
+      </c>
+      <c r="AR73" s="16" t="inlineStr">
+        <is>
+          <t>Costello, Mark J; Basher, Zeenatul; McLeod, Laura; Asaad, Irawan; Claus, Simon; Vandepitte, Leen; Yasuhara, Moriaki; Gislason, Henrik; Edwards, Martin; Appeltans, Ward; Enevoldsen, Henrik; Edgar, Graham J; Miloslavich, Patricia; De Monte, Silvia; Sousa Pinto, Isabel; Obura, David; Bates, Amanda E</t>
+        </is>
+      </c>
+      <c r="AS73" s="16" t="inlineStr">
+        <is>
+          <t>Foundational cross-cutting methods reference for the entire MEL framework — every aquaculture-type database can benefit from this chapter. Introduces the EBV/EOV framework, conceptually parallel to TNC's MEL indicator structure. Multi-tagged across all aquaculture types per Rule 2 because the methodology surveyed transfers universally.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ambrose, Alexandria; Munroe, Daphne</t>
+          <t>Ambrose, A. &amp; Munroe, D.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14983,11 +15954,6 @@
       <c r="T74" t="inlineStr">
         <is>
           <t>https://doi.org/10.2983/035.044.0XXX</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Abstract-only evaluation; J/AB/AC inferred from title + author affiliation (Munroe = Rutgers/NJ oyster ecologist). Confirm gear type and fauna methods from full text. Mid-Atlantic US oyster context highly likely.</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -15083,11 +16049,26 @@
       <c r="AN74" s="19" t="n"/>
       <c r="AO74" s="19" t="n"/>
       <c r="AP74" s="19" t="n"/>
+      <c r="AQ74" s="16" t="inlineStr">
+        <is>
+          <t>Fish &amp; Invertebrate Habitat Use on an Oyster Farm (Reference)</t>
+        </is>
+      </c>
+      <c r="AR74" s="16" t="inlineStr">
+        <is>
+          <t>Ambrose, Alexandria; Munroe, Daphne</t>
+        </is>
+      </c>
+      <c r="AS74" s="16" t="inlineStr">
+        <is>
+          <t>Abstract-only evaluation; J/AB/AC inferred from title + author affiliation (Munroe = Rutgers/NJ oyster ecologist). Confirm gear type and fauna methods from full text. Mid-Atlantic US oyster context highly likely.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cranford, Peter J; Anderson, Robin; Archambault, Philippe; Balch, Tim; Bates, Suzanne S; Bugden, Gary; Callier, Myriam D; Carver, Clare; Comeau, Luc; Hargrave, Barry; Harrison, W Glen; Horne, Edward; Kepkay, Paul E; Li, William K W; Mallet, Andre; Ouellette, Marc; Strain, Peter</t>
+          <t>Cranford, P. J., et al.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -15171,11 +16152,6 @@
       <c r="T75" t="inlineStr">
         <is>
           <t>https://www.dfo-mpo.gc.ca/csas-sccs/Publications/ResDocs-DocRech/2006/2006_034-eng.htm</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>PDF not present in project folder at chat 2 evaluation; values evaluated from DOI + title + sibling document (McKindsey 2006, row 58) context. WQ 1.1.1 inferred from broad 'indicators' scope (bioextraction routinely included in DFO framework) — confirm from full PDF when obtained. Companion to row 58.</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -15271,11 +16247,26 @@
       <c r="AN75" s="19" t="n"/>
       <c r="AO75" s="19" t="n"/>
       <c r="AP75" s="19" t="n"/>
+      <c r="AQ75" s="16" t="inlineStr">
+        <is>
+          <t>Indicators &amp; Thresholds for Shellfish-Aquaculture Impact (Synthesis)</t>
+        </is>
+      </c>
+      <c r="AR75" s="16" t="inlineStr">
+        <is>
+          <t>Cranford, Peter J; Anderson, Robin; Archambault, Philippe; Balch, Tim; Bates, Suzanne S; Bugden, Gary; Callier, Myriam D; Carver, Clare; Comeau, Luc; Hargrave, Barry; Harrison, W Glen; Horne, Edward; Kepkay, Paul E; Li, William K W; Mallet, Andre; Ouellette, Marc; Strain, Peter</t>
+        </is>
+      </c>
+      <c r="AS75" s="16" t="inlineStr">
+        <is>
+          <t>PDF not present in project folder at chat 2 evaluation; values evaluated from DOI + title + sibling document (McKindsey 2006, row 58) context. WQ 1.1.1 inferred from broad 'indicators' scope (bioextraction routinely included in DFO framework) — confirm from full PDF when obtained. Companion to row 58.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Edgar, Graham J; Macleod, Catriona K; Mawbey, Ron B; Shields, Damien</t>
+          <t>Edgar, G. J., et al.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -15366,7 +16357,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>Original system is Atlantic salmon (Finfish); benthic-impact methodology is directly transferable to mollusk farm monitoring (Rule 2). Multi-tagged Mollusk + Finfish — applies to both aquaculture types. Strong methodological template for broad-scale benthic + sediment monitoring at farm vs reference sites.</t>
+          <t>Developed at salmon farms; the method transfers directly to bivalve-farm benthic monitoring.</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -15462,11 +16453,26 @@
       <c r="AN76" s="19" t="n"/>
       <c r="AO76" s="19" t="n"/>
       <c r="AP76" s="19" t="n"/>
+      <c r="AQ76" s="16" t="inlineStr">
+        <is>
+          <t>Broad-Scale Benthic Impact Survey (Transferable to Bivalve Farms)</t>
+        </is>
+      </c>
+      <c r="AR76" s="16" t="inlineStr">
+        <is>
+          <t>Edgar, Graham J; Macleod, Catriona K; Mawbey, Ron B; Shields, Damien</t>
+        </is>
+      </c>
+      <c r="AS76" s="16" t="inlineStr">
+        <is>
+          <t>Original system is Atlantic salmon (Finfish); benthic-impact methodology is directly transferable to mollusk farm monitoring (Rule 2). Multi-tagged Mollusk + Finfish — applies to both aquaculture types. Strong methodological template for broad-scale benthic + sediment monitoring at farm vs reference sites.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sanchez-Jerez, Pablo; Krüger, Lotte; Casado-Coy, Nuria; Valle, Carlos; Carratalá, Adoración; Sanz-Lazaro, Carlos</t>
+          <t>Sanchez-Jerez, P., et al.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -15562,7 +16568,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Original system is finfish aquaculture; documents shell-debris accumulation under fish cages — methodologically informs benthic-substrate monitoring around bivalve farms by analogy. Multi-tagged Mollusk + Finfish per Rule 2 (transferable methodology).</t>
+          <t>Transfers by analogy to monitoring benthic-substrate change around bivalve farms.</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -15658,11 +16664,26 @@
       <c r="AN77" s="19" t="n"/>
       <c r="AO77" s="19" t="n"/>
       <c r="AP77" s="19" t="n"/>
+      <c r="AQ77" s="16" t="inlineStr">
+        <is>
+          <t>Shell-Debris Accumulation on the Seabed (Observational Reference)</t>
+        </is>
+      </c>
+      <c r="AR77" s="16" t="inlineStr">
+        <is>
+          <t>Sanchez-Jerez, Pablo; Krüger, Lotte; Casado-Coy, Nuria; Valle, Carlos; Carratalá, Adoración; Sanz-Lazaro, Carlos</t>
+        </is>
+      </c>
+      <c r="AS77" s="16" t="inlineStr">
+        <is>
+          <t>Original system is finfish aquaculture; documents shell-debris accumulation under fish cages — methodologically informs benthic-substrate monitoring around bivalve farms by analogy. Multi-tagged Mollusk + Finfish per Rule 2 (transferable methodology).</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sequeira, Ana; Ferreira, Joao Gomes; Hawkins, AJS; Nobre, Ana; Lourenço, Pedro; Zhang, X L; Yan, X; Nickell, Thom</t>
+          <t>Sequeira, A., et al.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -15758,7 +16779,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>Modelling framework paper. Likely uses FARM or ShellSIM models given co-authorship; confirm specifics from full text. WQ 1.1.1 may apply if the model couples bioextraction explicitly — defer until full PDF read.</t>
+          <t>A modelling tool for siting/stocking decisions rather than a field measurement.</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -15854,11 +16875,26 @@
       <c r="AN78" s="19" t="n"/>
       <c r="AO78" s="19" t="n"/>
       <c r="AP78" s="19" t="n"/>
+      <c r="AQ78" s="16" t="inlineStr">
+        <is>
+          <t>Modelling Production vs Benthic-Biodiversity Trade-Offs</t>
+        </is>
+      </c>
+      <c r="AR78" s="16" t="inlineStr">
+        <is>
+          <t>Sequeira, Ana; Ferreira, Joao Gomes; Hawkins, AJS; Nobre, Ana; Lourenço, Pedro; Zhang, X L; Yan, X; Nickell, Thom</t>
+        </is>
+      </c>
+      <c r="AS78" s="16" t="inlineStr">
+        <is>
+          <t>Modelling framework paper. Likely uses FARM or ShellSIM models given co-authorship; confirm specifics from full text. WQ 1.1.1 may apply if the model couples bioextraction explicitly — defer until full PDF read.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Murray, LG; Newell, CR; Seed, R</t>
+          <t>Murray, L., et al.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -15950,11 +16986,6 @@
       <c r="T79" t="inlineStr">
         <is>
           <t>https://doi.org/10.2983/0730-8000(2007)26[153:CITBOM]2.0.CO;2</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Two-method comparison; confirm exact structures (bottom vs longline vs bouchot) and species from full PDF. UK / Ireland mussel context highly likely (Seed = UK mussel ecologist).</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -16050,11 +17081,26 @@
       <c r="AN79" s="19" t="n"/>
       <c r="AO79" s="19" t="n"/>
       <c r="AP79" s="19" t="n"/>
+      <c r="AQ79" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity Under Two Mussel-Cultivation Methods (Reference)</t>
+        </is>
+      </c>
+      <c r="AR79" s="16" t="inlineStr">
+        <is>
+          <t>Murray, LG; Newell, CR; Seed, R</t>
+        </is>
+      </c>
+      <c r="AS79" s="16" t="inlineStr">
+        <is>
+          <t>Two-method comparison; confirm exact structures (bottom vs longline vs bouchot) and species from full PDF. UK / Ireland mussel context highly likely (Seed = UK mussel ecologist).</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ysebaert, Tom; Hart, Miron; Herman, Peter MJ</t>
+          <t>Ysebaert, T., et al.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -16146,11 +17192,6 @@
       <c r="T80" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s10152-008-0136-5</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Strong methodological template for culture-method-comparison benthic studies (bottom vs suspended). Companion to Murray 2007 (row 79) and Crawford 2003 (row 82). North Sea / Wadden context.</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -16246,11 +17287,26 @@
       <c r="AN80" s="19" t="n"/>
       <c r="AO80" s="19" t="n"/>
       <c r="AP80" s="19" t="n"/>
+      <c r="AQ80" s="16" t="inlineStr">
+        <is>
+          <t>Bottom vs Suspended Mussel Culture: Benthic Footprint Comparison</t>
+        </is>
+      </c>
+      <c r="AR80" s="16" t="inlineStr">
+        <is>
+          <t>Ysebaert, Tom; Hart, Miron; Herman, Peter MJ</t>
+        </is>
+      </c>
+      <c r="AS80" s="16" t="inlineStr">
+        <is>
+          <t>Strong methodological template for culture-method-comparison benthic studies (bottom vs suspended). Companion to Murray 2007 (row 79) and Crawford 2003 (row 82). North Sea / Wadden context.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>D'Amours, Olivier; Archambault, Philippe; McKindsey, Christopher W; Johnson, Ladd E</t>
+          <t>D'Amours, O., et al.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -16337,11 +17393,6 @@
       <c r="T81" t="inlineStr">
         <is>
           <t>https://doi.org/10.3354/meps07672</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Companion to McKindsey 2006 (row 58) framing of bivalve farms as artificial reefs. Quebec / Magdalen Islands mussel context highly likely (McKindsey + Archambault = DFO Quebec).</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -16437,11 +17488,26 @@
       <c r="AN81" s="19" t="n"/>
       <c r="AO81" s="19" t="n"/>
       <c r="AP81" s="19" t="n"/>
+      <c r="AQ81" s="16" t="inlineStr">
+        <is>
+          <t>Do Farm Gear &amp; Biodeposition Enhance Mobile Epibenthic Fauna?</t>
+        </is>
+      </c>
+      <c r="AR81" s="16" t="inlineStr">
+        <is>
+          <t>D'Amours, Olivier; Archambault, Philippe; McKindsey, Christopher W; Johnson, Ladd E</t>
+        </is>
+      </c>
+      <c r="AS81" s="16" t="inlineStr">
+        <is>
+          <t>Companion to McKindsey 2006 (row 58) framing of bivalve farms as artificial reefs. Quebec / Magdalen Islands mussel context highly likely (McKindsey + Archambault = DFO Quebec).</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Crawford, Christine M; Macleod, Catriona KA; Mitchell, Iona M</t>
+          <t>Crawford, C. M., et al.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -16533,11 +17599,6 @@
       <c r="T82" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/S0044-8486(03)00210-2</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Tasmanian shellfish-farm context (likely oysters and possibly mussels); confirm species mix from full PDF.</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -16633,11 +17694,26 @@
       <c r="AN82" s="19" t="n"/>
       <c r="AO82" s="19" t="n"/>
       <c r="AP82" s="19" t="n"/>
+      <c r="AQ82" s="16" t="inlineStr">
+        <is>
+          <t>Benthic Footprint of a Shellfish Farm (Paired-Site Survey)</t>
+        </is>
+      </c>
+      <c r="AR82" s="16" t="inlineStr">
+        <is>
+          <t>Crawford, Christine M; Macleod, Catriona KA; Mitchell, Iona M</t>
+        </is>
+      </c>
+      <c r="AS82" s="16" t="inlineStr">
+        <is>
+          <t>Tasmanian shellfish-farm context (likely oysters and possibly mussels); confirm species mix from full PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Yoo, Caitlin; Wilms, Tim JG; Stoehr, Svenja A; Lat, K; et al.</t>
+          <t>Yoo, C., et al.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -16719,11 +17795,6 @@
       <c r="T83" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.seares.2024.102498</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Mussel-reef framing may indicate restoration ecology context (rather than cultivated farm); confirm whether reefs are cultivated, restored, or natural from full PDF. Tag may need revision if non-cultivated.</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -16819,11 +17890,26 @@
       <c r="AN83" s="19" t="n"/>
       <c r="AO83" s="19" t="n"/>
       <c r="AP83" s="19" t="n"/>
+      <c r="AQ83" s="16" t="inlineStr">
+        <is>
+          <t>Mussel-Reef Mobile-Fauna Biodiversity (Reference)</t>
+        </is>
+      </c>
+      <c r="AR83" s="16" t="inlineStr">
+        <is>
+          <t>Yoo, Caitlin; Wilms, Tim JG; Stoehr, Svenja A; Lat, K; et al.</t>
+        </is>
+      </c>
+      <c r="AS83" s="16" t="inlineStr">
+        <is>
+          <t>Mussel-reef framing may indicate restoration ecology context (rather than cultivated farm); confirm whether reefs are cultivated, restored, or natural from full PDF. Tag may need revision if non-cultivated.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ferreira, JF; Besen, K; Wormsbecher, AG; Dos Santos, RC</t>
+          <t>Ferreira, J., et al.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -16916,7 +18002,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>Brown mussel (Perna perna) and Pacific oyster (Crassostrea gigas) are the main Santa Catarina culture species. May need 'Brown mussel (Perna perna)' added to vocabulary if not present — log for v1.3.</t>
+          <t>Descriptive baseline monitoring; use it for expected parameter ranges in a subtropical culture setting.</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -17012,11 +18098,26 @@
       <c r="AN84" s="19" t="n"/>
       <c r="AO84" s="19" t="n"/>
       <c r="AP84" s="19" t="n"/>
+      <c r="AQ84" s="16" t="inlineStr">
+        <is>
+          <t>Routine Physical-Chemical Monitoring at Mollusc Sites (Reference)</t>
+        </is>
+      </c>
+      <c r="AR84" s="16" t="inlineStr">
+        <is>
+          <t>Ferreira, JF; Besen, K; Wormsbecher, AG; Dos Santos, RC</t>
+        </is>
+      </c>
+      <c r="AS84" s="16" t="inlineStr">
+        <is>
+          <t>Brown mussel (Perna perna) and Pacific oyster (Crassostrea gigas) are the main Santa Catarina culture species. May need 'Brown mussel (Perna perna)' added to vocabulary if not present — log for v1.3.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Turner, Jessica S; Kellogg, M Lisa; Massey, Grace M; Friedrichs, Carl T</t>
+          <t>Turner, J. S., et al.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -17108,11 +18209,6 @@
       <c r="T85" t="inlineStr">
         <is>
           <t>https://doi.org/10.1371/journal.pone.0224768</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Strong template for paired-site WQ monitoring around bivalve farms. WQ 1.1.1 not assigned per Rule 1a (impact-detection framing, not bioextraction quantification); confirm tissue × biomass × area calc presence from full PDF.</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -17208,11 +18304,26 @@
       <c r="AN85" s="19" t="n"/>
       <c r="AO85" s="19" t="n"/>
       <c r="AP85" s="19" t="n"/>
+      <c r="AQ85" s="16" t="inlineStr">
+        <is>
+          <t>Detecting Oyster-Farm Water-Quality Effects (Moving-Vessel Transects)</t>
+        </is>
+      </c>
+      <c r="AR85" s="16" t="inlineStr">
+        <is>
+          <t>Turner, Jessica S; Kellogg, M Lisa; Massey, Grace M; Friedrichs, Carl T</t>
+        </is>
+      </c>
+      <c r="AS85" s="16" t="inlineStr">
+        <is>
+          <t>Strong template for paired-site WQ monitoring around bivalve farms. WQ 1.1.1 not assigned per Rule 1a (impact-detection framing, not bioextraction quantification); confirm tissue × biomass × area calc presence from full PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Christensen, Peter Bondo; Glud, Ronnie N; Dalsgaard, Tage; Gillespie, P A</t>
+          <t>Christensen, P. B., et al.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -17304,11 +18415,6 @@
       <c r="T86" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/S0044-8486(02)00587-2</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Companion paper to Nizzoli 2005/2006/2011 (rows 67/66/68) and Kaspar 1985 (row 65) for mussel-farm N-cycle synthesis. WQ 1.1.1 not assigned per Rule 1a (impact-detection framing); confirm from full PDF. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — intact-core sediment incubations under longline mussel farming (canonical Danish methodology, Glud + Dalsgaard co-authors). Mollusc-specific indicator added in v1.4.</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -17404,11 +18510,26 @@
       <c r="AN86" s="19" t="n"/>
       <c r="AO86" s="19" t="n"/>
       <c r="AP86" s="19" t="n"/>
+      <c r="AQ86" s="16" t="inlineStr">
+        <is>
+          <t>Sediment Oxygen &amp; Nitrogen Cycling Under a Longline Mussel Farm</t>
+        </is>
+      </c>
+      <c r="AR86" s="16" t="inlineStr">
+        <is>
+          <t>Christensen, Peter Bondo; Glud, Ronnie N; Dalsgaard, Tage; Gillespie, P A</t>
+        </is>
+      </c>
+      <c r="AS86" s="16" t="inlineStr">
+        <is>
+          <t>Companion paper to Nizzoli 2005/2006/2011 (rows 67/66/68) and Kaspar 1985 (row 65) for mussel-farm N-cycle synthesis. WQ 1.1.1 not assigned per Rule 1a (impact-detection framing); confirm from full PDF. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — intact-core sediment incubations under longline mussel farming (canonical Danish methodology, Glud + Dalsgaard co-authors). Mollusc-specific indicator added in v1.4.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Grant, J; Hatcher, A; Scott, DB; Pocklington, P; Schafer, CT; Winters, GV</t>
+          <t>Grant, J., et al.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -17504,7 +18625,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>Foundational 1990s mussel-farm benthic-impact paper; methodology influential for subsequent Atlantic Canada / mussel-farm studies including the Cranford 2007 (row 64) tradition.</t>
+          <t>The multi-method design (biodeposition traps plus sediment and foraminifera) is its enduring value.</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -17600,11 +18721,26 @@
       <c r="AN87" s="19" t="n"/>
       <c r="AO87" s="19" t="n"/>
       <c r="AP87" s="19" t="n"/>
+      <c r="AQ87" s="16" t="inlineStr">
+        <is>
+          <t>Multidisciplinary Benthic-Impact Assessment of a Mussel Farm</t>
+        </is>
+      </c>
+      <c r="AR87" s="16" t="inlineStr">
+        <is>
+          <t>Grant, J; Hatcher, A; Scott, DB; Pocklington, P; Schafer, CT; Winters, GV</t>
+        </is>
+      </c>
+      <c r="AS87" s="16" t="inlineStr">
+        <is>
+          <t>Foundational 1990s mussel-farm benthic-impact paper; methodology influential for subsequent Atlantic Canada / mussel-farm studies including the Cranford 2007 (row 64) tradition.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Souchu, Philippe; Vaquer, André; Collos, Yves; Landrein, Sébastien; Deslous-Paoli, Jean-Marc; Bibent, Bernard</t>
+          <t>Souchu, P., et al.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -17691,11 +18827,6 @@
       <c r="T88" t="inlineStr">
         <is>
           <t>https://doi.org/10.3354/meps218141</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Thau Lagoon Pacific-oyster (table/trestle) culture context. WQ 1.1.1 not assigned per Rule 1a (composition-influence framing); confirm bioextraction calc presence from full PDF. | v1.4 refinement: WQ 1.2.1 (Dissolved oxygen) removed — I-col confirms paper measures N/P/Si nutrients, Chl-a, and phytoplankton structure; DO is not listed among the measurements. v1.3 broad-usage WQ 1.2.1 tag narrowed to actual DO papers under v1.4. Flag for PDF confirm if needed.</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -17791,11 +18922,26 @@
       <c r="AN88" s="19" t="n"/>
       <c r="AO88" s="19" t="n"/>
       <c r="AP88" s="19" t="n"/>
+      <c r="AQ88" s="16" t="inlineStr">
+        <is>
+          <t>Farm Influence on Water-Column Nutrient &amp; Phytoplankton Chemistry</t>
+        </is>
+      </c>
+      <c r="AR88" s="16" t="inlineStr">
+        <is>
+          <t>Souchu, Philippe; Vaquer, André; Collos, Yves; Landrein, Sébastien; Deslous-Paoli, Jean-Marc; Bibent, Bernard</t>
+        </is>
+      </c>
+      <c r="AS88" s="16" t="inlineStr">
+        <is>
+          <t>Thau Lagoon Pacific-oyster (table/trestle) culture context. WQ 1.1.1 not assigned per Rule 1a (composition-influence framing); confirm bioextraction calc presence from full PDF. | v1.4 refinement: WQ 1.2.1 (Dissolved oxygen) removed — I-col confirms paper measures N/P/Si nutrients, Chl-a, and phytoplankton structure; DO is not listed among the measurements. v1.3 broad-usage WQ 1.2.1 tag narrowed to actual DO papers under v1.4. Flag for PDF confirm if needed.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Fernández-Tejedor, Margarita; Velasco, Jorge Enrique; Angles, Sílvia</t>
+          <t>Fernández-Tejedor, M., et al.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -17887,11 +19033,6 @@
       <c r="T89" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/rs14205235</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Excellent template for satellite-based Chl-a monitoring of shellfish-farming bays. Mediterranean mussel (Mytilus galloprovincialis) context.</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -17987,11 +19128,26 @@
       <c r="AN89" s="19" t="n"/>
       <c r="AO89" s="19" t="n"/>
       <c r="AP89" s="19" t="n"/>
+      <c r="AQ89" s="16" t="inlineStr">
+        <is>
+          <t>Satellite Chlorophyll-a Monitoring for a Shellfish Bay</t>
+        </is>
+      </c>
+      <c r="AR89" s="16" t="inlineStr">
+        <is>
+          <t>Fernández-Tejedor, Margarita; Velasco, Jorge Enrique; Angles, Sílvia</t>
+        </is>
+      </c>
+      <c r="AS89" s="16" t="inlineStr">
+        <is>
+          <t>Excellent template for satellite-based Chl-a monitoring of shellfish-farming bays. Mediterranean mussel (Mytilus galloprovincialis) context.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Toro, Jorge E; Paredes, Pamela I; Villagra, Darío J; Senn, Christian A</t>
+          <t>Toro, J. E., et al.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -18087,7 +19243,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>Southern Chile oyster context (likely Chilean oyster Tiostrea chilensis or Pacific oyster). May need 'Chilean oyster (Tiostrea chilensis / Ostrea chilensis)' added to vocabulary if not present — log for v1.3.</t>
+          <t>Monitoring rather than a hypothesis test; use it for seasonal food-supply context.</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -18183,11 +19339,26 @@
       <c r="AN90" s="19" t="n"/>
       <c r="AO90" s="19" t="n"/>
       <c r="AP90" s="19" t="n"/>
+      <c r="AQ90" s="16" t="inlineStr">
+        <is>
+          <t>Two-Year Phytoplankton &amp; Oyster-Growth Monitoring (Reference)</t>
+        </is>
+      </c>
+      <c r="AR90" s="16" t="inlineStr">
+        <is>
+          <t>Toro, Jorge E; Paredes, Pamela I; Villagra, Darío J; Senn, Christian A</t>
+        </is>
+      </c>
+      <c r="AS90" s="16" t="inlineStr">
+        <is>
+          <t>Southern Chile oyster context (likely Chilean oyster Tiostrea chilensis or Pacific oyster). May need 'Chilean oyster (Tiostrea chilensis / Ostrea chilensis)' added to vocabulary if not present — log for v1.3.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Valenzuela-Sanchez, Celia G; Pasten-Miranda, Norberto MA; Enriquez-Ocaña, L Felipe; Barraza-Guardado, Ramon H; Martínez-Córdova, Luis R</t>
+          <t>Valenzuela-Sanchez, C. G., et al.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -18279,11 +19450,6 @@
       <c r="T91" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.heliyon.2021.e06203</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Effluent-source aquaculture type unclear from title alone (mid Gulf of California has both shrimp and bivalve / pen-aquaculture); tagged Mollusk per CSV inclusion. Confirm system from full text — may warrant Finfish or Crustacean multi-tag. | v1.4 refinement: H&amp;B 2.1.1 → WQ 2.1.2 — paper measures phytoplankton composition + abundance as bioindicators of aquaculture-effluent impact, which is Mollusc WQ 2.1.2 (Microorganism and plankton community on the farm site), NOT H&amp;B 2.1.1 (which is "organisms directly associated with farmed biomass"). v1.3 mis-mapped phytoplankton community to H&amp;B 2.1.1. Y narrowed to Water Quality.  [v22] Methods confirmed (abstract + secondary descriptions): near/far-field phytoplankton community study across 3 seasons; water/plankton sampling practitioner-doable but taxonomic microscopy ID (60-70+ diatom/dinoflagellate spp.) needs partner lab -&gt; T3 Partnership.</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -18379,11 +19545,26 @@
       <c r="AN91" s="19" t="n"/>
       <c r="AO91" s="19" t="n"/>
       <c r="AP91" s="19" t="n"/>
+      <c r="AQ91" s="16" t="inlineStr">
+        <is>
+          <t>Phytoplankton as a Bioindicator of Aquaculture-Effluent Impact</t>
+        </is>
+      </c>
+      <c r="AR91" s="16" t="inlineStr">
+        <is>
+          <t>Valenzuela-Sanchez, Celia G; Pasten-Miranda, Norberto MA; Enriquez-Ocaña, L Felipe; Barraza-Guardado, Ramon H; Martínez-Córdova, Luis R</t>
+        </is>
+      </c>
+      <c r="AS91" s="16" t="inlineStr">
+        <is>
+          <t>Effluent-source aquaculture type unclear from title alone (mid Gulf of California has both shrimp and bivalve / pen-aquaculture); tagged Mollusk per CSV inclusion. Confirm system from full text — may warrant Finfish or Crustacean multi-tag. | v1.4 refinement: H&amp;B 2.1.1 → WQ 2.1.2 — paper measures phytoplankton composition + abundance as bioindicators of aquaculture-effluent impact, which is Mollusc WQ 2.1.2 (Microorganism and plankton community on the farm site), NOT H&amp;B 2.1.1 (which is "organisms directly associated with farmed biomass"). v1.3 mis-mapped phytoplankton community to H&amp;B 2.1.1. Y narrowed to Water Quality.  [v22] Methods confirmed (abstract + secondary descriptions): near/far-field phytoplankton community study across 3 seasons; water/plankton sampling practitioner-doable but taxonomic microscopy ID (60-70+ diatom/dinoflagellate spp.) needs partner lab -&gt; T3 Partnership.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Walker, Tony R; Grant, Jon</t>
+          <t>Walker, T. R. &amp; Grant, J.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -18475,11 +19656,6 @@
       <c r="T92" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.jmarsys.2008.07.009</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Useful for sediment-stability monitoring around mussel farms; companion to Grant 1995 (row 87) tradition.</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -18575,11 +19751,26 @@
       <c r="AN92" s="19" t="n"/>
       <c r="AO92" s="19" t="n"/>
       <c r="AP92" s="19" t="n"/>
+      <c r="AQ92" s="16" t="inlineStr">
+        <is>
+          <t>Sediment Erosion &amp; Stability Under Mussel Gear</t>
+        </is>
+      </c>
+      <c r="AR92" s="16" t="inlineStr">
+        <is>
+          <t>Walker, Tony R; Grant, Jon</t>
+        </is>
+      </c>
+      <c r="AS92" s="16" t="inlineStr">
+        <is>
+          <t>Useful for sediment-stability monitoring around mussel farms; companion to Grant 1995 (row 87) tradition.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Silva, Eliziane; Garbossa, Luis Hamilton Pospissil; Nunes, Maurício Laterça; Lapa, Katt Regina</t>
+          <t>Silva, E., et al.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -18670,7 +19861,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>Strong template for biodeposit-footprint prediction; Santa Catarina (subtropical Brazil) oyster + mussel context.</t>
+          <t>Predicts the deposition footprint for siting and monitoring design rather than measuring it.</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -18766,11 +19957,26 @@
       <c r="AN93" s="19" t="n"/>
       <c r="AO93" s="19" t="n"/>
       <c r="AP93" s="19" t="n"/>
+      <c r="AQ93" s="16" t="inlineStr">
+        <is>
+          <t>Modelling Where Bivalve Biodeposits Settle (Deposition Footprint)</t>
+        </is>
+      </c>
+      <c r="AR93" s="16" t="inlineStr">
+        <is>
+          <t>Silva, Eliziane; Garbossa, Luis Hamilton Pospissil; Nunes, Maurício Laterça; Lapa, Katt Regina</t>
+        </is>
+      </c>
+      <c r="AS93" s="16" t="inlineStr">
+        <is>
+          <t>Strong template for biodeposit-footprint prediction; Santa Catarina (subtropical Brazil) oyster + mussel context.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Fernández, Pamela A; Leal, Pablo P; Henríquez, Luis A</t>
+          <t>Fernández, P. A., et al.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -18866,7 +20072,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>IMTA paper (Mollusk + Seaweed multi-tag per IMTA-primacy convention). Methodology measures dissolved oxygen alongside pH / DIC (carbonate chemistry). Carbonate chemistry is NOT an MEL indicator — row retained only because the DO methodology aligns with WQ 1.2.1 and the IMTA design is independently relevant for co-culture studies. The OA-refuge framing is the paper's headline contribution but does not map to existing MEL indicators.</t>
+          <t>Within MEL scope only the dissolved-oxygen and co-culture design apply - carbonate chemistry is outside the indicator set.</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -18962,11 +20168,26 @@
       <c r="AN94" s="19" t="n"/>
       <c r="AO94" s="19" t="n"/>
       <c r="AP94" s="19" t="n"/>
+      <c r="AQ94" s="16" t="inlineStr">
+        <is>
+          <t>Macroalgae as an Acidification Refuge for Bivalves (IMTA Reference)</t>
+        </is>
+      </c>
+      <c r="AR94" s="16" t="inlineStr">
+        <is>
+          <t>Fernández, Pamela A; Leal, Pablo P; Henríquez, Luis A</t>
+        </is>
+      </c>
+      <c r="AS94" s="16" t="inlineStr">
+        <is>
+          <t>IMTA paper (Mollusk + Seaweed multi-tag per IMTA-primacy convention). Methodology measures dissolved oxygen alongside pH / DIC (carbonate chemistry). Carbonate chemistry is NOT an MEL indicator — row retained only because the DO methodology aligns with WQ 1.2.1 and the IMTA design is independently relevant for co-culture studies. The OA-refuge framing is the paper's headline contribution but does not map to existing MEL indicators.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ferriss, Bridget; Veggerby, Karl; Bogeberg, Molly; Conway-Cranos, Letitia; Hoberecht, Laura; Kiffney, Peter; Litle, Kate; Toft, Jodie; Sanderson, Beth</t>
+          <t>Ferriss, B., et al.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -19053,11 +20274,6 @@
       <c r="T95" t="inlineStr">
         <is>
           <t>https://doi.org/10.3354/aei00418</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Foundational underwater-video protocol paper for nearshore bivalve-aquaculture habitat assessment. Methods extended by Veggerby 2024 (row 97 — foraging behaviour at same sites) and parallel to Mercaldo-Allen 2021 (R57 — eDNA at oyster cages). Demonstrates regional-scale variation in aquaculture-ecological interactions at ~150 km spatial scale.</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -19153,11 +20369,26 @@
       <c r="AN95" s="19" t="n"/>
       <c r="AO95" s="19" t="n"/>
       <c r="AP95" s="19" t="n"/>
+      <c r="AQ95" s="16" t="inlineStr">
+        <is>
+          <t>Bivalve-Farm Habitat Function via Underwater Video</t>
+        </is>
+      </c>
+      <c r="AR95" s="16" t="inlineStr">
+        <is>
+          <t>Ferriss, Bridget; Veggerby, Karl; Bogeberg, Molly; Conway-Cranos, Letitia; Hoberecht, Laura; Kiffney, Peter; Litle, Kate; Toft, Jodie; Sanderson, Beth</t>
+        </is>
+      </c>
+      <c r="AS95" s="16" t="inlineStr">
+        <is>
+          <t>Foundational underwater-video protocol paper for nearshore bivalve-aquaculture habitat assessment. Methods extended by Veggerby 2024 (row 97 — foraging behaviour at same sites) and parallel to Mercaldo-Allen 2021 (R57 — eDNA at oyster cages). Demonstrates regional-scale variation in aquaculture-ecological interactions at ~150 km spatial scale.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Liu, Yi; Wang, Xinmeng; Wu, Wenguang; Zhang, Jihong</t>
+          <t>Liu, Y., et al.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -19244,11 +20475,6 @@
       <c r="T96" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.marenvres.2024.106558</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Adapts the Norwegian fish-farm MOM-B protocol to intertidal Manila clam culture. Strong methodological template for practitioner-or-partnership benthic monitoring. Companion to Zhang 2009 Sungo Bay (R99 = #12 new row) and Zhang 2020 Sungo (R50) MOM applications. Adds Chl-a, food availability, and planktonic larvae as supplementary parameters.</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -19344,11 +20570,26 @@
       <c r="AN96" s="19" t="n"/>
       <c r="AO96" s="19" t="n"/>
       <c r="AP96" s="19" t="n"/>
+      <c r="AQ96" s="16" t="inlineStr">
+        <is>
+          <t>MOM-B + Stable-Isotope Monitoring for Intertidal Clam Farms</t>
+        </is>
+      </c>
+      <c r="AR96" s="16" t="inlineStr">
+        <is>
+          <t>Liu, Yi; Wang, Xinmeng; Wu, Wenguang; Zhang, Jihong</t>
+        </is>
+      </c>
+      <c r="AS96" s="16" t="inlineStr">
+        <is>
+          <t>Adapts the Norwegian fish-farm MOM-B protocol to intertidal Manila clam culture. Strong methodological template for practitioner-or-partnership benthic monitoring. Companion to Zhang 2009 Sungo Bay (R99 = #12 new row) and Zhang 2020 Sungo (R50) MOM applications. Adds Chl-a, food availability, and planktonic larvae as supplementary parameters.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Whiteley, Jonathan; Bendell-Young, Leah</t>
+          <t>Whiteley, J. &amp; Bendell-Young, L.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -19442,7 +20683,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>BC Canada intertidal Manila clam farms with predator-exclusion netting on seeded clam beds. Reports limited site-scale impact on bivalve community structure but flags potential regional-scale cumulative impacts. Calls for regional-scale baseline + monitoring. Reference benchmark for intertidal clam-bed netting context. AC = Bottom culture chosen as closest vocab; the gear is laid-net-over-substrate rather than rack-and-bag — minor vocab gap to log for v1.4.</t>
+          <t>Site-scale effects may be limited even where regional cumulative effects warrant a broader baseline.</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -19538,11 +20779,26 @@
       <c r="AN97" s="19" t="n"/>
       <c r="AO97" s="19" t="n"/>
       <c r="AP97" s="19" t="n"/>
+      <c r="AQ97" s="16" t="inlineStr">
+        <is>
+          <t>Does Intertidal Clam Farming Change the Infaunal Community?</t>
+        </is>
+      </c>
+      <c r="AR97" s="16" t="inlineStr">
+        <is>
+          <t>Whiteley, Jonathan; Bendell-Young, Leah</t>
+        </is>
+      </c>
+      <c r="AS97" s="16" t="inlineStr">
+        <is>
+          <t>BC Canada intertidal Manila clam farms with predator-exclusion netting on seeded clam beds. Reports limited site-scale impact on bivalve community structure but flags potential regional-scale cumulative impacts. Calls for regional-scale baseline + monitoring. Reference benchmark for intertidal clam-bed netting context. AC = Bottom culture chosen as closest vocab; the gear is laid-net-over-substrate rather than rack-and-bag — minor vocab gap to log for v1.4.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Veggerby, Karl B; Scheuerell, Mark D; Sanderson, Beth L; Kiffney, Peter M; Ferriss, Bridget E</t>
+          <t>Veggerby, K. B., et al.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -19632,11 +20888,6 @@
       <c r="T98" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/mcf2.10282</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Companion to Ferriss 2021 (R95) using same study sites; extends from species presence to behaviour-level foraging modelling. Documents that pelagic fish (surfperch) use aquaculture growing gear more than unfarmed sites; Metacarcinus crabs prefer unfarmed mudflats. Strong methodological template for behaviour-level habitat-function assessment at bivalve farms.</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -19732,11 +20983,26 @@
       <c r="AN98" s="19" t="n"/>
       <c r="AO98" s="19" t="n"/>
       <c r="AP98" s="19" t="n"/>
+      <c r="AQ98" s="16" t="inlineStr">
+        <is>
+          <t>Farm Habitat as Fish Foraging Ground (Video Behaviour Scoring)</t>
+        </is>
+      </c>
+      <c r="AR98" s="16" t="inlineStr">
+        <is>
+          <t>Veggerby, Karl B; Scheuerell, Mark D; Sanderson, Beth L; Kiffney, Peter M; Ferriss, Bridget E</t>
+        </is>
+      </c>
+      <c r="AS98" s="16" t="inlineStr">
+        <is>
+          <t>Companion to Ferriss 2021 (R95) using same study sites; extends from species presence to behaviour-level foraging modelling. Documents that pelagic fish (surfperch) use aquaculture growing gear more than unfarmed sites; Metacarcinus crabs prefer unfarmed mudflats. Strong methodological template for behaviour-level habitat-function assessment at bivalve farms.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Žydelis, Ramūnas; Esler, Daniel; Kirk, Molly; Boyd, W Sean</t>
+          <t>Žydelis, R., et al.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -19830,7 +21096,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>Documents that off-bottom suspended oyster aquaculture provides winter foraging habitat for molluscivorous sea ducks (concentrated, energetically-rich prey). H&amp;B 1.2.1 (Mobile fauna — vertebrate top predators) is the focal indicator. Demonstrates positive habitat-function interaction (aquaculture supports sea-duck winter survival). Farm Structure: off-bottom suspended oyster — vocab is imperfect; 'Not gear-specific' chosen since the Mollusk-vocab suspended-oyster options (lantern net, longline) don't quite fit BC off-bottom oyster culture. Minor vocab gap to log for v1.4.  [v22] Methods confirmed: structured sea-duck density surveys (surf scoter, Barrow's goldeneye) vs habitat variables + statistical habitat-selection modelling. Field counts practitioner-doable with ID training; model selection needs partner -&gt; T3 Partnership.</t>
+          <t>Off-bottom suspended oyster culture can provide winter foraging habitat for sea ducks.</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -19916,11 +21182,21 @@
       <c r="AN99" s="19" t="n"/>
       <c r="AO99" s="19" t="n"/>
       <c r="AP99" s="19" t="n"/>
+      <c r="AR99" s="16" t="inlineStr">
+        <is>
+          <t>Žydelis, Ramūnas; Esler, Daniel; Kirk, Molly; Boyd, W Sean</t>
+        </is>
+      </c>
+      <c r="AS99" s="16" t="inlineStr">
+        <is>
+          <t>Documents that off-bottom suspended oyster aquaculture provides winter foraging habitat for molluscivorous sea ducks (concentrated, energetically-rich prey). H&amp;B 1.2.1 (Mobile fauna — vertebrate top predators) is the focal indicator. Demonstrates positive habitat-function interaction (aquaculture supports sea-duck winter survival). Farm Structure: off-bottom suspended oyster — vocab is imperfect; 'Not gear-specific' chosen since the Mollusk-vocab suspended-oyster options (lantern net, longline) don't quite fit BC off-bottom oyster culture. Minor vocab gap to log for v1.4.  [v22] Methods confirmed: structured sea-duck density surveys (surf scoter, Barrow's goldeneye) vs habitat variables + statistical habitat-selection modelling. Field counts practitioner-doable with ID training; model selection needs partner -&gt; T3 Partnership.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Maurin, Carissa Elizabeth; Byron, Carrie J; Wilson, Karen A; St Gelais, Adam T</t>
+          <t>Maurin, C. E., et al.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -20011,7 +21287,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>Stable-isotope food-web methodology adds a trophic dimension beyond standard biodiversity surveys. Floating dock controls (similar substrate, no mussels) provide an elegant structural-only contrast. Useful for studies that need to link biodiversity (H&amp;B) to trophic-function (food-web) indicators. Macroalgae biomass was higher on farm structures (green macroalgae driver).</t>
+          <t>Uses a non-mussel floating structure as a control to separate the mussels' effect from the hard substrate's.</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -20107,11 +21383,26 @@
       <c r="AN100" s="19" t="n"/>
       <c r="AO100" s="19" t="n"/>
       <c r="AP100" s="19" t="n"/>
+      <c r="AQ100" s="16" t="inlineStr">
+        <is>
+          <t>Linking Farm Biodiversity to Food-Web Function (Stable Isotopes)</t>
+        </is>
+      </c>
+      <c r="AR100" s="16" t="inlineStr">
+        <is>
+          <t>Maurin, Carissa Elizabeth; Byron, Carrie J; Wilson, Karen A; St Gelais, Adam T</t>
+        </is>
+      </c>
+      <c r="AS100" s="16" t="inlineStr">
+        <is>
+          <t>Stable-isotope food-web methodology adds a trophic dimension beyond standard biodiversity surveys. Floating dock controls (similar substrate, no mussels) provide an elegant structural-only contrast. Useful for studies that need to link biodiversity (H&amp;B) to trophic-function (food-web) indicators. Macroalgae biomass was higher on farm structures (green macroalgae driver).</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Callier, Myriam D; McKindsey, Christopher W; Desrosiers, Gaston</t>
+          <t>Callier, M. D., et al.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -20207,7 +21498,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>Canonical paper on benthic-indicator evaluation for mussel farm impacts; the within-/between-line transect design and SPI methodology are widely cited templates. Contrasting patterns across the two farms (GE = no gradient; HAM = clear gradient with Pectinaria granulata enrichment) illustrate why multi-site replication is essential. Companion to Cranford 2006 (R75) DFO indicators-and-thresholds report.</t>
+          <t>Farms differ in whether they show a clear enrichment gradient, so use multiple indicators and sites.</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -20303,11 +21594,26 @@
       <c r="AN101" s="19" t="n"/>
       <c r="AO101" s="19" t="n"/>
       <c r="AP101" s="19" t="n"/>
+      <c r="AQ101" s="16" t="inlineStr">
+        <is>
+          <t>Which Benthic Indicators Best Detect Mussel-Farm Impact?</t>
+        </is>
+      </c>
+      <c r="AR101" s="16" t="inlineStr">
+        <is>
+          <t>Callier, Myriam D; McKindsey, Christopher W; Desrosiers, Gaston</t>
+        </is>
+      </c>
+      <c r="AS101" s="16" t="inlineStr">
+        <is>
+          <t>Canonical paper on benthic-indicator evaluation for mussel farm impacts; the within-/between-line transect design and SPI methodology are widely cited templates. Contrasting patterns across the two farms (GE = no gradient; HAM = clear gradient with Pectinaria granulata enrichment) illustrate why multi-site replication is essential. Companion to Cranford 2006 (R75) DFO indicators-and-thresholds report.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Mascorda-Cabre, Llucia; Hosegood, Phil; Attrill, Martin J; Sheehan, Emma V</t>
+          <t>Mascorda-Cabre, L., et al.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -20398,7 +21704,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>Long-term BACI study at the UK's first commercial offshore mussel farm; rare 8-year record. Companion to Bridger 2022 (Lyme Bay restoration potential), Mascorda-Cabre 2024 R60 in v14 (local water circulation), and Underwood 2023 (R20 fish recruitment). Strong evidence base for biogenic-reef formation + OECM (Other Effective Area-Based Conservation Measures) framing. Three-mechanism framework (recruitment, settlement, subsidy) for explaining results.</t>
+          <t>A multi-year record is what makes reef formation and rising diversity detectable.</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -20494,11 +21800,26 @@
       <c r="AN102" s="19" t="n"/>
       <c r="AO102" s="19" t="n"/>
       <c r="AP102" s="19" t="n"/>
+      <c r="AQ102" s="16" t="inlineStr">
+        <is>
+          <t>Biogenic-Reef &amp; Biodiversity Effects of an Offshore Mussel Farm (8-yr BACI)</t>
+        </is>
+      </c>
+      <c r="AR102" s="16" t="inlineStr">
+        <is>
+          <t>Mascorda-Cabre, Llucia; Hosegood, Phil; Attrill, Martin J; Sheehan, Emma V</t>
+        </is>
+      </c>
+      <c r="AS102" s="16" t="inlineStr">
+        <is>
+          <t>Long-term BACI study at the UK's first commercial offshore mussel farm; rare 8-year record. Companion to Bridger 2022 (Lyme Bay restoration potential), Mascorda-Cabre 2024 R60 in v14 (local water circulation), and Underwood 2023 (R20 fish recruitment). Strong evidence base for biogenic-reef formation + OECM (Other Effective Area-Based Conservation Measures) framing. Three-mechanism framework (recruitment, settlement, subsidy) for explaining results.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Chan, Sharon SW; Wong, Ho Tin; Thomas, Marine; Alleway, Heidi K; Hancock, Boze; Russell, Bayden D</t>
+          <t>Chan, S. S., et al.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -20589,7 +21910,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>Subtropical Pearl River Delta context; traditional benthic oyster farms left fallow develop into complex habitats with biodiversity comparable to natural oyster reefs. Documents one invasive species (Xenostrobus securis) at lower densities than artificial-substrate controls. Cites D'Amours 2008 (R81) as comparator. AB = Pacific oyster used as closest vocab match; HK oysters are typically Magallana hongkongensis — minor vocab-gap to log for v1.4.</t>
+          <t>Watch for invasive species when interpreting the biodiversity gains.</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -20685,11 +22006,26 @@
       <c r="AN103" s="19" t="n"/>
       <c r="AO103" s="19" t="n"/>
       <c r="AP103" s="19" t="n"/>
+      <c r="AQ103" s="16" t="inlineStr">
+        <is>
+          <t>Habitat Value of Structured vs Fallow Oyster Culture</t>
+        </is>
+      </c>
+      <c r="AR103" s="16" t="inlineStr">
+        <is>
+          <t>Chan, Sharon SW; Wong, Ho Tin; Thomas, Marine; Alleway, Heidi K; Hancock, Boze; Russell, Bayden D</t>
+        </is>
+      </c>
+      <c r="AS103" s="16" t="inlineStr">
+        <is>
+          <t>Subtropical Pearl River Delta context; traditional benthic oyster farms left fallow develop into complex habitats with biodiversity comparable to natural oyster reefs. Documents one invasive species (Xenostrobus securis) at lower densities than artificial-substrate controls. Cites D'Amours 2008 (R81) as comparator. AB = Pacific oyster used as closest vocab match; HK oysters are typically Magallana hongkongensis — minor vocab-gap to log for v1.4.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Zhang, Jihong; Hansen, Pia Kupka; Fang, Jianguang; Wang, Wei; Jiang, Zengjie</t>
+          <t>Zhang, J., et al.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -20785,7 +22121,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>First adaptation of MOM-B from Norwegian fish-farm context to Chinese IMTA bivalve+seaweed system. Multi-tagged Mollusk + Seaweed per IMTA-primacy convention (Rule 2 / Example 1). Foundational companion paper to Zhang 2020 Sungo (R50) which extends to 10+ year trends, and to Liu 2024 (R96 = #3 new row) which adapts MOM-B to intertidal Manila clam culture. Sungo Bay is a 144 km² semi-enclosed bay with ~2/3 of area under bivalve+seaweed culture for &gt;30 years.  [v22] Methods confirmed: MOM B-investigation, 66 sediment samples / 10 stations via modified Van Veen grab (250 cm2); pH/Eh/sensory scoring practitioner-doable but macrofauna ID needs partner lab -&gt; T3 Partnership.</t>
+          <t>First adaptation of the Norwegian MOM-B to a Chinese IMTA bivalve+seaweed system.</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -20881,11 +22217,26 @@
       <c r="AN104" s="19" t="n"/>
       <c r="AO104" s="19" t="n"/>
       <c r="AP104" s="19" t="n"/>
+      <c r="AQ104" s="16" t="inlineStr">
+        <is>
+          <t>MOM-B Seabed Assessment for Bivalve+Seaweed Culture</t>
+        </is>
+      </c>
+      <c r="AR104" s="16" t="inlineStr">
+        <is>
+          <t>Zhang, Jihong; Hansen, Pia Kupka; Fang, Jianguang; Wang, Wei; Jiang, Zengjie</t>
+        </is>
+      </c>
+      <c r="AS104" s="16" t="inlineStr">
+        <is>
+          <t>First adaptation of MOM-B from Norwegian fish-farm context to Chinese IMTA bivalve+seaweed system. Multi-tagged Mollusk + Seaweed per IMTA-primacy convention (Rule 2 / Example 1). Foundational companion paper to Zhang 2020 Sungo (R50) which extends to 10+ year trends, and to Liu 2024 (R96 = #3 new row) which adapts MOM-B to intertidal Manila clam culture. Sungo Bay is a 144 km² semi-enclosed bay with ~2/3 of area under bivalve+seaweed culture for &gt;30 years.  [v22] Methods confirmed: MOM B-investigation, 66 sediment samples / 10 stations via modified Van Veen grab (250 cm2); pH/Eh/sensory scoring practitioner-doable but macrofauna ID needs partner lab -&gt; T3 Partnership.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ping, Xianyin; Zhang, Hui; Jiang, Yazhou; Ling, Jianzhong; Sun, Peng; Tang, Baojun</t>
+          <t>Ping, X., et al.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -20979,7 +22330,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>Combines two contrasting bivalve interventions: bottom stock-enhancement (ark shell, minimal benthic impact) and suspended raft oyster culture (elevated AVS + heavy metals, no suspension-feeders found in sediment beneath rafts). Useful for separating impact of infaunal bivalve enhancement vs suspended-culture biodeposition. Subtropical East China Sea context. AB uses 'Native oyster — other / unspecified' for C. sikamea (Suminoe oyster) and 'Native clam — other / unspecified' for ark shell — minor vocab gap to log for v1.4 (Suminoe oyster, ark shell).</t>
+          <t>Suspended raft culture tends to raise sediment sulphide and metals; infaunal enhancement leaves a lighter footprint.</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -21075,11 +22426,26 @@
       <c r="AN105" s="19" t="n"/>
       <c r="AO105" s="19" t="n"/>
       <c r="AP105" s="19" t="n"/>
+      <c r="AQ105" s="16" t="inlineStr">
+        <is>
+          <t>Benthic Effects: Bottom Enhancement vs Suspended Oyster Culture</t>
+        </is>
+      </c>
+      <c r="AR105" s="16" t="inlineStr">
+        <is>
+          <t>Ping, Xianyin; Zhang, Hui; Jiang, Yazhou; Ling, Jianzhong; Sun, Peng; Tang, Baojun</t>
+        </is>
+      </c>
+      <c r="AS105" s="16" t="inlineStr">
+        <is>
+          <t>Combines two contrasting bivalve interventions: bottom stock-enhancement (ark shell, minimal benthic impact) and suspended raft oyster culture (elevated AVS + heavy metals, no suspension-feeders found in sediment beneath rafts). Useful for separating impact of infaunal bivalve enhancement vs suspended-culture biodeposition. Subtropical East China Sea context. AB uses 'Native oyster — other / unspecified' for C. sikamea (Suminoe oyster) and 'Native clam — other / unspecified' for ark shell — minor vocab gap to log for v1.4 (Suminoe oyster, ark shell).</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Outinen, Okko; Forsström, Tiia; Yli-Rosti, Juho; Vesakoski, Outi; Lehtiniemi, Maiju</t>
+          <t>Outinen, O., et al.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -21166,11 +22532,6 @@
       <c r="T106" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.marpolbul.2019.02.055</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>NIS-focused epifauna monitoring methodology — not bivalve-aquaculture in original context, but directly transferable to fouling-NIS monitoring at bivalve farm sites (Rule 2). The American collector with oyster shells is the recommended NIS-detection device. Useful as a methodological reference for monitoring biofouling-mediated NIS introductions at shellfish farms. Multi-tagged Mollusk per Rule 2 transferable-methodology convention; AB = Not species-specific because original system is general nearshore.</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -21266,11 +22627,26 @@
       <c r="AN106" s="19" t="n"/>
       <c r="AO106" s="19" t="n"/>
       <c r="AP106" s="19" t="n"/>
+      <c r="AQ106" s="16" t="inlineStr">
+        <is>
+          <t>Trap &amp; Collector Monitoring for Non-Indigenous Fouling Species</t>
+        </is>
+      </c>
+      <c r="AR106" s="16" t="inlineStr">
+        <is>
+          <t>Outinen, Okko; Forsström, Tiia; Yli-Rosti, Juho; Vesakoski, Outi; Lehtiniemi, Maiju</t>
+        </is>
+      </c>
+      <c r="AS106" s="16" t="inlineStr">
+        <is>
+          <t>NIS-focused epifauna monitoring methodology — not bivalve-aquaculture in original context, but directly transferable to fouling-NIS monitoring at bivalve farm sites (Rule 2). The American collector with oyster shells is the recommended NIS-detection device. Useful as a methodological reference for monitoring biofouling-mediated NIS introductions at shellfish farms. Multi-tagged Mollusk per Rule 2 transferable-methodology convention; AB = Not species-specific because original system is general nearshore.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sun, Xin; Dong, Jianyu; Hu, Chengye; Zhang, Yuyang; Chen, Yong; Zhang, Xiumei</t>
+          <t>Sun, X., et al.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -21361,7 +22737,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>Multi-method indicator synthesis across 12 bivalve farms covering 4 culture methods (suspended cages — scallops; hanging ropes — mussels &amp; oysters; bottom culture — clams &amp; scallops). Demonstrates that culture method drives biological-trait composition more than cultivated species identity. Bottom-based culture causes least ecological impact in trait-compositional terms. Useful as a meta-template for trait-based assessment beyond standard diversity indices. Cross-zone (subtropical + temperate Pacific China coast).</t>
+          <t>Culture method drives community traits more than the cultivated species, with bottom culture generally lightest.</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -21457,11 +22833,26 @@
       <c r="AN107" s="19" t="n"/>
       <c r="AO107" s="19" t="n"/>
       <c r="AP107" s="19" t="n"/>
+      <c r="AQ107" s="16" t="inlineStr">
+        <is>
+          <t>Trait-Based Benthic Comparison Across Bivalve Culture Methods</t>
+        </is>
+      </c>
+      <c r="AR107" s="16" t="inlineStr">
+        <is>
+          <t>Sun, Xin; Dong, Jianyu; Hu, Chengye; Zhang, Yuyang; Chen, Yong; Zhang, Xiumei</t>
+        </is>
+      </c>
+      <c r="AS107" s="16" t="inlineStr">
+        <is>
+          <t>Multi-method indicator synthesis across 12 bivalve farms covering 4 culture methods (suspended cages — scallops; hanging ropes — mussels &amp; oysters; bottom culture — clams &amp; scallops). Demonstrates that culture method drives biological-trait composition more than cultivated species identity. Bottom-based culture causes least ecological impact in trait-compositional terms. Useful as a meta-template for trait-based assessment beyond standard diversity indices. Cross-zone (subtropical + temperate Pacific China coast).</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bridger, Danielle; Attrill, Martin J; Davies, Bede F R; Holmes, Luke A; Cartwright, Amy; Rees, Siân E; Mascorda Cabre, Llucia; Sheehan, Emma V</t>
+          <t>Bridger, D., et al.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -21548,11 +22939,6 @@
       <c r="T108" t="inlineStr">
         <is>
           <t>https://doi.org/10.1002/aff2.77</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>Foundational large-scale offshore mussel farm habitat-function paper. Companion to Mascorda Cabre 2023 (BTA on sediment recovery, same farm) and Bridger 2024 (later in the same monitoring programme). Lyme Bay site has 15 km² of historically dredge/trawl-degraded seabed; farm acts as both physical exclusion (no bottom-towed fishing) and habitat-creating structure. Strong analogue to mussel-reef restoration. Useful as a UK temperate-Atlantic counterpart to Sun 2021 (R107) trait-based bivalve farm assessment.</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -21648,11 +23034,26 @@
       <c r="AN108" s="19" t="n"/>
       <c r="AO108" s="19" t="n"/>
       <c r="AP108" s="19" t="n"/>
+      <c r="AQ108" s="16" t="inlineStr">
+        <is>
+          <t>Offshore Mussel-Farm Seabed Restoration Monitoring (Video BACI)</t>
+        </is>
+      </c>
+      <c r="AR108" s="16" t="inlineStr">
+        <is>
+          <t>Bridger, Danielle; Attrill, Martin J; Davies, Bede F R; Holmes, Luke A; Cartwright, Amy; Rees, Siân E; Mascorda Cabre, Llucia; Sheehan, Emma V</t>
+        </is>
+      </c>
+      <c r="AS108" s="16" t="inlineStr">
+        <is>
+          <t>Foundational large-scale offshore mussel farm habitat-function paper. Companion to Mascorda Cabre 2023 (BTA on sediment recovery, same farm) and Bridger 2024 (later in the same monitoring programme). Lyme Bay site has 15 km² of historically dredge/trawl-degraded seabed; farm acts as both physical exclusion (no bottom-towed fishing) and habitat-creating structure. Strong analogue to mussel-reef restoration. Useful as a UK temperate-Atlantic counterpart to Sun 2021 (R107) trait-based bivalve farm assessment.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Pedro, Sónia; Nogueira, Marta</t>
+          <t>Pedro, S. &amp; Nogueira, M.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -21744,11 +23145,6 @@
       <c r="T109" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/su18062864</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Pure regulatory-monitoring framework paper — most directly analogous to other national shellfish WQ monitoring papers (e.g. Bergquist 2009 FL hard clam, row 111; Cruz 2022 Portuguese biotoxin forecasting). Useful as a model for designing scaled national/regional WQ monitoring programmes in shellfish-producing regions. IPMA-led institutional study. | v1.4 refinement: WQ 1.2.1 narrowed to DO-only (v1.4 vocabulary correction). Pedro's national WFD monitoring suite includes DO among physico-chemical parameters.</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -21844,11 +23240,26 @@
       <c r="AN109" s="19" t="n"/>
       <c r="AO109" s="19" t="n"/>
       <c r="AP109" s="19" t="n"/>
+      <c r="AQ109" s="16" t="inlineStr">
+        <is>
+          <t>Regulatory Shellfish-Water Monitoring Programme (Chemical + Microbial)</t>
+        </is>
+      </c>
+      <c r="AR109" s="16" t="inlineStr">
+        <is>
+          <t>Pedro, Sónia; Nogueira, Marta</t>
+        </is>
+      </c>
+      <c r="AS109" s="16" t="inlineStr">
+        <is>
+          <t>Pure regulatory-monitoring framework paper — most directly analogous to other national shellfish WQ monitoring papers (e.g. Bergquist 2009 FL hard clam, row 111; Cruz 2022 Portuguese biotoxin forecasting). Useful as a model for designing scaled national/regional WQ monitoring programmes in shellfish-producing regions. IPMA-led institutional study. | v1.4 refinement: WQ 1.2.1 narrowed to DO-only (v1.4 vocabulary correction). Pedro's national WFD monitoring suite includes DO among physico-chemical parameters.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Maar, Marie; Larsen, Janus; Butenschön, Momme; Kristiansen, Trond; Thodsen, Hans; Taylor, Daniel; Schourup-Kristensen, Vibe</t>
+          <t>Maar, M., et al.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -21944,7 +23355,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Climate-projection paper coupling water quality + benthic mussel population + suspended mussel culture in one framework. Useful for MEL practitioners thinking about how carrying-capacity and WQ indicator baselines should be projected forward under climate change. Daniel Taylor co-authors with Maar in both row 110 (this paper, modelling) and row 119 (Taylor 2024 L&amp;O #34, empirical phytoplankton depletion at Limfjorden) — same site + research group, complementary methods. | v1.4 refinement: WQ 1.2.1 narrowed to DO (model output; v1.4 correction).</t>
+          <t>Use it to think about how carrying-capacity and water-quality baselines shift under climate change.</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -22040,11 +23451,26 @@
       <c r="AN110" s="19" t="n"/>
       <c r="AO110" s="19" t="n"/>
       <c r="AP110" s="19" t="n"/>
+      <c r="AQ110" s="16" t="inlineStr">
+        <is>
+          <t>Climate-Projection Model for Water Quality &amp; Mussel Culture (Reference)</t>
+        </is>
+      </c>
+      <c r="AR110" s="16" t="inlineStr">
+        <is>
+          <t>Maar, Marie; Larsen, Janus; Butenschön, Momme; Kristiansen, Trond; Thodsen, Hans; Taylor, Daniel; Schourup-Kristensen, Vibe</t>
+        </is>
+      </c>
+      <c r="AS110" s="16" t="inlineStr">
+        <is>
+          <t>Climate-projection paper coupling water quality + benthic mussel population + suspended mussel culture in one framework. Useful for MEL practitioners thinking about how carrying-capacity and WQ indicator baselines should be projected forward under climate change. Daniel Taylor co-authors with Maar in both row 110 (this paper, modelling) and row 119 (Taylor 2024 L&amp;O #34, empirical phytoplankton depletion at Limfjorden) — same site + research group, complementary methods. | v1.4 refinement: WQ 1.2.1 narrowed to DO (model output; v1.4 correction).</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Bergquist, Derk C; Heuberger, David; Sturmer, Leslie N; Baker, Shirley M</t>
+          <t>Bergquist, D. C., et al.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -22136,11 +23562,6 @@
       <c r="T111" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s10661-008-0171-3</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Foundational US shellfish-industry WQ monitoring paper. The Cedar Key / Dog Island / Gulf Jackson stations have continued in scaled-down form post-federal-funding via the USDA Risk Management Agency and UF IFAS extension. Directly comparable in scope to Pedro 2026 (R109, Portuguese national shellfish monitoring) — both implement regulatory/insurance-driven multi-station continuous WQ for shellfish industry. | v1.4 refinement: WQ 1.2.1 narrowed to DO (continuous DO sondes; v1.4 correction). Other parameters (T, salinity, turbidity, depth) measured but outside strict v1.4 WQ 1.2.1 indicator scope.</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -22236,11 +23657,26 @@
       <c r="AN111" s="19" t="n"/>
       <c r="AO111" s="19" t="n"/>
       <c r="AP111" s="19" t="n"/>
+      <c r="AQ111" s="16" t="inlineStr">
+        <is>
+          <t>Continuous Regional Water-Quality Monitoring for Shellfish Leases</t>
+        </is>
+      </c>
+      <c r="AR111" s="16" t="inlineStr">
+        <is>
+          <t>Bergquist, Derk C; Heuberger, David; Sturmer, Leslie N; Baker, Shirley M</t>
+        </is>
+      </c>
+      <c r="AS111" s="16" t="inlineStr">
+        <is>
+          <t>Foundational US shellfish-industry WQ monitoring paper. The Cedar Key / Dog Island / Gulf Jackson stations have continued in scaled-down form post-federal-funding via the USDA Risk Management Agency and UF IFAS extension. Directly comparable in scope to Pedro 2026 (R109, Portuguese national shellfish monitoring) — both implement regulatory/insurance-driven multi-station continuous WQ for shellfish industry. | v1.4 refinement: WQ 1.2.1 narrowed to DO (continuous DO sondes; v1.4 correction). Other parameters (T, salinity, turbidity, depth) measured but outside strict v1.4 WQ 1.2.1 indicator scope.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ray, Nicholas E; Li, Ji; Kangas, Patrick C; Terlizzi, Daniel E</t>
+          <t>Ray, N. E., et al.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -22331,7 +23767,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>Concise, methodologically clean upstream/downstream design — most useful as a 'fingerprint' protocol for confirming whether a given oyster farm is producing detectable WQ changes. Contrasts with Turner et al. 2019 (Chesapeake, minimal effects detected — small/low-density farms) and complements Ray's companion Algal Turf Scrubber paper (UM-SG-RS-2015-26) which closes the loop with N+P bioextraction. | v1.4 refinement: WQ 1.2.1 narrowed to DO (Ray measured DO upstream/downstream; nutrients also measured but outside v1.4 WQ 1.2.1 scope).</t>
+          <t>A clean 'fingerprint' design for confirming whether a farm produces detectable water-quality change.</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -22427,11 +23863,26 @@
       <c r="AN112" s="19" t="n"/>
       <c r="AO112" s="19" t="n"/>
       <c r="AP112" s="19" t="n"/>
+      <c r="AQ112" s="16" t="inlineStr">
+        <is>
+          <t>Upstream/Downstream Water-Quality Fingerprint of an Oyster Farm</t>
+        </is>
+      </c>
+      <c r="AR112" s="16" t="inlineStr">
+        <is>
+          <t>Ray, Nicholas E; Li, Ji; Kangas, Patrick C; Terlizzi, Daniel E</t>
+        </is>
+      </c>
+      <c r="AS112" s="16" t="inlineStr">
+        <is>
+          <t>Concise, methodologically clean upstream/downstream design — most useful as a 'fingerprint' protocol for confirming whether a given oyster farm is producing detectable WQ changes. Contrasts with Turner et al. 2019 (Chesapeake, minimal effects detected — small/low-density farms) and complements Ray's companion Algal Turf Scrubber paper (UM-SG-RS-2015-26) which closes the loop with N+P bioextraction. | v1.4 refinement: WQ 1.2.1 narrowed to DO (Ray measured DO upstream/downstream; nutrients also measured but outside v1.4 WQ 1.2.1 scope).</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Carmichael, Ruth H; Walton, William; Clark, Heidi</t>
+          <t>Carmichael, R. H., et al.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -22527,7 +23978,7 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>Canonical Sub-rule 1a paper for WQ 1.1.1 — tissue %N × biomass × area bioextraction methodology applied across 4 estuaries under contrasting N loads. Now established as the primary reference for harvest-based N removal estimates in subsequent oyster-bioextraction policy work (Rose 2015, Bricker 2018/2020, Kellogg 2014, Cornwell 2016). Often cited together with Carmichael's later ES&amp;T paper on shellfish-aquaculture-as-N-management. Companion in scope to Briant 2018 (FR coast) and Liénart 2025 (R116, FR multi-decadal C/N isotopes). | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper measures tissue %N + δ15N anthropogenic-N attribution; no DO measurement). δ15N as N-source proxy noted in U but does not map to a v1.4 indicator.</t>
+          <t>Primary reference for harvest-based nitrogen removal (tissue %N x biomass x area) across contrasting estuaries.</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
@@ -22613,11 +24064,21 @@
       <c r="AN113" s="19" t="n"/>
       <c r="AO113" s="19" t="n"/>
       <c r="AP113" s="19" t="n"/>
+      <c r="AR113" s="16" t="inlineStr">
+        <is>
+          <t>Carmichael, Ruth H; Walton, William; Clark, Heidi</t>
+        </is>
+      </c>
+      <c r="AS113" s="16" t="inlineStr">
+        <is>
+          <t>Canonical Sub-rule 1a paper for WQ 1.1.1 — tissue %N × biomass × area bioextraction methodology applied across 4 estuaries under contrasting N loads. Now established as the primary reference for harvest-based N removal estimates in subsequent oyster-bioextraction policy work (Rose 2015, Bricker 2018/2020, Kellogg 2014, Cornwell 2016). Often cited together with Carmichael's later ES&amp;T paper on shellfish-aquaculture-as-N-management. Companion in scope to Briant 2018 (FR coast) and Liénart 2025 (R116, FR multi-decadal C/N isotopes). | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper measures tissue %N + δ15N anthropogenic-N attribution; no DO measurement). δ15N as N-source proxy noted in U but does not map to a v1.4 indicator.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Pernet, Fabrice; Malet, Nathalie; Pastoureaud, Annie; Vaquer, André; Quéré, Claudie; Dubroca, Laurent</t>
+          <t>Pernet, F., et al.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -22708,7 +24169,7 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>Thau-lagoon trophic-ecology paper. The 'no significant aquaculture-effect on chl-a / POM δ13C' finding is methodologically informative — establishes baseline variability against which aquaculture footprints would have to be detected. Sub-rule 1a does not strictly apply here (δ13C tracer ≠ tissue %N bioextraction), but stable-isotope methodology is foundational for the WQ 1.1.1 family. Useful as a Mediterranean-lagoon trophic baseline alongside Souchu 2001 (also Thau) and Carmichael 2012 (R113, anthropogenic-source attribution).</t>
+          <t>The 'no significant farm effect on chlorophyll' finding sets the baseline variability a footprint must exceed to be detectable.</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
@@ -22804,11 +24265,26 @@
       <c r="AN114" s="19" t="n"/>
       <c r="AO114" s="19" t="n"/>
       <c r="AP114" s="19" t="n"/>
+      <c r="AQ114" s="16" t="inlineStr">
+        <is>
+          <t>Tracing Bivalve Diet &amp; Food Sources Over a Year (Isotopes/Fatty Acids)</t>
+        </is>
+      </c>
+      <c r="AR114" s="16" t="inlineStr">
+        <is>
+          <t>Pernet, Fabrice; Malet, Nathalie; Pastoureaud, Annie; Vaquer, André; Quéré, Claudie; Dubroca, Laurent</t>
+        </is>
+      </c>
+      <c r="AS114" s="16" t="inlineStr">
+        <is>
+          <t>Thau-lagoon trophic-ecology paper. The 'no significant aquaculture-effect on chl-a / POM δ13C' finding is methodologically informative — establishes baseline variability against which aquaculture footprints would have to be detected. Sub-rule 1a does not strictly apply here (δ13C tracer ≠ tissue %N bioextraction), but stable-isotope methodology is foundational for the WQ 1.1.1 family. Useful as a Mediterranean-lagoon trophic baseline alongside Souchu 2001 (also Thau) and Carmichael 2012 (R113, anthropogenic-source attribution).</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Nizzoli, Daniele; Welsh, David T; Fano, Elisa Anna; Viaroli, Pierluigi</t>
+          <t>Nizzoli, D., et al.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -22895,11 +24371,6 @@
       <c r="T115" t="inlineStr">
         <is>
           <t>https://doi.org/10.3354/meps315151</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>Distinct paper from Nizzoli 2006 Aquaculture (v14 R66, N + P budget) — same Sacca di Goro site and research group, but this MEPS paper focuses specifically on sediment N-cycling PATHWAYS via ¹⁵N-pairing. Key finding: clam (infaunal) farming stimulates coupled nitrification-denitrification (net N loss to atmosphere), whereas mussel (suspended) farming favors DNRA (N recycled to ammonium, retained in system) — fundamentally different ecosystem-service outcomes for the two culture types. Critical reference for distinguishing how farm structure affects N-cycling indicators. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — ¹⁵N-isotope pairing technique is the paper's core methodology; v1.4 added this indicator to the mollusc set (was missing in v1.3). WQ 1.2.1 narrowed to DO (sediment O₂ flux).</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -22995,11 +24466,26 @@
       <c r="AN115" s="19" t="n"/>
       <c r="AO115" s="19" t="n"/>
       <c r="AP115" s="19" t="n"/>
+      <c r="AQ115" s="16" t="inlineStr">
+        <is>
+          <t>Sediment Nitrogen-Cycling Pathways Under Clam &amp; Mussel Culture (Isotope Pairing)</t>
+        </is>
+      </c>
+      <c r="AR115" s="16" t="inlineStr">
+        <is>
+          <t>Nizzoli, Daniele; Welsh, David T; Fano, Elisa Anna; Viaroli, Pierluigi</t>
+        </is>
+      </c>
+      <c r="AS115" s="16" t="inlineStr">
+        <is>
+          <t>Distinct paper from Nizzoli 2006 Aquaculture (v14 R66, N + P budget) — same Sacca di Goro site and research group, but this MEPS paper focuses specifically on sediment N-cycling PATHWAYS via ¹⁵N-pairing. Key finding: clam (infaunal) farming stimulates coupled nitrification-denitrification (net N loss to atmosphere), whereas mussel (suspended) farming favors DNRA (N recycled to ammonium, retained in system) — fundamentally different ecosystem-service outcomes for the two culture types. Critical reference for distinguishing how farm structure affects N-cycling indicators. | v1.4 refinement: Added WQ 1.1.2 (Rate of denitrification) — ¹⁵N-isotope pairing technique is the paper's core methodology; v1.4 added this indicator to the mollusc set (was missing in v1.3). WQ 1.2.1 narrowed to DO (sediment O₂ flux).</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Liénart, Camilla; Fournioux, Edouard; Garbaras, Andrius; Blanchet, Nicolas; Briant, Nicolas; Dubois, Stanislas F; Gangnery, Aline; Grouhel-Pellouin, Anne et al.</t>
+          <t>Liénart, C., et al.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -23086,11 +24572,6 @@
       <c r="T116" t="inlineStr">
         <is>
           <t>https://doi.org/10.5194/essd-17-799-2025</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>Single most important Sub-rule 1a paper in this batch — 40-year national bivalve-tissue C/N isotope monitoring at unprecedented temporal + spatial scope. Companion paper to Briant 2018 (also French coast, multi-species C/N) — Briant 2018 (#22, awaiting upload) provides the shorter-term snapshot, Liénart 2025 the multi-decadal trajectory. ROCCH (Ifremer) coordinates the sampling backbone; Liénart team adds the C/N isotope layer. Useful template for designing scaled MEL bioindicator monitoring at national/regional level. Data deposited in SEANOE. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (tissue C/N + isotopes only; no DO measurement). δ15N as anthropogenic-N proxy noted in U but does not map to a v1.4 indicator.</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -23186,11 +24667,26 @@
       <c r="AN116" s="19" t="n"/>
       <c r="AO116" s="19" t="n"/>
       <c r="AP116" s="19" t="n"/>
+      <c r="AQ116" s="16" t="inlineStr">
+        <is>
+          <t>National Multi-Decadal Bivalve-Tissue C/N Isotope Bioindicator</t>
+        </is>
+      </c>
+      <c r="AR116" s="16" t="inlineStr">
+        <is>
+          <t>Liénart, Camilla; Fournioux, Edouard; Garbaras, Andrius; Blanchet, Nicolas; Briant, Nicolas; Dubois, Stanislas F; Gangnery, Aline; Grouhel-Pellouin, Anne et al.</t>
+        </is>
+      </c>
+      <c r="AS116" s="16" t="inlineStr">
+        <is>
+          <t>Single most important Sub-rule 1a paper in this batch — 40-year national bivalve-tissue C/N isotope monitoring at unprecedented temporal + spatial scope. Companion paper to Briant 2018 (also French coast, multi-species C/N) — Briant 2018 (#22, awaiting upload) provides the shorter-term snapshot, Liénart 2025 the multi-decadal trajectory. ROCCH (Ifremer) coordinates the sampling backbone; Liénart team adds the C/N isotope layer. Useful template for designing scaled MEL bioindicator monitoring at national/regional level. Data deposited in SEANOE. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (tissue C/N + isotopes only; no DO measurement). δ15N as anthropogenic-N proxy noted in U but does not map to a v1.4 indicator.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sasikumar, Geetha; Krishnakumar, P K</t>
+          <t>Sasikumar, G. &amp; Krishnakumar, P. K.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -23277,11 +24773,6 @@
       <c r="T117" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.ecolind.2010.06.008</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>Site-selection methodology paper. The condition-index-as-bioindicator framing is widely cited in downstream meta-analyses (e.g. Filgueira 2013 Ecol Indic, Sun 2021 R107 in part). Sub-rule 1b narrow retention: ambient WQ measurements (T, salinity, chl-a or food availability) underpin the site contrast and constitute the MEL-mappable component; CI itself sits outside the closed MEL indicator set as an operational farming-quality metric. Logged for v1.4: 'Condition Index' is a borderline vocab item — used in many bivalve papers but not in the framework. | v1.4 refinement: Rule 13 (v1.4) applied: Condition Index is not in MEL framework. Retention basis = WQ 2.1.1 (ambient chl-a / food-availability descriptors), not CI. WQ 1.2.1 removed (T/salinity are not MEL indicators; no DO measurement).  [v22] Methods confirmed: green-mussel Condition Index + biochemical/proximate composition related to environmental variables incl. chlorophyll-a + food quality. Retention basis = chl-a (WQ 2.1.1), survives Rule 13. chl-a / food-quality analysis needs partner lab -&gt; T3 Partnership, NOT T4 (the retention-basis measurement is not fully farmer-executable).</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -23377,11 +24868,26 @@
       <c r="AN117" s="19" t="n"/>
       <c r="AO117" s="19" t="n"/>
       <c r="AP117" s="19" t="n"/>
+      <c r="AQ117" s="16" t="inlineStr">
+        <is>
+          <t>Mussel Condition Index for Farm-Site Selection</t>
+        </is>
+      </c>
+      <c r="AR117" s="16" t="inlineStr">
+        <is>
+          <t>Sasikumar, Geetha; Krishnakumar, P K</t>
+        </is>
+      </c>
+      <c r="AS117" s="16" t="inlineStr">
+        <is>
+          <t>Site-selection methodology paper. The condition-index-as-bioindicator framing is widely cited in downstream meta-analyses (e.g. Filgueira 2013 Ecol Indic, Sun 2021 R107 in part). Sub-rule 1b narrow retention: ambient WQ measurements (T, salinity, chl-a or food availability) underpin the site contrast and constitute the MEL-mappable component; CI itself sits outside the closed MEL indicator set as an operational farming-quality metric. Logged for v1.4: 'Condition Index' is a borderline vocab item — used in many bivalve papers but not in the framework. | v1.4 refinement: Rule 13 (v1.4) applied: Condition Index is not in MEL framework. Retention basis = WQ 2.1.1 (ambient chl-a / food-availability descriptors), not CI. WQ 1.2.1 removed (T/salinity are not MEL indicators; no DO measurement).  [v22] Methods confirmed: green-mussel Condition Index + biochemical/proximate composition related to environmental variables incl. chlorophyll-a + food quality. Retention basis = chl-a (WQ 2.1.1), survives Rule 13. chl-a / food-quality analysis needs partner lab -&gt; T3 Partnership, NOT T4 (the retention-basis measurement is not fully farmer-executable).</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Gernez, Pierre; Doxaran, David; Barillé, Laurent</t>
+          <t>Gernez, P., et al.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -23472,7 +24978,7 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>Foundational satellite-remote-sensing paper for shellfish-aquaculture WQ at farm scale. Sentinel-2 is free and operational, which makes this approach highly scalable. Builds on Gernez 2014 + Thomas 2016 (same group). Companion to subsequent Mediterranean implementations (e.g. Ebro Delta Sentinel-2 paper, Spain). Useful as a MEL backbone for chl-a and turbidity monitoring at scale, where in-situ networks are sparse. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper retrieves SPM/turbidity from Sentinel-2 + chl-a; SPM/turbidity is not in the v1.4 WQ 1.2.1 indicator scope, which is DO-specific).</t>
+          <t>Sentinel-2 is free and operational, which makes this approach highly scalable.</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
@@ -23568,11 +25074,26 @@
       <c r="AN118" s="19" t="n"/>
       <c r="AO118" s="19" t="n"/>
       <c r="AP118" s="19" t="n"/>
+      <c r="AQ118" s="16" t="inlineStr">
+        <is>
+          <t>Shellfish-Bay Water Quality from Sentinel-2 (Turbidity, Chlorophyll, Feeding)</t>
+        </is>
+      </c>
+      <c r="AR118" s="16" t="inlineStr">
+        <is>
+          <t>Gernez, Pierre; Doxaran, David; Barillé, Laurent</t>
+        </is>
+      </c>
+      <c r="AS118" s="16" t="inlineStr">
+        <is>
+          <t>Foundational satellite-remote-sensing paper for shellfish-aquaculture WQ at farm scale. Sentinel-2 is free and operational, which makes this approach highly scalable. Builds on Gernez 2014 + Thomas 2016 (same group). Companion to subsequent Mediterranean implementations (e.g. Ebro Delta Sentinel-2 paper, Spain). Useful as a MEL backbone for chl-a and turbidity monitoring at scale, where in-situ networks are sparse. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper retrieves SPM/turbidity from Sentinel-2 + chl-a; SPM/turbidity is not in the v1.4 WQ 1.2.1 indicator scope, which is DO-specific).</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Wu, Shuo-En; Phongphaew, Napasorn; Zhai, Yichen; Yao, Lulu; Hsu, Hsun-Hao; Shiller, Alan; Azoulay, Jason D; Ng, Tse Nga</t>
+          <t>Wu, S., et al.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -23668,7 +25189,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>Rule 10 caveat: the available abstract and introduction describe a sensor-development paper, explicitly framed as 'platform for aquaculture studies', without yet reporting sea-deployment performance. Retaining per the methodology-paper precedent (cf. Outinen 2019 / R106) because (a) DO and salinity ranges are matched to bivalve-farm conditions, (b) the gape sensor targets oyster behavior in-farm. v1.4 log: a 'Sensor / wearable tag' entry would be useful in Method Category vocab. Companion to the broader open-source bivalve-tag literature (Burnett &amp; Carrington open-source review, 2022).</t>
+          <t>A printed in-situ sensor platform, still at development stage - no sea-deployment performance reported yet.</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
@@ -23754,11 +25275,21 @@
       <c r="AN119" s="19" t="n"/>
       <c r="AO119" s="19" t="n"/>
       <c r="AP119" s="19" t="n"/>
+      <c r="AR119" s="16" t="inlineStr">
+        <is>
+          <t>Wu, Shuo-En; Phongphaew, Napasorn; Zhai, Yichen; Yao, Lulu; Hsu, Hsun-Hao; Shiller, Alan; Azoulay, Jason D; Ng, Tse Nga</t>
+        </is>
+      </c>
+      <c r="AS119" s="16" t="inlineStr">
+        <is>
+          <t>Rule 10 caveat: the available abstract and introduction describe a sensor-development paper, explicitly framed as 'platform for aquaculture studies', without yet reporting sea-deployment performance. Retaining per the methodology-paper precedent (cf. Outinen 2019 / R106) because (a) DO and salinity ranges are matched to bivalve-farm conditions, (b) the gape sensor targets oyster behavior in-farm. v1.4 log: a 'Sensor / wearable tag' entry would be useful in Method Category vocab. Companion to the broader open-source bivalve-tag literature (Burnett &amp; Carrington open-source review, 2022).</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>George, Matthew N; Andino, Jessie; Huie, Jonathan; Carrington, Emily</t>
+          <t>George, M. N., et al.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -23854,7 +25385,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>Sub-rule 1b narrow retention parallel to Fernández 2019 (R94): pH is not in the closed MEL indicator set, but DO (WQ 1.2.1) is robustly measured. The microscale in-aggregation deployment is an unusual and useful methodological contribution — embedding aggregation sensors among cultured mussels allows DO/pH at the site of physiological action rather than only at ambient sonde depth. Companion to Carrington's broader OA/mussel-attachment program. v1.4 log: pH stays off the indicator set; if reconsidered, this paper would upgrade to 2.1.x candidate.</t>
+          <t>Captures the extreme acidification and hypoxia the animals actually experience within clumps, beyond ambient readings.</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -23950,11 +25481,26 @@
       <c r="AN120" s="19" t="n"/>
       <c r="AO120" s="19" t="n"/>
       <c r="AP120" s="19" t="n"/>
+      <c r="AQ120" s="16" t="inlineStr">
+        <is>
+          <t>Microscale pH &amp; Oxygen Inside Mussel Aggregations</t>
+        </is>
+      </c>
+      <c r="AR120" s="16" t="inlineStr">
+        <is>
+          <t>George, Matthew N; Andino, Jessie; Huie, Jonathan; Carrington, Emily</t>
+        </is>
+      </c>
+      <c r="AS120" s="16" t="inlineStr">
+        <is>
+          <t>Sub-rule 1b narrow retention parallel to Fernández 2019 (R94): pH is not in the closed MEL indicator set, but DO (WQ 1.2.1) is robustly measured. The microscale in-aggregation deployment is an unusual and useful methodological contribution — embedding aggregation sensors among cultured mussels allows DO/pH at the site of physiological action rather than only at ambient sonde depth. Companion to Carrington's broader OA/mussel-attachment program. v1.4 log: pH stays off the indicator set; if reconsidered, this paper would upgrade to 2.1.x candidate.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Nizzoli, Daniele; Bartoli, Marco; Viaroli, Pierluigi</t>
+          <t>Nizzoli, D., et al.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -24046,11 +25592,6 @@
       <c r="T121" t="inlineStr">
         <is>
           <t>https://doi.org/10.1007/s10750-007-0683-9</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>Direct companion to R115 (Nizzoli 2006 MEPS, same site/group) and to v14 R66 (Nizzoli 2006 Aquaculture, N + P budget). Together these three papers form the Sacca di Goro Manila-clam-vs-Mediterranean-mussel benthic-N research program. Key value here: temporal trajectory of fluxes across the farming cycle, complementing the snapshot pathway-partitioning of the MEPS paper. Bartoli/Nizzoli/Viaroli are the canonical reference group for this biogeochemistry. | v1.4 refinement: Added WQ 1.1.2 (denitrification, via DIN flux + N-cycling indicators); same site/group as R115 Nizzoli 2006 MEPS. WQ 1.2.1 narrowed to DO.</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -24146,11 +25687,26 @@
       <c r="AN121" s="19" t="n"/>
       <c r="AO121" s="19" t="n"/>
       <c r="AP121" s="19" t="n"/>
+      <c r="AQ121" s="16" t="inlineStr">
+        <is>
+          <t>Oxygen &amp; Ammonium Fluxes Over a Clam-Farming Cycle</t>
+        </is>
+      </c>
+      <c r="AR121" s="16" t="inlineStr">
+        <is>
+          <t>Nizzoli, Daniele; Bartoli, Marco; Viaroli, Pierluigi</t>
+        </is>
+      </c>
+      <c r="AS121" s="16" t="inlineStr">
+        <is>
+          <t>Direct companion to R115 (Nizzoli 2006 MEPS, same site/group) and to v14 R66 (Nizzoli 2006 Aquaculture, N + P budget). Together these three papers form the Sacca di Goro Manila-clam-vs-Mediterranean-mussel benthic-N research program. Key value here: temporal trajectory of fluxes across the farming cycle, complementing the snapshot pathway-partitioning of the MEPS paper. Bartoli/Nizzoli/Viaroli are the canonical reference group for this biogeochemistry. | v1.4 refinement: Added WQ 1.1.2 (denitrification, via DIN flux + N-cycling indicators); same site/group as R115 Nizzoli 2006 MEPS. WQ 1.2.1 narrowed to DO.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ogilvie, Shaun C; Ross, Alex H; Schiel, David R</t>
+          <t>Ogilvie, S. C., et al.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -24242,11 +25798,6 @@
       <c r="T122" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/S0044-8486(99)00219-7</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>Foundational green-shell-mussel-vs-phytoplankton paper for the Marlborough Sounds — the global centre of P. canaliculus aquaculture. Heavily cited by NZ DOC mussel-farming impact reviews. Companion to Ogilvie 2003 (in-situ enclosure experiments at same site) and Inglis et al. 2000 (carrying-capacity context). Phytoplankton depletion within farm boundaries shown to be season-dependent — important methodological insight for designing MEL chl-a baselines. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper measures DIN + DRP, not DO). Nutrients are not in v1.4 WQ 1.2.1 indicator scope.</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
@@ -24342,11 +25893,26 @@
       <c r="AN122" s="19" t="n"/>
       <c r="AO122" s="19" t="n"/>
       <c r="AP122" s="19" t="n"/>
+      <c r="AQ122" s="16" t="inlineStr">
+        <is>
+          <t>Chlorophyll Depletion by a Mussel Farm (Inside-vs-Outside Profiling)</t>
+        </is>
+      </c>
+      <c r="AR122" s="16" t="inlineStr">
+        <is>
+          <t>Ogilvie, Shaun C; Ross, Alex H; Schiel, David R</t>
+        </is>
+      </c>
+      <c r="AS122" s="16" t="inlineStr">
+        <is>
+          <t>Foundational green-shell-mussel-vs-phytoplankton paper for the Marlborough Sounds — the global centre of P. canaliculus aquaculture. Heavily cited by NZ DOC mussel-farming impact reviews. Companion to Ogilvie 2003 (in-situ enclosure experiments at same site) and Inglis et al. 2000 (carrying-capacity context). Phytoplankton depletion within farm boundaries shown to be season-dependent — important methodological insight for designing MEL chl-a baselines. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (paper measures DIN + DRP, not DO). Nutrients are not in v1.4 WQ 1.2.1 indicator scope.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Muñiz, Oihane; Revilla, Marta; Rodríguez, José Germán; Laza-Martínez, Aitor; Fontán, Almudena</t>
+          <t>Muñiz, O., et al.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -24442,7 +26008,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>Pre-development baseline paper — establishes phytoplankton + WQ conditions BEFORE bivalve farm implementation on the Basque coast. Useful template for MEL practitioners designing baseline campaigns. Companion to Muñiz et al. 2017/2018 toxic-phytoplankton evaluations and Bilbao 2020 inshore study. Methodologically clean baseline that future post-implementation surveys can compare against. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (nutrients + chl-a + phytoplankton community measured; no DO).</t>
+          <t>A pre-development baseline template - establishes phytoplankton and water-quality conditions before a farm is built.</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
@@ -24528,11 +26094,21 @@
       <c r="AN123" s="19" t="n"/>
       <c r="AO123" s="19" t="n"/>
       <c r="AP123" s="19" t="n"/>
+      <c r="AR123" s="16" t="inlineStr">
+        <is>
+          <t>Muñiz, Oihane; Revilla, Marta; Rodríguez, José Germán; Laza-Martínez, Aitor; Fontán, Almudena</t>
+        </is>
+      </c>
+      <c r="AS123" s="16" t="inlineStr">
+        <is>
+          <t>Pre-development baseline paper — establishes phytoplankton + WQ conditions BEFORE bivalve farm implementation on the Basque coast. Useful template for MEL practitioners designing baseline campaigns. Companion to Muñiz et al. 2017/2018 toxic-phytoplankton evaluations and Bilbao 2020 inshore study. Methodologically clean baseline that future post-implementation surveys can compare against. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (nutrients + chl-a + phytoplankton community measured; no DO).</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Taylor, Daniel; Jakobsen, Hans; Lyngsgaard, Maren Moltke; Darecki, Mirosław; Werther, Mortimer; Maar, Marie; Saurel, Camille</t>
+          <t>Taylor, D., et al.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -24623,7 +26199,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>Important multi-method integration paper for phytoplankton depletion — establishes that satellite RS, flow-cytometry, mooring, and synoptic survey all detect coherent farm-scale Chl-a depletion in a large mussel farm. Useful methodological template for designing MEL WQ 2.1.x assessments at large suspended-bivalve farms. Companion (same site, same group) to Maar 2024 (R110, climate-projection modelling at Limfjorden — Taylor is co-author there).</t>
+          <t>Agreement across independent methods (satellite, flow-cytometry, mooring, survey) is what makes a farm-scale depletion signal credible.</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
@@ -24719,11 +26295,26 @@
       <c r="AN124" s="19" t="n"/>
       <c r="AO124" s="19" t="n"/>
       <c r="AP124" s="19" t="n"/>
+      <c r="AQ124" s="16" t="inlineStr">
+        <is>
+          <t>Multi-Method Phytoplankton-Depletion Measurement at a Large Mussel Farm</t>
+        </is>
+      </c>
+      <c r="AR124" s="16" t="inlineStr">
+        <is>
+          <t>Taylor, Daniel; Jakobsen, Hans; Lyngsgaard, Maren Moltke; Darecki, Mirosław; Werther, Mortimer; Maar, Marie; Saurel, Camille</t>
+        </is>
+      </c>
+      <c r="AS124" s="16" t="inlineStr">
+        <is>
+          <t>Important multi-method integration paper for phytoplankton depletion — establishes that satellite RS, flow-cytometry, mooring, and synoptic survey all detect coherent farm-scale Chl-a depletion in a large mussel farm. Useful methodological template for designing MEL WQ 2.1.x assessments at large suspended-bivalve farms. Companion (same site, same group) to Maar 2024 (R110, climate-projection modelling at Limfjorden — Taylor is co-author there).</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cugier, Philippe; Struski, Caroline; Blanchard, Michel; Mazurié, Joseph; Pouvreau, Stéphane; Olivier, Frédéric; Trigui, Jihane R; Thiébaut, Eric</t>
+          <t>Cugier, P., et al.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -24819,7 +26410,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>Foundational coupled-model paper for the role of cultivated AND wild filter-feeders in shaping phytoplankton biomass at a major shellfish-farming site. Methodologically important conclusion for MEL: when wild/invasive filter-feeders are abundant, attributing chl-a depletion specifically to aquaculture requires careful disentangling. Companion to Cugier 2005 (same bay, nutrient-only model) and later applied to Bourgneuf Bay and Pertuis Charentais. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — paper's central methodology is a filter-feeder filtration model with partitioned per-species filtration pressure on phytoplankton biomass; v1.4 added this indicator. WQ 1.2.1 removed (model does not produce a DO output).</t>
+          <t>Where wild or invasive filter-feeders are abundant, attributing depletion to aquaculture requires disentangling their contribution.</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -24915,11 +26506,26 @@
       <c r="AN125" s="19" t="n"/>
       <c r="AO125" s="19" t="n"/>
       <c r="AP125" s="19" t="n"/>
+      <c r="AQ125" s="16" t="inlineStr">
+        <is>
+          <t>Coupled Model of Filter-Feeder Effects on Phytoplankton (Reference)</t>
+        </is>
+      </c>
+      <c r="AR125" s="16" t="inlineStr">
+        <is>
+          <t>Cugier, Philippe; Struski, Caroline; Blanchard, Michel; Mazurié, Joseph; Pouvreau, Stéphane; Olivier, Frédéric; Trigui, Jihane R; Thiébaut, Eric</t>
+        </is>
+      </c>
+      <c r="AS125" s="16" t="inlineStr">
+        <is>
+          <t>Foundational coupled-model paper for the role of cultivated AND wild filter-feeders in shaping phytoplankton biomass at a major shellfish-farming site. Methodologically important conclusion for MEL: when wild/invasive filter-feeders are abundant, attributing chl-a depletion specifically to aquaculture requires careful disentangling. Companion to Cugier 2005 (same bay, nutrient-only model) and later applied to Bourgneuf Bay and Pertuis Charentais. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — paper's central methodology is a filter-feeder filtration model with partitioned per-species filtration pressure on phytoplankton biomass; v1.4 added this indicator. WQ 1.2.1 removed (model does not produce a DO output).</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Jiang, Zhibing; Du, Ping; Liao, Yibo; Liu, Qiang; Chen, Quanzhen; Shou, Lu; Zeng, Jiangning; Chen, Jianfang</t>
+          <t>Jiang, Z., et al.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -25010,7 +26616,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>Important real-world paper showing oyster farming as a mitigation tool for thermal-discharge-induced algal blooms in a eutrophic subtropical bay. Confounded by thermal-discharge factor but design (OF vs CA in same thermal envelope) controls for that. After culture-raft removal, no significant differences between former-OF and CA — direct evidence the effect is the farming activity itself. Companion to Jiang 2012 (v15 R43), Jiang 2016 (#38 = R128), Jiang 2019a/b further work. Strong reference for MEL practitioners thinking about bivalve farming as ecological-restoration intervention. | v1.4 refinement: WQ 1.2.1 narrowed to DO (paper lists oxygen among measured physico-chemical variables).</t>
+          <t>Here oyster farming helped mitigate thermal-discharge algal blooms; the old-vs-new-farm design controls for the thermal signal.</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -25106,11 +26712,26 @@
       <c r="AN126" s="19" t="n"/>
       <c r="AO126" s="19" t="n"/>
       <c r="AP126" s="19" t="n"/>
+      <c r="AQ126" s="16" t="inlineStr">
+        <is>
+          <t>Attributing Phytoplankton Change to an Oyster Farm (Size-Fractionated)</t>
+        </is>
+      </c>
+      <c r="AR126" s="16" t="inlineStr">
+        <is>
+          <t>Jiang, Zhibing; Du, Ping; Liao, Yibo; Liu, Qiang; Chen, Quanzhen; Shou, Lu; Zeng, Jiangning; Chen, Jianfang</t>
+        </is>
+      </c>
+      <c r="AS126" s="16" t="inlineStr">
+        <is>
+          <t>Important real-world paper showing oyster farming as a mitigation tool for thermal-discharge-induced algal blooms in a eutrophic subtropical bay. Confounded by thermal-discharge factor but design (OF vs CA in same thermal envelope) controls for that. After culture-raft removal, no significant differences between former-OF and CA — direct evidence the effect is the farming activity itself. Companion to Jiang 2012 (v15 R43), Jiang 2016 (#38 = R128), Jiang 2019a/b further work. Strong reference for MEL practitioners thinking about bivalve farming as ecological-restoration intervention. | v1.4 refinement: WQ 1.2.1 narrowed to DO (paper lists oxygen among measured physico-chemical variables).</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Jiang, Tao; Chen, Feiyu; Yu, Zonghe; Lu, Lin; Wang, Zhaohui</t>
+          <t>Jiang, T., et al.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -25201,7 +26822,7 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>Different Jiang from R43/R126 (Z-B Jiang group) — this is Tao Jiang's group, focused on South China Sea / Daya Bay. Methodologically important for showing size-selective grazing fingerprint in pigment data — useful for MEL practitioners designing chl-a indicator measurements where filtering signal must be distinguished from background community shifts. Sub-rule 1a-adjacent framing: HPLC pigment chemotaxonomy complements but does not replace tissue %N bioextraction.</t>
+          <t>Reveals size-selective grazing that a bulk chlorophyll measurement would miss.</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
@@ -25297,11 +26918,26 @@
       <c r="AN127" s="19" t="n"/>
       <c r="AO127" s="19" t="n"/>
       <c r="AP127" s="19" t="n"/>
+      <c r="AQ127" s="16" t="inlineStr">
+        <is>
+          <t>Size-Selective Phytoplankton-Depletion Fingerprint (HPLC Pigments)</t>
+        </is>
+      </c>
+      <c r="AR127" s="16" t="inlineStr">
+        <is>
+          <t>Jiang, Tao; Chen, Feiyu; Yu, Zonghe; Lu, Lin; Wang, Zhaohui</t>
+        </is>
+      </c>
+      <c r="AS127" s="16" t="inlineStr">
+        <is>
+          <t>Different Jiang from R43/R126 (Z-B Jiang group) — this is Tao Jiang's group, focused on South China Sea / Daya Bay. Methodologically important for showing size-selective grazing fingerprint in pigment data — useful for MEL practitioners designing chl-a indicator measurements where filtering signal must be distinguished from background community shifts. Sub-rule 1a-adjacent framing: HPLC pigment chemotaxonomy complements but does not replace tissue %N bioextraction.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Rahman, M A; Henderson, S; Miller-Ezzy, P A; Li, X X; Qin, J G</t>
+          <t>Rahman, M. A., et al.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -25392,7 +27028,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>Sub-rule 1b boundary case — primarily a physiology paper, but the seston-particle measurements and chl-a depletion in chambers provide MEL-relevant quantification of filtering capacity per species. Useful for parameterising mass-balance / carrying-capacity models that depend on species-specific clearance rates. Coffin Bay site connects to broader South Australian shellfish industry. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — clearance-rate methodology is mollusc-specific WQ 1.3.1 indicator; v1.4 addition. CRs measured per species across natural seston assemblages.</t>
+          <t>Primarily physiology, but yields the per-species clearance rates needed to parameterise carrying-capacity models.</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -25488,11 +27124,26 @@
       <c r="AN128" s="19" t="n"/>
       <c r="AO128" s="19" t="n"/>
       <c r="AP128" s="19" t="n"/>
+      <c r="AQ128" s="16" t="inlineStr">
+        <is>
+          <t>Species-Specific Bivalve Filtration Parameters (Seston/Chlorophyll Chambers)</t>
+        </is>
+      </c>
+      <c r="AR128" s="16" t="inlineStr">
+        <is>
+          <t>Rahman, M A; Henderson, S; Miller-Ezzy, P A; Li, X X; Qin, J G</t>
+        </is>
+      </c>
+      <c r="AS128" s="16" t="inlineStr">
+        <is>
+          <t>Sub-rule 1b boundary case — primarily a physiology paper, but the seston-particle measurements and chl-a depletion in chambers provide MEL-relevant quantification of filtering capacity per species. Useful for parameterising mass-balance / carrying-capacity models that depend on species-specific clearance rates. Coffin Bay site connects to broader South Australian shellfish industry. | v1.4 refinement: Added WQ 1.3.1 (Rate of water filtration) — clearance-rate methodology is mollusc-specific WQ 1.3.1 indicator; v1.4 addition. CRs measured per species across natural seston assemblages.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ysebaert, Tom; Walles, Brenda; Haner, Judy; Hancock, Boze</t>
+          <t>Ysebaert, T., et al.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -25580,7 +27231,7 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>Distinct from v14 R80 Ysebaert 2009 (Tom Ysebaert's earlier ESM/J Sea Res paper on different topic) — new row added. This 2018 chapter is one of the most cited syntheses on bivalve-reef coastal-protection ecosystem services. Companion to Walles 2015 (Oosterschelde) and to the Alabama TNC oyster-reef program. Useful framework reference for MEL practitioners assessing H&amp;B + coastal-protection indicators. | v1.4 refinement: Added CC 3.1.1 (Wave attenuation / coastal protection) — chapter's primary deliverable is the ecosystem-engineering coastal-protection function of reef-building bivalves; v1.4 added this indicator (mollusc CC Goal 3). Y now multi-tagged H&amp;B + CC.  [v21 retier] Reference cannot hold an execution tier (T3/T4); reclassified to T2 as a usable framework synthesis.</t>
+          <t>A framework reference for restoration-oriented reef monitoring and coastal-protection benefit.</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
@@ -25676,11 +27327,26 @@
       <c r="AN129" s="19" t="n"/>
       <c r="AO129" s="19" t="n"/>
       <c r="AP129" s="19" t="n"/>
+      <c r="AQ129" s="16" t="inlineStr">
+        <is>
+          <t>Bivalve-Reef Coastal Protection &amp; Ecosystem Engineering (Synthesis)</t>
+        </is>
+      </c>
+      <c r="AR129" s="16" t="inlineStr">
+        <is>
+          <t>Ysebaert, Tom; Walles, Brenda; Haner, Judy; Hancock, Boze</t>
+        </is>
+      </c>
+      <c r="AS129" s="16" t="inlineStr">
+        <is>
+          <t>Distinct from v14 R80 Ysebaert 2009 (Tom Ysebaert's earlier ESM/J Sea Res paper on different topic) — new row added. This 2018 chapter is one of the most cited syntheses on bivalve-reef coastal-protection ecosystem services. Companion to Walles 2015 (Oosterschelde) and to the Alabama TNC oyster-reef program. Useful framework reference for MEL practitioners assessing H&amp;B + coastal-protection indicators. | v1.4 refinement: Added CC 3.1.1 (Wave attenuation / coastal protection) — chapter's primary deliverable is the ecosystem-engineering coastal-protection function of reef-building bivalves; v1.4 added this indicator (mollusc CC Goal 3). Y now multi-tagged H&amp;B + CC.  [v21 retier] Reference cannot hold an execution tier (T3/T4); reclassified to T2 as a usable framework synthesis.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Goedefroo, Nanou; Benham, Peter; Debusschere, Elisabeth; Deneudt, Klaas; Mascart, Thibaud; Semeraro, Alexia; Sterckx, Tomas; Van Hoey, Gert</t>
+          <t>Goedefroo, N., et al.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -25771,7 +27437,7 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>Pilot-project paper for the Coastbusters NBS program (Belgium). Important methodological contribution: testing whether longline mussel aquaculture technique can be redirected from harvest goal to coastal-protection goal. Companion to Coastbusters 2.0 (Boulenger 2023 ff.). Useful for MEL practitioners thinking about repurposing aquaculture infrastructure for habitat + coastal-protection services. | v1.4 refinement: Added CC 3.1.1 — explicit nature-based-solution paper for coastal erosion mitigation off Belgian coast; matches mollusc CC Obj 3.1 directly. Y now multi-tagged H&amp;B + CC.</t>
+          <t>Tests whether the mussel-farming technique can be redirected from harvest to coastal protection.</t>
         </is>
       </c>
       <c r="V130" t="inlineStr">
@@ -25867,11 +27533,26 @@
       <c r="AN130" s="19" t="n"/>
       <c r="AO130" s="19" t="n"/>
       <c r="AP130" s="19" t="n"/>
+      <c r="AQ130" s="16" t="inlineStr">
+        <is>
+          <t>Longline-Mussel Nature-Based Solution: Reef &amp; Biodiversity Assessment (BACI)</t>
+        </is>
+      </c>
+      <c r="AR130" s="16" t="inlineStr">
+        <is>
+          <t>Goedefroo, Nanou; Benham, Peter; Debusschere, Elisabeth; Deneudt, Klaas; Mascart, Thibaud; Semeraro, Alexia; Sterckx, Tomas; Van Hoey, Gert</t>
+        </is>
+      </c>
+      <c r="AS130" s="16" t="inlineStr">
+        <is>
+          <t>Pilot-project paper for the Coastbusters NBS program (Belgium). Important methodological contribution: testing whether longline mussel aquaculture technique can be redirected from harvest goal to coastal-protection goal. Companion to Coastbusters 2.0 (Boulenger 2023 ff.). Useful for MEL practitioners thinking about repurposing aquaculture infrastructure for habitat + coastal-protection services. | v1.4 refinement: Added CC 3.1.1 — explicit nature-based-solution paper for coastal erosion mitigation off Belgian coast; matches mollusc CC Obj 3.1 directly. Y now multi-tagged H&amp;B + CC.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Lin, Jun; Li, Chunyan; Zhang, Shouyu</t>
+          <t>Lin, J., et al.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -25962,7 +27643,7 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>Foundational paper for documenting that suspended-bivalve farms act as porous physical canopies in the surface layer, reducing horizontal flow and inducing downwelling. The 80% chl-a depletion result is striking and matches the seston-depletion + carrying-capacity literature. Important for MEL practitioners: chl-a measurements 'inside' farms are physically distorted by reduced current — sampling design must account for canopy-induced vertical mixing. Companion to R125 Cugier 2010 (modelling), R110 Maar 2024 (modelling). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — paper measures canopy-induced flow modification which contributes to wave-energy attenuation by suspended bivalve farms; does not compute wave-decay coefficient directly, so retained under Sub-rule 1c with caveat. Y now multi-tagged WQ + CC.</t>
+          <t>Documents how a large suspended farm acts as a porous canopy that reduces flow and can strongly deplete chlorophyll.</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
@@ -26048,11 +27729,21 @@
       <c r="AN131" s="19" t="n"/>
       <c r="AO131" s="19" t="n"/>
       <c r="AP131" s="19" t="n"/>
+      <c r="AR131" s="16" t="inlineStr">
+        <is>
+          <t>Lin, Jun; Li, Chunyan; Zhang, Shouyu</t>
+        </is>
+      </c>
+      <c r="AS131" s="16" t="inlineStr">
+        <is>
+          <t>Foundational paper for documenting that suspended-bivalve farms act as porous physical canopies in the surface layer, reducing horizontal flow and inducing downwelling. The 80% chl-a depletion result is striking and matches the seston-depletion + carrying-capacity literature. Important for MEL practitioners: chl-a measurements 'inside' farms are physically distorted by reduced current — sampling design must account for canopy-induced vertical mixing. Companion to R125 Cugier 2010 (modelling), R110 Maar 2024 (modelling). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — paper measures canopy-induced flow modification which contributes to wave-energy attenuation by suspended bivalve farms; does not compute wave-decay coefficient directly, so retained under Sub-rule 1c with caveat. Y now multi-tagged WQ + CC.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Shi, Benwei; Pratolongo, Paula D; Du, Yongfen; Li, Jiasheng; Yang, S L; Wu, Jihua; Xu, Kehui; Wang, Ya Ping</t>
+          <t>Shi, B., et al.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -26148,7 +27839,7 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>Important paper for the COUNTERINTUITIVE finding that high-density bivalve cultivation can DESTABILISE rather than stabilise sediments (the opposite of reef-building bivalves in Ysebaert 2018 R129) — context matters: the action of clams burrowing + protruding their shells reduces critical erosion shear stress. Important for MEL practitioners using H&amp;B 1.4.1 sediment-dynamics indicators on clam-cultivation sites: cultivation may shift the system toward erosion. Companion to Shi 2021 (L&amp;O, typhoon-induced erosion at same site) and Li 2021 (Ecohydrology &amp; Hydrobiology, same site, ~23% threshold drop confirmed). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — sediment-erosion threshold under clam cultivation is directly relevant to mollusc CC Obj 3.1 (coastal erosion), as a COUNTER-EXAMPLE showing high-density clam farming reduces critical erosion shear stress (i.e., destabilises sediment). Important contrast with reef-building bivalves (R129, R130). Y now multi-tagged H&amp;B + CC.</t>
+          <t>Counterintuitively, high-density burrowing, shell-protruding clams can lower the erosion threshold and destabilise the bed - the opposite of reef-builders.</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
@@ -26244,11 +27935,26 @@
       <c r="AN132" s="19" t="n"/>
       <c r="AO132" s="19" t="n"/>
       <c r="AP132" s="19" t="n"/>
+      <c r="AQ132" s="16" t="inlineStr">
+        <is>
+          <t>Do Dense Infaunal Bivalves Stabilise or Erode Sediment?</t>
+        </is>
+      </c>
+      <c r="AR132" s="16" t="inlineStr">
+        <is>
+          <t>Shi, Benwei; Pratolongo, Paula D; Du, Yongfen; Li, Jiasheng; Yang, S L; Wu, Jihua; Xu, Kehui; Wang, Ya Ping</t>
+        </is>
+      </c>
+      <c r="AS132" s="16" t="inlineStr">
+        <is>
+          <t>Important paper for the COUNTERINTUITIVE finding that high-density bivalve cultivation can DESTABILISE rather than stabilise sediments (the opposite of reef-building bivalves in Ysebaert 2018 R129) — context matters: the action of clams burrowing + protruding their shells reduces critical erosion shear stress. Important for MEL practitioners using H&amp;B 1.4.1 sediment-dynamics indicators on clam-cultivation sites: cultivation may shift the system toward erosion. Companion to Shi 2021 (L&amp;O, typhoon-induced erosion at same site) and Li 2021 (Ecohydrology &amp; Hydrobiology, same site, ~23% threshold drop confirmed). | v1.4 refinement: Added CC 3.1.1 per Sub-rule 1c (v1.4) — sediment-erosion threshold under clam cultivation is directly relevant to mollusc CC Obj 3.1 (coastal erosion), as a COUNTER-EXAMPLE showing high-density clam farming reduces critical erosion shear stress (i.e., destabilises sediment). Important contrast with reef-building bivalves (R129, R130). Y now multi-tagged H&amp;B + CC.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Briant, Nicolas; Savoye, Nicolas; Chouvelon, Tiphaine; David, Valérie; Rodriguez, Samuel; Charlier, Karine; Sonke, Jeroen E; Chiffoleau, Jean François; Brach-Papa, Christophe; Knoery, Joël</t>
+          <t>Briant, N., et al.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -26337,11 +28043,6 @@
       <c r="T133" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.scitotenv.2017.08.281</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>Canonical Sub-rule 1a precursor to R116 Liénart 2025 — same ROCCH network (Ifremer), same research consortium (Briant himself is co-author of Liénart 2025). Briant 2018 established the cross-scale (spatial + seasonal + decadal) methodology with 189 samples across 74 sites; Liénart 2025 extended it to 1141 samples × 1981–2021 at a curated 33-station subset. Together the pair represents the deepest multi-decadal bivalve-tissue bioindication dataset in MEL-relevant literature. Companion to Carmichael 2012 (R113, USA Atlantic estuaries) and the broader Sub-rule 1a corpus. Note: added at R134 out of CSV order (after R133 #44 Shi 2020) because the PDF arrived after the rest of the chat had been processed. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (tissue C/N + δ13C + δ15N only; no DO measurement). δ15N anthropogenic-N proxy framing noted in U but does not map to a v1.4 indicator.</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
@@ -26437,11 +28138,26 @@
       <c r="AN133" s="19" t="n"/>
       <c r="AO133" s="19" t="n"/>
       <c r="AP133" s="19" t="n"/>
+      <c r="AQ133" s="16" t="inlineStr">
+        <is>
+          <t>Multi-Scale Bivalve-Tissue C/N Isotope Bioindicator Baseline</t>
+        </is>
+      </c>
+      <c r="AR133" s="16" t="inlineStr">
+        <is>
+          <t>Briant, Nicolas; Savoye, Nicolas; Chouvelon, Tiphaine; David, Valérie; Rodriguez, Samuel; Charlier, Karine; Sonke, Jeroen E; Chiffoleau, Jean François; Brach-Papa, Christophe; Knoery, Joël</t>
+        </is>
+      </c>
+      <c r="AS133" s="16" t="inlineStr">
+        <is>
+          <t>Canonical Sub-rule 1a precursor to R116 Liénart 2025 — same ROCCH network (Ifremer), same research consortium (Briant himself is co-author of Liénart 2025). Briant 2018 established the cross-scale (spatial + seasonal + decadal) methodology with 189 samples across 74 sites; Liénart 2025 extended it to 1141 samples × 1981–2021 at a curated 33-station subset. Together the pair represents the deepest multi-decadal bivalve-tissue bioindication dataset in MEL-relevant literature. Companion to Carmichael 2012 (R113, USA Atlantic estuaries) and the broader Sub-rule 1a corpus. Note: added at R134 out of CSV order (after R133 #44 Shi 2020) because the PDF arrived after the rest of the chat had been processed. | v1.4 refinement: WQ 1.2.1 removed under v1.4 (tissue C/N + δ13C + δ15N only; no DO measurement). δ15N anthropogenic-N proxy framing noted in U but does not map to a v1.4 indicator.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO / Tennenbaum Marine Observatories Network</t>
+          <t>Smithsonian MarineGEO</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -26524,7 +28240,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>Smithsonian MarineGEO suite — the closest direct analogue to the Oyster-Reef protocol for the epibiota-on-structures case. ARMS (Autonomous Reef Monitoring Structures) is the metabarcoding-based cousin for cryptobiota where panel ID is impractical. Built for natural hard-bottom; transfers cleanly to aquaculture gear.</t>
+          <t>Built for natural hard-bottom but transfers cleanly to farm gear; where organisms are too cryptic to ID from panels, an ARMS plus DNA-metabarcoding approach is the alternative.</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
@@ -26620,6 +28336,21 @@
       <c r="AN134" s="19" t="n"/>
       <c r="AO134" s="19" t="n"/>
       <c r="AP134" s="19" t="n"/>
+      <c r="AQ134" s="16" t="inlineStr">
+        <is>
+          <t>Settlement-Panel Monitoring of Fouling &amp; Epibiont Communities on Farm Gear</t>
+        </is>
+      </c>
+      <c r="AR134" s="16" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO / Tennenbaum Marine Observatories Network</t>
+        </is>
+      </c>
+      <c r="AS134" s="16" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO suite — the closest direct analogue to the Oyster-Reef protocol for the epibiota-on-structures case. ARMS (Autonomous Reef Monitoring Structures) is the metabarcoding-based cousin for cryptobiota where panel ID is impractical. Built for natural hard-bottom; transfers cleanly to aquaculture gear.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -26707,7 +28438,7 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>Specific to eastern oyster (Crassostrea virginica) but design transfers to other bivalve reef/longline contexts. Pairs with the Baggett 2014 handbook (next row), the methodological parent.</t>
+          <t>Specific to eastern oyster but the design transfers to other bivalve reef/longline contexts.</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
@@ -26803,11 +28534,26 @@
       <c r="AN135" s="19" t="n"/>
       <c r="AO135" s="19" t="n"/>
       <c r="AP135" s="19" t="n"/>
+      <c r="AQ135" s="16" t="inlineStr">
+        <is>
+          <t>Oyster-Reef Habitat Structure &amp; Associated-Fauna Survey</t>
+        </is>
+      </c>
+      <c r="AR135" s="16" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="AS135" s="16" t="inlineStr">
+        <is>
+          <t>Specific to eastern oyster (Crassostrea virginica) but design transfers to other bivalve reef/longline contexts. Pairs with the Baggett 2014 handbook (next row), the methodological parent.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Baggett, L.P.; Powers, S.P.; Brumbaugh, R.D.; Coen, L.D.; DeAngelis, B.M.; Greene, J.K.; Hancock, B.T.; Morlock, S.M.</t>
+          <t>Baggett, L. P., et al.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -26895,7 +28641,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>TNC-authored — direct lineage with this MEL framework. Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming H&amp;B/WQ. The coastal-protection goal-based metric set is the practitioner route to CC 3.1.1 (shoreline position/elevation + wave-gauge/pressure-logger field methods).</t>
+          <t>Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming; the goal-based coastal-protection metrics are the practitioner route to wave attenuation.</t>
         </is>
       </c>
       <c r="V136" t="inlineStr">
@@ -26991,11 +28737,26 @@
       <c r="AN136" s="19" t="n"/>
       <c r="AO136" s="19" t="n"/>
       <c r="AP136" s="19" t="n"/>
+      <c r="AQ136" s="16" t="inlineStr">
+        <is>
+          <t>TNC Oyster Restoration Monitoring Handbook (Universal Metrics)</t>
+        </is>
+      </c>
+      <c r="AR136" s="16" t="inlineStr">
+        <is>
+          <t>Baggett, L.P.; Powers, S.P.; Brumbaugh, R.D.; Coen, L.D.; DeAngelis, B.M.; Greene, J.K.; Hancock, B.T.; Morlock, S.M.</t>
+        </is>
+      </c>
+      <c r="AS136" s="16" t="inlineStr">
+        <is>
+          <t>TNC-authored — direct lineage with this MEL framework. Restoration-oriented but the universal metrics and environmental variables transfer to bivalve farming H&amp;B/WQ. The coastal-protection goal-based metric set is the practitioner route to CC 3.1.1 (shoreline position/elevation + wave-gauge/pressure-logger field methods).</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Native Oyster Network (UK &amp; Ireland); Native Oyster Restoration Alliance (NORA)</t>
+          <t>Native Oyster Network (UK &amp; Ireland)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -27078,7 +28839,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>Use for European flat-oyster (Ostrea edulis) contexts where Baggett 2014 methods need adaptation. Complementary to the MarineGEO Oyster-Reef protocol and Baggett handbook.</t>
+          <t>Use it for European flat-oyster (Ostrea edulis) settings where the TNC handbook methods need adapting.</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
@@ -27174,6 +28935,21 @@
       <c r="AN137" s="19" t="n"/>
       <c r="AO137" s="19" t="n"/>
       <c r="AP137" s="19" t="n"/>
+      <c r="AQ137" s="16" t="inlineStr">
+        <is>
+          <t>European Native-Oyster Restoration Monitoring Guidelines</t>
+        </is>
+      </c>
+      <c r="AR137" s="16" t="inlineStr">
+        <is>
+          <t>Native Oyster Network (UK &amp; Ireland); Native Oyster Restoration Alliance (NORA)</t>
+        </is>
+      </c>
+      <c r="AS137" s="16" t="inlineStr">
+        <is>
+          <t>Use for European flat-oyster (Ostrea edulis) contexts where Baggett 2014 methods need adaptation. Complementary to the MarineGEO Oyster-Reef protocol and Baggett handbook.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -27261,7 +29037,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>Reef Life Survey (RLS) provides an equivalent globally standardized diver visual-census methods manual and trained-diver network — an alternative where added rigour or a citizen-science cohort is wanted. Requires dive competency and reasonable water clarity.</t>
+          <t>Needs dive/snorkel competency and reasonable clarity; Reef Life Survey is an equivalent with a trained-diver network.</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
@@ -27357,6 +29133,21 @@
       <c r="AN138" s="19" t="n"/>
       <c r="AO138" s="19" t="n"/>
       <c r="AP138" s="19" t="n"/>
+      <c r="AQ138" s="16" t="inlineStr">
+        <is>
+          <t>Diver Belt-Transect Visual Census of Mobile Fauna</t>
+        </is>
+      </c>
+      <c r="AR138" s="16" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="AS138" s="16" t="inlineStr">
+        <is>
+          <t>Reef Life Survey (RLS) provides an equivalent globally standardized diver visual-census methods manual and trained-diver network — an alternative where added rigour or a citizen-science cohort is wanted. Requires dive competency and reasonable water clarity.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -27444,7 +29235,7 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>Best for shallow, wadeable, soft-bottom margins; complements diver/BRUV methods for the mobile-fauna indicator.</t>
+          <t>Best for shallow, wadeable, soft-bottom margins.</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
@@ -27540,6 +29331,21 @@
       <c r="AN139" s="19" t="n"/>
       <c r="AO139" s="19" t="n"/>
       <c r="AP139" s="19" t="n"/>
+      <c r="AQ139" s="16" t="inlineStr">
+        <is>
+          <t>Beach-Seine Sampling of Nearshore Nekton</t>
+        </is>
+      </c>
+      <c r="AR139" s="16" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="AS139" s="16" t="inlineStr">
+        <is>
+          <t>Best for shallow, wadeable, soft-bottom margins; complements diver/BRUV methods for the mobile-fauna indicator.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -27627,7 +29433,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>Image archives are re-analysable and auditable. Captures epibenthic cover (not soft-sediment infauna). Pairs with the Sediment Organic Matter protocol for soft-sediment characterisation.</t>
+          <t>Captures epibenthic cover, not soft-sediment infauna - pair with a sediment protocol for the seabed itself.</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
@@ -27723,6 +29529,21 @@
       <c r="AN140" s="19" t="n"/>
       <c r="AO140" s="19" t="n"/>
       <c r="AP140" s="19" t="n"/>
+      <c r="AQ140" s="16" t="inlineStr">
+        <is>
+          <t>Benthic Photoquadrat Cover Survey (Point-Count Imaging)</t>
+        </is>
+      </c>
+      <c r="AR140" s="16" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="AS140" s="16" t="inlineStr">
+        <is>
+          <t>Image archives are re-analysable and auditable. Captures epibenthic cover (not soft-sediment infauna). Pairs with the Sediment Organic Matter protocol for soft-sediment characterisation.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -27810,7 +29631,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, DIN flux) use the SEPA / NS 9410 benthic standards (rows below).</t>
+          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry use a benthic standard such as SEPA or NS 9410.</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
@@ -27906,11 +29727,26 @@
       <c r="AN141" s="19" t="n"/>
       <c r="AO141" s="19" t="n"/>
       <c r="AP141" s="19" t="n"/>
+      <c r="AQ141" s="16" t="inlineStr">
+        <is>
+          <t>Sediment Organic-Matter Monitoring (Loss-on-Ignition)</t>
+        </is>
+      </c>
+      <c r="AR141" s="16" t="inlineStr">
+        <is>
+          <t>Smithsonian MarineGEO</t>
+        </is>
+      </c>
+      <c r="AS141" s="16" t="inlineStr">
+        <is>
+          <t>A simple, low-cost sediment-condition metric; for full biogeochemistry (redox, sulphide, DIN flux) use the SEPA / NS 9410 benthic standards (rows below).</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Langlois, T.; Goetze, J.; Bond, T.; et al. (NESP Marine Biodiversity Hub)</t>
+          <t>Langlois, T., et al.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -28001,7 +29837,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>Single-camera baited cameras (BRUVs) are a lower-cost practitioner variant (relative abundance only, no lengths). GlobalArchive (globalarchive.org) is the standardized data repository. Part of the NESP Marine Sampling Field Manuals collection (next row). For finfish, this is the route to the fish-attraction facet of Finfish H&amp;B 2.1.1.</t>
+          <t>A single-camera BRUV is a lower-cost variant (relative abundance only, no lengths).</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
@@ -28097,11 +29933,26 @@
       <c r="AN142" s="19" t="n"/>
       <c r="AO142" s="19" t="n"/>
       <c r="AP142" s="19" t="n"/>
+      <c r="AQ142" s="16" t="inlineStr">
+        <is>
+          <t>Baited Stereo-Video Survey of Fish Assemblages (Stereo-BRUV)</t>
+        </is>
+      </c>
+      <c r="AR142" s="16" t="inlineStr">
+        <is>
+          <t>Langlois, T.; Goetze, J.; Bond, T.; et al. (NESP Marine Biodiversity Hub)</t>
+        </is>
+      </c>
+      <c r="AS142" s="16" t="inlineStr">
+        <is>
+          <t>Single-camera baited cameras (BRUVs) are a lower-cost practitioner variant (relative abundance only, no lengths). GlobalArchive (globalarchive.org) is the standardized data repository. Part of the NESP Marine Sampling Field Manuals collection (next row). For finfish, this is the route to the fish-attraction facet of Finfish H&amp;B 2.1.1.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Przeslawski, R.; Foster, S. (eds.) — NESP Marine Biodiversity Hub</t>
+          <t>Przeslawski, R. &amp; Foster, S. (. ). —. N. M. B. H.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -28184,7 +30035,7 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>Most useful for designing comparable benthic/mobile-fauna campaigns; lifts indicator-specific manuals (e.g., the stereo-BRUV manual above) into a coherent programme. Tier T2 as a researcher-grade design tool.</t>
+          <t>Use it to design comparable benthic and mobile-fauna campaigns and to standardise across individual manuals.</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
@@ -28280,6 +30131,21 @@
       <c r="AN143" s="19" t="n"/>
       <c r="AO143" s="19" t="n"/>
       <c r="AP143" s="19" t="n"/>
+      <c r="AQ143" s="16" t="inlineStr">
+        <is>
+          <t>Australian Marine-Sampling Field Manuals (Design Reference)</t>
+        </is>
+      </c>
+      <c r="AR143" s="16" t="inlineStr">
+        <is>
+          <t>Przeslawski, R.; Foster, S. (eds.) — NESP Marine Biodiversity Hub</t>
+        </is>
+      </c>
+      <c r="AS143" s="16" t="inlineStr">
+        <is>
+          <t>Most useful for designing comparable benthic/mobile-fauna campaigns; lifts indicator-specific manuals (e.g., the stereo-BRUV manual above) into a coherent programme. Tier T2 as a researcher-grade design tool.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -28367,7 +30233,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>A regulatory impact-monitoring standard rather than a benefit protocol, but the grab→IQI workflow is the standard route to the benthic-infauna and sediment indicators. Directly comparable to Norway NS 9410 / MOM (next row).</t>
+          <t>A regulatory impact standard; the grab-to-IQI workflow is the standard route to the benthic-infauna and sediment indicators.</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -28463,6 +30329,21 @@
       <c r="AN144" s="19" t="n"/>
       <c r="AO144" s="19" t="n"/>
       <c r="AP144" s="19" t="n"/>
+      <c r="AQ144" s="16" t="inlineStr">
+        <is>
+          <t>Regulated Benthic Monitoring: Grab Survey to Infaunal Quality Index</t>
+        </is>
+      </c>
+      <c r="AR144" s="16" t="inlineStr">
+        <is>
+          <t>Scottish Environment Protection Agency (SEPA)</t>
+        </is>
+      </c>
+      <c r="AS144" s="16" t="inlineStr">
+        <is>
+          <t>A regulatory impact-monitoring standard rather than a benefit protocol, but the grab→IQI workflow is the standard route to the benthic-infauna and sediment indicators. Directly comparable to Norway NS 9410 / MOM (next row).</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -28550,7 +30431,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>Standard document is paywalled; methodology well-documented in secondary literature. Tier set conservatively at T2 (Sub-rule 14a) pending a read of the standard itself — the B-survey component is plausibly T3/Partnership once confirmed. Directly comparable to the SEPA manual.</t>
+          <t>The standard itself is paywalled, so confirm the exact thresholds from the document before relying on them.</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
@@ -28646,11 +30527,26 @@
       <c r="AN145" s="19" t="n"/>
       <c r="AO145" s="19" t="n"/>
       <c r="AP145" s="19" t="n"/>
+      <c r="AQ145" s="16" t="inlineStr">
+        <is>
+          <t>Norwegian MOM Benthic-Monitoring Standard (NS 9410)</t>
+        </is>
+      </c>
+      <c r="AR145" s="16" t="inlineStr">
+        <is>
+          <t>Standards Norway</t>
+        </is>
+      </c>
+      <c r="AS145" s="16" t="inlineStr">
+        <is>
+          <t>Standard document is paywalled; methodology well-documented in secondary literature. Tier set conservatively at T2 (Sub-rule 14a) pending a read of the standard itself — the B-survey component is plausibly T3/Partnership once confirmed. Directly comparable to the SEPA manual.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Scottish Salmon Producers' Org. (Code of Good Practice); Institute of Marine Research (Norway); Norwegian Food Safety Authority</t>
+          <t>Scottish Salmon Producers' Org. (Code of Good Practice)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -28729,11 +30625,6 @@
       <c r="T146" t="inlineStr">
         <is>
           <t>Scottish Code of Good Practice: thecodeofgoodpractice.co.uk ; Norway IMR: https://www.hi.no/en/hi/nettrapporter/rapport-fra-havforskningen-en-2024-61</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>The Norwegian Salmon Lice Directive (FOR-2009-08-18-1095) is the regulatory framework mandating counting; the IMR protocol is the certified standardized count for the national wild-salmonid programme. Farm-level counting alone is closer to T4; tier set at T3 to cover the full indicator (incl. wild-population surveillance to ~2.5 km). Tagged with the generic 'H&amp;B 2.1.1' string; under the finfish set this is fish-attraction / parasite surveillance.</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
@@ -28829,11 +30720,26 @@
       <c r="AN146" s="19" t="n"/>
       <c r="AO146" s="19" t="n"/>
       <c r="AP146" s="19" t="n"/>
+      <c r="AQ146" s="16" t="inlineStr">
+        <is>
+          <t>Sea-Lice Counting &amp; Surveillance Protocol</t>
+        </is>
+      </c>
+      <c r="AR146" s="16" t="inlineStr">
+        <is>
+          <t>Scottish Salmon Producers' Org. (Code of Good Practice); Institute of Marine Research (Norway); Norwegian Food Safety Authority</t>
+        </is>
+      </c>
+      <c r="AS146" s="16" t="inlineStr">
+        <is>
+          <t>The Norwegian Salmon Lice Directive (FOR-2009-08-18-1095) is the regulatory framework mandating counting; the IMR protocol is the certified standardized count for the national wild-salmonid programme. Farm-level counting alone is closer to T4; tier set at T3 to cover the full indicator (incl. wild-population surveillance to ~2.5 km). Tagged with the generic 'H&amp;B 2.1.1' string; under the finfish set this is fish-attraction / parasite surveillance.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Reichert-Nguyen, J.; Cornwell, J.; et al. — Oyster BMP Expert Panel (Chesapeake Bay Program / Oyster Recovery Partnership)</t>
+          <t>Reichert-Nguyen, J., et al.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -28916,7 +30822,7 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>TNC-relevant (TNC sits on the partnership). Restoration + aquaculture both covered. Shell-assimilation accounting is N/P (not carbon); a shell-CARBON storage protocol for CC 2.1.1 (mollusc) does not yet exist. Default tissue/shell coefficients make a desk estimate feasible without a lab.</t>
+          <t>Default tissue/shell coefficients make a credible desk estimate feasible without a lab; shell accounting here is for N and P, not carbon.</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
@@ -29012,6 +30918,21 @@
       <c r="AN147" s="19" t="n"/>
       <c r="AO147" s="19" t="n"/>
       <c r="AP147" s="19" t="n"/>
+      <c r="AQ147" s="16" t="inlineStr">
+        <is>
+          <t>Oyster Nutrient-Reduction Crediting Protocol (Tissue/Shell/Denitrification)</t>
+        </is>
+      </c>
+      <c r="AR147" s="16" t="inlineStr">
+        <is>
+          <t>Reichert-Nguyen, J.; Cornwell, J.; et al. — Oyster BMP Expert Panel (Chesapeake Bay Program / Oyster Recovery Partnership)</t>
+        </is>
+      </c>
+      <c r="AS147" s="16" t="inlineStr">
+        <is>
+          <t>TNC-relevant (TNC sits on the partnership). Restoration + aquaculture both covered. Shell-assimilation accounting is N/P (not carbon); a shell-CARBON storage protocol for CC 2.1.1 (mollusc) does not yet exist. Default tissue/shell coefficients make a desk estimate feasible without a lab.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -29099,7 +31020,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>Implements the Chesapeake Oyster BMP framework (previous row) for restoration credits. Useful where reef restoration rather than harvest is the practice.</t>
+          <t>Use it where reef restoration, rather than harvest, is the practice.</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
@@ -29195,11 +31116,26 @@
       <c r="AN148" s="19" t="n"/>
       <c r="AO148" s="19" t="n"/>
       <c r="AP148" s="19" t="n"/>
+      <c r="AQ148" s="16" t="inlineStr">
+        <is>
+          <t>Oyster-Reef Restoration Nutrient-Assimilation Crediting</t>
+        </is>
+      </c>
+      <c r="AR148" s="16" t="inlineStr">
+        <is>
+          <t>Maryland Department of Natural Resources</t>
+        </is>
+      </c>
+      <c r="AS148" s="16" t="inlineStr">
+        <is>
+          <t>Implements the Chesapeake Oyster BMP framework (previous row) for restoration credits. Useful where reef restoration rather than harvest is the practice.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Hawkins, A.J.S.; et al. (ShellSIM)</t>
+          <t>Hawkins, A. J. S. &amp; et al. (ShellSIM)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -29282,7 +31218,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>Farm-/bay-scale carrying-capacity models (FARM, EcoWin) and the Dame depletion indices (clearance vs. residence vs. primary-production time) are the complementary frameworks for filtration-as-service. Modelling tool → T2.</t>
+          <t>A modelling tool for the filtration service; complementary carrying-capacity models are FARM and EcoWin.</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -29378,11 +31314,26 @@
       <c r="AN149" s="19" t="n"/>
       <c r="AO149" s="19" t="n"/>
       <c r="AP149" s="19" t="n"/>
+      <c r="AQ149" s="16" t="inlineStr">
+        <is>
+          <t>ShellSIM Bivalve Filtration &amp; Growth Model (Reference)</t>
+        </is>
+      </c>
+      <c r="AR149" s="16" t="inlineStr">
+        <is>
+          <t>Hawkins, A.J.S.; et al. (ShellSIM)</t>
+        </is>
+      </c>
+      <c r="AS149" s="16" t="inlineStr">
+        <is>
+          <t>Farm-/bay-scale carrying-capacity models (FARM, EcoWin) and the Dame depletion indices (clearance vs. residence vs. primary-production time) are the complementary frameworks for filtration-as-service. Modelling tool → T2.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OSPAR Commission (JAMP); ICES</t>
+          <t>OSPAR Commission (JAMP)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -29465,7 +31416,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>The ICES TIMES 'Standard procedure for the determination of chlorophyll a by spectroscopic methods' (Aminot &amp; Rey 2000) and the UNESCO/SCOR pigment monographs (Jeffrey et al. 1997) are the underpinning analytical references. Satellite ocean-colour chl-a is the remote-sensing complement.</t>
+          <t>The standard analytical route to the chlorophyll-a indicator; satellite ocean-colour is the remote-sensing complement.</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
@@ -29561,11 +31512,26 @@
       <c r="AN150" s="19" t="n"/>
       <c r="AO150" s="19" t="n"/>
       <c r="AP150" s="19" t="n"/>
+      <c r="AQ150" s="16" t="inlineStr">
+        <is>
+          <t>Standard Chlorophyll-a Determination SOP (JAMP)</t>
+        </is>
+      </c>
+      <c r="AR150" s="16" t="inlineStr">
+        <is>
+          <t>OSPAR Commission (JAMP); ICES</t>
+        </is>
+      </c>
+      <c r="AS150" s="16" t="inlineStr">
+        <is>
+          <t>The ICES TIMES 'Standard procedure for the determination of chlorophyll a by spectroscopic methods' (Aminot &amp; Rey 2000) and the UNESCO/SCOR pigment monographs (Jeffrey et al. 1997) are the underpinning analytical references. Satellite ocean-colour chl-a is the remote-sensing complement.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Karlson, B.; Cusack, C.; Bresnan, E. (eds.) — UNESCO/IOC</t>
+          <t>Karlson, B., et al.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -29651,7 +31617,7 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>HELCOM Phytoplankton Expert Group species lists and the AQUACOSM phytoplankton SOP give the practical sampling/ID workflow. eDNA metabarcoding (row 24) is the emerging molecular complement.</t>
+          <t>The standard route to the phytoplankton/microorganism indicator; eDNA metabarcoding is the emerging molecular complement.</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
@@ -29747,6 +31713,21 @@
       <c r="AN151" s="19" t="n"/>
       <c r="AO151" s="19" t="n"/>
       <c r="AP151" s="19" t="n"/>
+      <c r="AQ151" s="16" t="inlineStr">
+        <is>
+          <t>Quantitative Phytoplankton Analysis Manual (Microscopy + Molecular)</t>
+        </is>
+      </c>
+      <c r="AR151" s="16" t="inlineStr">
+        <is>
+          <t>Karlson, B.; Cusack, C.; Bresnan, E. (eds.) — UNESCO/IOC</t>
+        </is>
+      </c>
+      <c r="AS151" s="16" t="inlineStr">
+        <is>
+          <t>HELCOM Phytoplankton Expert Group species lists and the AQUACOSM phytoplankton SOP give the practical sampling/ID workflow. eDNA metabarcoding (row 24) is the emerging molecular complement.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -29834,7 +31815,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>Lowers the OA-monitoring barrier dramatically vs. research-grade SOPs (next row). The EPA 'Guidelines for Measuring Changes in Seawater pH... Eastern US' (Pimenta &amp; Grear 2018) and the SDG 14.3.1 indicator methodology are companion references. Also relevant to mollusc shell/carbonate contexts.</t>
+          <t>Built around the low-cost 'GOA-ON in a Box' kit and aimed at low-resource teams; the Dickson guide is the research-grade reference behind it.</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
@@ -29930,11 +31911,26 @@
       <c r="AN152" s="19" t="n"/>
       <c r="AO152" s="19" t="n"/>
       <c r="AP152" s="19" t="n"/>
+      <c r="AQ152" s="16" t="inlineStr">
+        <is>
+          <t>Low-Cost Ocean-Acidification Monitoring (GOA-ON Cookbook)</t>
+        </is>
+      </c>
+      <c r="AR152" s="16" t="inlineStr">
+        <is>
+          <t>Global Ocean Acidification Observing Network (GOA-ON)</t>
+        </is>
+      </c>
+      <c r="AS152" s="16" t="inlineStr">
+        <is>
+          <t>Lowers the OA-monitoring barrier dramatically vs. research-grade SOPs (next row). The EPA 'Guidelines for Measuring Changes in Seawater pH... Eastern US' (Pimenta &amp; Grear 2018) and the SDG 14.3.1 indicator methodology are companion references. Also relevant to mollusc shell/carbonate contexts.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Dickson, A.G.; Sabine, C.L.; Christian, J.R. (eds.); Riebesell, U.; et al.</t>
+          <t>Dickson, A. G., et al.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -30017,7 +32013,7 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>The reference standard for weather-quality OA data; pair with the practitioner-facing OA Cookbook (previous row) for field deployment. Tier T2 as a researcher-grade design tool.</t>
+          <t>Pair it with the practitioner OA cookbook for low-cost field deployment.</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
@@ -30113,11 +32109,26 @@
       <c r="AN153" s="19" t="n"/>
       <c r="AO153" s="19" t="n"/>
       <c r="AP153" s="19" t="n"/>
+      <c r="AQ153" s="16" t="inlineStr">
+        <is>
+          <t>Research-Grade Ocean-Acidification Measurement SOPs (Reference)</t>
+        </is>
+      </c>
+      <c r="AR153" s="16" t="inlineStr">
+        <is>
+          <t>Dickson, A.G.; Sabine, C.L.; Christian, J.R. (eds.); Riebesell, U.; et al.</t>
+        </is>
+      </c>
+      <c r="AS153" s="16" t="inlineStr">
+        <is>
+          <t>The reference standard for weather-quality OA data; pair with the practitioner-facing OA Cookbook (previous row) for field deployment. Tier T2 as a researcher-grade design tool.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Verra; Oceans 2050 (input)</t>
+          <t>Verra</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -30200,7 +32211,7 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>Included to flag a live grey-lit area (seaweed carbon MRV) that the MEL framework intentionally does NOT measure — only the cradle-to-grave GHG (CC 1.2.1) overlaps. The earlier standalone removals methodology was archived (June 2024); development moved into M0172. Tier T2.</t>
+          <t>MEL does not measure seaweed carbon sequestration - only the cradle-to-grave greenhouse-gas footprint overlaps; treat carbon-removal crediting as outside scope.</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
@@ -30296,6 +32307,21 @@
       <c r="AN154" s="19" t="n"/>
       <c r="AO154" s="19" t="n"/>
       <c r="AP154" s="19" t="n"/>
+      <c r="AQ154" s="16" t="inlineStr">
+        <is>
+          <t>Seaweed Carbon-Project Accounting Framework (GHG-Footprint Overlap Only)</t>
+        </is>
+      </c>
+      <c r="AR154" s="16" t="inlineStr">
+        <is>
+          <t>Verra; Oceans 2050 (input)</t>
+        </is>
+      </c>
+      <c r="AS154" s="16" t="inlineStr">
+        <is>
+          <t>Included to flag a live grey-lit area (seaweed carbon MRV) that the MEL framework intentionally does NOT measure — only the cradle-to-grave GHG (CC 1.2.1) overlaps. The earlier standalone removals methodology was archived (June 2024); development moved into M0172. Tier T2.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -30388,7 +32414,7 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>Honest caveat across this literature: there are as yet no established MRV protocols for macroalgae carbon capture/permanence. The EDF 'Carbon Sequestration by Seaweed' report is a companion NGO context piece. Only the cradle-to-grave GHG (CC 1.2.1) overlaps MEL.</t>
+          <t>Only the greenhouse-gas-footprint component maps to MEL; there are as yet no established MRV protocols for macroalgae carbon capture or permanence.</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
@@ -30484,11 +32510,26 @@
       <c r="AN155" s="19" t="n"/>
       <c r="AO155" s="19" t="n"/>
       <c r="AP155" s="19" t="n"/>
+      <c r="AQ155" s="16" t="inlineStr">
+        <is>
+          <t>Macroalgae Carbon-Removal MRV Methods Review (Reference)</t>
+        </is>
+      </c>
+      <c r="AR155" s="16" t="inlineStr">
+        <is>
+          <t>Pacific Northwest National Laboratory (PNNL)</t>
+        </is>
+      </c>
+      <c r="AS155" s="16" t="inlineStr">
+        <is>
+          <t>Honest caveat across this literature: there are as yet no established MRV protocols for macroalgae carbon capture/permanence. The EDF 'Carbon Sequestration by Seaweed' report is a companion NGO context piece. Only the cradle-to-grave GHG (CC 1.2.1) overlaps MEL.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ISO; BSI (PAS 2050)</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -30571,7 +32612,7 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>General-knowledge entry (not a fetched source this session); included so the cradle-to-grave GHG indicator has a protocol home. Seafood-specific LCA guidance and ASC/MSC footprint work build on these. Note the dual numbering: cradle-to-grave GHG = CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
+          <t>The methodological backbone for any aquaculture carbon-footprint study; note GHG is CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
@@ -30667,11 +32708,26 @@
       <c r="AN156" s="19" t="n"/>
       <c r="AO156" s="19" t="n"/>
       <c r="AP156" s="19" t="n"/>
+      <c r="AQ156" s="16" t="inlineStr">
+        <is>
+          <t>Life-Cycle Assessment Standards for GHG Footprinting (Reference)</t>
+        </is>
+      </c>
+      <c r="AR156" s="16" t="inlineStr">
+        <is>
+          <t>ISO; BSI (PAS 2050)</t>
+        </is>
+      </c>
+      <c r="AS156" s="16" t="inlineStr">
+        <is>
+          <t>General-knowledge entry (not a fetched source this session); included so the cradle-to-grave GHG indicator has a protocol home. Seafood-specific LCA guidance and ASC/MSC footprint work build on these. Note the dual numbering: cradle-to-grave GHG = CC 1.1.1 for molluscs/finfish but CC 1.2.1 for seaweed.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Gold, Z.; Sprague, J.; Kushner, D.J.; et al.</t>
+          <t>Gold, Z., et al.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -30762,7 +32818,7 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>A Springer protocol chapter ('Environmental DNA from Marine Waters and Substrates: Protocols for Sampling and eDNA Extraction') gives the bench SOP; formal ISO/CEN eDNA standardisation is still in progress. Pairs with MarineGEO Fouling/ARMS (cryptobiota) and IOC phytoplankton. The framework already cites Mercaldo-Allen 2021 (eDNA at oyster cages).</t>
+          <t>A programme-design guide; a Springer protocol chapter gives the bench SOP, and formal eDNA standardisation is still in progress.</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
@@ -30858,6 +32914,21 @@
       <c r="AN157" s="19" t="n"/>
       <c r="AO157" s="19" t="n"/>
       <c r="AP157" s="19" t="n"/>
+      <c r="AQ157" s="16" t="inlineStr">
+        <is>
+          <t>Designing an eDNA Metabarcoding Monitoring Programme (Manager's Guide)</t>
+        </is>
+      </c>
+      <c r="AR157" s="16" t="inlineStr">
+        <is>
+          <t>Gold, Z.; Sprague, J.; Kushner, D.J.; et al.</t>
+        </is>
+      </c>
+      <c r="AS157" s="16" t="inlineStr">
+        <is>
+          <t>A Springer protocol chapter ('Environmental DNA from Marine Waters and Substrates: Protocols for Sampling and eDNA Extraction') gives the bench SOP; formal ISO/CEN eDNA standardisation is still in progress. Pairs with MarineGEO Fouling/ARMS (cryptobiota) and IOC phytoplankton. The framework already cites Mercaldo-Allen 2021 (eDNA at oyster cages).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="9">
